--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43FC95B-A0CB-44AF-921E-970C566E4381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705CC433-CCE7-4CEB-8AAD-0A6DCB1FFD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
     <sheet name="Register" sheetId="2" r:id="rId2"/>
     <sheet name="Login" sheetId="3" r:id="rId3"/>
+    <sheet name="Logout" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="381">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -1119,6 +1120,191 @@
   </si>
   <si>
     <t>Database bypass fails. System securely handles the payload and rejects the login attempt.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_001</t>
+  </si>
+  <si>
+    <t>Verify successful logout via Right Column menu</t>
+  </si>
+  <si>
+    <t>User is logged in and on the My Account page</t>
+  </si>
+  <si>
+    <t>1. Locate the right-hand navigation list.</t>
+  </si>
+  <si>
+    <t>2. Click on the 'Logout' link at the bottom of the list.</t>
+  </si>
+  <si>
+    <t>User session is terminated, and the user is redirected to the Account Logout page.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_002</t>
+  </si>
+  <si>
+    <t>Verify successful logout via Top Header menu</t>
+  </si>
+  <si>
+    <t>User is logged in</t>
+  </si>
+  <si>
+    <t>1. Click on the 'My Account' dropdown in the top header menu.</t>
+  </si>
+  <si>
+    <t>2. Click on the 'Logout' option.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_003</t>
+  </si>
+  <si>
+    <t>Verify redirection after Account Logout</t>
+  </si>
+  <si>
+    <t>User has just clicked 'Logout'</t>
+  </si>
+  <si>
+    <t>1. Observe the page loaded after clicking Logout.</t>
+  </si>
+  <si>
+    <t>User is presented with a logout confirmation message/page confirming the session has been cleared.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_004</t>
+  </si>
+  <si>
+    <t>Verify 'Continue' button on the Logout Success page</t>
+  </si>
+  <si>
+    <t>User is on the Account Logout page</t>
+  </si>
+  <si>
+    <t>1. Click the 'Continue' button on the logout confirmation page.</t>
+  </si>
+  <si>
+    <t>User is redirected to the Store's Home Page.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_005</t>
+  </si>
+  <si>
+    <t>Verify restricted access via browser 'Back' button post-logout</t>
+  </si>
+  <si>
+    <t>User has successfully logged out</t>
+  </si>
+  <si>
+    <t>1. Click the browser's 'Back' arrow button to return to the My Account page.</t>
+  </si>
+  <si>
+    <t>User is not shown the secure My Account page; instead, they are forced to the Login page or the page reloads as a guest view.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_006</t>
+  </si>
+  <si>
+    <t>Verify restricted access via direct URL post-logout</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Copy the URL for the My Account page (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>index.php?route=account/account</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Paste it into the address bar and press Enter.</t>
+  </si>
+  <si>
+    <t>System prevents access and redirects the user to the Login page.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_007</t>
+  </si>
+  <si>
+    <t>Verify Top Header 'My Account' menu updates post-logout</t>
+  </si>
+  <si>
+    <t>The 'Logout' option is no longer present. The options should revert to 'Register' and 'Login'.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_008</t>
+  </si>
+  <si>
+    <t>Verify Right Column menu updates post-logout</t>
+  </si>
+  <si>
+    <t>User has successfully logged out and navigated to the Login page</t>
+  </si>
+  <si>
+    <t>1. Observe the right-hand column menu.</t>
+  </si>
+  <si>
+    <t>The 'Logout' link is no longer present in the list; it is replaced by guest-appropriate links like Login and Register.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_009</t>
+  </si>
+  <si>
+    <t>Verify session termination across multiple browser tabs</t>
+  </si>
+  <si>
+    <t>User is logged in on two separate browser tabs</t>
+  </si>
+  <si>
+    <t>1. On Tab 1, click 'Logout'.</t>
+  </si>
+  <si>
+    <t>2. Switch to Tab 2 and refresh the page or click any secure account link.</t>
+  </si>
+  <si>
+    <t>Tab 2 recognizes the session is terminated and redirects the user to the Login page.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_010</t>
+  </si>
+  <si>
+    <t>Verify auto-logout after prolonged session inactivity</t>
+  </si>
+  <si>
+    <t>1. Leave the browser idle on the My Account page for a duration exceeding the server's session timeout limit (e.g., 30+ minutes).</t>
+  </si>
+  <si>
+    <t>2. Attempt to click a secure link like 'Order History'.</t>
+  </si>
+  <si>
+    <t>The session is automatically terminated, and the user is redirected to the Login page.</t>
+  </si>
+  <si>
+    <t>TC_LOGOUT_011</t>
+  </si>
+  <si>
+    <t>Verify system stability when rapidly clicking Logout</t>
+  </si>
+  <si>
+    <t>1. Navigate to the right-hand column menu.</t>
+  </si>
+  <si>
+    <t>2. Rapidly double-click or triple-click the 'Logout' link.</t>
+  </si>
+  <si>
+    <t>The user is safely logged out once, and no application crashes or server-side errors occur.</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1822,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="50">
+  <dxfs count="65">
     <dxf>
       <font>
         <b val="0"/>
@@ -1659,9 +1845,7 @@
         <left style="medium">
           <color theme="1"/>
         </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
+        <right/>
         <top/>
         <bottom/>
         <vertical/>
@@ -1946,9 +2130,7 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
+        <left/>
         <right style="medium">
           <color theme="1"/>
         </right>
@@ -1956,6 +2138,22 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2014,16 +2212,388 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color rgb="FFC4C7C5"/>
         </left>
         <right style="medium">
           <color rgb="FFC4C7C5"/>
         </right>
-        <top style="medium">
-          <color rgb="FFC4C7C5"/>
-        </top>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
@@ -2752,12 +3322,12 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="6" xr9:uid="{DD3ECB35-2970-4076-8662-E1865940DEEF}">
-      <tableStyleElement type="firstColumn" dxfId="26"/>
-      <tableStyleElement type="lastColumn" dxfId="27"/>
-      <tableStyleElement type="firstRowStripe" dxfId="29"/>
-      <tableStyleElement type="secondRowStripe" dxfId="28"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="31"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="30"/>
+      <tableStyleElement type="firstColumn" dxfId="41"/>
+      <tableStyleElement type="lastColumn" dxfId="42"/>
+      <tableStyleElement type="firstRowStripe" dxfId="44"/>
+      <tableStyleElement type="secondRowStripe" dxfId="43"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="46"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="45"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2772,25 +3342,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="63">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="45" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42" totalsRowBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2800,7 +3370,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="64"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2808,40 +3378,60 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" headerRowBorderDxfId="33" tableBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" headerRowBorderDxfId="48" tableBorderDxfId="47">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="11" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="27" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="26">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="12" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="11">
+  <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5941,8 +6531,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="85.5">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:11" ht="57">
+      <c r="A7" s="32" t="s">
         <v>229</v>
       </c>
       <c r="B7" s="15" t="s">
@@ -5964,10 +6554,10 @@
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+      <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="12"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="12"/>
       <c r="C8" s="33"/>
       <c r="D8" s="12"/>
@@ -5977,10 +6567,10 @@
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" spans="1:11" ht="28.5">
-      <c r="A9" s="12"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="12"/>
       <c r="C9" s="33"/>
       <c r="D9" s="12"/>
@@ -5992,10 +6582,10 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
+      <c r="K9" s="18"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="12"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="12"/>
       <c r="C10" s="33"/>
       <c r="D10" s="12"/>
@@ -6005,10 +6595,10 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
+      <c r="K10" s="18"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A11" s="13"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="13"/>
       <c r="C11" s="34"/>
       <c r="D11" s="13"/>
@@ -6020,10 +6610,10 @@
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-    </row>
-    <row r="12" spans="1:11" ht="85.5">
-      <c r="A12" s="15" t="s">
+      <c r="K11" s="19"/>
+    </row>
+    <row r="12" spans="1:11" ht="57">
+      <c r="A12" s="32" t="s">
         <v>236</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -6045,10 +6635,10 @@
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
+      <c r="K12" s="17"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="12"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="12"/>
       <c r="C13" s="33"/>
       <c r="D13" s="12"/>
@@ -6058,10 +6648,10 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
+      <c r="K13" s="18"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="12"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="12"/>
       <c r="C14" s="33"/>
       <c r="D14" s="12"/>
@@ -6073,10 +6663,10 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
+      <c r="K14" s="18"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="12"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="12"/>
       <c r="C15" s="33"/>
       <c r="D15" s="12"/>
@@ -6086,10 +6676,10 @@
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
+      <c r="K15" s="18"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A16" s="13"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="13"/>
       <c r="C16" s="34"/>
       <c r="D16" s="13"/>
@@ -6101,10 +6691,10 @@
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="K16" s="19"/>
     </row>
     <row r="17" spans="1:11" ht="57">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="32" t="s">
         <v>242</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -6126,10 +6716,10 @@
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
+      <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="12"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="12"/>
       <c r="C18" s="33"/>
       <c r="D18" s="12"/>
@@ -6139,10 +6729,10 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
+      <c r="K18" s="18"/>
     </row>
     <row r="19" spans="1:11" ht="28.5">
-      <c r="A19" s="12"/>
+      <c r="A19" s="33"/>
       <c r="B19" s="12"/>
       <c r="C19" s="33"/>
       <c r="D19" s="12"/>
@@ -6154,10 +6744,10 @@
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
+      <c r="K19" s="18"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="12"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="12"/>
       <c r="C20" s="33"/>
       <c r="D20" s="12"/>
@@ -6167,10 +6757,10 @@
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
+      <c r="K20" s="18"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A21" s="13"/>
+      <c r="A21" s="34"/>
       <c r="B21" s="13"/>
       <c r="C21" s="34"/>
       <c r="D21" s="13"/>
@@ -6182,10 +6772,10 @@
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="K21" s="19"/>
     </row>
     <row r="22" spans="1:11" ht="42.75">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="32" t="s">
         <v>245</v>
       </c>
       <c r="B22" s="15" t="s">
@@ -6207,10 +6797,10 @@
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
+      <c r="K22" s="17"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="12"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="12"/>
       <c r="C23" s="33"/>
       <c r="D23" s="12"/>
@@ -6220,10 +6810,10 @@
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="18"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="12"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="12"/>
       <c r="C24" s="33"/>
       <c r="D24" s="12"/>
@@ -6235,10 +6825,10 @@
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="18"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="12"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="12"/>
       <c r="C25" s="33"/>
       <c r="D25" s="12"/>
@@ -6248,10 +6838,10 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
+      <c r="K25" s="18"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A26" s="13"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="13"/>
       <c r="C26" s="34"/>
       <c r="D26" s="13"/>
@@ -6263,10 +6853,10 @@
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="K26" s="19"/>
     </row>
     <row r="27" spans="1:11" ht="42.75">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="32" t="s">
         <v>249</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -6288,10 +6878,10 @@
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
+      <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="12"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="12"/>
       <c r="C28" s="33"/>
       <c r="D28" s="12"/>
@@ -6301,10 +6891,10 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="18"/>
     </row>
     <row r="29" spans="1:11" ht="28.5">
-      <c r="A29" s="12"/>
+      <c r="A29" s="33"/>
       <c r="B29" s="12"/>
       <c r="C29" s="33"/>
       <c r="D29" s="12"/>
@@ -6316,10 +6906,10 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
+      <c r="K29" s="18"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="12"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="12"/>
       <c r="C30" s="33"/>
       <c r="D30" s="12"/>
@@ -6329,10 +6919,10 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
+      <c r="K30" s="18"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A31" s="13"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="13"/>
       <c r="C31" s="34"/>
       <c r="D31" s="13"/>
@@ -6344,10 +6934,10 @@
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
+      <c r="K31" s="19"/>
     </row>
     <row r="32" spans="1:11" ht="42.75">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="32" t="s">
         <v>252</v>
       </c>
       <c r="B32" s="15" t="s">
@@ -6369,10 +6959,10 @@
       <c r="H32" s="15"/>
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
+      <c r="K32" s="17"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="12"/>
+      <c r="A33" s="33"/>
       <c r="B33" s="12"/>
       <c r="C33" s="33"/>
       <c r="D33" s="12"/>
@@ -6382,10 +6972,10 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
+      <c r="K33" s="18"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="12"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="12"/>
       <c r="C34" s="33"/>
       <c r="D34" s="12"/>
@@ -6397,10 +6987,10 @@
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
+      <c r="K34" s="18"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="12"/>
+      <c r="A35" s="33"/>
       <c r="B35" s="12"/>
       <c r="C35" s="33"/>
       <c r="D35" s="12"/>
@@ -6410,10 +7000,10 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
+      <c r="K35" s="18"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A36" s="13"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="13"/>
       <c r="C36" s="34"/>
       <c r="D36" s="13"/>
@@ -6425,10 +7015,10 @@
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
+      <c r="K36" s="19"/>
     </row>
     <row r="37" spans="1:11" ht="57">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="32" t="s">
         <v>257</v>
       </c>
       <c r="B37" s="15" t="s">
@@ -6450,10 +7040,10 @@
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
       <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
+      <c r="K37" s="17"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="12"/>
+      <c r="A38" s="33"/>
       <c r="B38" s="12"/>
       <c r="C38" s="33"/>
       <c r="D38" s="12"/>
@@ -6463,10 +7053,10 @@
       <c r="H38" s="12"/>
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
+      <c r="K38" s="18"/>
     </row>
     <row r="39" spans="1:11" ht="28.5">
-      <c r="A39" s="12"/>
+      <c r="A39" s="33"/>
       <c r="B39" s="12"/>
       <c r="C39" s="33"/>
       <c r="D39" s="12"/>
@@ -6478,10 +7068,10 @@
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
+      <c r="K39" s="18"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="12"/>
+      <c r="A40" s="33"/>
       <c r="B40" s="12"/>
       <c r="C40" s="33"/>
       <c r="D40" s="12"/>
@@ -6491,10 +7081,10 @@
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
+      <c r="K40" s="18"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A41" s="13"/>
+      <c r="A41" s="34"/>
       <c r="B41" s="13"/>
       <c r="C41" s="34"/>
       <c r="D41" s="13"/>
@@ -6506,10 +7096,10 @@
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
+      <c r="K41" s="19"/>
     </row>
     <row r="42" spans="1:11" ht="42.75">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="32" t="s">
         <v>260</v>
       </c>
       <c r="B42" s="15" t="s">
@@ -6531,10 +7121,10 @@
       <c r="H42" s="15"/>
       <c r="I42" s="15"/>
       <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
+      <c r="K42" s="17"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="12"/>
+      <c r="A43" s="33"/>
       <c r="B43" s="12"/>
       <c r="C43" s="33"/>
       <c r="D43" s="12"/>
@@ -6544,10 +7134,10 @@
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
       <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
+      <c r="K43" s="18"/>
     </row>
     <row r="44" spans="1:11" ht="57">
-      <c r="A44" s="12"/>
+      <c r="A44" s="33"/>
       <c r="B44" s="12"/>
       <c r="C44" s="33"/>
       <c r="D44" s="12"/>
@@ -6559,10 +7149,10 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
+      <c r="K44" s="18"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="12"/>
+      <c r="A45" s="33"/>
       <c r="B45" s="12"/>
       <c r="C45" s="33"/>
       <c r="D45" s="12"/>
@@ -6572,10 +7162,10 @@
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
       <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
+      <c r="K45" s="18"/>
     </row>
     <row r="46" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A46" s="13"/>
+      <c r="A46" s="34"/>
       <c r="B46" s="13"/>
       <c r="C46" s="34"/>
       <c r="D46" s="13"/>
@@ -6587,10 +7177,10 @@
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
+      <c r="K46" s="19"/>
     </row>
     <row r="47" spans="1:11" ht="57">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="32" t="s">
         <v>264</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -6612,10 +7202,10 @@
       <c r="H47" s="15"/>
       <c r="I47" s="15"/>
       <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
+      <c r="K47" s="17"/>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="12"/>
+      <c r="A48" s="33"/>
       <c r="B48" s="12"/>
       <c r="C48" s="33"/>
       <c r="D48" s="12"/>
@@ -6625,10 +7215,10 @@
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
+      <c r="K48" s="18"/>
     </row>
     <row r="49" spans="1:11" ht="28.5">
-      <c r="A49" s="12"/>
+      <c r="A49" s="33"/>
       <c r="B49" s="12"/>
       <c r="C49" s="33"/>
       <c r="D49" s="12"/>
@@ -6640,10 +7230,10 @@
       <c r="H49" s="12"/>
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
+      <c r="K49" s="18"/>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="12"/>
+      <c r="A50" s="33"/>
       <c r="B50" s="12"/>
       <c r="C50" s="33"/>
       <c r="D50" s="12"/>
@@ -6653,10 +7243,10 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
+      <c r="K50" s="18"/>
     </row>
     <row r="51" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A51" s="13"/>
+      <c r="A51" s="34"/>
       <c r="B51" s="13"/>
       <c r="C51" s="34"/>
       <c r="D51" s="13"/>
@@ -6668,10 +7258,10 @@
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
+      <c r="K51" s="19"/>
     </row>
     <row r="52" spans="1:11" ht="57">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="32" t="s">
         <v>268</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -6693,10 +7283,10 @@
       <c r="H52" s="15"/>
       <c r="I52" s="15"/>
       <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
+      <c r="K52" s="17"/>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="12"/>
+      <c r="A53" s="33"/>
       <c r="B53" s="12"/>
       <c r="C53" s="33"/>
       <c r="D53" s="12"/>
@@ -6706,10 +7296,10 @@
       <c r="H53" s="12"/>
       <c r="I53" s="12"/>
       <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
+      <c r="K53" s="18"/>
     </row>
     <row r="54" spans="1:11" ht="28.5">
-      <c r="A54" s="12"/>
+      <c r="A54" s="33"/>
       <c r="B54" s="12"/>
       <c r="C54" s="33"/>
       <c r="D54" s="12"/>
@@ -6721,10 +7311,10 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
+      <c r="K54" s="18"/>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="12"/>
+      <c r="A55" s="33"/>
       <c r="B55" s="12"/>
       <c r="C55" s="33"/>
       <c r="D55" s="12"/>
@@ -6734,10 +7324,10 @@
       <c r="H55" s="12"/>
       <c r="I55" s="12"/>
       <c r="J55" s="12"/>
-      <c r="K55" s="12"/>
+      <c r="K55" s="18"/>
     </row>
     <row r="56" spans="1:11" ht="43.5" thickBot="1">
-      <c r="A56" s="13"/>
+      <c r="A56" s="34"/>
       <c r="B56" s="13"/>
       <c r="C56" s="34"/>
       <c r="D56" s="13"/>
@@ -6749,10 +7339,10 @@
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
       <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
+      <c r="K56" s="19"/>
     </row>
     <row r="57" spans="1:11" ht="57.75" thickBot="1">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="41" t="s">
         <v>271</v>
       </c>
       <c r="B57" s="28" t="s">
@@ -6774,10 +7364,10 @@
       <c r="H57" s="28"/>
       <c r="I57" s="28"/>
       <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
+      <c r="K57" s="29"/>
     </row>
     <row r="58" spans="1:11" ht="42.75">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="32" t="s">
         <v>273</v>
       </c>
       <c r="B58" s="15" t="s">
@@ -6799,10 +7389,10 @@
       <c r="H58" s="15"/>
       <c r="I58" s="15"/>
       <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
+      <c r="K58" s="17"/>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59" s="12"/>
+      <c r="A59" s="33"/>
       <c r="B59" s="12"/>
       <c r="C59" s="33"/>
       <c r="D59" s="12"/>
@@ -6812,10 +7402,10 @@
       <c r="H59" s="12"/>
       <c r="I59" s="12"/>
       <c r="J59" s="12"/>
-      <c r="K59" s="12"/>
+      <c r="K59" s="18"/>
     </row>
     <row r="60" spans="1:11" ht="29.25" thickBot="1">
-      <c r="A60" s="13"/>
+      <c r="A60" s="34"/>
       <c r="B60" s="13"/>
       <c r="C60" s="34"/>
       <c r="D60" s="13"/>
@@ -6827,10 +7417,10 @@
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
+      <c r="K60" s="19"/>
     </row>
     <row r="61" spans="1:11" ht="42.75">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="32" t="s">
         <v>278</v>
       </c>
       <c r="B61" s="15" t="s">
@@ -6852,10 +7442,10 @@
       <c r="H61" s="15"/>
       <c r="I61" s="15"/>
       <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
+      <c r="K61" s="17"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="12"/>
+      <c r="A62" s="33"/>
       <c r="B62" s="12"/>
       <c r="C62" s="33"/>
       <c r="D62" s="12"/>
@@ -6865,10 +7455,10 @@
       <c r="H62" s="12"/>
       <c r="I62" s="12"/>
       <c r="J62" s="12"/>
-      <c r="K62" s="12"/>
+      <c r="K62" s="18"/>
     </row>
     <row r="63" spans="1:11" ht="43.5" thickBot="1">
-      <c r="A63" s="13"/>
+      <c r="A63" s="34"/>
       <c r="B63" s="13"/>
       <c r="C63" s="34"/>
       <c r="D63" s="13"/>
@@ -6880,10 +7470,10 @@
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
       <c r="J63" s="13"/>
-      <c r="K63" s="13"/>
+      <c r="K63" s="19"/>
     </row>
     <row r="64" spans="1:11" ht="42.75">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="32" t="s">
         <v>283</v>
       </c>
       <c r="B64" s="15" t="s">
@@ -6905,10 +7495,10 @@
       <c r="H64" s="15"/>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
+      <c r="K64" s="17"/>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="12"/>
+      <c r="A65" s="33"/>
       <c r="B65" s="12"/>
       <c r="C65" s="33"/>
       <c r="D65" s="12"/>
@@ -6918,10 +7508,10 @@
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
+      <c r="K65" s="18"/>
     </row>
     <row r="66" spans="1:11" ht="29.25" thickBot="1">
-      <c r="A66" s="13"/>
+      <c r="A66" s="34"/>
       <c r="B66" s="13"/>
       <c r="C66" s="34"/>
       <c r="D66" s="13"/>
@@ -6933,10 +7523,10 @@
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
+      <c r="K66" s="19"/>
     </row>
     <row r="67" spans="1:11" ht="28.5">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="32" t="s">
         <v>286</v>
       </c>
       <c r="B67" s="15" t="s">
@@ -6958,10 +7548,10 @@
       <c r="H67" s="15"/>
       <c r="I67" s="15"/>
       <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
+      <c r="K67" s="17"/>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" s="12"/>
+      <c r="A68" s="33"/>
       <c r="B68" s="12"/>
       <c r="C68" s="33"/>
       <c r="D68" s="12"/>
@@ -6971,10 +7561,10 @@
       <c r="H68" s="12"/>
       <c r="I68" s="12"/>
       <c r="J68" s="12"/>
-      <c r="K68" s="12"/>
+      <c r="K68" s="18"/>
     </row>
     <row r="69" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A69" s="13"/>
+      <c r="A69" s="34"/>
       <c r="B69" s="13"/>
       <c r="C69" s="34"/>
       <c r="D69" s="13"/>
@@ -6986,10 +7576,10 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
+      <c r="K69" s="19"/>
     </row>
     <row r="70" spans="1:11" ht="42.75">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="32" t="s">
         <v>289</v>
       </c>
       <c r="B70" s="15" t="s">
@@ -7011,10 +7601,10 @@
       <c r="H70" s="15"/>
       <c r="I70" s="15"/>
       <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
+      <c r="K70" s="17"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="12"/>
+      <c r="A71" s="33"/>
       <c r="B71" s="12"/>
       <c r="C71" s="33"/>
       <c r="D71" s="12"/>
@@ -7024,10 +7614,10 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
+      <c r="K71" s="18"/>
     </row>
     <row r="72" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A72" s="13"/>
+      <c r="A72" s="34"/>
       <c r="B72" s="13"/>
       <c r="C72" s="34"/>
       <c r="D72" s="13"/>
@@ -7039,10 +7629,10 @@
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
       <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
+      <c r="K72" s="19"/>
     </row>
     <row r="73" spans="1:11" ht="42.75">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="33" t="s">
         <v>294</v>
       </c>
       <c r="B73" s="12" t="s">
@@ -7064,10 +7654,10 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
+      <c r="K73" s="18"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="12"/>
+      <c r="A74" s="33"/>
       <c r="B74" s="12"/>
       <c r="C74" s="33"/>
       <c r="D74" s="12"/>
@@ -7077,10 +7667,10 @@
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
       <c r="J74" s="12"/>
-      <c r="K74" s="12"/>
+      <c r="K74" s="18"/>
     </row>
     <row r="75" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A75" s="12"/>
+      <c r="A75" s="33"/>
       <c r="B75" s="12"/>
       <c r="C75" s="33"/>
       <c r="D75" s="12"/>
@@ -7092,10 +7682,10 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
+      <c r="K75" s="18"/>
     </row>
     <row r="76" spans="1:11" ht="42.75">
-      <c r="A76" s="15" t="s">
+      <c r="A76" s="32" t="s">
         <v>299</v>
       </c>
       <c r="B76" s="15" t="s">
@@ -7117,10 +7707,10 @@
       <c r="H76" s="15"/>
       <c r="I76" s="15"/>
       <c r="J76" s="15"/>
-      <c r="K76" s="15"/>
+      <c r="K76" s="17"/>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="12"/>
+      <c r="A77" s="33"/>
       <c r="B77" s="12"/>
       <c r="C77" s="33"/>
       <c r="D77" s="12"/>
@@ -7130,10 +7720,10 @@
       <c r="H77" s="12"/>
       <c r="I77" s="12"/>
       <c r="J77" s="12"/>
-      <c r="K77" s="12"/>
+      <c r="K77" s="18"/>
     </row>
     <row r="78" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A78" s="13"/>
+      <c r="A78" s="34"/>
       <c r="B78" s="13"/>
       <c r="C78" s="34"/>
       <c r="D78" s="13"/>
@@ -7145,10 +7735,10 @@
       <c r="H78" s="13"/>
       <c r="I78" s="13"/>
       <c r="J78" s="13"/>
-      <c r="K78" s="13"/>
+      <c r="K78" s="19"/>
     </row>
     <row r="79" spans="1:11" ht="98.25" customHeight="1">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="32" t="s">
         <v>303</v>
       </c>
       <c r="B79" s="15" t="s">
@@ -7170,10 +7760,10 @@
       <c r="H79" s="15"/>
       <c r="I79" s="15"/>
       <c r="J79" s="15"/>
-      <c r="K79" s="15"/>
+      <c r="K79" s="17"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="12"/>
+      <c r="A80" s="33"/>
       <c r="B80" s="12"/>
       <c r="C80" s="33"/>
       <c r="D80" s="12"/>
@@ -7183,10 +7773,10 @@
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
       <c r="J80" s="12"/>
-      <c r="K80" s="12"/>
+      <c r="K80" s="18"/>
     </row>
     <row r="81" spans="1:11" ht="29.25" thickBot="1">
-      <c r="A81" s="12"/>
+      <c r="A81" s="33"/>
       <c r="B81" s="12"/>
       <c r="C81" s="33"/>
       <c r="D81" s="12"/>
@@ -7198,10 +7788,10 @@
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
       <c r="J81" s="12"/>
-      <c r="K81" s="12"/>
+      <c r="K81" s="18"/>
     </row>
     <row r="82" spans="1:11" ht="71.25">
-      <c r="A82" s="15" t="s">
+      <c r="A82" s="32" t="s">
         <v>306</v>
       </c>
       <c r="B82" s="15" t="s">
@@ -7223,10 +7813,10 @@
       <c r="H82" s="15"/>
       <c r="I82" s="15"/>
       <c r="J82" s="15"/>
-      <c r="K82" s="15"/>
+      <c r="K82" s="17"/>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="12"/>
+      <c r="A83" s="33"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="D83" s="18"/>
@@ -7236,10 +7826,10 @@
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
       <c r="J83" s="12"/>
-      <c r="K83" s="12"/>
+      <c r="K83" s="18"/>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" s="12"/>
+      <c r="A84" s="33"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
       <c r="D84" s="18"/>
@@ -7251,10 +7841,10 @@
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
       <c r="J84" s="12"/>
-      <c r="K84" s="12"/>
+      <c r="K84" s="18"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="12"/>
+      <c r="A85" s="33"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
       <c r="D85" s="18"/>
@@ -7264,10 +7854,10 @@
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
       <c r="J85" s="12"/>
-      <c r="K85" s="12"/>
+      <c r="K85" s="18"/>
     </row>
     <row r="86" spans="1:11" ht="29.25" thickBot="1">
-      <c r="A86" s="13"/>
+      <c r="A86" s="34"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
       <c r="D86" s="19"/>
@@ -7279,10 +7869,10 @@
       <c r="H86" s="13"/>
       <c r="I86" s="13"/>
       <c r="J86" s="13"/>
-      <c r="K86" s="13"/>
+      <c r="K86" s="19"/>
     </row>
     <row r="87" spans="1:11" ht="85.5">
-      <c r="A87" s="15" t="s">
+      <c r="A87" s="32" t="s">
         <v>312</v>
       </c>
       <c r="B87" s="15" t="s">
@@ -7304,10 +7894,10 @@
       <c r="H87" s="15"/>
       <c r="I87" s="15"/>
       <c r="J87" s="15"/>
-      <c r="K87" s="15"/>
+      <c r="K87" s="17"/>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="12"/>
+      <c r="A88" s="33"/>
       <c r="B88" s="12"/>
       <c r="C88" s="33"/>
       <c r="D88" s="12"/>
@@ -7317,10 +7907,10 @@
       <c r="H88" s="12"/>
       <c r="I88" s="12"/>
       <c r="J88" s="12"/>
-      <c r="K88" s="12"/>
+      <c r="K88" s="18"/>
     </row>
     <row r="89" spans="1:11" ht="43.5" thickBot="1">
-      <c r="A89" s="13"/>
+      <c r="A89" s="34"/>
       <c r="B89" s="13"/>
       <c r="C89" s="34"/>
       <c r="D89" s="13"/>
@@ -7332,10 +7922,10 @@
       <c r="H89" s="13"/>
       <c r="I89" s="13"/>
       <c r="J89" s="13"/>
-      <c r="K89" s="13"/>
+      <c r="K89" s="19"/>
     </row>
     <row r="90" spans="1:11" ht="42.75">
-      <c r="A90" s="15" t="s">
+      <c r="A90" s="32" t="s">
         <v>317</v>
       </c>
       <c r="B90" s="15" t="s">
@@ -7357,10 +7947,10 @@
       <c r="H90" s="15"/>
       <c r="I90" s="15"/>
       <c r="J90" s="15"/>
-      <c r="K90" s="15"/>
+      <c r="K90" s="17"/>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="12"/>
+      <c r="A91" s="33"/>
       <c r="B91" s="12"/>
       <c r="C91" s="33"/>
       <c r="D91" s="12"/>
@@ -7370,10 +7960,10 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
       <c r="J91" s="12"/>
-      <c r="K91" s="12"/>
+      <c r="K91" s="18"/>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" s="12"/>
+      <c r="A92" s="33"/>
       <c r="B92" s="12"/>
       <c r="C92" s="33"/>
       <c r="D92" s="12"/>
@@ -7385,10 +7975,10 @@
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
       <c r="J92" s="12"/>
-      <c r="K92" s="12"/>
+      <c r="K92" s="18"/>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="12"/>
+      <c r="A93" s="33"/>
       <c r="B93" s="12"/>
       <c r="C93" s="33"/>
       <c r="D93" s="12"/>
@@ -7398,10 +7988,10 @@
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
       <c r="J93" s="12"/>
-      <c r="K93" s="12"/>
+      <c r="K93" s="18"/>
     </row>
     <row r="94" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A94" s="13"/>
+      <c r="A94" s="34"/>
       <c r="B94" s="13"/>
       <c r="C94" s="34"/>
       <c r="D94" s="13"/>
@@ -7413,10 +8003,10 @@
       <c r="H94" s="13"/>
       <c r="I94" s="13"/>
       <c r="J94" s="13"/>
-      <c r="K94" s="13"/>
+      <c r="K94" s="19"/>
     </row>
     <row r="95" spans="1:11" ht="57">
-      <c r="A95" s="15" t="s">
+      <c r="A95" s="32" t="s">
         <v>323</v>
       </c>
       <c r="B95" s="15" t="s">
@@ -7438,10 +8028,10 @@
       <c r="H95" s="15"/>
       <c r="I95" s="15"/>
       <c r="J95" s="15"/>
-      <c r="K95" s="15"/>
+      <c r="K95" s="17"/>
     </row>
     <row r="96" spans="1:11">
-      <c r="A96" s="12"/>
+      <c r="A96" s="33"/>
       <c r="B96" s="12"/>
       <c r="C96" s="33"/>
       <c r="D96" s="12"/>
@@ -7451,10 +8041,10 @@
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
       <c r="J96" s="12"/>
-      <c r="K96" s="12"/>
+      <c r="K96" s="18"/>
     </row>
     <row r="97" spans="1:11">
-      <c r="A97" s="12"/>
+      <c r="A97" s="33"/>
       <c r="B97" s="12"/>
       <c r="C97" s="33"/>
       <c r="D97" s="12"/>
@@ -7466,10 +8056,10 @@
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
       <c r="J97" s="12"/>
-      <c r="K97" s="12"/>
+      <c r="K97" s="18"/>
     </row>
     <row r="98" spans="1:11">
-      <c r="A98" s="12"/>
+      <c r="A98" s="33"/>
       <c r="B98" s="12"/>
       <c r="C98" s="33"/>
       <c r="D98" s="12"/>
@@ -7479,22 +8069,538 @@
       <c r="H98" s="12"/>
       <c r="I98" s="12"/>
       <c r="J98" s="12"/>
-      <c r="K98" s="12"/>
-    </row>
-    <row r="99" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A99" s="13"/>
-      <c r="B99" s="13"/>
-      <c r="C99" s="34"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13" t="s">
+      <c r="K98" s="18"/>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="33"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="33"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="13"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC31D8B-9B0E-4531-A155-66DF15E94C38}">
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" customWidth="1"/>
+    <col min="6" max="6" width="27.7109375" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="36"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="37"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="71.25">
+      <c r="A8" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="17"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="33"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A10" s="34"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="19"/>
+    </row>
+    <row r="11" spans="1:11" ht="71.25">
+      <c r="A11" s="32" t="s">
+        <v>332</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="17"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="33"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="18"/>
+    </row>
+    <row r="13" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A13" s="34"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="19"/>
+    </row>
+    <row r="14" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A14" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="29"/>
+    </row>
+    <row r="15" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A15" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="29"/>
+    </row>
+    <row r="16" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A16" s="41" t="s">
+        <v>347</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="29"/>
+    </row>
+    <row r="17" spans="1:11" ht="57">
+      <c r="A17" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="17"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="33"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="18"/>
+    </row>
+    <row r="19" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A19" s="34"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="19"/>
+    </row>
+    <row r="20" spans="1:11" ht="72" thickBot="1">
+      <c r="A20" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="29"/>
+    </row>
+    <row r="21" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A21" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>362</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="29"/>
+    </row>
+    <row r="22" spans="1:11" ht="57">
+      <c r="A22" s="32" t="s">
+        <v>365</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="33"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="18"/>
+    </row>
+    <row r="24" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A24" s="34"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="19"/>
+    </row>
+    <row r="25" spans="1:11" ht="71.25">
+      <c r="A25" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="33"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="18"/>
+    </row>
+    <row r="27" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A27" s="34"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="19"/>
+    </row>
+    <row r="28" spans="1:11" ht="71.25">
+      <c r="A28" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="33"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="18"/>
+    </row>
+    <row r="30" spans="1:11" ht="28.5">
+      <c r="A30" s="35"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705CC433-CCE7-4CEB-8AAD-0A6DCB1FFD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D07AA81-F3FA-46F5-97BA-F34731546BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
     <sheet name="Register" sheetId="2" r:id="rId2"/>
     <sheet name="Login" sheetId="3" r:id="rId3"/>
     <sheet name="Logout" sheetId="4" r:id="rId4"/>
+    <sheet name="ForgotPassword" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="487">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -1305,6 +1306,364 @@
   </si>
   <si>
     <t>The user is safely logged out once, and no application crashes or server-side errors occur.</t>
+  </si>
+  <si>
+    <t>TC_FP_001</t>
+  </si>
+  <si>
+    <t>Verify successful submission with a valid registered E-Mail Address</t>
+  </si>
+  <si>
+    <t>User is on the Forgotten Password page</t>
+  </si>
+  <si>
+    <t>1. Enter a valid, registered E-Mail Address.</t>
+  </si>
+  <si>
+    <t>A success message is displayed indicating a reset link has been sent, and user is redirected to the Login page.</t>
+  </si>
+  <si>
+    <t>TC_FP_002</t>
+  </si>
+  <si>
+    <t>Verify validation message when E-Mail Address is left blank</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation warning message states that an E-Mail Address is required.</t>
+  </si>
+  <si>
+    <t>TC_FP_003</t>
+  </si>
+  <si>
+    <t>Verify validation message when E-Mail Address is unregistered</t>
+  </si>
+  <si>
+    <t>1. Enter an E-Mail Address that is not registered in the system.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A warning message states that the E-Mail Address was not found in our records.</t>
+  </si>
+  <si>
+    <t>TC_FP_004</t>
+  </si>
+  <si>
+    <t>Verify validation message with invalid email format (missing '@')</t>
+  </si>
+  <si>
+    <t>1. Enter an email address missing the '@' symbol.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A standard invalid email format error is displayed.</t>
+  </si>
+  <si>
+    <t>TC_FP_005</t>
+  </si>
+  <si>
+    <t>Verify validation message with invalid email format (missing domain)</t>
+  </si>
+  <si>
+    <t>1. Enter an email address without a valid domain extension.</t>
+  </si>
+  <si>
+    <t>TC_FP_006</t>
+  </si>
+  <si>
+    <t>Verify submission with valid E-Mail Address containing uppercase letters</t>
+  </si>
+  <si>
+    <t>1. Enter a valid registered E-Mail Address using mixed case (e.g., User@Domain.com).</t>
+  </si>
+  <si>
+    <t>Submission is successful, confirming email validation is case-insensitive.</t>
+  </si>
+  <si>
+    <t>TC_FP_007</t>
+  </si>
+  <si>
+    <t>Verify system trims leading and trailing whitespaces</t>
+  </si>
+  <si>
+    <t>1. Enter a valid registered E-Mail Address with spaces at the start and end.</t>
+  </si>
+  <si>
+    <t>Submission is successful. The system should automatically trim the whitespace characters.</t>
+  </si>
+  <si>
+    <t>TC_FP_008</t>
+  </si>
+  <si>
+    <t>Verify 'Back' button functionality</t>
+  </si>
+  <si>
+    <t>1. Click the 'Back' button located on the bottom left.</t>
+  </si>
+  <si>
+    <t>User is navigated back to the previous page (typically the Login page).</t>
+  </si>
+  <si>
+    <t>TC_FP_009</t>
+  </si>
+  <si>
+    <t>Verify submission using the 'Enter' key</t>
+  </si>
+  <si>
+    <t>1. Enter a valid registered E-Mail Address.</t>
+  </si>
+  <si>
+    <t>2. Press the 'Enter' key on the keyboard.</t>
+  </si>
+  <si>
+    <t>Submission is triggered successfully as if the 'Continue' button was clicked.</t>
+  </si>
+  <si>
+    <t>TC_FP_010</t>
+  </si>
+  <si>
+    <t>Verify instructional text is displayed correctly</t>
+  </si>
+  <si>
+    <t>1. Observe the text below "Forgot Your Password?".</t>
+  </si>
+  <si>
+    <t>The instructional text matches expected content ("Enter the e-mail address associated with your account...").</t>
+  </si>
+  <si>
+    <t>TC_FP_011</t>
+  </si>
+  <si>
+    <t>Verify 'Home' icon in breadcrumbs navigates to Home page</t>
+  </si>
+  <si>
+    <t>TC_FP_012</t>
+  </si>
+  <si>
+    <t>Verify 'Account' link in breadcrumbs navigates to Login page</t>
+  </si>
+  <si>
+    <t>User is redirected to the Login page (assuming guest status).</t>
+  </si>
+  <si>
+    <t>TC_FP_013</t>
+  </si>
+  <si>
+    <t>Verify Right Column 'Login' link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Locate the right-hand column menu.</t>
+  </si>
+  <si>
+    <t>User is redirected to the Login page.</t>
+  </si>
+  <si>
+    <t>TC_FP_014</t>
+  </si>
+  <si>
+    <t>Verify Right Column 'Register' link navigates correctly</t>
+  </si>
+  <si>
+    <t>User is redirected to the Register Account page.</t>
+  </si>
+  <si>
+    <t>TC_FP_015</t>
+  </si>
+  <si>
+    <t>Verify Right Column 'Forgotten Password' link reloads current page</t>
+  </si>
+  <si>
+    <t>The Forgotten Password page reloads or remains active.</t>
+  </si>
+  <si>
+    <t>TC_FP_016</t>
+  </si>
+  <si>
+    <t>Focus moves logically from E-Mail Address to the 'Back' button, and then to the 'Continue' button.</t>
+  </si>
+  <si>
+    <t>TC_FP_017</t>
+  </si>
+  <si>
+    <t>Verify multiple rapid clicks on 'Continue' do not cause duplicate actions</t>
+  </si>
+  <si>
+    <t>2. Rapidly double or triple-click the 'Continue' button.</t>
+  </si>
+  <si>
+    <t>Only one password reset email is sent to the user, and no server errors occur.</t>
+  </si>
+  <si>
+    <t>TC_FP_018</t>
+  </si>
+  <si>
+    <t>Verify Security: XSS injection attempt in E-Mail Address field</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter a script tag (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;script&gt;alert('XSS')&lt;/script&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Script is not executed. System treats it as an invalid email format.</t>
+  </si>
+  <si>
+    <t>TC_FP_019</t>
+  </si>
+  <si>
+    <t>Verify Security: SQL injection attempt in E-Mail Address field</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter an SQL payload (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>' OR 1=1 --</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>Database is protected. Submission is rejected as an invalid or unregistered email.</t>
+  </si>
+  <si>
+    <t>TC_FP_020</t>
+  </si>
+  <si>
+    <t>Verify user receives the password reset email upon successful submission</t>
+  </si>
+  <si>
+    <t>User has successfully requested a password reset</t>
+  </si>
+  <si>
+    <t>1. Open the inbox of the email address used.</t>
+  </si>
+  <si>
+    <t>2. Check for the reset email from the store.</t>
+  </si>
+  <si>
+    <t>An email containing a password reset link is received within a reasonable timeframe.</t>
+  </si>
+  <si>
+    <t>TC_FP_021</t>
+  </si>
+  <si>
+    <t>Verify the reset link within the email directs to the correct reset page</t>
+  </si>
+  <si>
+    <t>User has received the password reset email</t>
+  </si>
+  <si>
+    <t>1. Click the reset link provided in the email body.</t>
+  </si>
+  <si>
+    <t>User is directed to a secure 'Reset Password' page where a new password can be entered.</t>
+  </si>
+  <si>
+    <t>TC_FP_022</t>
+  </si>
+  <si>
+    <t>Verify successful password update using the reset link</t>
+  </si>
+  <si>
+    <t>User is on the secure 'Reset Password' page</t>
+  </si>
+  <si>
+    <t>1. Enter a new password.</t>
+  </si>
+  <si>
+    <t>2. Confirm the new password.</t>
+  </si>
+  <si>
+    <t>3. Submit the form.</t>
+  </si>
+  <si>
+    <t>Password is successfully updated, and a success message is displayed to the user.</t>
+  </si>
+  <si>
+    <t>TC_FP_023</t>
+  </si>
+  <si>
+    <t>Verify the reset link becomes invalid after it has been used once</t>
+  </si>
+  <si>
+    <t>User has successfully updated their password via reset link</t>
+  </si>
+  <si>
+    <t>1. Return to the password reset email.</t>
+  </si>
+  <si>
+    <t>2. Click the same reset link again.</t>
+  </si>
+  <si>
+    <t>The system displays an error message stating the link is invalid, expired, or has already been used.</t>
+  </si>
+  <si>
+    <t>TC_FP_024</t>
+  </si>
+  <si>
+    <t>Verify the reset link expires after the system's defined timeframe</t>
+  </si>
+  <si>
+    <t>1. Wait for the reset link expiration duration (e.g., 24 hours).</t>
+  </si>
+  <si>
+    <t>2. Click the reset link in the email.</t>
+  </si>
+  <si>
+    <t>The system displays an error message stating the link has expired.</t>
+  </si>
+  <si>
+    <t>TC_FP_025</t>
+  </si>
+  <si>
+    <t>Verify user can login with the new password and old password is rejected</t>
+  </si>
+  <si>
+    <t>User has successfully updated their password</t>
+  </si>
+  <si>
+    <t>1. Navigate to the Login page.</t>
+  </si>
+  <si>
+    <t>2. Attempt login with the old password.</t>
+  </si>
+  <si>
+    <t>3. Attempt login with the new password.</t>
+  </si>
+  <si>
+    <t>Login fails with the old password. Login is successful with the newly updated password.</t>
   </si>
 </sst>
 </file>
@@ -1706,7 +2065,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -1817,12 +2176,406 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="80">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3322,12 +4075,12 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="6" xr9:uid="{DD3ECB35-2970-4076-8662-E1865940DEEF}">
-      <tableStyleElement type="firstColumn" dxfId="41"/>
-      <tableStyleElement type="lastColumn" dxfId="42"/>
-      <tableStyleElement type="firstRowStripe" dxfId="44"/>
-      <tableStyleElement type="secondRowStripe" dxfId="43"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="46"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="45"/>
+      <tableStyleElement type="firstColumn" dxfId="56"/>
+      <tableStyleElement type="lastColumn" dxfId="57"/>
+      <tableStyleElement type="firstRowStripe" dxfId="59"/>
+      <tableStyleElement type="secondRowStripe" dxfId="58"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="61"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="60"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3342,25 +4095,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="78">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="77"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="76"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="75" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72" totalsRowBorderDxfId="71">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3370,7 +4123,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="79"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3378,60 +4131,80 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" headerRowBorderDxfId="48" tableBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64" headerRowBorderDxfId="63" tableBorderDxfId="62">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="27" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="42" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="41">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="12" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="27" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="26">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="12" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="11">
+  <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8608,4 +9381,1374 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987330F4-D290-477A-980A-159E894E07A2}">
+  <dimension ref="A1:K77"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="31.85546875" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="11" max="11" width="24.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="36"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="37"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A4" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" s="43" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="155.25" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="12"/>
+    </row>
+    <row r="7" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="13"/>
+    </row>
+    <row r="8" spans="1:11" ht="112.5" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F10" s="13"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="13"/>
+    </row>
+    <row r="11" spans="1:11" ht="57">
+      <c r="A11" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F13" s="13"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" ht="57">
+      <c r="A14" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11" ht="57">
+      <c r="A17" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="15"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="12"/>
+    </row>
+    <row r="19" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F19" s="13"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" ht="71.25">
+      <c r="A20" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" ht="57">
+      <c r="A23" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="12"/>
+    </row>
+    <row r="25" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A26" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="F26" s="28"/>
+      <c r="G26" s="29" t="s">
+        <v>411</v>
+      </c>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="28"/>
+    </row>
+    <row r="27" spans="1:11" ht="42.75">
+      <c r="A27" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="F27" s="15"/>
+      <c r="G27" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="15"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="12"/>
+    </row>
+    <row r="29" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A30" s="28" t="s">
+        <v>417</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>418</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="F30" s="28"/>
+      <c r="G30" s="29" t="s">
+        <v>420</v>
+      </c>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="28"/>
+    </row>
+    <row r="31" spans="1:11" ht="57">
+      <c r="A31" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="F31" s="15"/>
+      <c r="G31" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="15"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="12"/>
+    </row>
+    <row r="33" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="13"/>
+    </row>
+    <row r="34" spans="1:11" ht="57">
+      <c r="A34" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="F34" s="15"/>
+      <c r="G34" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="15"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="F36" s="13"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="13"/>
+    </row>
+    <row r="37" spans="1:11" ht="42.75">
+      <c r="A37" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="F37" s="15"/>
+      <c r="G37" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="15"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="12"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="12"/>
+    </row>
+    <row r="39" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F39" s="13"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" spans="1:11" ht="42.75">
+      <c r="A40" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="F40" s="15"/>
+      <c r="G40" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="15"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="12"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="12"/>
+    </row>
+    <row r="42" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F42" s="13"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="13"/>
+    </row>
+    <row r="43" spans="1:11" ht="57">
+      <c r="A43" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="F43" s="15"/>
+      <c r="G43" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="15"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="12"/>
+    </row>
+    <row r="45" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="F45" s="13"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="13"/>
+    </row>
+    <row r="46" spans="1:11" ht="57">
+      <c r="A46" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F46" s="15"/>
+      <c r="G46" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="15"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="12"/>
+    </row>
+    <row r="48" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" s="13"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="13"/>
+    </row>
+    <row r="49" spans="1:11" ht="57">
+      <c r="A49" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="F49" s="15"/>
+      <c r="G49" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="15"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="12"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="F51" s="13"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" spans="1:11" ht="55.5">
+      <c r="A52" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="F52" s="15"/>
+      <c r="G52" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="15"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="12"/>
+    </row>
+    <row r="54" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F54" s="13"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="13"/>
+    </row>
+    <row r="55" spans="1:11" ht="112.5" customHeight="1">
+      <c r="A55" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="F55" s="15"/>
+      <c r="G55" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="15"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="12"/>
+    </row>
+    <row r="57" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F57" s="13"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="19"/>
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" spans="1:11" ht="57">
+      <c r="A58" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="F58" s="15"/>
+      <c r="G58" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="15"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="12"/>
+    </row>
+    <row r="60" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A60" s="13"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="F60" s="13"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="13"/>
+    </row>
+    <row r="61" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A61" s="28" t="s">
+        <v>457</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>458</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>459</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="F61" s="28"/>
+      <c r="G61" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="28"/>
+    </row>
+    <row r="62" spans="1:11" ht="57">
+      <c r="A62" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="F62" s="15"/>
+      <c r="G62" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="15"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="12"/>
+    </row>
+    <row r="64" spans="1:11" ht="28.5">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="F64" s="12"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="12"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="12"/>
+    </row>
+    <row r="66" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A66" s="13"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="F66" s="13"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="13"/>
+    </row>
+    <row r="67" spans="1:11" ht="71.25">
+      <c r="A67" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="F67" s="15"/>
+      <c r="G67" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="15"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="12"/>
+    </row>
+    <row r="69" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="F69" s="13"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="13"/>
+    </row>
+    <row r="70" spans="1:11" ht="57">
+      <c r="A70" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="F70" s="15"/>
+      <c r="G70" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="15"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="12"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="12"/>
+    </row>
+    <row r="72" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A72" s="13"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="F72" s="13"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="13"/>
+    </row>
+    <row r="73" spans="1:11" ht="57">
+      <c r="A73" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="F73" s="15"/>
+      <c r="G73" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="17"/>
+      <c r="K73" s="15"/>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="12"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="12"/>
+    </row>
+    <row r="75" spans="1:11" ht="28.5">
+      <c r="A75" s="12"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="F75" s="12"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="12"/>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="12"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="18"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="12"/>
+    </row>
+    <row r="77" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A77" s="13"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="F77" s="13"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="19"/>
+      <c r="K77" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D07AA81-F3FA-46F5-97BA-F34731546BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6F221C-EB02-48BD-8DCB-AFF6DD5209E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Login" sheetId="3" r:id="rId3"/>
     <sheet name="Logout" sheetId="4" r:id="rId4"/>
     <sheet name="ForgotPassword" sheetId="5" r:id="rId5"/>
+    <sheet name="TopMenu" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="563">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -1664,6 +1665,292 @@
   </si>
   <si>
     <t>Login fails with the old password. Login is successful with the newly updated password.</t>
+  </si>
+  <si>
+    <t>TC_NAV_001</t>
+  </si>
+  <si>
+    <t>Verify visibility of the Top Navigation Menu</t>
+  </si>
+  <si>
+    <t>User is on the Store Home Page</t>
+  </si>
+  <si>
+    <t>1. Observe the header section of the page.</t>
+  </si>
+  <si>
+    <t>The Top Navigation Menu (blue bar) displaying categories is clearly visible and spans the correct width.</t>
+  </si>
+  <si>
+    <t>TC_NAV_002</t>
+  </si>
+  <si>
+    <t>Verify hover functionality on a category with sub-categories</t>
+  </si>
+  <si>
+    <t>User is on any store page</t>
+  </si>
+  <si>
+    <t>1. Hover the mouse cursor over a main category known to have sub-categories (e.g., 'Desktops' or 'Laptops &amp; Notebooks').</t>
+  </si>
+  <si>
+    <t>A dropdown menu smoothly appears displaying the relevant sub-categories and a 'Show All...' link.</t>
+  </si>
+  <si>
+    <t>TC_NAV_003</t>
+  </si>
+  <si>
+    <t>Verify hover out functionality on dropdown menus</t>
+  </si>
+  <si>
+    <t>User is viewing a category dropdown</t>
+  </si>
+  <si>
+    <t>1. Hover over 'Desktops' to trigger the dropdown.</t>
+  </si>
+  <si>
+    <t>2. Move the mouse cursor away from the menu area.</t>
+  </si>
+  <si>
+    <t>The dropdown menu collapses/disappears immediately or with a smooth transition.</t>
+  </si>
+  <si>
+    <t>TC_NAV_004</t>
+  </si>
+  <si>
+    <t>Verify navigation clicking a main category without sub-categories</t>
+  </si>
+  <si>
+    <t>1. Click on a main category that does not typically have a dropdown (e.g., 'Tablets' or 'Software').</t>
+  </si>
+  <si>
+    <t>User is routed directly to the selected Category Listing Page.</t>
+  </si>
+  <si>
+    <t>TC_NAV_005</t>
+  </si>
+  <si>
+    <t>Verify navigation clicking a sub-category</t>
+  </si>
+  <si>
+    <t>1. Hover over 'Desktops'.</t>
+  </si>
+  <si>
+    <t>2. Click on a specific sub-category (e.g., 'Mac' or 'PC').</t>
+  </si>
+  <si>
+    <t>User is routed directly to the selected Sub-Category Listing Page displaying relevant products.</t>
+  </si>
+  <si>
+    <t>TC_NAV_006</t>
+  </si>
+  <si>
+    <t>Verify the 'Show All [Category]' link functionality</t>
+  </si>
+  <si>
+    <t>1. Hover over 'Components'.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Show All Components' link at the bottom of the dropdown.</t>
+  </si>
+  <si>
+    <t>User is routed to the parent Category Listing Page showing all items from all its sub-categories.</t>
+  </si>
+  <si>
+    <t>TC_NAV_007</t>
+  </si>
+  <si>
+    <t>Verify breadcrumb updates on main category navigation</t>
+  </si>
+  <si>
+    <t>1. Click on 'Tablets' from the top menu.</t>
+  </si>
+  <si>
+    <t>2. Observe the breadcrumb trail below the header.</t>
+  </si>
+  <si>
+    <t>The breadcrumb updates accurately to reflect the path (e.g., Home &gt; Tablets).</t>
+  </si>
+  <si>
+    <t>TC_NAV_008</t>
+  </si>
+  <si>
+    <t>Verify breadcrumb updates on sub-category navigation</t>
+  </si>
+  <si>
+    <t>1. Hover over 'Desktops' and click a sub-category.</t>
+  </si>
+  <si>
+    <t>2. Observe the breadcrumb trail.</t>
+  </si>
+  <si>
+    <t>The breadcrumb updates accurately to reflect the parent/child hierarchy (e.g., Home &gt; Desktops &gt; Mac).</t>
+  </si>
+  <si>
+    <t>TC_NAV_009</t>
+  </si>
+  <si>
+    <t>Verify page title dynamically updates based on category</t>
+  </si>
+  <si>
+    <t>1. Click on 'Phones &amp; PDAs' from the top menu.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Look at the browser tab title and the main </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> header on the page.</t>
+    </r>
+  </si>
+  <si>
+    <t>The browser tab title and main page heading accurately display "Phones &amp; PDAs".</t>
+  </si>
+  <si>
+    <t>TC_NAV_010</t>
+  </si>
+  <si>
+    <t>Verify URL routing matches category selection</t>
+  </si>
+  <si>
+    <t>1. Click on 'Cameras' from the top menu.</t>
+  </si>
+  <si>
+    <t>2. Observe the URL in the browser address bar.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The URL routes correctly (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>route=product/category&amp;path=...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or an SEO-friendly URL like </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>/cameras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>TC_NAV_011</t>
+  </si>
+  <si>
+    <t>Verify display message for an empty category</t>
+  </si>
+  <si>
+    <t>1. Click on a category known to have no products (often 'Software' in default data).</t>
+  </si>
+  <si>
+    <t>User is routed to the category page and sees the message "There are no products to list in this category." and a 'Continue' button.</t>
+  </si>
+  <si>
+    <t>TC_NAV_012</t>
+  </si>
+  <si>
+    <t>Verify Top Menu persistence across different modules</t>
+  </si>
+  <si>
+    <t>User is on a non-catalog page (e.g., Checkout or My Account)</t>
+  </si>
+  <si>
+    <t>1. Navigate to the Shopping Cart or My Account page.</t>
+  </si>
+  <si>
+    <t>2. Attempt to use the Top Menu to navigate to 'MP3 Players'.</t>
+  </si>
+  <si>
+    <t>The Top Menu is visible on secure/non-catalog pages and routing works seamlessly.</t>
+  </si>
+  <si>
+    <t>TC_NAV_013</t>
+  </si>
+  <si>
+    <t>Verify active state styling of selected menu item</t>
+  </si>
+  <si>
+    <t>User has navigated to a category</t>
+  </si>
+  <si>
+    <t>1. Click on 'Laptops &amp; Notebooks'.</t>
+  </si>
+  <si>
+    <t>2. Observe the styling of the 'Laptops &amp; Notebooks' link in the top menu.</t>
+  </si>
+  <si>
+    <t>The active category link may have distinct styling (e.g., a darker background or bold text) to indicate current location.</t>
+  </si>
+  <si>
+    <t>TC_NAV_014</t>
+  </si>
+  <si>
+    <t>Verify clicking outside a dropdown closes it</t>
+  </si>
+  <si>
+    <t>1. Hover over 'Components' to open the menu.</t>
+  </si>
+  <si>
+    <t>2. Click anywhere else on the page body (outside the menu).</t>
+  </si>
+  <si>
+    <t>The dropdown menu closes immediately upon clicking outside of it.</t>
+  </si>
+  <si>
+    <t>TC_NAV_015</t>
+  </si>
+  <si>
+    <t>Verify keyboard Tab navigation through the top menu</t>
+  </si>
+  <si>
+    <t>1. Click on the Store Logo.</t>
+  </si>
+  <si>
+    <t>2. Press the 'Tab' key repeatedly to cycle through the Top Menu links.</t>
+  </si>
+  <si>
+    <t>Focus moves logically from left to right across the main categories, allowing navigation without a mouse.</t>
   </si>
 </sst>
 </file>
@@ -2187,7 +2474,402 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="80">
+  <dxfs count="95">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4075,12 +4757,12 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="6" xr9:uid="{DD3ECB35-2970-4076-8662-E1865940DEEF}">
-      <tableStyleElement type="firstColumn" dxfId="56"/>
-      <tableStyleElement type="lastColumn" dxfId="57"/>
-      <tableStyleElement type="firstRowStripe" dxfId="59"/>
-      <tableStyleElement type="secondRowStripe" dxfId="58"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="61"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="60"/>
+      <tableStyleElement type="firstColumn" dxfId="71"/>
+      <tableStyleElement type="lastColumn" dxfId="72"/>
+      <tableStyleElement type="firstRowStripe" dxfId="74"/>
+      <tableStyleElement type="secondRowStripe" dxfId="73"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="76"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="75"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4095,25 +4777,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="93">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="77"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="76"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="91"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="75" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72" totalsRowBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="90" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87" totalsRowBorderDxfId="86">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4123,7 +4805,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="94"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4131,80 +4813,100 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64" headerRowBorderDxfId="63" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="80" dataDxfId="79" headerRowBorderDxfId="78" tableBorderDxfId="77">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="42" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="57" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="56">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="27" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="42" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="41">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="12" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="27" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="26">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+  <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10751,4 +11453,760 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1459B75A-A115-406E-A0F9-D479130746DE}">
+  <dimension ref="A1:K44"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+    <col min="11" max="11" width="23.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="36"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="37"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A8" s="28" t="s">
+        <v>487</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>488</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>489</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+    </row>
+    <row r="9" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A9" s="28" t="s">
+        <v>492</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>493</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>494</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>495</v>
+      </c>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28" t="s">
+        <v>496</v>
+      </c>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+    </row>
+    <row r="10" spans="1:11" ht="57">
+      <c r="A10" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A13" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>494</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+    </row>
+    <row r="14" spans="1:11" ht="71.25">
+      <c r="A14" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11" ht="71.25">
+      <c r="A17" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+    </row>
+    <row r="19" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" ht="57">
+      <c r="A20" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" ht="71.25">
+      <c r="A23" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+    </row>
+    <row r="25" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" ht="71.25">
+      <c r="A26" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+    </row>
+    <row r="28" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" ht="84">
+      <c r="A29" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+    </row>
+    <row r="31" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+    </row>
+    <row r="32" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A32" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>494</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>539</v>
+      </c>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28" t="s">
+        <v>540</v>
+      </c>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+    </row>
+    <row r="33" spans="1:11" ht="71.25">
+      <c r="A33" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+    </row>
+    <row r="35" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+    </row>
+    <row r="36" spans="1:11" ht="85.5">
+      <c r="A36" s="15" t="s">
+        <v>547</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+    </row>
+    <row r="38" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" spans="1:11" ht="57">
+      <c r="A39" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="12"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+    </row>
+    <row r="41" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+    </row>
+    <row r="42" spans="1:11" ht="85.5">
+      <c r="A42" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+    </row>
+    <row r="44" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A44" s="13"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2913E7-C0F0-492A-B69F-242D4495EA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD74C246-3AC3-4A22-9608-60E90EDD889A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="ForgotPassword" sheetId="5" r:id="rId5"/>
     <sheet name="TopMenu" sheetId="6" r:id="rId6"/>
     <sheet name="CurrencySwitch" sheetId="7" r:id="rId7"/>
+    <sheet name="LanguageSwitch" sheetId="8" r:id="rId8"/>
+    <sheet name="Search" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="775">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -2126,6 +2128,566 @@
   </si>
   <si>
     <t>The previously selected currency is remembered via browser cookies/session and is actively applied.</t>
+  </si>
+  <si>
+    <t>TC_LANG_001</t>
+  </si>
+  <si>
+    <t>Verify visibility of the Language Switcher</t>
+  </si>
+  <si>
+    <t>1. Observe the top-left corner of the global header, next to the Currency Switcher.</t>
+  </si>
+  <si>
+    <t>The Language Switcher button is clearly visible and displays the currently active language (e.g., flag icon or "English").</t>
+  </si>
+  <si>
+    <t>TC_LANG_002</t>
+  </si>
+  <si>
+    <t>Verify clicking the Language Switcher expands the menu</t>
+  </si>
+  <si>
+    <t>1. Click on the Language Switcher dropdown button.</t>
+  </si>
+  <si>
+    <t>A dropdown menu expands displaying a list of available languages configured in the store (e.g., English, Spanish, French).</t>
+  </si>
+  <si>
+    <t>TC_LANG_003</t>
+  </si>
+  <si>
+    <t>Verify selecting a new language translates static UI text</t>
+  </si>
+  <si>
+    <t>1. Click the Language dropdown.</t>
+  </si>
+  <si>
+    <t>2. Select a different language (e.g., Spanish).</t>
+  </si>
+  <si>
+    <t>The page refreshes and hardcoded UI elements (like "Shopping Cart", "Checkout", "Search") are translated into the selected language.</t>
+  </si>
+  <si>
+    <t>TC_LANG_004</t>
+  </si>
+  <si>
+    <t>Verify language change translates dynamic catalog data</t>
+  </si>
+  <si>
+    <t>Store has translated products configured</t>
+  </si>
+  <si>
+    <t>1. Navigate to a product page.</t>
+  </si>
+  <si>
+    <t>2. Change the language via the header dropdown.</t>
+  </si>
+  <si>
+    <t>The Product Title, Description, and Category names update to reflect the translated versions of that specific data.</t>
+  </si>
+  <si>
+    <t>TC_LANG_005</t>
+  </si>
+  <si>
+    <t>Verify language selection persists across page navigation</t>
+  </si>
+  <si>
+    <t>User has changed the default language</t>
+  </si>
+  <si>
+    <t>1. Change the language to 'French'.</t>
+  </si>
+  <si>
+    <t>2. Navigate to a different page (e.g., click 'Desktops').</t>
+  </si>
+  <si>
+    <t>The selected language ('French') persists, and the newly loaded page renders in French.</t>
+  </si>
+  <si>
+    <t>TC_LANG_006</t>
+  </si>
+  <si>
+    <t>Verify language selection persists during the Checkout process</t>
+  </si>
+  <si>
+    <t>User has items in cart and has changed the language</t>
+  </si>
+  <si>
+    <t>2. Observe the checkout steps and form labels.</t>
+  </si>
+  <si>
+    <t>All instructions, form labels, and buttons throughout the checkout pipeline remain in the user-selected language.</t>
+  </si>
+  <si>
+    <t>TC_LANG_007</t>
+  </si>
+  <si>
+    <t>User has expanded the Language dropdown</t>
+  </si>
+  <si>
+    <t>1. Click the Language dropdown so the list is visible.</t>
+  </si>
+  <si>
+    <t>The dropdown menu collapses immediately without changing the active language.</t>
+  </si>
+  <si>
+    <t>TC_LANG_008</t>
+  </si>
+  <si>
+    <t>Verify language selection is retained for logged-in users</t>
+  </si>
+  <si>
+    <t>1. Change the language to 'Spanish'.</t>
+  </si>
+  <si>
+    <t>The system remembers the user's preference and loads the interface in 'Spanish' upon logging back in.</t>
+  </si>
+  <si>
+    <t>TC_LANG_009</t>
+  </si>
+  <si>
+    <t>Verify language selection is saved in session for guest users</t>
+  </si>
+  <si>
+    <t>1. Change the language to a non-default option.</t>
+  </si>
+  <si>
+    <t>The previously selected language is remembered via browser cookies/session and the site loads in that language.</t>
+  </si>
+  <si>
+    <t>TC_LANG_010</t>
+  </si>
+  <si>
+    <t>Verify URL updates accurately reflect language routing (if applicable)</t>
+  </si>
+  <si>
+    <t>1. Change the language to a secondary option.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If the store uses SEO language routing, the URL updates to reflect the language code (e.g., appending </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>?lang=es</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or routing to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>/es/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>estCaseId</t>
+  </si>
+  <si>
+    <t>TC_SRCH_001</t>
+  </si>
+  <si>
+    <t>Verify Basic Search with a valid exact keyword</t>
+  </si>
+  <si>
+    <t>1. Enter an exact existing product name (e.g., "MacBook") in the global search bar.</t>
+  </si>
+  <si>
+    <t>2. Click the magnifying glass Search button.</t>
+  </si>
+  <si>
+    <t>User is routed to the Search Results page displaying the exact matching product(s).</t>
+  </si>
+  <si>
+    <t>Verify Basic Search with a valid partial keyword</t>
+  </si>
+  <si>
+    <t>1. Enter a partial product name (e.g., "Mac") in the global search bar.</t>
+  </si>
+  <si>
+    <t>2. Click the Search button.</t>
+  </si>
+  <si>
+    <t>Search Results page displays all products containing "Mac" in their title.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_003</t>
+  </si>
+  <si>
+    <t>Verify Basic Search with no matching results</t>
+  </si>
+  <si>
+    <t>1. Enter a random, non-existent string (e.g., "XYZ999").</t>
+  </si>
+  <si>
+    <t>Search Results page displays the message: "There is no product that matches the search criteria."</t>
+  </si>
+  <si>
+    <t>TC_SRCH_004</t>
+  </si>
+  <si>
+    <t>Verify Basic Search leaving the search field blank</t>
+  </si>
+  <si>
+    <t>1. Leave the global search bar completely empty.</t>
+  </si>
+  <si>
+    <t>User is routed to the Search page and the "There is no product that matches the search criteria." message is displayed.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_005</t>
+  </si>
+  <si>
+    <t>Verify Basic Search execution using the 'Enter' key</t>
+  </si>
+  <si>
+    <t>1. Enter a valid product name.</t>
+  </si>
+  <si>
+    <t>Search is triggered successfully and results are displayed exactly as if the button was clicked.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_006</t>
+  </si>
+  <si>
+    <t>Verify Search keyword case insensitivity</t>
+  </si>
+  <si>
+    <t>1. Enter a valid product name using mixed/incorrect casing (e.g., "mAcBoOk").</t>
+  </si>
+  <si>
+    <t>Search Results page accurately displays the matching product(s) regardless of casing.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_007</t>
+  </si>
+  <si>
+    <t>Verify Search handles leading and trailing whitespaces</t>
+  </si>
+  <si>
+    <t>1. Enter a valid product name with spaces at the beginning and end.</t>
+  </si>
+  <si>
+    <t>Search is successful. The system trims the whitespaces and returns the correct product(s).</t>
+  </si>
+  <si>
+    <t>TC_SRCH_008</t>
+  </si>
+  <si>
+    <t>Verify Search with special characters</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter special characters (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>@#$%^&amp;*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>System safely processes the request and returns "no product matches" without throwing server errors.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_009</t>
+  </si>
+  <si>
+    <t>Verify Search with alphanumeric combinations</t>
+  </si>
+  <si>
+    <t>1. Enter an alphanumeric product code or name (e.g., "iPhone 5" or a specific SKU).</t>
+  </si>
+  <si>
+    <t>Search Results page accurately displays the matching alphanumeric product(s).</t>
+  </si>
+  <si>
+    <t>TC_SRCH_010</t>
+  </si>
+  <si>
+    <t>Verify maximum character limit of the Search bar</t>
+  </si>
+  <si>
+    <t>1. Paste a string of 255+ characters into the global search bar.</t>
+  </si>
+  <si>
+    <t>The search executes safely; it either truncates the input to the max limit or returns no results without crashing.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_011</t>
+  </si>
+  <si>
+    <t>Verify Security: XSS injection in Search bar</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter a basic script tag (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;script&gt;alert(1)&lt;/script&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) into the search bar.</t>
+    </r>
+  </si>
+  <si>
+    <t>Script is not executed. The input is sanitized and reflected safely as text on the results page.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_012</t>
+  </si>
+  <si>
+    <t>Verify Security: SQL injection in Search bar</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter an SQL payload (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>' OR 1=1 --</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) into the search bar.</t>
+    </r>
+  </si>
+  <si>
+    <t>Database bypass fails. System safely handles the payload and returns no results.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_013</t>
+  </si>
+  <si>
+    <t>Verify Advanced Search: Search in product descriptions</t>
+  </si>
+  <si>
+    <t>User is on the Search Results page</t>
+  </si>
+  <si>
+    <t>1. Enter a keyword known to be in a description but NOT the title.</t>
+  </si>
+  <si>
+    <t>2. Check the 'Search in product descriptions' checkbox.</t>
+  </si>
+  <si>
+    <t>3. Click the Advanced 'Search' button.</t>
+  </si>
+  <si>
+    <t>The product is successfully found and displayed in the results.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_014</t>
+  </si>
+  <si>
+    <t>Verify Advanced Search: Search within a specific category</t>
+  </si>
+  <si>
+    <t>1. Enter a generic keyword (e.g., "Apple").</t>
+  </si>
+  <si>
+    <t>2. Select a specific category from the dropdown (e.g., 'Monitors').</t>
+  </si>
+  <si>
+    <t>3. Click 'Search'.</t>
+  </si>
+  <si>
+    <t>Results only display products containing "Apple" that are strictly within the 'Monitors' category.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_015</t>
+  </si>
+  <si>
+    <t>Verify Advanced Search: Search within subcategories</t>
+  </si>
+  <si>
+    <t>1. Enter a keyword.</t>
+  </si>
+  <si>
+    <t>2. Select a parent category.</t>
+  </si>
+  <si>
+    <t>3. Check the 'Search in subcategories' checkbox.</t>
+  </si>
+  <si>
+    <t>4. Click 'Search'.</t>
+  </si>
+  <si>
+    <t>Results display matching products from the parent category AND all its child subcategories.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_016</t>
+  </si>
+  <si>
+    <t>Verify Advanced Search: Multiple keywords</t>
+  </si>
+  <si>
+    <t>1. Enter multiple words separated by space (e.g., "Apple Cinema 30").</t>
+  </si>
+  <si>
+    <t>2. Click 'Search'.</t>
+  </si>
+  <si>
+    <t>Results correctly parse the string and return the specific matching product(s).</t>
+  </si>
+  <si>
+    <t>TC_SRCH_017</t>
+  </si>
+  <si>
+    <t>Verify sorting functionality on Search Results</t>
+  </si>
+  <si>
+    <t>User has performed a search yielding multiple results</t>
+  </si>
+  <si>
+    <t>1. Click the 'Sort By' dropdown on the results page.</t>
+  </si>
+  <si>
+    <t>2. Select 'Price (Low &gt; High)'.</t>
+  </si>
+  <si>
+    <t>The search results dynamically reorder to display the cheapest items first.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_018</t>
+  </si>
+  <si>
+    <t>Verify 'Show' limit functionality on Search Results</t>
+  </si>
+  <si>
+    <t>User has performed a search yielding 20+ results</t>
+  </si>
+  <si>
+    <t>1. Click the 'Show' dropdown on the results page.</t>
+  </si>
+  <si>
+    <t>2. Select a limit (e.g., '15').</t>
+  </si>
+  <si>
+    <t>The page refreshes and strictly displays a maximum of 15 products on the current page.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_019</t>
+  </si>
+  <si>
+    <t>Verify Pagination on Search Results</t>
+  </si>
+  <si>
+    <t>User has performed a search where results exceed the 'Show' limit</t>
+  </si>
+  <si>
+    <t>1. Scroll to the bottom of the results list.</t>
+  </si>
+  <si>
+    <t>2. Click on page '2' or the 'Next &gt;' button.</t>
+  </si>
+  <si>
+    <t>User is routed to the second page of search results accurately.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_020</t>
+  </si>
+  <si>
+    <t>Verify List/Grid View toggle on Search Results</t>
+  </si>
+  <si>
+    <t>1. Locate the view toggle buttons (List / Grid) near the top right of the results.</t>
+  </si>
+  <si>
+    <t>2. Click 'List' and then 'Grid'.</t>
+  </si>
+  <si>
+    <t>The layout of the products seamlessly switches between a vertical list format and a horizontal grid format.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_021</t>
+  </si>
+  <si>
+    <t>Verify navigating to a product from Search Results</t>
+  </si>
+  <si>
+    <t>User has performed a successful search</t>
+  </si>
+  <si>
+    <t>1. Click on the image or title of a product in the search results list.</t>
+  </si>
+  <si>
+    <t>User is routed correctly to the detailed Product Display Page (PDP) for that specific item.</t>
+  </si>
+  <si>
+    <t>TC_SRCH_022</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Cart' directly from Search Results</t>
+  </si>
+  <si>
+    <t>1. Locate a product in the search results.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Add to Cart' button (cart icon) on its listing card.</t>
+  </si>
+  <si>
+    <t>A success banner appears indicating the item was added to the cart, and the mini-cart total updates.</t>
   </si>
 </sst>
 </file>
@@ -2229,7 +2791,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -2541,12 +3103,111 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2570,7 +3231,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2625,9 +3286,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2663,12 +3323,828 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="110">
+  <dxfs count="134">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2991,38 +4467,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color rgb="FFC4C7C5"/>
-        </vertical>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color theme="1"/>
@@ -3066,155 +4510,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right/>
-        <top style="medium">
-          <color rgb="FFC4C7C5"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFC4C7C5"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFC4C7C5"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFC4C7C5"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -3224,24 +4519,25 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="11"/>
         <color theme="1"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
         <right style="medium">
           <color rgb="FFC4C7C5"/>
         </right>
-        <top style="medium">
+        <top/>
+        <bottom/>
+        <vertical style="medium">
           <color rgb="FFC4C7C5"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
+        </vertical>
       </border>
     </dxf>
     <dxf>
@@ -3266,9 +4562,7 @@
         <left style="medium">
           <color theme="1"/>
         </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
+        <right/>
         <top/>
         <bottom/>
         <vertical/>
@@ -3553,9 +4847,7 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
+        <left/>
         <right style="medium">
           <color theme="1"/>
         </right>
@@ -3563,38 +4855,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color rgb="FFC4C7C5"/>
-        </vertical>
       </border>
     </dxf>
     <dxf>
@@ -3637,6 +4897,35 @@
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3974,6 +5263,32 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -3999,32 +5314,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -4362,35 +5651,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -4417,339 +5677,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top style="medium">
-          <color theme="1"/>
-        </top>
-        <bottom style="medium">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -4775,32 +5702,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -5122,12 +6023,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
@@ -5145,13 +6040,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -5169,6 +6057,13 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -5200,6 +6095,185 @@
         <vertical style="medium">
           <color rgb="FFC4C7C5"/>
         </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -5224,6 +6298,25 @@
           <color rgb="FFC4C7C5"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -5317,6 +6410,369 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -5328,21 +6784,28 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="Aptos Narrow"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Table Style 1" pivot="0" count="6" xr9:uid="{DD3ECB35-2970-4076-8662-E1865940DEEF}">
-      <tableStyleElement type="firstColumn" dxfId="92"/>
-      <tableStyleElement type="lastColumn" dxfId="93"/>
-      <tableStyleElement type="firstRowStripe" dxfId="95"/>
-      <tableStyleElement type="secondRowStripe" dxfId="94"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="97"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="96"/>
-    </tableStyle>
+    <tableStyle name="Table Style 1" pivot="0" count="6" xr9:uid="{DD3ECB35-2970-4076-8662-E1865940DEEF}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5356,25 +6819,65 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="118">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="107"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="106"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="117"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="116"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="27" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="26">
+  <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+  <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="105" dataDxfId="15" headerRowBorderDxfId="104" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="115" dataDxfId="113" headerRowBorderDxfId="114" tableBorderDxfId="112" totalsRowBorderDxfId="111">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="110"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="108"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="107"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="106"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5384,7 +6887,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="105"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5392,120 +6895,120 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="101" dataDxfId="100" headerRowBorderDxfId="99" tableBorderDxfId="98">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="91"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="86"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="85"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="83"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="78" dataDxfId="79" headerRowBorderDxfId="80" tableBorderDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="73"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="72"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="70"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="69"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="68"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="67"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="63" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="48" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="32" dataDxfId="34" headerRowBorderDxfId="35" tableBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41">
   <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130">
   <autoFilter ref="A6:K40" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="129"/>
+    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="128"/>
+    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="127"/>
+    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="126"/>
+    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="124"/>
+    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="123"/>
+    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="121"/>
+    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="119"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5868,19 +7371,19 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="39">
+      <c r="E2" s="38">
         <v>27</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -5891,19 +7394,19 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="30.75" thickBot="1">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="39">
+      <c r="E3" s="38">
         <v>23</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -5914,19 +7417,19 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="30.75" thickBot="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="39">
+      <c r="E4" s="38">
         <v>11</v>
       </c>
       <c r="K4" s="1" t="s">
@@ -5937,19 +7440,19 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="38">
         <v>25</v>
       </c>
       <c r="K5" s="1" t="s">
@@ -5960,19 +7463,19 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="38">
         <v>15</v>
       </c>
       <c r="K6" s="1" t="s">
@@ -5983,560 +7486,560 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="38">
         <v>10</v>
       </c>
       <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="38">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="38">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="38">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="38">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="38">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="30.75" thickBot="1">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="38">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="30.75" thickBot="1">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="38">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30.75" thickBot="1">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="38">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="38">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="38">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30.75" thickBot="1">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="38">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="38">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="38">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="38">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30.75" thickBot="1">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="38">
         <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="38">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="38">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="38">
         <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="30.75" thickBot="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="39">
+      <c r="E26" s="38">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="30.75" thickBot="1">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="38" t="s">
+      <c r="D27" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="39">
+      <c r="E27" s="38">
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="39">
+      <c r="E28" s="38">
         <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="38" t="s">
+      <c r="B29" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="D29" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="39">
+      <c r="E29" s="38">
         <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A30" s="37" t="s">
+      <c r="A30" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="38" t="s">
+      <c r="B30" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="38">
         <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="30.75" thickBot="1">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="39">
+      <c r="E31" s="38">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A32" s="37" t="s">
+      <c r="A32" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="38" t="s">
+      <c r="B32" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="D32" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="39">
+      <c r="E32" s="38">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="38" t="s">
+      <c r="B33" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="C33" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="39">
+      <c r="E33" s="38">
         <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A34" s="37" t="s">
+      <c r="A34" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="38" t="s">
+      <c r="B34" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="38" t="s">
+      <c r="C34" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="39">
+      <c r="E34" s="38">
         <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="30.75" thickBot="1">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="C35" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="38" t="s">
+      <c r="D35" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="38">
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="38" t="s">
+      <c r="B36" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="D36" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="38">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A37" s="37" t="s">
+      <c r="A37" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="38" t="s">
+      <c r="C37" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="38" t="s">
+      <c r="D37" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="39">
+      <c r="E37" s="38">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="45.75" thickBot="1">
-      <c r="A38" s="37" t="s">
+      <c r="A38" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B38" s="38" t="s">
+      <c r="B38" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E38" s="39">
+      <c r="E38" s="38">
         <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="31.5">
-      <c r="A39" s="40" t="s">
+      <c r="A39" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="41"/>
-      <c r="C39" s="42" t="s">
+      <c r="B39" s="40"/>
+      <c r="C39" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="41"/>
-      <c r="E39" s="43">
+      <c r="D39" s="40"/>
+      <c r="E39" s="42">
         <v>607</v>
       </c>
     </row>
@@ -8546,7 +10049,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
     <col min="3" max="3" width="31.5703125" customWidth="1"/>
     <col min="4" max="4" width="32.42578125" customWidth="1"/>
     <col min="5" max="5" width="28.140625" customWidth="1"/>
@@ -8559,16 +10062,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="29"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1">
       <c r="A6" s="9" t="s">
@@ -8580,25 +10083,25 @@
       <c r="C6" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="33" t="s">
+      <c r="J6" s="32" t="s">
         <v>108</v>
       </c>
       <c r="K6" s="17" t="s">
@@ -9416,13 +10919,13 @@
       <c r="K56" s="12"/>
     </row>
     <row r="57" spans="1:11" ht="57.75" thickBot="1">
-      <c r="A57" s="34" t="s">
+      <c r="A57" s="33" t="s">
         <v>271</v>
       </c>
       <c r="B57" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" s="33" t="s">
         <v>203</v>
       </c>
       <c r="D57" s="21" t="s">
@@ -10187,46 +11690,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="29"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" thickBot="1">
       <c r="A7" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="32" t="s">
         <v>108</v>
       </c>
       <c r="K7" s="17" t="s">
@@ -10340,7 +11843,7 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14" spans="1:11" ht="86.25" thickBot="1">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="33" t="s">
         <v>337</v>
       </c>
       <c r="B14" s="21" t="s">
@@ -10365,7 +11868,7 @@
       <c r="K14" s="22"/>
     </row>
     <row r="15" spans="1:11" ht="43.5" thickBot="1">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="33" t="s">
         <v>342</v>
       </c>
       <c r="B15" s="21" t="s">
@@ -10390,7 +11893,7 @@
       <c r="K15" s="22"/>
     </row>
     <row r="16" spans="1:11" ht="100.5" thickBot="1">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="33" t="s">
         <v>347</v>
       </c>
       <c r="B16" s="21" t="s">
@@ -10468,7 +11971,7 @@
       <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:11" ht="72" thickBot="1">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="33" t="s">
         <v>357</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -10493,7 +11996,7 @@
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" ht="86.25" thickBot="1">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="33" t="s">
         <v>360</v>
       </c>
       <c r="B21" s="21" t="s">
@@ -10662,7 +12165,6 @@
       <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="28.5">
-      <c r="A30" s="28"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -10703,40 +12205,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="29"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1">
       <c r="A4" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="32" t="s">
         <v>104</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>106</v>
       </c>
       <c r="I4" s="7" t="s">
@@ -10745,7 +12247,7 @@
       <c r="J4" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>109</v>
       </c>
     </row>
@@ -12073,46 +13575,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="29"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" thickBot="1">
       <c r="A7" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="32" t="s">
         <v>108</v>
       </c>
       <c r="K7" s="17" t="s">
@@ -12829,46 +14331,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="29"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1">
       <c r="A6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="33" t="s">
+      <c r="J6" s="32" t="s">
         <v>108</v>
       </c>
       <c r="K6" s="17" t="s">
@@ -13467,4 +14969,1930 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{232D45A9-C56E-4AF9-90D2-A867BB226C20}">
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A8" s="49" t="s">
+        <v>621</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>622</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>623</v>
+      </c>
+      <c r="F8" s="49"/>
+      <c r="G8" s="50" t="s">
+        <v>624</v>
+      </c>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+    </row>
+    <row r="9" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A9" s="47" t="s">
+        <v>625</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>626</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="F9" s="43"/>
+      <c r="G9" s="46" t="s">
+        <v>628</v>
+      </c>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="48"/>
+    </row>
+    <row r="10" spans="1:11" ht="112.5" customHeight="1">
+      <c r="A10" s="51" t="s">
+        <v>629</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>630</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>489</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>631</v>
+      </c>
+      <c r="F10" s="51"/>
+      <c r="G10" s="52" t="s">
+        <v>633</v>
+      </c>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+    </row>
+    <row r="12" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44" t="s">
+        <v>632</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+    </row>
+    <row r="13" spans="1:11" ht="84" customHeight="1">
+      <c r="A13" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>635</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>636</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="46" t="s">
+        <v>639</v>
+      </c>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="48"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="47"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="48"/>
+    </row>
+    <row r="15" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A15" s="47"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43" t="s">
+        <v>638</v>
+      </c>
+      <c r="F15" s="43"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="48"/>
+    </row>
+    <row r="16" spans="1:11" ht="71.25">
+      <c r="A16" s="51" t="s">
+        <v>640</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>641</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>642</v>
+      </c>
+      <c r="E16" s="51" t="s">
+        <v>643</v>
+      </c>
+      <c r="F16" s="51"/>
+      <c r="G16" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A18" s="44"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44" t="s">
+        <v>644</v>
+      </c>
+      <c r="F18" s="44"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+    </row>
+    <row r="19" spans="1:11" ht="99.75">
+      <c r="A19" s="51" t="s">
+        <v>646</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>647</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>648</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>598</v>
+      </c>
+      <c r="F19" s="51"/>
+      <c r="G19" s="52" t="s">
+        <v>650</v>
+      </c>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44" t="s">
+        <v>649</v>
+      </c>
+      <c r="F21" s="44"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+    </row>
+    <row r="22" spans="1:11" ht="85.5">
+      <c r="A22" s="47" t="s">
+        <v>651</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>602</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>653</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="46" t="s">
+        <v>654</v>
+      </c>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="48"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="47"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="48"/>
+    </row>
+    <row r="24" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A24" s="47"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43" t="s">
+        <v>605</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="48"/>
+    </row>
+    <row r="25" spans="1:11" ht="99.75">
+      <c r="A25" s="51" t="s">
+        <v>655</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>656</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>609</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>657</v>
+      </c>
+      <c r="F25" s="51"/>
+      <c r="G25" s="52" t="s">
+        <v>658</v>
+      </c>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="28.5">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43" t="s">
+        <v>611</v>
+      </c>
+      <c r="F27" s="43"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44" t="s">
+        <v>612</v>
+      </c>
+      <c r="F29" s="44"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+    </row>
+    <row r="30" spans="1:11" ht="99.75">
+      <c r="A30" s="47" t="s">
+        <v>659</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>660</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>616</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>661</v>
+      </c>
+      <c r="F30" s="43"/>
+      <c r="G30" s="46" t="s">
+        <v>662</v>
+      </c>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="48"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="47"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="48"/>
+    </row>
+    <row r="32" spans="1:11" ht="42.75">
+      <c r="A32" s="47"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43" t="s">
+        <v>618</v>
+      </c>
+      <c r="F32" s="43"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="48"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="47"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="48"/>
+    </row>
+    <row r="34" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A34" s="47"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43" t="s">
+        <v>619</v>
+      </c>
+      <c r="F34" s="43"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="48"/>
+    </row>
+    <row r="35" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A35" s="51" t="s">
+        <v>663</v>
+      </c>
+      <c r="B35" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>664</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>489</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>665</v>
+      </c>
+      <c r="F35" s="51"/>
+      <c r="G35" s="52" t="s">
+        <v>666</v>
+      </c>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="43"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A37" s="44"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44" t="s">
+        <v>535</v>
+      </c>
+      <c r="F37" s="44"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206473C7-58F5-4D01-B463-092AFD30E91D}">
+  <dimension ref="A1:K79"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="71.25">
+      <c r="A8" s="51" t="s">
+        <v>668</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>669</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>489</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>670</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>672</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44" t="s">
+        <v>671</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+    </row>
+    <row r="11" spans="1:11" ht="71.25">
+      <c r="A11" s="43" t="s">
+        <v>567</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>673</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>674</v>
+      </c>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43" t="s">
+        <v>676</v>
+      </c>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43" t="s">
+        <v>675</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" ht="85.5">
+      <c r="A14" s="51" t="s">
+        <v>677</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>678</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>489</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>679</v>
+      </c>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51" t="s">
+        <v>680</v>
+      </c>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44" t="s">
+        <v>675</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+    </row>
+    <row r="17" spans="1:11" ht="183.75" customHeight="1">
+      <c r="A17" s="43" t="s">
+        <v>681</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>682</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>683</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43" t="s">
+        <v>684</v>
+      </c>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43" t="s">
+        <v>675</v>
+      </c>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="85.5">
+      <c r="A20" s="51" t="s">
+        <v>685</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>686</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>489</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>687</v>
+      </c>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51" t="s">
+        <v>688</v>
+      </c>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44" t="s">
+        <v>415</v>
+      </c>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+    </row>
+    <row r="23" spans="1:11" ht="99.75">
+      <c r="A23" s="43" t="s">
+        <v>689</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>690</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>691</v>
+      </c>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43" t="s">
+        <v>692</v>
+      </c>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43" t="s">
+        <v>675</v>
+      </c>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="85.5">
+      <c r="A26" s="51" t="s">
+        <v>693</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>694</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>489</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>695</v>
+      </c>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51" t="s">
+        <v>696</v>
+      </c>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44" t="s">
+        <v>675</v>
+      </c>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
+    </row>
+    <row r="29" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A29" s="43" t="s">
+        <v>697</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>698</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>699</v>
+      </c>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43" t="s">
+        <v>700</v>
+      </c>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43" t="s">
+        <v>675</v>
+      </c>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="85.5">
+      <c r="A32" s="51" t="s">
+        <v>701</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>702</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>489</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>703</v>
+      </c>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51" t="s">
+        <v>704</v>
+      </c>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="43"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44" t="s">
+        <v>675</v>
+      </c>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
+    </row>
+    <row r="35" spans="1:11" ht="99.75">
+      <c r="A35" s="43" t="s">
+        <v>705</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>706</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>707</v>
+      </c>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43" t="s">
+        <v>708</v>
+      </c>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="43"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43" t="s">
+        <v>675</v>
+      </c>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="85.5">
+      <c r="A38" s="51" t="s">
+        <v>709</v>
+      </c>
+      <c r="B38" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>710</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>489</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>711</v>
+      </c>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51" t="s">
+        <v>712</v>
+      </c>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="51"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A40" s="44"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44" t="s">
+        <v>675</v>
+      </c>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="44"/>
+    </row>
+    <row r="41" spans="1:11" ht="71.25">
+      <c r="A41" s="43" t="s">
+        <v>713</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>714</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>715</v>
+      </c>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43" t="s">
+        <v>716</v>
+      </c>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+    </row>
+    <row r="43" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A43" s="43"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43" t="s">
+        <v>675</v>
+      </c>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+    </row>
+    <row r="44" spans="1:11" ht="57">
+      <c r="A44" s="51" t="s">
+        <v>717</v>
+      </c>
+      <c r="B44" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="51" t="s">
+        <v>718</v>
+      </c>
+      <c r="D44" s="51" t="s">
+        <v>719</v>
+      </c>
+      <c r="E44" s="51" t="s">
+        <v>720</v>
+      </c>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51" t="s">
+        <v>723</v>
+      </c>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
+      <c r="K44" s="51"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:11" ht="57">
+      <c r="A46" s="43"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43" t="s">
+        <v>721</v>
+      </c>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44" t="s">
+        <v>722</v>
+      </c>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+    </row>
+    <row r="49" spans="1:11" ht="85.5">
+      <c r="A49" s="43" t="s">
+        <v>724</v>
+      </c>
+      <c r="B49" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>725</v>
+      </c>
+      <c r="D49" s="43" t="s">
+        <v>719</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>726</v>
+      </c>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43" t="s">
+        <v>729</v>
+      </c>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+    </row>
+    <row r="51" spans="1:11" ht="57">
+      <c r="A51" s="43"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43" t="s">
+        <v>727</v>
+      </c>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="43"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+    </row>
+    <row r="53" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A53" s="43"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43" t="s">
+        <v>728</v>
+      </c>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+    </row>
+    <row r="54" spans="1:11" ht="85.5">
+      <c r="A54" s="51" t="s">
+        <v>730</v>
+      </c>
+      <c r="B54" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="51" t="s">
+        <v>731</v>
+      </c>
+      <c r="D54" s="51" t="s">
+        <v>719</v>
+      </c>
+      <c r="E54" s="51" t="s">
+        <v>732</v>
+      </c>
+      <c r="F54" s="51"/>
+      <c r="G54" s="51" t="s">
+        <v>736</v>
+      </c>
+      <c r="H54" s="51"/>
+      <c r="I54" s="51"/>
+      <c r="J54" s="51"/>
+      <c r="K54" s="51"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="43"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43"/>
+    </row>
+    <row r="56" spans="1:11" ht="28.5">
+      <c r="A56" s="43"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43" t="s">
+        <v>733</v>
+      </c>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="43"/>
+      <c r="J56" s="43"/>
+      <c r="K56" s="43"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="43"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="43"/>
+      <c r="I57" s="43"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="43"/>
+    </row>
+    <row r="58" spans="1:11" ht="57">
+      <c r="A58" s="43"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43" t="s">
+        <v>734</v>
+      </c>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="43"/>
+      <c r="J58" s="43"/>
+      <c r="K58" s="43"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="43"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="43"/>
+    </row>
+    <row r="60" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A60" s="44"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44" t="s">
+        <v>735</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="44"/>
+      <c r="J60" s="44"/>
+      <c r="K60" s="44"/>
+    </row>
+    <row r="61" spans="1:11" ht="71.25">
+      <c r="A61" s="43" t="s">
+        <v>737</v>
+      </c>
+      <c r="B61" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" s="43" t="s">
+        <v>738</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>719</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>739</v>
+      </c>
+      <c r="F61" s="43"/>
+      <c r="G61" s="43" t="s">
+        <v>741</v>
+      </c>
+      <c r="H61" s="43"/>
+      <c r="I61" s="43"/>
+      <c r="J61" s="43"/>
+      <c r="K61" s="43"/>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="43"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="43"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="43"/>
+      <c r="G62" s="43"/>
+      <c r="H62" s="43"/>
+      <c r="I62" s="43"/>
+      <c r="J62" s="43"/>
+      <c r="K62" s="43"/>
+    </row>
+    <row r="63" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="43" t="s">
+        <v>740</v>
+      </c>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="43"/>
+      <c r="I63" s="43"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+    </row>
+    <row r="64" spans="1:11" ht="71.25">
+      <c r="A64" s="51" t="s">
+        <v>742</v>
+      </c>
+      <c r="B64" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="51" t="s">
+        <v>743</v>
+      </c>
+      <c r="D64" s="51" t="s">
+        <v>744</v>
+      </c>
+      <c r="E64" s="51" t="s">
+        <v>745</v>
+      </c>
+      <c r="F64" s="51"/>
+      <c r="G64" s="51" t="s">
+        <v>747</v>
+      </c>
+      <c r="H64" s="51"/>
+      <c r="I64" s="51"/>
+      <c r="J64" s="51"/>
+      <c r="K64" s="51"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="43"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="43"/>
+      <c r="G65" s="43"/>
+      <c r="H65" s="43"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+    </row>
+    <row r="66" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A66" s="44"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="44"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44" t="s">
+        <v>746</v>
+      </c>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="44"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="44"/>
+    </row>
+    <row r="67" spans="1:11" ht="85.5">
+      <c r="A67" s="43" t="s">
+        <v>748</v>
+      </c>
+      <c r="B67" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" s="43" t="s">
+        <v>749</v>
+      </c>
+      <c r="D67" s="43" t="s">
+        <v>750</v>
+      </c>
+      <c r="E67" s="43" t="s">
+        <v>751</v>
+      </c>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43" t="s">
+        <v>753</v>
+      </c>
+      <c r="H67" s="43"/>
+      <c r="I67" s="43"/>
+      <c r="J67" s="43"/>
+      <c r="K67" s="43"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="43"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="45"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43"/>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="43"/>
+    </row>
+    <row r="69" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A69" s="43"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43" t="s">
+        <v>752</v>
+      </c>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
+      <c r="H69" s="43"/>
+      <c r="I69" s="43"/>
+      <c r="J69" s="43"/>
+      <c r="K69" s="43"/>
+    </row>
+    <row r="70" spans="1:11" ht="71.25">
+      <c r="A70" s="51" t="s">
+        <v>754</v>
+      </c>
+      <c r="B70" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" s="51" t="s">
+        <v>755</v>
+      </c>
+      <c r="D70" s="51" t="s">
+        <v>756</v>
+      </c>
+      <c r="E70" s="51" t="s">
+        <v>757</v>
+      </c>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51" t="s">
+        <v>759</v>
+      </c>
+      <c r="H70" s="51"/>
+      <c r="I70" s="51"/>
+      <c r="J70" s="51"/>
+      <c r="K70" s="51"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="43"/>
+      <c r="B71" s="43"/>
+      <c r="C71" s="43"/>
+      <c r="D71" s="43"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="43"/>
+      <c r="G71" s="43"/>
+      <c r="H71" s="43"/>
+      <c r="I71" s="43"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+    </row>
+    <row r="72" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A72" s="44"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="44"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="44" t="s">
+        <v>758</v>
+      </c>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
+      <c r="I72" s="44"/>
+      <c r="J72" s="44"/>
+      <c r="K72" s="44"/>
+    </row>
+    <row r="73" spans="1:11" ht="99.75">
+      <c r="A73" s="43" t="s">
+        <v>760</v>
+      </c>
+      <c r="B73" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="43" t="s">
+        <v>761</v>
+      </c>
+      <c r="D73" s="43" t="s">
+        <v>744</v>
+      </c>
+      <c r="E73" s="43" t="s">
+        <v>762</v>
+      </c>
+      <c r="F73" s="43"/>
+      <c r="G73" s="43" t="s">
+        <v>764</v>
+      </c>
+      <c r="H73" s="43"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="43"/>
+      <c r="K73" s="43"/>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="43"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="43"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="43"/>
+      <c r="G74" s="43"/>
+      <c r="H74" s="43"/>
+      <c r="I74" s="43"/>
+      <c r="J74" s="43"/>
+      <c r="K74" s="43"/>
+    </row>
+    <row r="75" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A75" s="43"/>
+      <c r="B75" s="43"/>
+      <c r="C75" s="43"/>
+      <c r="D75" s="43"/>
+      <c r="E75" s="43" t="s">
+        <v>763</v>
+      </c>
+      <c r="F75" s="43"/>
+      <c r="G75" s="43"/>
+      <c r="H75" s="43"/>
+      <c r="I75" s="43"/>
+      <c r="J75" s="43"/>
+      <c r="K75" s="43"/>
+    </row>
+    <row r="76" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A76" s="49" t="s">
+        <v>765</v>
+      </c>
+      <c r="B76" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="49" t="s">
+        <v>766</v>
+      </c>
+      <c r="D76" s="49" t="s">
+        <v>767</v>
+      </c>
+      <c r="E76" s="49" t="s">
+        <v>768</v>
+      </c>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49" t="s">
+        <v>769</v>
+      </c>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
+    </row>
+    <row r="77" spans="1:11" ht="85.5">
+      <c r="A77" s="51" t="s">
+        <v>770</v>
+      </c>
+      <c r="B77" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" s="51" t="s">
+        <v>771</v>
+      </c>
+      <c r="D77" s="51" t="s">
+        <v>767</v>
+      </c>
+      <c r="E77" s="51" t="s">
+        <v>772</v>
+      </c>
+      <c r="F77" s="51"/>
+      <c r="G77" s="51" t="s">
+        <v>774</v>
+      </c>
+      <c r="H77" s="51"/>
+      <c r="I77" s="51"/>
+      <c r="J77" s="51"/>
+      <c r="K77" s="51"/>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="43"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="43"/>
+      <c r="D78" s="43"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="43"/>
+      <c r="G78" s="43"/>
+      <c r="H78" s="43"/>
+      <c r="I78" s="43"/>
+      <c r="J78" s="43"/>
+      <c r="K78" s="43"/>
+    </row>
+    <row r="79" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A79" s="44"/>
+      <c r="B79" s="44"/>
+      <c r="C79" s="44"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="44" t="s">
+        <v>773</v>
+      </c>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="44"/>
+      <c r="J79" s="44"/>
+      <c r="K79" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD74C246-3AC3-4A22-9608-60E90EDD889A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4865A725-D552-4795-92A5-F1F51347BAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="9" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="CurrencySwitch" sheetId="7" r:id="rId7"/>
     <sheet name="LanguageSwitch" sheetId="8" r:id="rId8"/>
     <sheet name="Search" sheetId="9" r:id="rId9"/>
+    <sheet name="CategoryListing" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="907">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -2688,6 +2689,402 @@
   </si>
   <si>
     <t>A success banner appears indicating the item was added to the cart, and the mini-cart total updates.</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Refine Search' area or left-hand menu.</t>
+  </si>
+  <si>
+    <t>2. Click a subcategory link.</t>
+  </si>
+  <si>
+    <t>1. Change the 'Show' limit.</t>
+  </si>
+  <si>
+    <t>2. Observe the pagination summary text (e.g., at the bottom of the page).</t>
+  </si>
+  <si>
+    <t>1. Scroll to pagination controls.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Next &gt;' button or the '&gt;' icon.</t>
+  </si>
+  <si>
+    <t>2. Click directly on page number '3'.</t>
+  </si>
+  <si>
+    <t>1. Set Sort By to 'Price (High &gt; Low)'.</t>
+  </si>
+  <si>
+    <t>2. Click to page '2' of the results.</t>
+  </si>
+  <si>
+    <t>1. Locate a product card.</t>
+  </si>
+  <si>
+    <t>2. Click the primary 'Add to Cart' button/icon.</t>
+  </si>
+  <si>
+    <t>1. Click the 'Exchange/Compare' icon on two different product cards.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Product Compare' link in the success banner.</t>
+  </si>
+  <si>
+    <t>Items are successfully added to the comparison tool, and the user can view them side-by-side on the Compare page.</t>
+  </si>
+  <si>
+    <t>TC_CAT_001</t>
+  </si>
+  <si>
+    <t>Verify Category Page elements load correctly</t>
+  </si>
+  <si>
+    <t>1. Click a category from the top menu that contains products (e.g., 'Desktops' &gt; 'Mac').</t>
+  </si>
+  <si>
+    <t>Page title, breadcrumbs, product grid/list, sorting dropdowns, and 'Refine Search' (if applicable) are visible.</t>
+  </si>
+  <si>
+    <t>TC_CAT_002</t>
+  </si>
+  <si>
+    <t>Verify empty category message</t>
+  </si>
+  <si>
+    <t>1. Click a category known to have zero products.</t>
+  </si>
+  <si>
+    <t>A message "There are no products to list in this category" and a 'Continue' button are displayed.</t>
+  </si>
+  <si>
+    <t>TC_CAT_003</t>
+  </si>
+  <si>
+    <t>Verify 'Refine Search' subcategory links</t>
+  </si>
+  <si>
+    <t>User is on a Category Page with subcategories</t>
+  </si>
+  <si>
+    <t>User is routed to the selected subcategory listing page, and the product list updates accordingly.</t>
+  </si>
+  <si>
+    <t>TC_CAT_004</t>
+  </si>
+  <si>
+    <t>Verify default view mode</t>
+  </si>
+  <si>
+    <t>User navigates to a populated Category Page</t>
+  </si>
+  <si>
+    <t>1. Observe the layout of the products.</t>
+  </si>
+  <si>
+    <t>Products are displayed in the system's default view format (usually List View or Grid View).</t>
+  </si>
+  <si>
+    <t>TC_CAT_005</t>
+  </si>
+  <si>
+    <t>Verify toggle to 'List' View</t>
+  </si>
+  <si>
+    <t>User is on a Category Page in Grid View</t>
+  </si>
+  <si>
+    <t>1. Click the 'List' icon near the sorting controls.</t>
+  </si>
+  <si>
+    <t>The products immediately reformat into a vertical list format, stacking one below the other with descriptions visible.</t>
+  </si>
+  <si>
+    <t>TC_CAT_006</t>
+  </si>
+  <si>
+    <t>Verify toggle to 'Grid' View</t>
+  </si>
+  <si>
+    <t>User is on a Category Page in List View</t>
+  </si>
+  <si>
+    <t>1. Click the 'Grid' icon near the sorting controls.</t>
+  </si>
+  <si>
+    <t>The products immediately reformat into a horizontal grid format (e.g., 3 or 4 products per row).</t>
+  </si>
+  <si>
+    <t>TC_CAT_007</t>
+  </si>
+  <si>
+    <t>Verify View preference persists during session</t>
+  </si>
+  <si>
+    <t>User has toggled the view to 'Grid'</t>
+  </si>
+  <si>
+    <t>1. Navigate to a different category page.</t>
+  </si>
+  <si>
+    <t>The newly loaded category page remembers the user's preference and renders in 'Grid' view.</t>
+  </si>
+  <si>
+    <t>TC_CAT_008</t>
+  </si>
+  <si>
+    <t>Verify default Sorting order</t>
+  </si>
+  <si>
+    <t>User is on a populated Category Page</t>
+  </si>
+  <si>
+    <t>1. Observe the 'Sort By' dropdown and the list of products.</t>
+  </si>
+  <si>
+    <t>The dropdown shows 'Default', and products are listed according to the admin-defined default sort order.</t>
+  </si>
+  <si>
+    <t>TC_CAT_009</t>
+  </si>
+  <si>
+    <t>Verify Sorting: Name (A - Z)</t>
+  </si>
+  <si>
+    <t>1. Select 'Name (A - Z)' from the 'Sort By' dropdown.</t>
+  </si>
+  <si>
+    <t>Page reloads. Products are strictly ordered alphabetically from A to Z based on their title.</t>
+  </si>
+  <si>
+    <t>TC_CAT_010</t>
+  </si>
+  <si>
+    <t>Verify Sorting: Name (Z - A)</t>
+  </si>
+  <si>
+    <t>1. Select 'Name (Z - A)' from the 'Sort By' dropdown.</t>
+  </si>
+  <si>
+    <t>Page reloads. Products are strictly ordered reverse-alphabetically from Z to A.</t>
+  </si>
+  <si>
+    <t>TC_CAT_011</t>
+  </si>
+  <si>
+    <t>Verify Sorting: Price (Low &gt; High)</t>
+  </si>
+  <si>
+    <t>1. Select 'Price (Low &gt; High)' from the 'Sort By' dropdown.</t>
+  </si>
+  <si>
+    <t>Page reloads. Products are ordered from cheapest to most expensive.</t>
+  </si>
+  <si>
+    <t>TC_CAT_012</t>
+  </si>
+  <si>
+    <t>Verify Sorting: Price (High &gt; Low)</t>
+  </si>
+  <si>
+    <t>1. Select 'Price (High &gt; Low)' from the 'Sort By' dropdown.</t>
+  </si>
+  <si>
+    <t>Page reloads. Products are ordered from most expensive to cheapest.</t>
+  </si>
+  <si>
+    <t>TC_CAT_013</t>
+  </si>
+  <si>
+    <t>Verify Sorting: Rating (Highest)</t>
+  </si>
+  <si>
+    <t>User is on a Category Page with reviewed products</t>
+  </si>
+  <si>
+    <t>1. Select 'Rating (Highest)' from the 'Sort By' dropdown.</t>
+  </si>
+  <si>
+    <t>Page reloads. Products are ordered by customer rating, starting with 5-star items.</t>
+  </si>
+  <si>
+    <t>TC_CAT_014</t>
+  </si>
+  <si>
+    <t>Verify Sorting: Rating (Lowest)</t>
+  </si>
+  <si>
+    <t>1. Select 'Rating (Lowest)' from the 'Sort By' dropdown.</t>
+  </si>
+  <si>
+    <t>Page reloads. Products are ordered by customer rating, starting with unrated or lowest-rated items.</t>
+  </si>
+  <si>
+    <t>TC_CAT_015</t>
+  </si>
+  <si>
+    <t>Verify Sorting: Model (A - Z)</t>
+  </si>
+  <si>
+    <t>1. Select 'Model (A - Z)' from the 'Sort By' dropdown.</t>
+  </si>
+  <si>
+    <t>Page reloads. Products are sorted alphanumerically based on their hidden/displayed Model Number.</t>
+  </si>
+  <si>
+    <t>TC_CAT_016</t>
+  </si>
+  <si>
+    <t>Verify Sorting: Model (Z - A)</t>
+  </si>
+  <si>
+    <t>1. Select 'Model (Z - A)' from the 'Sort By' dropdown.</t>
+  </si>
+  <si>
+    <t>Page reloads. Products are sorted in reverse-alphanumeric order based on Model Number.</t>
+  </si>
+  <si>
+    <t>TC_CAT_017</t>
+  </si>
+  <si>
+    <t>Verify default 'Show' limit functionality</t>
+  </si>
+  <si>
+    <t>User is on a Category Page with &gt; 20 products</t>
+  </si>
+  <si>
+    <t>1. Observe the 'Show' dropdown and count the number of products displayed.</t>
+  </si>
+  <si>
+    <t>The dropdown shows the default limit (e.g., '15'), and exactly that maximum number of products is displayed.</t>
+  </si>
+  <si>
+    <t>TC_CAT_018</t>
+  </si>
+  <si>
+    <t>Verify changing 'Show' limit updates product count</t>
+  </si>
+  <si>
+    <t>User is on a Category Page with &gt; 25 products</t>
+  </si>
+  <si>
+    <t>1. Select '25' from the 'Show' dropdown.</t>
+  </si>
+  <si>
+    <t>Page reloads. Up to 25 products are now displayed on the single page.</t>
+  </si>
+  <si>
+    <t>TC_CAT_019</t>
+  </si>
+  <si>
+    <t>Verify 'Showing X to Y of Z' text updates accurately</t>
+  </si>
+  <si>
+    <t>User changes the 'Show' limit</t>
+  </si>
+  <si>
+    <t>The text dynamically updates to reflect the accurate math (e.g., "Showing 1 to 25 of 40 (2 Pages)").</t>
+  </si>
+  <si>
+    <t>TC_CAT_020</t>
+  </si>
+  <si>
+    <t>Verify Pagination: 'Next' button functionality</t>
+  </si>
+  <si>
+    <t>User is on Page 1 of a category with multiple pages</t>
+  </si>
+  <si>
+    <t>User is routed to Page 2 of the category listing.</t>
+  </si>
+  <si>
+    <t>TC_CAT_021</t>
+  </si>
+  <si>
+    <t>Verify Pagination: Specific page number routing</t>
+  </si>
+  <si>
+    <t>User is on a category with 3+ pages</t>
+  </si>
+  <si>
+    <t>User is routed directly to the third page of the product list.</t>
+  </si>
+  <si>
+    <t>TC_CAT_022</t>
+  </si>
+  <si>
+    <t>Verify Pagination preserves sorting parameters</t>
+  </si>
+  <si>
+    <t>User has applied a custom sort filter</t>
+  </si>
+  <si>
+    <t>Page 2 loads, and the products remain sorted from highest to lowest price.</t>
+  </si>
+  <si>
+    <t>TC_CAT_023</t>
+  </si>
+  <si>
+    <t>Verify clicking Product Image navigates to PDP</t>
+  </si>
+  <si>
+    <t>1. Click on the thumbnail image of a product card.</t>
+  </si>
+  <si>
+    <t>User is navigated to the detailed Product Display Page (PDP) for that specific item.</t>
+  </si>
+  <si>
+    <t>TC_CAT_024</t>
+  </si>
+  <si>
+    <t>Verify clicking Product Title navigates to PDP</t>
+  </si>
+  <si>
+    <t>1. Click on the blue hyperlink title of a product card.</t>
+  </si>
+  <si>
+    <t>TC_CAT_025</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Cart' button from Category List</t>
+  </si>
+  <si>
+    <t>A success banner appears, and the item is added to the mini-cart without forcing navigation away from the category page.</t>
+  </si>
+  <si>
+    <t>TC_CAT_026</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Cart' for products requiring options (e.g., sizes)</t>
+  </si>
+  <si>
+    <t>User is on a Category Page</t>
+  </si>
+  <si>
+    <t>1. Click 'Add to Cart' on a product that requires mandatory options (e.g., an Apple Cinema monitor requiring a size selection).</t>
+  </si>
+  <si>
+    <t>System does not add the item to cart; instead, it redirects the user to the PDP or opens a modal prompting for the required options.</t>
+  </si>
+  <si>
+    <t>TC_CAT_027</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Wish List' button from Category List</t>
+  </si>
+  <si>
+    <t>User is logged in and on a Category Page</t>
+  </si>
+  <si>
+    <t>1. Click the 'Heart' icon on a product card.</t>
+  </si>
+  <si>
+    <t>A success banner appears confirming the product has been added to the user's Wish List.</t>
+  </si>
+  <si>
+    <t>TC_CAT_028</t>
+  </si>
+  <si>
+    <t>Verify 'Compare this Product' button from Category List</t>
   </si>
 </sst>
 </file>
@@ -3361,7 +3758,444 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="149">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -6819,65 +7653,85 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="118">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="133">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="117"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="116"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="132"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="131"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="27" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="42" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="41">
   <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+  <autoFilter ref="A7:K49" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="115" dataDxfId="113" headerRowBorderDxfId="114" tableBorderDxfId="112" totalsRowBorderDxfId="111">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="130" dataDxfId="128" headerRowBorderDxfId="129" tableBorderDxfId="127" totalsRowBorderDxfId="126">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="110"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="109"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="108"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="107"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="106"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="125"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="124"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="123"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="122"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="121"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6887,7 +7741,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="120"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6895,120 +7749,120 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="110"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="105"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56">
   <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="148" dataDxfId="146" headerRowBorderDxfId="147" tableBorderDxfId="145">
   <autoFilter ref="A6:K40" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="129"/>
-    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="128"/>
-    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="127"/>
-    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="126"/>
-    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="124"/>
-    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="123"/>
-    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="121"/>
-    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="119"/>
+    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="144"/>
+    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="143"/>
+    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="142"/>
+    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="141"/>
+    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="140"/>
+    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="139"/>
+    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="138"/>
+    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="137"/>
+    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="136"/>
+    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="135"/>
+    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="134"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8054,6 +8908,975 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{326C1D1C-019A-491E-A87F-586318B068DF}">
+  <dimension ref="A1:K49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" customWidth="1"/>
+    <col min="10" max="10" width="25.28515625" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="129" thickBot="1">
+      <c r="A8" s="49" t="s">
+        <v>789</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>790</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49" t="s">
+        <v>792</v>
+      </c>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+    </row>
+    <row r="9" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A9" s="43" t="s">
+        <v>793</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>794</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>795</v>
+      </c>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43" t="s">
+        <v>796</v>
+      </c>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="99.75">
+      <c r="A10" s="51" t="s">
+        <v>797</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>798</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>799</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>775</v>
+      </c>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51" t="s">
+        <v>800</v>
+      </c>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+    </row>
+    <row r="12" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44" t="s">
+        <v>776</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+    </row>
+    <row r="13" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A13" s="43" t="s">
+        <v>801</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>802</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>803</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>804</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43" t="s">
+        <v>805</v>
+      </c>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A14" s="49" t="s">
+        <v>806</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>807</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>808</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>809</v>
+      </c>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49" t="s">
+        <v>810</v>
+      </c>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+    </row>
+    <row r="15" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A15" s="43" t="s">
+        <v>811</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>812</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>813</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>814</v>
+      </c>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43" t="s">
+        <v>815</v>
+      </c>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A16" s="49" t="s">
+        <v>816</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>817</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>818</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>819</v>
+      </c>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49" t="s">
+        <v>820</v>
+      </c>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="49"/>
+    </row>
+    <row r="17" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A17" s="43" t="s">
+        <v>821</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>822</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>823</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>824</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43" t="s">
+        <v>825</v>
+      </c>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A18" s="49" t="s">
+        <v>826</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>827</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>823</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>828</v>
+      </c>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49" t="s">
+        <v>829</v>
+      </c>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+    </row>
+    <row r="19" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A19" s="43" t="s">
+        <v>830</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>831</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>823</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>832</v>
+      </c>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43" t="s">
+        <v>833</v>
+      </c>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="72" thickBot="1">
+      <c r="A20" s="49" t="s">
+        <v>834</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>835</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>823</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>836</v>
+      </c>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49" t="s">
+        <v>837</v>
+      </c>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+    </row>
+    <row r="21" spans="1:11" ht="72" thickBot="1">
+      <c r="A21" s="43" t="s">
+        <v>838</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>839</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>823</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>840</v>
+      </c>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43" t="s">
+        <v>841</v>
+      </c>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A22" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>843</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>844</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>845</v>
+      </c>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49" t="s">
+        <v>846</v>
+      </c>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="49"/>
+    </row>
+    <row r="23" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A23" s="43" t="s">
+        <v>847</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>848</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>844</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>849</v>
+      </c>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43" t="s">
+        <v>850</v>
+      </c>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A24" s="49" t="s">
+        <v>851</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>852</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>823</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>853</v>
+      </c>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49" t="s">
+        <v>854</v>
+      </c>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+    </row>
+    <row r="25" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A25" s="43" t="s">
+        <v>855</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>856</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>823</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>857</v>
+      </c>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43" t="s">
+        <v>858</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A26" s="49" t="s">
+        <v>859</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>860</v>
+      </c>
+      <c r="D26" s="49" t="s">
+        <v>861</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>862</v>
+      </c>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49" t="s">
+        <v>863</v>
+      </c>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+    </row>
+    <row r="27" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A27" s="43" t="s">
+        <v>864</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>865</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>866</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>867</v>
+      </c>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43" t="s">
+        <v>868</v>
+      </c>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="99.75">
+      <c r="A28" s="51" t="s">
+        <v>869</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>870</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>871</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>777</v>
+      </c>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51" t="s">
+        <v>872</v>
+      </c>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44" t="s">
+        <v>778</v>
+      </c>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+    </row>
+    <row r="31" spans="1:11" ht="57">
+      <c r="A31" s="43" t="s">
+        <v>873</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>874</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>875</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>779</v>
+      </c>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43" t="s">
+        <v>876</v>
+      </c>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A33" s="43"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43" t="s">
+        <v>780</v>
+      </c>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11" ht="57">
+      <c r="A34" s="51" t="s">
+        <v>877</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>878</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>879</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>779</v>
+      </c>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51" t="s">
+        <v>880</v>
+      </c>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="51"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A36" s="44"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44" t="s">
+        <v>781</v>
+      </c>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44"/>
+    </row>
+    <row r="37" spans="1:11" ht="71.25">
+      <c r="A37" s="43" t="s">
+        <v>881</v>
+      </c>
+      <c r="B37" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>882</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>883</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>782</v>
+      </c>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43" t="s">
+        <v>884</v>
+      </c>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43" t="s">
+        <v>783</v>
+      </c>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" spans="1:11" ht="72" thickBot="1">
+      <c r="A40" s="49" t="s">
+        <v>885</v>
+      </c>
+      <c r="B40" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="49" t="s">
+        <v>886</v>
+      </c>
+      <c r="D40" s="49" t="s">
+        <v>823</v>
+      </c>
+      <c r="E40" s="49" t="s">
+        <v>887</v>
+      </c>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49" t="s">
+        <v>888</v>
+      </c>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
+      <c r="K40" s="49"/>
+    </row>
+    <row r="41" spans="1:11" ht="72" thickBot="1">
+      <c r="A41" s="43" t="s">
+        <v>889</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>890</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>823</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>891</v>
+      </c>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43" t="s">
+        <v>888</v>
+      </c>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11" ht="112.5" customHeight="1">
+      <c r="A42" s="51" t="s">
+        <v>892</v>
+      </c>
+      <c r="B42" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>893</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>823</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>784</v>
+      </c>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51" t="s">
+        <v>894</v>
+      </c>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="51"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="43"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+    </row>
+    <row r="44" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A44" s="44"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44" t="s">
+        <v>785</v>
+      </c>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
+    </row>
+    <row r="45" spans="1:11" ht="171.75" thickBot="1">
+      <c r="A45" s="43" t="s">
+        <v>895</v>
+      </c>
+      <c r="B45" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="43" t="s">
+        <v>896</v>
+      </c>
+      <c r="D45" s="43" t="s">
+        <v>897</v>
+      </c>
+      <c r="E45" s="43" t="s">
+        <v>898</v>
+      </c>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43" t="s">
+        <v>899</v>
+      </c>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:11" ht="72" thickBot="1">
+      <c r="A46" s="49" t="s">
+        <v>900</v>
+      </c>
+      <c r="B46" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" s="49" t="s">
+        <v>901</v>
+      </c>
+      <c r="D46" s="49" t="s">
+        <v>902</v>
+      </c>
+      <c r="E46" s="49" t="s">
+        <v>903</v>
+      </c>
+      <c r="F46" s="49"/>
+      <c r="G46" s="49" t="s">
+        <v>904</v>
+      </c>
+      <c r="H46" s="49"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="49"/>
+      <c r="K46" s="49"/>
+    </row>
+    <row r="47" spans="1:11" ht="99.75">
+      <c r="A47" s="51" t="s">
+        <v>905</v>
+      </c>
+      <c r="B47" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="51" t="s">
+        <v>906</v>
+      </c>
+      <c r="D47" s="51" t="s">
+        <v>897</v>
+      </c>
+      <c r="E47" s="51" t="s">
+        <v>786</v>
+      </c>
+      <c r="F47" s="51"/>
+      <c r="G47" s="51" t="s">
+        <v>788</v>
+      </c>
+      <c r="H47" s="51"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="51"/>
+      <c r="K47" s="51"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="43"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A49" s="44"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44" t="s">
+        <v>787</v>
+      </c>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBF1778A-A95C-4341-A78F-0724A072BB4A}">
   <dimension ref="A1:K118"/>

--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4865A725-D552-4795-92A5-F1F51347BAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BF25FB-2B63-4682-9FF4-511A684EE980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="9" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="6" activeTab="13" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,11 @@
     <sheet name="LanguageSwitch" sheetId="8" r:id="rId8"/>
     <sheet name="Search" sheetId="9" r:id="rId9"/>
     <sheet name="CategoryListing" sheetId="10" r:id="rId10"/>
+    <sheet name="ProductCompare" sheetId="11" r:id="rId11"/>
+    <sheet name="ProductDisPage" sheetId="12" r:id="rId12"/>
+    <sheet name="Review" sheetId="13" r:id="rId13"/>
+    <sheet name="AddToCart" sheetId="14" r:id="rId14"/>
+    <sheet name="Sheet8" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="1323">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -3085,6 +3090,1274 @@
   </si>
   <si>
     <t>Verify 'Compare this Product' button from Category List</t>
+  </si>
+  <si>
+    <t>TC_COMP_001</t>
+  </si>
+  <si>
+    <t>Verify adding a product to Compare from Category Page</t>
+  </si>
+  <si>
+    <t>User is on a Category Listing Page</t>
+  </si>
+  <si>
+    <t>1. Hover over or locate a product card.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Compare this Product' icon.</t>
+  </si>
+  <si>
+    <t>A success banner appears confirming the product was added to the product comparison list.</t>
+  </si>
+  <si>
+    <t>TC_COMP_002</t>
+  </si>
+  <si>
+    <t>Verify adding a product to Compare from Product Display Page (PDP)</t>
+  </si>
+  <si>
+    <t>User is on a Product Display Page</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Compare this Product' icon/link near the Add to Cart button.</t>
+  </si>
+  <si>
+    <t>2. Click it.</t>
+  </si>
+  <si>
+    <t>TC_COMP_003</t>
+  </si>
+  <si>
+    <t>Verify adding a product to Compare from Search Results</t>
+  </si>
+  <si>
+    <t>User has performed a search yielding products</t>
+  </si>
+  <si>
+    <t>A success banner appears confirming the product was added.</t>
+  </si>
+  <si>
+    <t>TC_COMP_004</t>
+  </si>
+  <si>
+    <t>Verify adding a product to Compare from Home Page Featured Module</t>
+  </si>
+  <si>
+    <t>1. Locate a product in the 'Featured' section.</t>
+  </si>
+  <si>
+    <t>TC_COMP_005</t>
+  </si>
+  <si>
+    <t>Verify dynamic update of 'Product Compare' counter link</t>
+  </si>
+  <si>
+    <t>User adds a product to the compare list</t>
+  </si>
+  <si>
+    <t>1. Observe the 'Product Compare (X)' hyperlink (usually found near the category header or sorting tools).</t>
+  </si>
+  <si>
+    <t>The counter 'X' dynamically increments by 1 without requiring a full page reload.</t>
+  </si>
+  <si>
+    <t>TC_COMP_006</t>
+  </si>
+  <si>
+    <t>Verify navigation via the success banner link</t>
+  </si>
+  <si>
+    <t>User has just clicked 'Compare this Product'</t>
+  </si>
+  <si>
+    <t>1. Click the 'Product Compare' link inside the green success alert banner.</t>
+  </si>
+  <si>
+    <t>User is routed directly to the Product Comparison page.</t>
+  </si>
+  <si>
+    <t>TC_COMP_007</t>
+  </si>
+  <si>
+    <t>Verify navigation via the static Category Page link</t>
+  </si>
+  <si>
+    <t>User is on a Category Page with items in the compare list</t>
+  </si>
+  <si>
+    <t>1. Click the 'Product Compare (X)' text link near the sorting dropdowns.</t>
+  </si>
+  <si>
+    <t>User is routed to the Product Comparison page.</t>
+  </si>
+  <si>
+    <t>TC_COMP_008</t>
+  </si>
+  <si>
+    <t>Verify adding the exact same product twice</t>
+  </si>
+  <si>
+    <t>User has Product A in the compare list</t>
+  </si>
+  <si>
+    <t>1. Navigate back to Product A.</t>
+  </si>
+  <si>
+    <t>2. Click 'Compare this Product' again.</t>
+  </si>
+  <si>
+    <t>A success banner appears, but the product is not duplicated on the Compare page. The counter does not increment.</t>
+  </si>
+  <si>
+    <t>TC_COMP_009</t>
+  </si>
+  <si>
+    <t>Verify adding maximum allowed products (e.g., 4)</t>
+  </si>
+  <si>
+    <t>User is browsing products</t>
+  </si>
+  <si>
+    <t>1. Add 4 different products to the comparison list.</t>
+  </si>
+  <si>
+    <t>2. Navigate to the Compare page.</t>
+  </si>
+  <si>
+    <t>All 4 products are displayed side-by-side in the comparison table.</t>
+  </si>
+  <si>
+    <t>TC_COMP_010</t>
+  </si>
+  <si>
+    <t>Verify system behavior when exceeding maximum compare limit</t>
+  </si>
+  <si>
+    <t>User has 4 items in the compare list</t>
+  </si>
+  <si>
+    <t>1. Attempt to add a 5th product to the comparison list.</t>
+  </si>
+  <si>
+    <t>System behavior depends on configuration: either the oldest item is replaced, or an error banner alerts the user the limit is reached.</t>
+  </si>
+  <si>
+    <t>TC_COMP_011</t>
+  </si>
+  <si>
+    <t>Verify Compare Page UI Table Layout</t>
+  </si>
+  <si>
+    <t>User is on the Compare page with 2+ items</t>
+  </si>
+  <si>
+    <t>1. Observe the layout of the page.</t>
+  </si>
+  <si>
+    <t>Information is organized in a clear matrix. Rows represent attributes (Price, Model, etc.) and columns represent the products.</t>
+  </si>
+  <si>
+    <t>TC_COMP_012</t>
+  </si>
+  <si>
+    <t>Verify Basic Details match PDP exactly</t>
+  </si>
+  <si>
+    <t>User is on the Compare page</t>
+  </si>
+  <si>
+    <t>1. Check Product Image, Title, Price, Model, and Brand columns for accuracy against the PDP.</t>
+  </si>
+  <si>
+    <t>All basic details accurately reflect the current data on the corresponding Product Display Pages.</t>
+  </si>
+  <si>
+    <t>TC_COMP_013</t>
+  </si>
+  <si>
+    <t>Verify Discount/Special Prices are displayed</t>
+  </si>
+  <si>
+    <t>User compares a product on sale</t>
+  </si>
+  <si>
+    <t>1. Add a product with a discounted 'Special' price to compare.</t>
+  </si>
+  <si>
+    <t>2. View the Compare page.</t>
+  </si>
+  <si>
+    <t>The price row displays both the original price (usually struck through) and the new discounted price.</t>
+  </si>
+  <si>
+    <t>TC_COMP_014</t>
+  </si>
+  <si>
+    <t>Verify Specification Attributes are aligned</t>
+  </si>
+  <si>
+    <t>User compares two products from the same category</t>
+  </si>
+  <si>
+    <t>1. Observe the specification rows (e.g., Processor, RAM, Dimensions, Weight).</t>
+  </si>
+  <si>
+    <t>Attributes are correctly aligned horizontally so users can easily compare the specs of both items.</t>
+  </si>
+  <si>
+    <t>TC_COMP_015</t>
+  </si>
+  <si>
+    <t>Verify 'Availability' status is accurate</t>
+  </si>
+  <si>
+    <t>User compares items with different stock statuses</t>
+  </si>
+  <si>
+    <t>1. Add an 'In Stock' item and an 'Out of Stock' item.</t>
+  </si>
+  <si>
+    <t>2. View the 'Availability' row on the Compare page.</t>
+  </si>
+  <si>
+    <t>The statuses accurately reflect the stock levels (e.g., "In Stock" vs "2-3 Days" or "Out of Stock").</t>
+  </si>
+  <si>
+    <t>TC_COMP_016</t>
+  </si>
+  <si>
+    <t>Verify 'Rating' and 'Summary' rows</t>
+  </si>
+  <si>
+    <t>User compares products with user reviews</t>
+  </si>
+  <si>
+    <t>1. Observe the Rating (stars) and Summary (review counts) rows.</t>
+  </si>
+  <si>
+    <t>Star ratings and the total number of reviews are displayed accurately for each compared product.</t>
+  </si>
+  <si>
+    <t>TC_COMP_017</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Cart' functionality from Compare Page</t>
+  </si>
+  <si>
+    <t>1. Click the 'Add to Cart' button for a simple product in the comparison table.</t>
+  </si>
+  <si>
+    <t>A success banner appears, the mini-cart total updates, and the user remains on the Compare page.</t>
+  </si>
+  <si>
+    <t>TC_COMP_018</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Cart' for products requiring options</t>
+  </si>
+  <si>
+    <t>1. Click 'Add to Cart' for a product that requires mandatory options (e.g., size or color).</t>
+  </si>
+  <si>
+    <t>The user is redirected to that specific item's PDP to select the required options before adding it to the cart.</t>
+  </si>
+  <si>
+    <t>TC_COMP_019</t>
+  </si>
+  <si>
+    <t>1. Click the image of a product in the comparison table.</t>
+  </si>
+  <si>
+    <t>User is routed to the detailed Product Display Page for that item.</t>
+  </si>
+  <si>
+    <t>TC_COMP_020</t>
+  </si>
+  <si>
+    <t>1. Click the hyperlinked name of a product in the comparison table.</t>
+  </si>
+  <si>
+    <t>TC_COMP_021</t>
+  </si>
+  <si>
+    <t>Verify removing a single product from the Compare list</t>
+  </si>
+  <si>
+    <t>1. Click the 'Remove' button/icon at the bottom of a specific product's column.</t>
+  </si>
+  <si>
+    <t>The page reloads, a success banner confirms removal, the product disappears from the table, and the counter decreases by 1.</t>
+  </si>
+  <si>
+    <t>TC_COMP_022</t>
+  </si>
+  <si>
+    <t>Verify removing all products triggers empty state</t>
+  </si>
+  <si>
+    <t>User has 1 item left in the Compare list</t>
+  </si>
+  <si>
+    <t>1. Click the 'Remove' button for the final product.</t>
+  </si>
+  <si>
+    <t>The page reloads displaying the empty state text: "You have not chosen any products to compare."</t>
+  </si>
+  <si>
+    <t>TC_COMP_023</t>
+  </si>
+  <si>
+    <t>Verify session persistence of the Compare list</t>
+  </si>
+  <si>
+    <t>User has items in the Compare list</t>
+  </si>
+  <si>
+    <t>1. Navigate away from the store to a different website.</t>
+  </si>
+  <si>
+    <t>2. Return to the store in the same browsing session.</t>
+  </si>
+  <si>
+    <t>3. Open the Compare page.</t>
+  </si>
+  <si>
+    <t>The items previously added to the comparison list are still present in the table.</t>
+  </si>
+  <si>
+    <t>TC_COMP_024</t>
+  </si>
+  <si>
+    <t>Verify Compare list persistence upon user Login</t>
+  </si>
+  <si>
+    <t>Guest user has items in the Compare list</t>
+  </si>
+  <si>
+    <t>1. Browse as a guest and add 2 items to compare.</t>
+  </si>
+  <si>
+    <t>2. Log into a registered account.</t>
+  </si>
+  <si>
+    <t>The items added during the guest session are successfully merged and retained in the logged-in session's compare list.</t>
+  </si>
+  <si>
+    <t>TC_PDP_001</t>
+  </si>
+  <si>
+    <t>Verify PDP loads correctly with basic UI elements</t>
+  </si>
+  <si>
+    <t>User navigates to a Product Display Page</t>
+  </si>
+  <si>
+    <t>1. Observe the loaded page.</t>
+  </si>
+  <si>
+    <t>Page title, Main Image, Product Name, Price, and 'Add to Cart' button are clearly visible.</t>
+  </si>
+  <si>
+    <t>TC_PDP_002</t>
+  </si>
+  <si>
+    <t>Verify Breadcrumb navigation on PDP</t>
+  </si>
+  <si>
+    <t>User is on a PDP</t>
+  </si>
+  <si>
+    <t>1. Observe the breadcrumb trail.</t>
+  </si>
+  <si>
+    <t>2. Click the parent category link in the breadcrumb.</t>
+  </si>
+  <si>
+    <t>Breadcrumbs accurately reflect the path (e.g., Home &gt; Desktops &gt; iMac), and clicking a link routes correctly.</t>
+  </si>
+  <si>
+    <t>TC_PDP_003</t>
+  </si>
+  <si>
+    <t>Verify Main Product Image loading</t>
+  </si>
+  <si>
+    <t>1. Observe the main product image.</t>
+  </si>
+  <si>
+    <t>High-quality image loads without distortion, broken link icons, or overlapping UI elements.</t>
+  </si>
+  <si>
+    <t>TC_PDP_004</t>
+  </si>
+  <si>
+    <t>Verify clicking Main Image opens Lightbox/Zoom</t>
+  </si>
+  <si>
+    <t>1. Click directly on the main product image.</t>
+  </si>
+  <si>
+    <t>A modal lightbox or zoom overlay opens, displaying the full-resolution version of the image.</t>
+  </si>
+  <si>
+    <t>TC_PDP_005</t>
+  </si>
+  <si>
+    <t>Verify clicking Additional Thumbnails updates Main Image</t>
+  </si>
+  <si>
+    <t>User is on a PDP with multiple images</t>
+  </si>
+  <si>
+    <t>1. Locate the smaller thumbnail images below the main image.</t>
+  </si>
+  <si>
+    <t>2. Click a thumbnail.</t>
+  </si>
+  <si>
+    <t>The Main Image dynamically updates to display the selected thumbnail without reloading the whole page.</t>
+  </si>
+  <si>
+    <t>TC_PDP_006</t>
+  </si>
+  <si>
+    <t>Verify Lightbox navigation for additional images</t>
+  </si>
+  <si>
+    <t>User has opened the Lightbox view</t>
+  </si>
+  <si>
+    <t>1. Click the 'Next' (right arrow) and 'Prev' (left arrow) buttons inside the lightbox.</t>
+  </si>
+  <si>
+    <t>The lightbox cycles smoothly through all available product images.</t>
+  </si>
+  <si>
+    <t>TC_PDP_007</t>
+  </si>
+  <si>
+    <t>Verify 'Brand' (Manufacturer) hyperlink</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Brand:' detail.</t>
+  </si>
+  <si>
+    <t>2. Click the brand name hyperlink (e.g., Apple).</t>
+  </si>
+  <si>
+    <t>User is routed to the Manufacturer listing page displaying all products by that brand.</t>
+  </si>
+  <si>
+    <t>TC_PDP_008</t>
+  </si>
+  <si>
+    <t>Verify 'Product Code' (Model) text is displayed</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Product Code:' detail below the title.</t>
+  </si>
+  <si>
+    <t>The alphanumeric model number is displayed accurately matching the backend data.</t>
+  </si>
+  <si>
+    <t>TC_PDP_009</t>
+  </si>
+  <si>
+    <t>Verify 'Reward Points' value is displayed</t>
+  </si>
+  <si>
+    <t>User is on a PDP for a product offering points</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Reward Points:' detail.</t>
+  </si>
+  <si>
+    <t>The correct amount of reward points earned for purchasing the item is displayed.</t>
+  </si>
+  <si>
+    <t>TC_PDP_010</t>
+  </si>
+  <si>
+    <t>Verify 'Availability' status for an In-Stock item</t>
+  </si>
+  <si>
+    <t>User is on a PDP for an item with inventory &gt; 0</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Availability:' detail.</t>
+  </si>
+  <si>
+    <t>Status clearly displays "In Stock" (or the specific configured stock status text).</t>
+  </si>
+  <si>
+    <t>TC_PDP_011</t>
+  </si>
+  <si>
+    <t>Verify 'Availability' status for an Out-of-Stock item</t>
+  </si>
+  <si>
+    <t>User is on a PDP for an item with 0 inventory</t>
+  </si>
+  <si>
+    <t>Status displays "Out of Stock" (or "Pre-Order" depending on configuration).</t>
+  </si>
+  <si>
+    <t>TC_PDP_012</t>
+  </si>
+  <si>
+    <t>Verify standard Price display and formatting</t>
+  </si>
+  <si>
+    <t>1. Observe the primary price.</t>
+  </si>
+  <si>
+    <t>Price is formatted correctly according to the active currency (e.g., $122.00).</t>
+  </si>
+  <si>
+    <t>TC_PDP_013</t>
+  </si>
+  <si>
+    <t>Verify Ex-Tax price is displayed accurately</t>
+  </si>
+  <si>
+    <t>1. Observe the secondary price text usually located directly below the main price.</t>
+  </si>
+  <si>
+    <t>"Ex Tax: [Amount]" is calculated and displayed accurately based on tax class rules.</t>
+  </si>
+  <si>
+    <t>TC_PDP_014</t>
+  </si>
+  <si>
+    <t>Verify Special/Discount price rendering</t>
+  </si>
+  <si>
+    <t>User is on a PDP for a discounted item</t>
+  </si>
+  <si>
+    <t>1. Observe the pricing section.</t>
+  </si>
+  <si>
+    <t>Original price is displayed with a strike-through, and the new discounted price is highlighted/bolded.</t>
+  </si>
+  <si>
+    <t>TC_PDP_015</t>
+  </si>
+  <si>
+    <t>Verify Bulk/Discount pricing table display</t>
+  </si>
+  <si>
+    <t>User is on a PDP for an item with volume discounts</t>
+  </si>
+  <si>
+    <t>1. Observe the area below the price.</t>
+  </si>
+  <si>
+    <t>A table or list shows discounts (e.g., "Buy 2 or more for $110.00 each").</t>
+  </si>
+  <si>
+    <t>TC_PDP_016</t>
+  </si>
+  <si>
+    <t>Verify Product Options: Radio Buttons</t>
+  </si>
+  <si>
+    <t>User is on a PDP with radio button options</t>
+  </si>
+  <si>
+    <t>1. Click different radio buttons (e.g., Size: Small, Medium).</t>
+  </si>
+  <si>
+    <t>Only one radio button can be selected at a time within the group.</t>
+  </si>
+  <si>
+    <t>TC_PDP_017</t>
+  </si>
+  <si>
+    <t>Verify Product Options: Checkboxes</t>
+  </si>
+  <si>
+    <t>User is on a PDP with checkbox options</t>
+  </si>
+  <si>
+    <t>1. Check multiple checkboxes (e.g., Add-ons: Cable, Warranty).</t>
+  </si>
+  <si>
+    <t>Multiple checkboxes can be selected or deselected simultaneously.</t>
+  </si>
+  <si>
+    <t>TC_PDP_018</t>
+  </si>
+  <si>
+    <t>Verify Product Options: Select Dropdown</t>
+  </si>
+  <si>
+    <t>User is on a PDP with a dropdown option</t>
+  </si>
+  <si>
+    <t>1. Click the dropdown menu and select a value (e.g., Color: Red).</t>
+  </si>
+  <si>
+    <t>The dropdown updates to reflect the user's selected value.</t>
+  </si>
+  <si>
+    <t>TC_PDP_019</t>
+  </si>
+  <si>
+    <t>Verify Product Options: Text Input</t>
+  </si>
+  <si>
+    <t>User is on a PDP with a text option</t>
+  </si>
+  <si>
+    <t>1. Type alphanumeric text into the input field (e.g., Custom Name).</t>
+  </si>
+  <si>
+    <t>Field accepts the text correctly up to any configured character limits.</t>
+  </si>
+  <si>
+    <t>TC_PDP_020</t>
+  </si>
+  <si>
+    <t>Verify Product Options: Text Area</t>
+  </si>
+  <si>
+    <t>User is on a PDP with a text area option</t>
+  </si>
+  <si>
+    <t>1. Type multi-line text into the text area (e.g., Custom Engraving message).</t>
+  </si>
+  <si>
+    <t>Field accepts multi-line text correctly.</t>
+  </si>
+  <si>
+    <t>TC_PDP_021</t>
+  </si>
+  <si>
+    <t>Verify Product Options: File Upload</t>
+  </si>
+  <si>
+    <t>User is on a PDP with a file upload option</t>
+  </si>
+  <si>
+    <t>1. Click the 'Upload File' button.</t>
+  </si>
+  <si>
+    <t>2. Select a valid image file from the OS dialog.</t>
+  </si>
+  <si>
+    <t>File uploads successfully, and a success message or file name is displayed.</t>
+  </si>
+  <si>
+    <t>TC_PDP_022</t>
+  </si>
+  <si>
+    <t>Verify Product Options: Date/Time Picker</t>
+  </si>
+  <si>
+    <t>User is on a PDP with a date/time option</t>
+  </si>
+  <si>
+    <t>1. Click the calendar/clock icon next to the input field.</t>
+  </si>
+  <si>
+    <t>The interactive widget opens allowing the user to select a valid date/time.</t>
+  </si>
+  <si>
+    <t>TC_PDP_023</t>
+  </si>
+  <si>
+    <t>Verify validation error for missing Mandatory Options</t>
+  </si>
+  <si>
+    <t>User is on a PDP with mandatory options (marked with *)</t>
+  </si>
+  <si>
+    <t>1. Leave mandatory options blank or unselected.</t>
+  </si>
+  <si>
+    <t>2. Click 'Add to Cart'.</t>
+  </si>
+  <si>
+    <t>Item is not added. A validation warning appears (e.g., red text "Option required!").</t>
+  </si>
+  <si>
+    <t>TC_PDP_024</t>
+  </si>
+  <si>
+    <t>Verify dynamic price update upon option selection</t>
+  </si>
+  <si>
+    <t>User is on a PDP where options modify the price</t>
+  </si>
+  <si>
+    <t>1. Select an option labeled with a price modifier (e.g., "+$10.00").</t>
+  </si>
+  <si>
+    <t>The main total price dynamically updates to reflect the base price plus the option cost.</t>
+  </si>
+  <si>
+    <t>TC_PDP_025</t>
+  </si>
+  <si>
+    <t>Verify Quantity field default value</t>
+  </si>
+  <si>
+    <t>User navigates to a new PDP</t>
+  </si>
+  <si>
+    <t>1. Observe the 'Qty' input box.</t>
+  </si>
+  <si>
+    <t>The default value in the input box is '1' (unless a higher minimum is forced).</t>
+  </si>
+  <si>
+    <t>TC_PDP_026</t>
+  </si>
+  <si>
+    <t>Verify manual update of Quantity field</t>
+  </si>
+  <si>
+    <t>1. Delete '1' and type '5' in the Qty box.</t>
+  </si>
+  <si>
+    <t>Success banner appears, and exactly 5 items are added to the cart.</t>
+  </si>
+  <si>
+    <t>TC_PDP_027</t>
+  </si>
+  <si>
+    <t>Verify system behavior with 0 or negative quantity</t>
+  </si>
+  <si>
+    <t>1. Enter '0' or '-1' in the Qty box.</t>
+  </si>
+  <si>
+    <t>Validation fails. System either defaults back to '1' or displays an error preventing the action.</t>
+  </si>
+  <si>
+    <t>TC_PDP_028</t>
+  </si>
+  <si>
+    <t>Verify Minimum Quantity enforcement</t>
+  </si>
+  <si>
+    <t>User is on a PDP where minimum order is 2</t>
+  </si>
+  <si>
+    <t>1. Enter '1' in the Qty box.</t>
+  </si>
+  <si>
+    <t>Warning message is displayed stating "This product has a minimum quantity of 2".</t>
+  </si>
+  <si>
+    <t>TC_PDP_029</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Cart' functionality</t>
+  </si>
+  <si>
+    <t>1. Ensure valid quantity and options are selected.</t>
+  </si>
+  <si>
+    <t>2. Click the primary 'Add to Cart' button.</t>
+  </si>
+  <si>
+    <t>The system processes the request without redirecting away from the PDP.</t>
+  </si>
+  <si>
+    <t>TC_PDP_030</t>
+  </si>
+  <si>
+    <t>Verify Add to Cart success banner</t>
+  </si>
+  <si>
+    <t>User clicks 'Add to Cart'</t>
+  </si>
+  <si>
+    <t>1. Observe the top of the page.</t>
+  </si>
+  <si>
+    <t>A green success alert banner drops down containing a link to the shopping cart.</t>
+  </si>
+  <si>
+    <t>TC_PDP_031</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Wish List' button</t>
+  </si>
+  <si>
+    <t>User is logged in and on a PDP</t>
+  </si>
+  <si>
+    <t>1. Click the Heart icon / 'Add to Wish List' button.</t>
+  </si>
+  <si>
+    <t>Success banner confirms the item was added to the user's Wish List.</t>
+  </si>
+  <si>
+    <t>TC_PDP_032</t>
+  </si>
+  <si>
+    <t>Verify 'Compare this Product' button</t>
+  </si>
+  <si>
+    <t>1. Click the Exchange icon / 'Compare this Product' button.</t>
+  </si>
+  <si>
+    <t>Success banner confirms the item was added to the comparison list.</t>
+  </si>
+  <si>
+    <t>TC_PDP_033</t>
+  </si>
+  <si>
+    <t>Verify 'Description' tab content</t>
+  </si>
+  <si>
+    <t>1. Click the 'Description' tab (usually active by default).</t>
+  </si>
+  <si>
+    <t>Rich text, HTML, and images configured in the backend description render correctly.</t>
+  </si>
+  <si>
+    <t>TC_PDP_034</t>
+  </si>
+  <si>
+    <t>Verify 'Specification' tab content</t>
+  </si>
+  <si>
+    <t>User is on a PDP for an item with attributes</t>
+  </si>
+  <si>
+    <t>1. Click the 'Specification' tab.</t>
+  </si>
+  <si>
+    <t>Data is displayed cleanly in an organized table format (e.g., Processor: Intel Core i5).</t>
+  </si>
+  <si>
+    <t>TC_PDP_035</t>
+  </si>
+  <si>
+    <t>Verify 'Reviews' tab content</t>
+  </si>
+  <si>
+    <t>User is on a PDP for an item with existing reviews</t>
+  </si>
+  <si>
+    <t>1. Click the 'Reviews' tab.</t>
+  </si>
+  <si>
+    <t>Existing customer reviews, star ratings, and the "Write a Review" form are displayed.</t>
+  </si>
+  <si>
+    <t>TC_PDP_036</t>
+  </si>
+  <si>
+    <t>Verify 'Related Products' module renders</t>
+  </si>
+  <si>
+    <t>User is on a PDP with related items configured</t>
+  </si>
+  <si>
+    <t>1. Scroll to the bottom of the PDP.</t>
+  </si>
+  <si>
+    <t>A carousel or grid of "Related Products" is clearly visible.</t>
+  </si>
+  <si>
+    <t>TC_PDP_037</t>
+  </si>
+  <si>
+    <t>Verify 'Related Products' navigation</t>
+  </si>
+  <si>
+    <t>User locates the Related Products module</t>
+  </si>
+  <si>
+    <t>1. Click the image or title of a related product.</t>
+  </si>
+  <si>
+    <t>User is successfully navigated to the selected product's PDP.</t>
+  </si>
+  <si>
+    <t>TC_REV_001</t>
+  </si>
+  <si>
+    <t>Verify visibility of the 'Write a review' form</t>
+  </si>
+  <si>
+    <t>1. Click on the 'Reviews' tab.</t>
+  </si>
+  <si>
+    <t>2. Scroll to the "Write a review" section.</t>
+  </si>
+  <si>
+    <t>The form containing 'Your Name', 'Your Review', 'Rating' (1 to 5 stars/radio buttons), and a 'Continue' button is clearly visible.</t>
+  </si>
+  <si>
+    <t>TC_REV_002</t>
+  </si>
+  <si>
+    <t>Verify successful review submission with valid data</t>
+  </si>
+  <si>
+    <t>User is on the Reviews tab of a PDP</t>
+  </si>
+  <si>
+    <t>1. Enter a valid name in 'Your Name'.</t>
+  </si>
+  <si>
+    <t>2. Enter a valid review (over 25 characters) in 'Your Review'.</t>
+  </si>
+  <si>
+    <t>3. Select a Rating (e.g., 4 or 5).</t>
+  </si>
+  <si>
+    <t>4. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Submission is successful. A success banner states: "Thank you for your review. It has been submitted to the webmaster for approval."</t>
+  </si>
+  <si>
+    <t>TC_REV_003</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Your Name' is left blank</t>
+  </si>
+  <si>
+    <t>1. Leave 'Your Name' blank.</t>
+  </si>
+  <si>
+    <t>2. Enter a valid Review and select a Rating.</t>
+  </si>
+  <si>
+    <t>3. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Submission fails. A validation error states that the Name must be between 3 and 25 characters.</t>
+  </si>
+  <si>
+    <t>TC_REV_004</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Your Name' is below minimum length</t>
+  </si>
+  <si>
+    <t>1. Enter only 1 or 2 characters in 'Your Name'.</t>
+  </si>
+  <si>
+    <t>TC_REV_005</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Your Name' exceeds maximum length</t>
+  </si>
+  <si>
+    <t>1. Enter a name exceeding 25 characters.</t>
+  </si>
+  <si>
+    <t>TC_REV_006</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Your Review' text is left blank</t>
+  </si>
+  <si>
+    <t>1. Enter a valid Name.</t>
+  </si>
+  <si>
+    <t>2. Leave 'Your Review' text area blank.</t>
+  </si>
+  <si>
+    <t>3. Select a Rating.</t>
+  </si>
+  <si>
+    <t>Submission fails. A validation error states that the Review Text must be between 25 and 1000 characters.</t>
+  </si>
+  <si>
+    <t>TC_REV_007</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Your Review' is below minimum length</t>
+  </si>
+  <si>
+    <t>2. Enter a short review (e.g., "Good").</t>
+  </si>
+  <si>
+    <t>TC_REV_008</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Your Review' exceeds maximum length</t>
+  </si>
+  <si>
+    <t>2. Paste a review exceeding 1000 characters.</t>
+  </si>
+  <si>
+    <t>TC_REV_009</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Rating' is not selected</t>
+  </si>
+  <si>
+    <t>2. Enter a valid Review (over 25 characters).</t>
+  </si>
+  <si>
+    <t>3. Do not select any Rating radio buttons.</t>
+  </si>
+  <si>
+    <t>Submission fails. A validation error states that a review rating is required.</t>
+  </si>
+  <si>
+    <t>TC_REV_010</t>
+  </si>
+  <si>
+    <t>Verify Captcha validation when left blank (if enabled)</t>
+  </si>
+  <si>
+    <t>User is on the Reviews tab with Captcha enabled</t>
+  </si>
+  <si>
+    <t>1. Fill all review fields correctly.</t>
+  </si>
+  <si>
+    <t>2. Leave the Captcha input field blank.</t>
+  </si>
+  <si>
+    <t>Submission fails. A validation error states that the verification code does not match the image.</t>
+  </si>
+  <si>
+    <t>TC_REV_011</t>
+  </si>
+  <si>
+    <t>Verify Captcha validation with incorrect input (if enabled)</t>
+  </si>
+  <si>
+    <t>2. Enter a deliberately incorrect string in the Captcha field.</t>
+  </si>
+  <si>
+    <t>TC_REV_012</t>
+  </si>
+  <si>
+    <t>Verify submitted review requires Admin moderation</t>
+  </si>
+  <si>
+    <t>User has just successfully submitted a review</t>
+  </si>
+  <si>
+    <t>1. Refresh the Product Display Page.</t>
+  </si>
+  <si>
+    <t>2. Check the 'Reviews' tab list.</t>
+  </si>
+  <si>
+    <t>The newly submitted review does not appear immediately. It requires admin approval via the backend before becoming visible.</t>
+  </si>
+  <si>
+    <t>TC_REV_013</t>
+  </si>
+  <si>
+    <t>Verify visibility of existing approved reviews</t>
+  </si>
+  <si>
+    <t>Admin has approved a review for the product</t>
+  </si>
+  <si>
+    <t>1. Navigate to the PDP of the reviewed product.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Reviews' tab.</t>
+  </si>
+  <si>
+    <t>The approved review is visible, displaying the Reviewer's Name, Date added, Rating (in stars), and the Review Text.</t>
+  </si>
+  <si>
+    <t>TC_REV_014</t>
+  </si>
+  <si>
+    <t>Verify aggregate Rating stars update on PDP</t>
+  </si>
+  <si>
+    <t>Multiple reviews exist for a product</t>
+  </si>
+  <si>
+    <t>1. Observe the aggregate star rating under the Product Title.</t>
+  </si>
+  <si>
+    <t>2. Check the individual ratings in the 'Reviews' tab.</t>
+  </si>
+  <si>
+    <t>The main aggregate rating accurately reflects the mathematical average of all approved review ratings.</t>
+  </si>
+  <si>
+    <t>TC_REV_015</t>
+  </si>
+  <si>
+    <t>Verify Security: XSS injection in Review Text</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;script&gt;alert('XSS')&lt;/script&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the 'Your Review' field (padding to 25+ chars).</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Complete form and submit.</t>
+  </si>
+  <si>
+    <t>3. Admin approves review.</t>
+  </si>
+  <si>
+    <t>Script is not executed when viewing the review on the frontend. The input is sanitized and rendered securely as plain text.</t>
+  </si>
+  <si>
+    <t>TC_ATC_001</t>
+  </si>
+  <si>
+    <t>Verify adding a simple product to the cart from PDP</t>
+  </si>
+  <si>
+    <t>User is on the Product Display Page of a simple product</t>
+  </si>
+  <si>
+    <t>1. Ensure quantity is set to 1.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Add to Cart' button.</t>
+  </si>
+  <si>
+    <t>A success banner appears, and the item is successfully added to the shopping cart.</t>
+  </si>
+  <si>
+    <t>TC_ATC_002</t>
+  </si>
+  <si>
+    <t>Verify adding a product with unselected mandatory options</t>
+  </si>
+  <si>
+    <t>User is on the PDP of a product with mandatory options (e.g., Size, Color)</t>
+  </si>
+  <si>
+    <t>1. Leave the mandatory options unselected.</t>
+  </si>
+  <si>
+    <t>The item is not added. Validation error messages appear next to the required fields indicating they must be selected.</t>
+  </si>
+  <si>
+    <t>TC_ATC_003</t>
+  </si>
+  <si>
+    <t>Verify adding a product with selected mandatory options</t>
+  </si>
+  <si>
+    <t>User is on the PDP of a product with mandatory options</t>
+  </si>
+  <si>
+    <t>1. Select valid values for all mandatory options.</t>
+  </si>
+  <si>
+    <t>A success banner appears, and the item with its selected options is successfully added to the cart.</t>
+  </si>
+  <si>
+    <t>TC_ATC_004</t>
+  </si>
+  <si>
+    <t>Verify adding a simple product directly from the Category Listing Page</t>
+  </si>
+  <si>
+    <t>1. Locate a simple product in the grid/list.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Add to Cart' button/icon on the product card.</t>
+  </si>
+  <si>
+    <t>A success banner appears, the mini-cart updates, and the user is not forced to leave the Category page.</t>
+  </si>
+  <si>
+    <t>TC_ATC_005</t>
+  </si>
+  <si>
+    <t>Verify adding a product with options from the Category Listing Page</t>
+  </si>
+  <si>
+    <t>1. Locate a product that requires mandatory options.</t>
+  </si>
+  <si>
+    <t>The user is redirected to the Product Display Page to fulfill the mandatory option requirements before adding to cart.</t>
+  </si>
+  <si>
+    <t>TC_ATC_006</t>
+  </si>
+  <si>
+    <t>Verify adding an 'Out of Stock' product to the cart</t>
+  </si>
+  <si>
+    <t>User is on the PDP of an out-of-stock item</t>
+  </si>
+  <si>
+    <t>1. Click the 'Add to Cart' button.</t>
+  </si>
+  <si>
+    <t>Depending on store configuration, the item is either added with a warning that it will be back-ordered, or the button is disabled/rejects the addition.</t>
+  </si>
+  <si>
+    <t>TC_ATC_007</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Cart' with a quantity below the minimum requirement</t>
+  </si>
+  <si>
+    <t>User is on the PDP of a product with a minimum order quantity of 2</t>
+  </si>
+  <si>
+    <t>1. Set the quantity to '1'.</t>
+  </si>
+  <si>
+    <t>The item is not added. A warning message appears stating "This product has a minimum quantity of 2".</t>
+  </si>
+  <si>
+    <t>TC_ATC_008</t>
+  </si>
+  <si>
+    <t>Verify the dynamic success banner UI</t>
+  </si>
+  <si>
+    <t>User adds any valid product to the cart</t>
+  </si>
+  <si>
+    <t>1. Click 'Add to Cart'.</t>
+  </si>
+  <si>
+    <t>2. Observe the top of the screen.</t>
+  </si>
+  <si>
+    <t>A green success banner drops down stating "Success: You have added [Product Name] to your shopping cart!", containing a hyperlink to the cart.</t>
+  </si>
+  <si>
+    <t>TC_ATC_009</t>
+  </si>
+  <si>
+    <t>Verify dynamic update of the Mini-Cart header total</t>
+  </si>
+  <si>
+    <t>1. Note the current item count and total price in the black Mini-Cart header button.</t>
+  </si>
+  <si>
+    <t>The Mini-Cart button dynamically updates instantly (without page reload) to reflect the new item count and new combined total price.</t>
   </si>
 </sst>
 </file>
@@ -3758,7 +5031,1651 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="149">
+  <dxfs count="209">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -7653,85 +10570,165 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="133">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="193">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="132"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="131"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="192"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="191"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="42" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="102" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="101">
   <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="86" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87">
   <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="71" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72">
   <autoFilter ref="A7:K49" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="60"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="56" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+  <autoFilter ref="A7:K55" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="45"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="41" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
+  <autoFilter ref="A7:K62" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+  <autoFilter ref="A7:K84" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+  <autoFilter ref="A7:K32" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="130" dataDxfId="128" headerRowBorderDxfId="129" tableBorderDxfId="127" totalsRowBorderDxfId="126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="190" dataDxfId="188" headerRowBorderDxfId="189" tableBorderDxfId="187" totalsRowBorderDxfId="186">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="125"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="124"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="123"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="122"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="121"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="185"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="184"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="183"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="182"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="181"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7741,7 +10738,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="180"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -7749,120 +10746,120 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="174"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="173"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="172"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="171"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="170"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="169"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="168"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="167"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="166"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="165"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="157"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="156"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="155"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="154"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="153"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="152"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="151"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="128"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="127"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="123"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="122"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="121"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
   <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="110"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="105"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="148" dataDxfId="146" headerRowBorderDxfId="147" tableBorderDxfId="145">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="208" dataDxfId="206" headerRowBorderDxfId="207" tableBorderDxfId="205">
   <autoFilter ref="A6:K40" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="144"/>
-    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="143"/>
-    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="142"/>
-    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="141"/>
-    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="140"/>
-    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="139"/>
-    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="138"/>
-    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="137"/>
-    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="136"/>
-    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="135"/>
-    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="134"/>
+    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="204"/>
+    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="203"/>
+    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="202"/>
+    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="201"/>
+    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="200"/>
+    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="199"/>
+    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="198"/>
+    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="197"/>
+    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="196"/>
+    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="195"/>
+    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="194"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9877,6 +12874,4128 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35FD261B-9BF2-4D78-AE58-3181DD23363E}">
+  <dimension ref="A1:K55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" customWidth="1"/>
+    <col min="7" max="7" width="28.140625" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="85.5">
+      <c r="A8" s="51" t="s">
+        <v>907</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>908</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>909</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>910</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>912</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44" t="s">
+        <v>911</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+    </row>
+    <row r="11" spans="1:11" ht="85.5">
+      <c r="A11" s="43" t="s">
+        <v>913</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>914</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>915</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>916</v>
+      </c>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43" t="s">
+        <v>912</v>
+      </c>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43" t="s">
+        <v>917</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" ht="57">
+      <c r="A14" s="51" t="s">
+        <v>918</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>919</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>920</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>772</v>
+      </c>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51" t="s">
+        <v>921</v>
+      </c>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44" t="s">
+        <v>911</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+    </row>
+    <row r="17" spans="1:11" ht="71.25">
+      <c r="A17" s="43" t="s">
+        <v>922</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>923</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>924</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43" t="s">
+        <v>921</v>
+      </c>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43" t="s">
+        <v>911</v>
+      </c>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="143.25" thickBot="1">
+      <c r="A20" s="49" t="s">
+        <v>925</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>926</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>927</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>928</v>
+      </c>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49" t="s">
+        <v>929</v>
+      </c>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+    </row>
+    <row r="21" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A21" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>931</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>932</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>933</v>
+      </c>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A22" s="49" t="s">
+        <v>935</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>936</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>937</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>938</v>
+      </c>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49" t="s">
+        <v>939</v>
+      </c>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="49"/>
+    </row>
+    <row r="23" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A23" s="43" t="s">
+        <v>940</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>941</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>942</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>943</v>
+      </c>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43" t="s">
+        <v>944</v>
+      </c>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="85.5">
+      <c r="A26" s="51" t="s">
+        <v>946</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>947</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>948</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>949</v>
+      </c>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51" t="s">
+        <v>951</v>
+      </c>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44" t="s">
+        <v>950</v>
+      </c>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
+    </row>
+    <row r="29" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A29" s="43" t="s">
+        <v>952</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>953</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>954</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>955</v>
+      </c>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43" t="s">
+        <v>956</v>
+      </c>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A30" s="49" t="s">
+        <v>957</v>
+      </c>
+      <c r="B30" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="49" t="s">
+        <v>958</v>
+      </c>
+      <c r="D30" s="49" t="s">
+        <v>959</v>
+      </c>
+      <c r="E30" s="49" t="s">
+        <v>960</v>
+      </c>
+      <c r="F30" s="49"/>
+      <c r="G30" s="49" t="s">
+        <v>961</v>
+      </c>
+      <c r="H30" s="49"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="49"/>
+    </row>
+    <row r="31" spans="1:11" ht="129" thickBot="1">
+      <c r="A31" s="43" t="s">
+        <v>962</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>963</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>964</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>965</v>
+      </c>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43" t="s">
+        <v>966</v>
+      </c>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="99.75">
+      <c r="A32" s="51" t="s">
+        <v>967</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>968</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>969</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>970</v>
+      </c>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51" t="s">
+        <v>972</v>
+      </c>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="43"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44" t="s">
+        <v>971</v>
+      </c>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
+    </row>
+    <row r="35" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A35" s="43" t="s">
+        <v>973</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>974</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>975</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>976</v>
+      </c>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43" t="s">
+        <v>977</v>
+      </c>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11" ht="85.5">
+      <c r="A36" s="51" t="s">
+        <v>978</v>
+      </c>
+      <c r="B36" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>979</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>980</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>981</v>
+      </c>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51" t="s">
+        <v>983</v>
+      </c>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="51"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="72" thickBot="1">
+      <c r="A38" s="44"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44" t="s">
+        <v>982</v>
+      </c>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44"/>
+    </row>
+    <row r="39" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A39" s="43" t="s">
+        <v>984</v>
+      </c>
+      <c r="B39" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>985</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>986</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>987</v>
+      </c>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43" t="s">
+        <v>988</v>
+      </c>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A40" s="49" t="s">
+        <v>989</v>
+      </c>
+      <c r="B40" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="49" t="s">
+        <v>990</v>
+      </c>
+      <c r="D40" s="49" t="s">
+        <v>964</v>
+      </c>
+      <c r="E40" s="49" t="s">
+        <v>991</v>
+      </c>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49" t="s">
+        <v>992</v>
+      </c>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
+      <c r="K40" s="49"/>
+    </row>
+    <row r="41" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A41" s="43" t="s">
+        <v>993</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>994</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>964</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>995</v>
+      </c>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43" t="s">
+        <v>996</v>
+      </c>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A42" s="49" t="s">
+        <v>997</v>
+      </c>
+      <c r="B42" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="49" t="s">
+        <v>886</v>
+      </c>
+      <c r="D42" s="49" t="s">
+        <v>964</v>
+      </c>
+      <c r="E42" s="49" t="s">
+        <v>998</v>
+      </c>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49" t="s">
+        <v>999</v>
+      </c>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+    </row>
+    <row r="43" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A43" s="43" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B43" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>890</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>964</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43" t="s">
+        <v>999</v>
+      </c>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+    </row>
+    <row r="44" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A44" s="49" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B44" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D44" s="49" t="s">
+        <v>959</v>
+      </c>
+      <c r="E44" s="49" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F44" s="49"/>
+      <c r="G44" s="49" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H44" s="49"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="49"/>
+    </row>
+    <row r="45" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A45" s="43" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B45" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="43" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D45" s="43" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E45" s="43" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:11" ht="71.25">
+      <c r="A46" s="51" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B46" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="51" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D46" s="51" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E46" s="51" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
+      <c r="J46" s="51"/>
+      <c r="K46" s="51"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" spans="1:11" ht="71.25">
+      <c r="A48" s="43"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="43"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+    </row>
+    <row r="50" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A50" s="44"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+    </row>
+    <row r="51" spans="1:11" ht="114">
+      <c r="A51" s="51" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B51" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="51" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D51" s="51" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E51" s="51" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F51" s="51"/>
+      <c r="G51" s="51" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H51" s="51"/>
+      <c r="I51" s="51"/>
+      <c r="J51" s="51"/>
+      <c r="K51" s="51"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="43"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+    </row>
+    <row r="53" spans="1:11" ht="42.75">
+      <c r="A53" s="43"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="43"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+    </row>
+    <row r="55" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A55" s="44"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B01C9E-A64D-4633-B3A0-388AD8D49BBC}">
+  <dimension ref="A1:K62"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="41.140625" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="72" thickBot="1">
+      <c r="A8" s="49" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+    </row>
+    <row r="9" spans="1:11" ht="98.25" customHeight="1">
+      <c r="A9" s="43" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="72" thickBot="1">
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+    </row>
+    <row r="12" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A12" s="49" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+    </row>
+    <row r="13" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A13" s="43" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" ht="99.75">
+      <c r="A14" s="51" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+    </row>
+    <row r="17" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A17" s="43" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="85.5">
+      <c r="A18" s="51" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E18" s="51" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+    </row>
+    <row r="21" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A21" s="43" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="72" thickBot="1">
+      <c r="A22" s="49" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="49"/>
+    </row>
+    <row r="23" spans="1:11" ht="72" thickBot="1">
+      <c r="A23" s="43" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11" ht="72" thickBot="1">
+      <c r="A24" s="49" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+    </row>
+    <row r="25" spans="1:11" ht="72" thickBot="1">
+      <c r="A25" s="43" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="129" thickBot="1">
+      <c r="A26" s="49" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D26" s="49" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+    </row>
+    <row r="27" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A27" s="43" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="72" thickBot="1">
+      <c r="A28" s="49" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B28" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D28" s="49" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E28" s="49" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="49"/>
+    </row>
+    <row r="29" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A29" s="43" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A30" s="49" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B30" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="49" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D30" s="49" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E30" s="49" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F30" s="49"/>
+      <c r="G30" s="49" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H30" s="49"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="49"/>
+    </row>
+    <row r="31" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A31" s="43" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A32" s="49" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B32" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="49" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D32" s="49" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F32" s="49"/>
+      <c r="G32" s="49" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+    </row>
+    <row r="33" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A33" s="43" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11" ht="71.25">
+      <c r="A34" s="51" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="51"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A36" s="44"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44"/>
+    </row>
+    <row r="37" spans="1:11" ht="72" thickBot="1">
+      <c r="A37" s="43" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B37" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="71.25">
+      <c r="A38" s="51" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B38" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="51"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A40" s="44"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="44"/>
+    </row>
+    <row r="41" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A41" s="43" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11" ht="72" thickBot="1">
+      <c r="A42" s="49" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B42" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="49" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D42" s="49" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E42" s="49" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+    </row>
+    <row r="43" spans="1:11" ht="57">
+      <c r="A43" s="43" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B43" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="43"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:11" ht="112.5" customHeight="1">
+      <c r="A46" s="51" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B46" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="51" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D46" s="51" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E46" s="51" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
+      <c r="J46" s="51"/>
+      <c r="K46" s="51"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+    </row>
+    <row r="49" spans="1:11" ht="112.5" customHeight="1">
+      <c r="A49" s="43" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B49" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D49" s="43" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+    </row>
+    <row r="51" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A51" s="43"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+    </row>
+    <row r="52" spans="1:11" ht="71.25">
+      <c r="A52" s="51" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B52" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="51" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D52" s="51" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E52" s="51" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F52" s="51"/>
+      <c r="G52" s="51" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
+      <c r="J52" s="51"/>
+      <c r="K52" s="51"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="43"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+    </row>
+    <row r="54" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A54" s="44"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="44"/>
+    </row>
+    <row r="55" spans="1:11" ht="72" thickBot="1">
+      <c r="A55" s="43" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B55" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="43" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E55" s="43" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43"/>
+    </row>
+    <row r="56" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A56" s="49" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B56" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="49" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D56" s="49" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E56" s="49" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H56" s="49"/>
+      <c r="I56" s="49"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
+    </row>
+    <row r="57" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A57" s="43" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B57" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E57" s="43" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H57" s="43"/>
+      <c r="I57" s="43"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="43"/>
+    </row>
+    <row r="58" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A58" s="49" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B58" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="49" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D58" s="49" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E58" s="49" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+      <c r="J58" s="49"/>
+      <c r="K58" s="49"/>
+    </row>
+    <row r="59" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A59" s="43" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B59" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="43" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D59" s="43" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E59" s="43" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="43"/>
+    </row>
+    <row r="60" spans="1:11" ht="72" thickBot="1">
+      <c r="A60" s="49" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B60" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="49" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D60" s="49" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E60" s="49" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F60" s="49"/>
+      <c r="G60" s="49" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H60" s="49"/>
+      <c r="I60" s="49"/>
+      <c r="J60" s="49"/>
+      <c r="K60" s="49"/>
+    </row>
+    <row r="61" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A61" s="43" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B61" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="43" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F61" s="43"/>
+      <c r="G61" s="43" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H61" s="43"/>
+      <c r="I61" s="43"/>
+      <c r="J61" s="43"/>
+      <c r="K61" s="43"/>
+    </row>
+    <row r="62" spans="1:11" ht="72" thickBot="1">
+      <c r="A62" s="49" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B62" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" s="49" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D62" s="49" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="49" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F62" s="49"/>
+      <c r="G62" s="49" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
+      <c r="J62" s="49"/>
+      <c r="K62" s="49"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4F66818-3145-4D6F-AC59-520A7CE99507}">
+  <dimension ref="A1:K84"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="5" max="5" width="36.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="98.25" customHeight="1">
+      <c r="A8" s="51" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>915</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+    </row>
+    <row r="11" spans="1:11" ht="128.25">
+      <c r="A11" s="43" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="85.5">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="42.75">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="85.5">
+      <c r="A18" s="51" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E18" s="51" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="57">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+    </row>
+    <row r="23" spans="1:11" ht="85.5">
+      <c r="A23" s="43" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="57">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="85.5">
+      <c r="A28" s="51" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="57">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A32" s="44"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+    </row>
+    <row r="33" spans="1:11" ht="85.5">
+      <c r="A33" s="43" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="43"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+    </row>
+    <row r="35" spans="1:11" ht="57">
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="43"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="1:11" ht="28.5">
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" spans="1:11" ht="85.5">
+      <c r="A40" s="51" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="51"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11" ht="57">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="43"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+    </row>
+    <row r="44" spans="1:11" ht="28.5">
+      <c r="A44" s="43"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+    </row>
+    <row r="47" spans="1:11" ht="85.5">
+      <c r="A47" s="43" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B47" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="43" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D47" s="43" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E47" s="43" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="43"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" spans="1:11" ht="71.25">
+      <c r="A49" s="43"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+    </row>
+    <row r="51" spans="1:11" ht="28.5">
+      <c r="A51" s="43"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="43"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+    </row>
+    <row r="53" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A53" s="43"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+    </row>
+    <row r="54" spans="1:11" ht="57">
+      <c r="A54" s="51" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B54" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="51" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D54" s="51" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E54" s="51" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F54" s="51"/>
+      <c r="G54" s="51" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H54" s="51"/>
+      <c r="I54" s="51"/>
+      <c r="J54" s="51"/>
+      <c r="K54" s="51"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="43"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43"/>
+    </row>
+    <row r="56" spans="1:11" ht="57">
+      <c r="A56" s="43"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="43"/>
+      <c r="J56" s="43"/>
+      <c r="K56" s="43"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="43"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="43"/>
+      <c r="I57" s="43"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="43"/>
+    </row>
+    <row r="58" spans="1:11" ht="57">
+      <c r="A58" s="43"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="43"/>
+      <c r="J58" s="43"/>
+      <c r="K58" s="43"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="43"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="43"/>
+    </row>
+    <row r="60" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A60" s="44"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="44"/>
+      <c r="J60" s="44"/>
+      <c r="K60" s="44"/>
+    </row>
+    <row r="61" spans="1:11" ht="85.5">
+      <c r="A61" s="43" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B61" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="43" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F61" s="43"/>
+      <c r="G61" s="43" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H61" s="43"/>
+      <c r="I61" s="43"/>
+      <c r="J61" s="43"/>
+      <c r="K61" s="43"/>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="43"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="43"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="43"/>
+      <c r="G62" s="43"/>
+      <c r="H62" s="43"/>
+      <c r="I62" s="43"/>
+      <c r="J62" s="43"/>
+      <c r="K62" s="43"/>
+    </row>
+    <row r="63" spans="1:11" ht="57">
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="43" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="43"/>
+      <c r="I63" s="43"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="43"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="45"/>
+      <c r="F64" s="43"/>
+      <c r="G64" s="43"/>
+      <c r="H64" s="43"/>
+      <c r="I64" s="43"/>
+      <c r="J64" s="43"/>
+      <c r="K64" s="43"/>
+    </row>
+    <row r="65" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A65" s="43"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F65" s="43"/>
+      <c r="G65" s="43"/>
+      <c r="H65" s="43"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+    </row>
+    <row r="66" spans="1:11" ht="85.5">
+      <c r="A66" s="51" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B66" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" s="51" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D66" s="51" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E66" s="51" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F66" s="51"/>
+      <c r="G66" s="51" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H66" s="51"/>
+      <c r="I66" s="51"/>
+      <c r="J66" s="51"/>
+      <c r="K66" s="51"/>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="43"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="43"/>
+      <c r="J67" s="43"/>
+      <c r="K67" s="43"/>
+    </row>
+    <row r="68" spans="1:11" ht="85.5">
+      <c r="A68" s="43"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="43" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43"/>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="43"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="43"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
+      <c r="H69" s="43"/>
+      <c r="I69" s="43"/>
+      <c r="J69" s="43"/>
+      <c r="K69" s="43"/>
+    </row>
+    <row r="70" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A70" s="44"/>
+      <c r="B70" s="44"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F70" s="44"/>
+      <c r="G70" s="44"/>
+      <c r="H70" s="44"/>
+      <c r="I70" s="44"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="44"/>
+    </row>
+    <row r="71" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A71" s="43" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B71" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="43" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D71" s="43" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E71" s="43" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F71" s="43"/>
+      <c r="G71" s="43" t="s">
+        <v>1259</v>
+      </c>
+      <c r="H71" s="43"/>
+      <c r="I71" s="43"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="43"/>
+      <c r="B72" s="43"/>
+      <c r="C72" s="43"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="45"/>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43"/>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+    </row>
+    <row r="73" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A73" s="43"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F73" s="43"/>
+      <c r="G73" s="43"/>
+      <c r="H73" s="43"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="43"/>
+      <c r="K73" s="43"/>
+    </row>
+    <row r="74" spans="1:11" ht="155.25" customHeight="1">
+      <c r="A74" s="51" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B74" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="51" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D74" s="51" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E74" s="51" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F74" s="51"/>
+      <c r="G74" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H74" s="51"/>
+      <c r="I74" s="51"/>
+      <c r="J74" s="51"/>
+      <c r="K74" s="51"/>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="43"/>
+      <c r="B75" s="43"/>
+      <c r="C75" s="43"/>
+      <c r="D75" s="43"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="43"/>
+      <c r="G75" s="43"/>
+      <c r="H75" s="43"/>
+      <c r="I75" s="43"/>
+      <c r="J75" s="43"/>
+      <c r="K75" s="43"/>
+    </row>
+    <row r="76" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A76" s="44"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="44" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F76" s="44"/>
+      <c r="G76" s="44"/>
+      <c r="H76" s="44"/>
+      <c r="I76" s="44"/>
+      <c r="J76" s="44"/>
+      <c r="K76" s="44"/>
+    </row>
+    <row r="77" spans="1:11" ht="99.75">
+      <c r="A77" s="43" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B77" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C77" s="43" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D77" s="43" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E77" s="43" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F77" s="43"/>
+      <c r="G77" s="43" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H77" s="43"/>
+      <c r="I77" s="43"/>
+      <c r="J77" s="43"/>
+      <c r="K77" s="43"/>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="43"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="43"/>
+      <c r="D78" s="43"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="43"/>
+      <c r="G78" s="43"/>
+      <c r="H78" s="43"/>
+      <c r="I78" s="43"/>
+      <c r="J78" s="43"/>
+      <c r="K78" s="43"/>
+    </row>
+    <row r="79" spans="1:11" ht="72" thickBot="1">
+      <c r="A79" s="43"/>
+      <c r="B79" s="43"/>
+      <c r="C79" s="43"/>
+      <c r="D79" s="43"/>
+      <c r="E79" s="43" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F79" s="43"/>
+      <c r="G79" s="43"/>
+      <c r="H79" s="43"/>
+      <c r="I79" s="43"/>
+      <c r="J79" s="43"/>
+      <c r="K79" s="43"/>
+    </row>
+    <row r="80" spans="1:11" ht="114">
+      <c r="A80" s="51" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B80" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C80" s="51" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D80" s="51" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E80" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F80" s="51"/>
+      <c r="G80" s="51" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H80" s="51"/>
+      <c r="I80" s="51"/>
+      <c r="J80" s="51"/>
+      <c r="K80" s="51"/>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="43"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="43"/>
+      <c r="D81" s="43"/>
+      <c r="E81" s="45"/>
+      <c r="F81" s="43"/>
+      <c r="G81" s="43"/>
+      <c r="H81" s="43"/>
+      <c r="I81" s="43"/>
+      <c r="J81" s="43"/>
+      <c r="K81" s="43"/>
+    </row>
+    <row r="82" spans="1:11" ht="42.75">
+      <c r="A82" s="43"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="43"/>
+      <c r="D82" s="43"/>
+      <c r="E82" s="43" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F82" s="43"/>
+      <c r="G82" s="43"/>
+      <c r="H82" s="43"/>
+      <c r="I82" s="43"/>
+      <c r="J82" s="43"/>
+      <c r="K82" s="43"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="43"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="43"/>
+      <c r="D83" s="43"/>
+      <c r="E83" s="45"/>
+      <c r="F83" s="43"/>
+      <c r="G83" s="43"/>
+      <c r="H83" s="43"/>
+      <c r="I83" s="43"/>
+      <c r="J83" s="43"/>
+      <c r="K83" s="43"/>
+    </row>
+    <row r="84" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A84" s="44"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="44"/>
+      <c r="J84" s="44"/>
+      <c r="K84" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC3C8B5-B97E-41D5-8325-294AC185332F}">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="31.42578125" customWidth="1"/>
+    <col min="8" max="8" width="27.42578125" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.28515625" customWidth="1"/>
+    <col min="11" max="11" width="24.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="84" customHeight="1">
+      <c r="A8" s="51" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="141" customHeight="1">
+      <c r="A11" s="51" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+    </row>
+    <row r="14" spans="1:11" ht="85.5">
+      <c r="A14" s="43" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11" ht="85.5">
+      <c r="A17" s="51" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>909</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11" ht="72" thickBot="1">
+      <c r="A19" s="44"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+    </row>
+    <row r="20" spans="1:11" ht="114">
+      <c r="A20" s="43" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>909</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="72" thickBot="1">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11" ht="129" thickBot="1">
+      <c r="A23" s="49" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="49" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D23" s="49" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E23" s="49" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
+    </row>
+    <row r="24" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A24" s="43" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43" t="s">
+        <v>1312</v>
+      </c>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="169.5" customHeight="1">
+      <c r="A27" s="51" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51" t="s">
+        <v>1318</v>
+      </c>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+    </row>
+    <row r="30" spans="1:11" ht="114">
+      <c r="A30" s="51" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A32" s="44"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD21624-4E0C-4A0B-B299-8A13E9DE85D8}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBF1778A-A95C-4341-A78F-0724A072BB4A}">
   <dimension ref="A1:K118"/>

--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BF25FB-2B63-4682-9FF4-511A684EE980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD94ABF-F706-4550-9593-768163843099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="6" activeTab="13" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="16" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,13 @@
     <sheet name="ProductDisPage" sheetId="12" r:id="rId12"/>
     <sheet name="Review" sheetId="13" r:id="rId13"/>
     <sheet name="AddToCart" sheetId="14" r:id="rId14"/>
-    <sheet name="Sheet8" sheetId="15" r:id="rId15"/>
+    <sheet name="WishList" sheetId="15" r:id="rId15"/>
+    <sheet name="Cart" sheetId="16" r:id="rId16"/>
+    <sheet name="Sheet2" sheetId="17" r:id="rId17"/>
+    <sheet name="Sheet3" sheetId="18" r:id="rId18"/>
+    <sheet name="Sheet4" sheetId="19" r:id="rId19"/>
+    <sheet name="Sheet5" sheetId="20" r:id="rId20"/>
+    <sheet name="Sheet6" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="1323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="1652">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -4358,6 +4364,1051 @@
   </si>
   <si>
     <t>The Mini-Cart button dynamically updates instantly (without page reload) to reflect the new item count and new combined total price.</t>
+  </si>
+  <si>
+    <t>TC_WISH_001</t>
+  </si>
+  <si>
+    <t>Verify adding a product to Wish List from Category Page</t>
+  </si>
+  <si>
+    <t>User is logged in and on a Category Listing Page</t>
+  </si>
+  <si>
+    <t>2. Click the 'Add to Wish List' (Heart) icon.</t>
+  </si>
+  <si>
+    <t>A success banner appears confirming the product was added to the wish list.</t>
+  </si>
+  <si>
+    <t>TC_WISH_002</t>
+  </si>
+  <si>
+    <t>Verify adding a product to Wish List from Product Display Page (PDP)</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Add to Wish List' icon/button.</t>
+  </si>
+  <si>
+    <t>TC_WISH_003</t>
+  </si>
+  <si>
+    <t>Verify adding a product to Wish List from Search Results</t>
+  </si>
+  <si>
+    <t>User is logged in and has searched for a product</t>
+  </si>
+  <si>
+    <t>2. Click the 'Add to Wish List' icon.</t>
+  </si>
+  <si>
+    <t>TC_WISH_004</t>
+  </si>
+  <si>
+    <t>Verify adding a product to Wish List from Home Page Featured</t>
+  </si>
+  <si>
+    <t>User is logged in and on the Home Page</t>
+  </si>
+  <si>
+    <t>TC_WISH_005</t>
+  </si>
+  <si>
+    <t>Verify Guest User behavior when clicking 'Add to Wish List'</t>
+  </si>
+  <si>
+    <t>User is browsing as a Guest (Logged Out)</t>
+  </si>
+  <si>
+    <t>1. Click the 'Add to Wish List' icon on any product.</t>
+  </si>
+  <si>
+    <t>A banner appears stating the user must login or create an account to save the item. The item is not added.</t>
+  </si>
+  <si>
+    <t>TC_WISH_006</t>
+  </si>
+  <si>
+    <t>Verify dynamic update of the Header 'Wish List (X)' counter</t>
+  </si>
+  <si>
+    <t>1. Note the current number in the 'Wish List (X)' header link.</t>
+  </si>
+  <si>
+    <t>2. Add a new product to the wish list.</t>
+  </si>
+  <si>
+    <t>TC_WISH_007</t>
+  </si>
+  <si>
+    <t>User has just added an item to the wish list</t>
+  </si>
+  <si>
+    <t>1. Click the 'wish list' hyperlink inside the green success alert banner.</t>
+  </si>
+  <si>
+    <t>User is routed directly to the My Wish List page.</t>
+  </si>
+  <si>
+    <t>TC_WISH_008</t>
+  </si>
+  <si>
+    <t>Verify navigation via the Global Header link</t>
+  </si>
+  <si>
+    <t>1. Click the 'Wish List (X)' link located in the top global header.</t>
+  </si>
+  <si>
+    <t>User is routed to the My Wish List page.</t>
+  </si>
+  <si>
+    <t>TC_WISH_009</t>
+  </si>
+  <si>
+    <t>Verify navigation via the My Account Dashboard</t>
+  </si>
+  <si>
+    <t>User is on their My Account page</t>
+  </si>
+  <si>
+    <t>1. Locate the 'My Orders' section.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Modify your wish list' link.</t>
+  </si>
+  <si>
+    <t>TC_WISH_010</t>
+  </si>
+  <si>
+    <t>Verify navigation via the Right Column Menu</t>
+  </si>
+  <si>
+    <t>User is on any My Account related page</t>
+  </si>
+  <si>
+    <t>2. Click the 'Wish List' link.</t>
+  </si>
+  <si>
+    <t>TC_WISH_011</t>
+  </si>
+  <si>
+    <t>Verify Wish List page UI and Table Layout</t>
+  </si>
+  <si>
+    <t>User is on the My Wish List page</t>
+  </si>
+  <si>
+    <t>1. Observe the layout and columns.</t>
+  </si>
+  <si>
+    <t>Information is organized in a table containing Image, Product Name, Model, Stock, Price, and Action (Add to Cart / Remove).</t>
+  </si>
+  <si>
+    <t>TC_WISH_012</t>
+  </si>
+  <si>
+    <t>Verify 'Stock' status accuracy in Wish List</t>
+  </si>
+  <si>
+    <t>User has items with varying inventory in the wish list</t>
+  </si>
+  <si>
+    <t>1. Observe the 'Stock' column for an in-stock and an out-of-stock item.</t>
+  </si>
+  <si>
+    <t>The statuses accurately reflect current inventory (e.g., "In Stock", "Out Of Stock", "Pre-Order").</t>
+  </si>
+  <si>
+    <t>TC_WISH_013</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Cart' functionality from Wish List (Simple Product)</t>
+  </si>
+  <si>
+    <t>1. Click the 'Add to Cart' (shopping cart icon) for a simple product.</t>
+  </si>
+  <si>
+    <t>A success banner appears, the mini-cart updates, and the user remains on the Wish List page.</t>
+  </si>
+  <si>
+    <t>TC_WISH_014</t>
+  </si>
+  <si>
+    <t>Verify 'Add to Cart' from Wish List (Product with Options)</t>
+  </si>
+  <si>
+    <t>1. Click 'Add to Cart' for a product that requires mandatory options (e.g., Size).</t>
+  </si>
+  <si>
+    <t>TC_WISH_015</t>
+  </si>
+  <si>
+    <t>1. Click the thumbnail image of a product in the list.</t>
+  </si>
+  <si>
+    <t>TC_WISH_016</t>
+  </si>
+  <si>
+    <t>1. Click the hyperlinked name of a product in the list.</t>
+  </si>
+  <si>
+    <t>TC_WISH_017</t>
+  </si>
+  <si>
+    <t>Verify removing a single product from the Wish List</t>
+  </si>
+  <si>
+    <t>User is on the My Wish List page with 2+ items</t>
+  </si>
+  <si>
+    <t>1. Click the 'Remove' (red X) button in the Action column for a specific product.</t>
+  </si>
+  <si>
+    <t>Page reloads, a success banner confirms removal, the product disappears, and the header counter decreases by 1.</t>
+  </si>
+  <si>
+    <t>TC_WISH_018</t>
+  </si>
+  <si>
+    <t>Verify removing the last product triggers empty state</t>
+  </si>
+  <si>
+    <t>User has exactly 1 item in the Wish List</t>
+  </si>
+  <si>
+    <t>1. Click the 'Remove' button.</t>
+  </si>
+  <si>
+    <t>The page reloads displaying the empty state text: "Your wish list is empty."</t>
+  </si>
+  <si>
+    <t>TC_WISH_019</t>
+  </si>
+  <si>
+    <t>User has Product A in their wish list</t>
+  </si>
+  <si>
+    <t>2. Click 'Add to Wish List' again.</t>
+  </si>
+  <si>
+    <t>A success banner appears, but the product is not duplicated on the Wish List page. The counter does not increment.</t>
+  </si>
+  <si>
+    <t>TC_WISH_020</t>
+  </si>
+  <si>
+    <t>Verify 'Continue' button functionality</t>
+  </si>
+  <si>
+    <t>1. Click the 'Continue' button at the bottom right.</t>
+  </si>
+  <si>
+    <t>User is navigated back to the My Account dashboard page.</t>
+  </si>
+  <si>
+    <t>TC_WISH_021</t>
+  </si>
+  <si>
+    <t>Verify Wish List persistence across sessions</t>
+  </si>
+  <si>
+    <t>User is logged in and has items in the wish list</t>
+  </si>
+  <si>
+    <t>1. Log out of the account.</t>
+  </si>
+  <si>
+    <t>2. Log back into the same account.</t>
+  </si>
+  <si>
+    <t>3. Open the Wish List.</t>
+  </si>
+  <si>
+    <t>The items previously added to the wish list are successfully retained and visible.</t>
+  </si>
+  <si>
+    <t>TC_CART_001</t>
+  </si>
+  <si>
+    <t>Verify navigation to Shopping Cart via Global Header link</t>
+  </si>
+  <si>
+    <t>User has items in the cart</t>
+  </si>
+  <si>
+    <t>1. Click the 'Shopping Cart' link in the top global header menu.</t>
+  </si>
+  <si>
+    <t>User is routed to the detailed Shopping Cart page.</t>
+  </si>
+  <si>
+    <t>TC_CART_002</t>
+  </si>
+  <si>
+    <t>Verify navigation to Shopping Cart via Mini-Cart dropdown</t>
+  </si>
+  <si>
+    <t>1. Click the black Mini-Cart button (top right).</t>
+  </si>
+  <si>
+    <t>2. Click the 'View Cart' link inside the dropdown.</t>
+  </si>
+  <si>
+    <t>TC_CART_003</t>
+  </si>
+  <si>
+    <t>Verify navigation via 'Add to Cart' success banner</t>
+  </si>
+  <si>
+    <t>User is on a Product page</t>
+  </si>
+  <si>
+    <t>2. Click the 'shopping cart' link inside the green success banner.</t>
+  </si>
+  <si>
+    <t>TC_CART_004</t>
+  </si>
+  <si>
+    <t>Verify Shopping Cart table UI layout</t>
+  </si>
+  <si>
+    <t>User is on the Shopping Cart page</t>
+  </si>
+  <si>
+    <t>1. Observe the main cart table.</t>
+  </si>
+  <si>
+    <t>Table columns are clearly displayed: Image, Product Name, Model, Quantity, Unit Price, and Total.</t>
+  </si>
+  <si>
+    <t>TC_CART_005</t>
+  </si>
+  <si>
+    <t>Verify Product Name and Model accuracy</t>
+  </si>
+  <si>
+    <t>1. Compare the Product Name and Model text to the original Product Display Page.</t>
+  </si>
+  <si>
+    <t>The Name and alphanumeric Model exactly match the backend data for the added item.</t>
+  </si>
+  <si>
+    <t>TC_CART_006</t>
+  </si>
+  <si>
+    <t>Verify Product Options are displayed</t>
+  </si>
+  <si>
+    <t>User has added a product with selected options (e.g., Size)</t>
+  </si>
+  <si>
+    <t>1. Observe the text immediately below the Product Name in the table.</t>
+  </si>
+  <si>
+    <t>The selected options (e.g., "- Size: Large") are clearly listed.</t>
+  </si>
+  <si>
+    <t>TC_CART_007</t>
+  </si>
+  <si>
+    <t>Verify Reward Points display (if applicable)</t>
+  </si>
+  <si>
+    <t>User adds a product offering reward points</t>
+  </si>
+  <si>
+    <t>1. Observe the text under the Product Name.</t>
+  </si>
+  <si>
+    <t>The expected reward points text is displayed (e.g., "Reward Points: 100").</t>
+  </si>
+  <si>
+    <t>TC_CART_008</t>
+  </si>
+  <si>
+    <t>1. Click the thumbnail image of the product in the cart row.</t>
+  </si>
+  <si>
+    <t>User is routed back to the detailed Product Display Page for that item.</t>
+  </si>
+  <si>
+    <t>TC_CART_009</t>
+  </si>
+  <si>
+    <t>Verify clicking Product Name navigates to PDP</t>
+  </si>
+  <si>
+    <t>1. Click the hyperlinked Product Name.</t>
+  </si>
+  <si>
+    <t>TC_CART_010</t>
+  </si>
+  <si>
+    <t>Verify Unit Price matches PDP</t>
+  </si>
+  <si>
+    <t>1. Observe the 'Unit Price' column.</t>
+  </si>
+  <si>
+    <t>The price accurately matches the base price (plus any selected option markups) from the PDP.</t>
+  </si>
+  <si>
+    <t>TC_CART_011</t>
+  </si>
+  <si>
+    <t>Verify Row Total calculation</t>
+  </si>
+  <si>
+    <t>User has added Qty 3 of an item</t>
+  </si>
+  <si>
+    <t>1. Observe the 'Total' column for that specific row.</t>
+  </si>
+  <si>
+    <r>
+      <t>The row total is mathematically accurate (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Unit Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>TC_CART_012</t>
+  </si>
+  <si>
+    <t>Verify updating quantity to a higher valid number</t>
+  </si>
+  <si>
+    <t>1. Change the number in the 'Quantity' input field from 1 to 3.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Update' (blue refresh) button next to it.</t>
+  </si>
+  <si>
+    <t>A success banner appears, the page reloads, and the row total recalculates accurately.</t>
+  </si>
+  <si>
+    <t>TC_CART_013</t>
+  </si>
+  <si>
+    <t>Verify updating quantity to a lower valid number</t>
+  </si>
+  <si>
+    <t>User has Qty 5 of an item in the cart</t>
+  </si>
+  <si>
+    <t>1. Change the number in the 'Quantity' input field from 5 to 2.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Update' button.</t>
+  </si>
+  <si>
+    <t>A success banner appears, the page reloads, and the row total decreases accurately.</t>
+  </si>
+  <si>
+    <t>TC_CART_014</t>
+  </si>
+  <si>
+    <t>Verify updating quantity using the 'Enter' key</t>
+  </si>
+  <si>
+    <t>1. Click inside the 'Quantity' input box.</t>
+  </si>
+  <si>
+    <t>2. Change the number.</t>
+  </si>
+  <si>
+    <t>3. Press the 'Enter' key on the keyboard.</t>
+  </si>
+  <si>
+    <t>The cart updates successfully exactly as if the 'Update' button was clicked.</t>
+  </si>
+  <si>
+    <t>TC_CART_015</t>
+  </si>
+  <si>
+    <t>Verify updating quantity to 0</t>
+  </si>
+  <si>
+    <t>1. Enter '0' in the Quantity field.</t>
+  </si>
+  <si>
+    <t>The item is entirely removed from the shopping cart.</t>
+  </si>
+  <si>
+    <t>TC_CART_016</t>
+  </si>
+  <si>
+    <t>Verify updating quantity to a negative number</t>
+  </si>
+  <si>
+    <t>1. Enter '-1' or '-5' in the Quantity field.</t>
+  </si>
+  <si>
+    <t>The system rejects the input. It either throws a validation error or defaults the quantity back to 1.</t>
+  </si>
+  <si>
+    <t>TC_CART_017</t>
+  </si>
+  <si>
+    <t>Verify updating quantity with non-numeric characters</t>
+  </si>
+  <si>
+    <t>1. Enter 'ABC' or special characters in the Quantity field.</t>
+  </si>
+  <si>
+    <t>The system rejects the input and handles the validation without crashing.</t>
+  </si>
+  <si>
+    <t>TC_CART_018</t>
+  </si>
+  <si>
+    <t>Verify stock warning when updating quantity beyond available inventory</t>
+  </si>
+  <si>
+    <t>User attempts to order more than is in stock</t>
+  </si>
+  <si>
+    <t>1. Enter a very high quantity (e.g., 9999).</t>
+  </si>
+  <si>
+    <t>A warning banner appears stating products marked with *** are not available in the desired quantity.</t>
+  </si>
+  <si>
+    <t>TC_CART_019</t>
+  </si>
+  <si>
+    <t>Verify minimum order quantity enforcement during update</t>
+  </si>
+  <si>
+    <t>User has a product with a minimum order quantity of 3</t>
+  </si>
+  <si>
+    <t>1. Change the cart quantity to '2'.</t>
+  </si>
+  <si>
+    <t>The system rejects the update and displays a warning about the minimum quantity requirement.</t>
+  </si>
+  <si>
+    <t>TC_CART_020</t>
+  </si>
+  <si>
+    <t>Verify removing an item via the 'Remove' button</t>
+  </si>
+  <si>
+    <t>User is on the Shopping Cart page with multiple items</t>
+  </si>
+  <si>
+    <t>1. Click the 'Remove' (red X) button in the Quantity column for Item A.</t>
+  </si>
+  <si>
+    <t>The page reloads, Item A is completely removed, and a success banner is displayed.</t>
+  </si>
+  <si>
+    <t>TC_CART_021</t>
+  </si>
+  <si>
+    <t>Verify totals recalculate after item removal</t>
+  </si>
+  <si>
+    <t>User removes an item from the cart</t>
+  </si>
+  <si>
+    <t>1. Observe the Sub-Total and Total values at the bottom of the page after removal.</t>
+  </si>
+  <si>
+    <t>The totals accurately decrease by the exact amount of the removed item's row total.</t>
+  </si>
+  <si>
+    <t>TC_CART_022</t>
+  </si>
+  <si>
+    <t>Verify Mini-Cart sync after item removal</t>
+  </si>
+  <si>
+    <t>User removes an item from the main cart page</t>
+  </si>
+  <si>
+    <t>1. Observe the black Mini-Cart button in the top right header.</t>
+  </si>
+  <si>
+    <t>The Mini-Cart item count and total price dynamically sync to match the updated main cart.</t>
+  </si>
+  <si>
+    <t>TC_CART_023</t>
+  </si>
+  <si>
+    <t>Verify removing the last item triggers the Empty Cart state</t>
+  </si>
+  <si>
+    <t>User has exactly 1 item in the cart</t>
+  </si>
+  <si>
+    <t>1. Click the 'Remove' (red X) button.</t>
+  </si>
+  <si>
+    <t>The page reloads and displays the empty state text: "Your shopping cart is empty!"</t>
+  </si>
+  <si>
+    <t>TC_CART_024</t>
+  </si>
+  <si>
+    <t>Verify Sub-Total calculation at the bottom of the page</t>
+  </si>
+  <si>
+    <t>User has multiple different items in the cart</t>
+  </si>
+  <si>
+    <t>1. Scroll to the totals section at the bottom.</t>
+  </si>
+  <si>
+    <t>2. Manually add up all the 'Row Totals'.</t>
+  </si>
+  <si>
+    <t>The 'Sub-Total' field matches the exact sum of all individual row totals before taxes.</t>
+  </si>
+  <si>
+    <t>TC_CART_025</t>
+  </si>
+  <si>
+    <t>Verify Tax calculation rendering</t>
+  </si>
+  <si>
+    <t>User has taxable items in the cart</t>
+  </si>
+  <si>
+    <t>1. Observe the totals section.</t>
+  </si>
+  <si>
+    <t>Applicable taxes (e.g., Eco Tax, VAT) are listed as separate line items above the final Total.</t>
+  </si>
+  <si>
+    <t>TC_CART_026</t>
+  </si>
+  <si>
+    <t>Verify Final Total calculation</t>
+  </si>
+  <si>
+    <t>User has multiple items and taxes</t>
+  </si>
+  <si>
+    <t>1. Manually add the Sub-Total plus any displayed tax line items.</t>
+  </si>
+  <si>
+    <t>The final 'Total' field matches this mathematical calculation exactly.</t>
+  </si>
+  <si>
+    <t>TC_CART_027</t>
+  </si>
+  <si>
+    <t>Verify 'Continue Shopping' button functionality</t>
+  </si>
+  <si>
+    <t>User is on a populated Shopping Cart page</t>
+  </si>
+  <si>
+    <t>1. Click the 'Continue Shopping' button at the bottom left.</t>
+  </si>
+  <si>
+    <t>User is navigated back to the Store Home Page.</t>
+  </si>
+  <si>
+    <t>TC_CART_028</t>
+  </si>
+  <si>
+    <t>Verify 'Checkout' button functionality</t>
+  </si>
+  <si>
+    <t>1. Click the primary 'Checkout' button at the bottom right.</t>
+  </si>
+  <si>
+    <t>User is navigated to the Checkout pipeline (or Login page if guest checkout is disabled).</t>
+  </si>
+  <si>
+    <t>TC_CART_029</t>
+  </si>
+  <si>
+    <t>Verify 'Continue' button on Empty Cart page</t>
+  </si>
+  <si>
+    <t>User is on the Empty Cart page</t>
+  </si>
+  <si>
+    <t>1. Click the 'Continue' button.</t>
+  </si>
+  <si>
+    <t>TC_CART_030</t>
+  </si>
+  <si>
+    <t>Verify out-of-stock item indicators</t>
+  </si>
+  <si>
+    <t>User has an out-of-stock item in the cart</t>
+  </si>
+  <si>
+    <t>1. Observe the product name in the cart table.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The product name is appended with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>***</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to visually indicate a stock shortage.</t>
+    </r>
+  </si>
+  <si>
+    <t>TC_CART_031</t>
+  </si>
+  <si>
+    <t>Verify cart persistence during active session</t>
+  </si>
+  <si>
+    <t>1. Navigate away to various category pages, information pages, and search pages.</t>
+  </si>
+  <si>
+    <t>2. Return to the Shopping Cart.</t>
+  </si>
+  <si>
+    <t>All items, quantities, and totals remain exactly as the user left them.</t>
+  </si>
+  <si>
+    <t>TC_CART_032</t>
+  </si>
+  <si>
+    <t>Verify cart persistence after closing browser (Guest)</t>
+  </si>
+  <si>
+    <t>Guest user has items in the cart</t>
+  </si>
+  <si>
+    <t>1. Close the browser entirely.</t>
+  </si>
+  <si>
+    <t>2. Reopen the browser and navigate back to the store.</t>
+  </si>
+  <si>
+    <t>Depending on cookie/session configuration, the items should still be in the cart.</t>
+  </si>
+  <si>
+    <t>TC_CART_033</t>
+  </si>
+  <si>
+    <t>Verify Cart Merge upon Login</t>
+  </si>
+  <si>
+    <t>Guest user has Item A in cart, but Registered User account has Item B saved in cart</t>
+  </si>
+  <si>
+    <t>1. As a guest, add Item A.</t>
+  </si>
+  <si>
+    <t>2. Log into the registered account.</t>
+  </si>
+  <si>
+    <t>3. Open the Shopping Cart.</t>
+  </si>
+  <si>
+    <t>The cart successfully merges both sessions, displaying both Item A and Item B without data loss.</t>
+  </si>
+  <si>
+    <t>TC_COUP_001</t>
+  </si>
+  <si>
+    <t>Verify successful application of a valid Coupon Code</t>
+  </si>
+  <si>
+    <t>User has an applicable item in the cart</t>
+  </si>
+  <si>
+    <t>1. Navigate to the Shopping Cart.</t>
+  </si>
+  <si>
+    <t>2. Click 'Use Coupon Code' to expand the panel.</t>
+  </si>
+  <si>
+    <t>3. Enter a valid, active coupon code.</t>
+  </si>
+  <si>
+    <t>4. Click 'Apply Coupon'.</t>
+  </si>
+  <si>
+    <t>A success banner appears, and the discount is listed as a new line item in the Totals section.</t>
+  </si>
+  <si>
+    <t>TC_COUP_002</t>
+  </si>
+  <si>
+    <t>Verify validation message for an invalid Coupon Code</t>
+  </si>
+  <si>
+    <t>1. Expand the 'Use Coupon Code' panel.</t>
+  </si>
+  <si>
+    <t>2. Enter a random, non-existent code.</t>
+  </si>
+  <si>
+    <t>3. Click 'Apply Coupon'.</t>
+  </si>
+  <si>
+    <t>Application fails. A warning banner states: "Warning: Coupon is either invalid, expired or reached its usage limit!"</t>
+  </si>
+  <si>
+    <t>TC_COUP_003</t>
+  </si>
+  <si>
+    <t>Verify validation when Coupon Code field is left blank</t>
+  </si>
+  <si>
+    <t>2. Leave the input field completely empty.</t>
+  </si>
+  <si>
+    <t>Application fails. A warning banner prompts the user to enter a coupon code.</t>
+  </si>
+  <si>
+    <t>TC_COUP_004</t>
+  </si>
+  <si>
+    <t>Verify application of an expired Coupon Code</t>
+  </si>
+  <si>
+    <t>1. Enter a coupon code that is past its configured end date.</t>
+  </si>
+  <si>
+    <t>2. Click 'Apply Coupon'.</t>
+  </si>
+  <si>
+    <t>Application fails with the standard invalid/expired warning message.</t>
+  </si>
+  <si>
+    <t>TC_COUP_005</t>
+  </si>
+  <si>
+    <t>Verify application of a Coupon Code that has reached its usage limit</t>
+  </si>
+  <si>
+    <t>1. Enter a coupon code that has zero remaining uses.</t>
+  </si>
+  <si>
+    <t>Application fails with the standard invalid/expired/usage limit warning message.</t>
+  </si>
+  <si>
+    <t>TC_COUP_006</t>
+  </si>
+  <si>
+    <t>Verify Coupon Code application below the minimum cart total requirement</t>
+  </si>
+  <si>
+    <t>User has $10 worth of items in the cart</t>
+  </si>
+  <si>
+    <t>1. Enter a valid coupon code that requires a $50 minimum spend.</t>
+  </si>
+  <si>
+    <t>Application fails. A warning message indicates the cart does not meet the minimum total required for the coupon.</t>
+  </si>
+  <si>
+    <t>TC_COUP_007</t>
+  </si>
+  <si>
+    <t>Verify Coupon Code applied to restricted products/categories</t>
+  </si>
+  <si>
+    <t>User has Product A in the cart</t>
+  </si>
+  <si>
+    <t>1. Enter a valid coupon code that is only configured to work on Product B.</t>
+  </si>
+  <si>
+    <t>Application fails. A warning indicates the coupon is not valid for the products currently in the cart.</t>
+  </si>
+  <si>
+    <t>TC_COUP_008</t>
+  </si>
+  <si>
+    <t>Verify cart Total calculation with a Percentage (%) discount coupon</t>
+  </si>
+  <si>
+    <t>User has $100 worth of applicable items</t>
+  </si>
+  <si>
+    <t>1. Apply a valid 10% off coupon code.</t>
+  </si>
+  <si>
+    <t>The totals section displays a discount line item of -$10.00, and the Final Total is mathematically accurate.</t>
+  </si>
+  <si>
+    <t>TC_COUP_009</t>
+  </si>
+  <si>
+    <t>Verify cart Total calculation with a Fixed Amount discount coupon</t>
+  </si>
+  <si>
+    <t>1. Apply a valid $15.00 off fixed amount coupon code.</t>
+  </si>
+  <si>
+    <t>The totals section displays a discount line item of -$15.00, and the Final Total is mathematically accurate.</t>
+  </si>
+  <si>
+    <t>TC_COUP_010</t>
+  </si>
+  <si>
+    <t>Verify removing an successfully applied Coupon Code</t>
+  </si>
+  <si>
+    <t>User has successfully applied a coupon</t>
+  </si>
+  <si>
+    <t>1. Locate the applied coupon line in the Totals section at the bottom.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Remove' (red X) button next to it.</t>
+  </si>
+  <si>
+    <t>Page reloads, the discount line item is removed, a success banner appears, and the Final Total reverts to its original amount.</t>
+  </si>
+  <si>
+    <t>TC_GIFT_011</t>
+  </si>
+  <si>
+    <t>Verify successful application of a valid Gift Certificate (Voucher) code</t>
+  </si>
+  <si>
+    <t>User has an item in the cart</t>
+  </si>
+  <si>
+    <t>1. Click 'Use Gift Certificate' to expand the panel.</t>
+  </si>
+  <si>
+    <t>2. Enter a valid, funded voucher code.</t>
+  </si>
+  <si>
+    <t>3. Click 'Apply Gift Certificate'.</t>
+  </si>
+  <si>
+    <t>A success banner appears, and the voucher amount is deducted as a new line item in the Totals section.</t>
+  </si>
+  <si>
+    <t>TC_GIFT_012</t>
+  </si>
+  <si>
+    <t>Verify validation message for an invalid Gift Certificate code</t>
+  </si>
+  <si>
+    <t>1. Expand the 'Use Gift Certificate' panel.</t>
+  </si>
+  <si>
+    <t>Application fails. A warning banner states: "Warning: Gift Certificate is either invalid or the balance has been used up!"</t>
+  </si>
+  <si>
+    <t>TC_GIFT_013</t>
+  </si>
+  <si>
+    <t>Verify validation when Gift Certificate field is left blank</t>
+  </si>
+  <si>
+    <t>2. Leave the input field empty.</t>
+  </si>
+  <si>
+    <t>Application fails. A warning banner prompts the user to enter a voucher code.</t>
+  </si>
+  <si>
+    <t>TC_GIFT_014</t>
+  </si>
+  <si>
+    <t>Verify Gift Certificate deduction logic when voucher exceeds cart total</t>
+  </si>
+  <si>
+    <t>Cart total is $50. User has a $100 voucher</t>
+  </si>
+  <si>
+    <t>1. Apply the $100 Gift Certificate code.</t>
+  </si>
+  <si>
+    <t>The cart Final Total becomes $0.00. The remaining $50 balance stays attached to the voucher code for future use.</t>
+  </si>
+  <si>
+    <t>TC_GIFT_015</t>
+  </si>
+  <si>
+    <t>Verify removing an successfully applied Gift Certificate</t>
+  </si>
+  <si>
+    <t>User has successfully applied a gift certificate</t>
+  </si>
+  <si>
+    <t>1. Locate the applied voucher line in the Totals section.</t>
+  </si>
+  <si>
+    <t>Page reloads, the voucher line item is removed, and the Final Total reverts to its original amount.</t>
+  </si>
+  <si>
+    <t>TC_COUP_016</t>
+  </si>
+  <si>
+    <t>Verify applying both a Coupon Code and a Gift Certificate simultaneously</t>
+  </si>
+  <si>
+    <t>User has valid codes for both</t>
+  </si>
+  <si>
+    <t>1. Apply a valid Coupon Code.</t>
+  </si>
+  <si>
+    <t>2. Apply a valid Gift Certificate code.</t>
+  </si>
+  <si>
+    <t>3. Check the totals table.</t>
+  </si>
+  <si>
+    <t>Both discounts stack successfully. The Percentage/Fixed coupon applies first, and the Gift Certificate deducts from the remaining total.</t>
   </si>
 </sst>
 </file>
@@ -4461,7 +5512,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -4872,12 +5923,113 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5002,7 +6154,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5026,12 +6178,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="209">
+  <dxfs count="254">
     <dxf>
       <font>
         <b val="0"/>
@@ -5383,6 +6556,14 @@
         <vertical style="medium">
           <color rgb="FFC4C7C5"/>
         </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -5419,13 +6600,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -5778,6 +6952,766 @@
         <vertical style="medium">
           <color rgb="FFC4C7C5"/>
         </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -5820,6 +7754,38 @@
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
       </border>
     </dxf>
     <dxf>
@@ -6208,38 +8174,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color rgb="FFC4C7C5"/>
-        </vertical>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -6279,6 +8213,38 @@
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
       </border>
     </dxf>
     <dxf>
@@ -6603,38 +8569,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color rgb="FFC4C7C5"/>
-        </vertical>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -6674,6 +8608,38 @@
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
       </border>
     </dxf>
     <dxf>
@@ -7040,38 +9006,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color rgb="FFC4C7C5"/>
-        </vertical>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -7111,6 +9045,38 @@
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
       </border>
     </dxf>
     <dxf>
@@ -7435,38 +9401,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color rgb="FFC4C7C5"/>
-        </vertical>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -7506,6 +9440,38 @@
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
       </border>
     </dxf>
     <dxf>
@@ -7843,6 +9809,32 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -7888,12 +9880,381 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
       </border>
     </dxf>
     <dxf>
@@ -10179,10 +12540,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10210,10 +12571,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10241,10 +12602,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10272,10 +12633,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10303,10 +12664,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10334,10 +12695,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10348,10 +12709,10 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <vertical/>
       </border>
@@ -10376,10 +12737,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10407,10 +12768,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10438,10 +12799,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10469,10 +12830,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -10483,16 +12844,16 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </right>
         <top style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </top>
         <bottom style="medium">
-          <color theme="1"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -10556,7 +12917,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Table Style 1" pivot="0" count="6" xr9:uid="{DD3ECB35-2970-4076-8662-E1865940DEEF}"/>
+    <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{DD3ECB35-2970-4076-8662-E1865940DEEF}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -10570,165 +12931,225 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="193">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="238">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="192"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="191"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="237"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="236"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="102" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
   <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="128"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="127"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="123"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="122"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="121"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="86" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
   <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="84"/>
-    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="110"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="105"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="71" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
   <autoFilter ref="A7:K49" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="56" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86">
   <autoFilter ref="A7:K55" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="49"/>
-    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="41" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
   <autoFilter ref="A7:K62" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56">
   <autoFilter ref="A7:K84" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="253" dataDxfId="251" headerRowBorderDxfId="252" tableBorderDxfId="250">
   <autoFilter ref="A7:K32" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="249"/>
+    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="248"/>
+    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="247"/>
+    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="246"/>
+    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="245"/>
+    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="244"/>
+    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="243"/>
+    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="242"/>
+    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="241"/>
+    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="240"/>
+    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="239"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="42" dataDxfId="44" headerRowBorderDxfId="43" tableBorderDxfId="41">
+  <autoFilter ref="A7:K48" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="26" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+  <autoFilter ref="A7:K72" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="11" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13">
+  <autoFilter ref="A7:K65" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="190" dataDxfId="188" headerRowBorderDxfId="189" tableBorderDxfId="187" totalsRowBorderDxfId="186">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="235" dataDxfId="233" headerRowBorderDxfId="234" tableBorderDxfId="232" totalsRowBorderDxfId="231">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="185"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="184"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="183"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="182"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="181"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="230"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="229"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="228"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="227"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="226"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10738,7 +13159,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="180"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="225"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10746,120 +13167,120 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="173"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="172"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="171"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="170"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="169"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="168"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="167"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="166"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="165"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="220"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="219"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="218"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="217"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="216"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="215"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="214"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="213"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="212"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="211"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="210"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="160"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="159"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="158"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="157"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="156"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="155"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="154"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="153"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="152"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="151"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="150"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="205"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="204"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="203"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="202"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="201"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="200"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="199"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="198"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="197"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="196"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="195"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="142"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="140"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="139"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="138"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="137"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="136"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="135"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="190"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="189"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="188"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="187"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="186"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="185"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="184"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="183"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="182"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="181"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="180"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="130"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="129"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="127"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="126"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="125"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="124"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="123"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="122"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="121"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="174"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="173"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="172"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="171"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="170"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="169"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="168"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="167"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="166"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="165"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
   <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="157"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="156"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="155"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="154"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="153"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="152"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="151"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="208" dataDxfId="206" headerRowBorderDxfId="207" tableBorderDxfId="205">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
   <autoFilter ref="A6:K40" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="204"/>
-    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="203"/>
-    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="202"/>
-    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="201"/>
-    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="200"/>
-    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="199"/>
-    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="198"/>
-    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="197"/>
-    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="196"/>
-    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="195"/>
-    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="194"/>
+    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11970,7 +14391,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="129" thickBot="1">
+    <row r="8" spans="1:11" ht="72" thickBot="1">
       <c r="A8" s="49" t="s">
         <v>789</v>
       </c>
@@ -11995,7 +14416,7 @@
       <c r="J8" s="49"/>
       <c r="K8" s="49"/>
     </row>
-    <row r="9" spans="1:11" ht="86.25" thickBot="1">
+    <row r="9" spans="1:11" ht="57.75" thickBot="1">
       <c r="A9" s="43" t="s">
         <v>793</v>
       </c>
@@ -12020,7 +14441,7 @@
       <c r="J9" s="43"/>
       <c r="K9" s="43"/>
     </row>
-    <row r="10" spans="1:11" ht="99.75">
+    <row r="10" spans="1:11" ht="57">
       <c r="A10" s="51" t="s">
         <v>797</v>
       </c>
@@ -12058,7 +14479,7 @@
       <c r="J11" s="43"/>
       <c r="K11" s="43"/>
     </row>
-    <row r="12" spans="1:11" ht="43.5" thickBot="1">
+    <row r="12" spans="1:11" ht="29.25" thickBot="1">
       <c r="A12" s="44"/>
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
@@ -12073,7 +14494,7 @@
       <c r="J12" s="44"/>
       <c r="K12" s="44"/>
     </row>
-    <row r="13" spans="1:11" ht="86.25" thickBot="1">
+    <row r="13" spans="1:11" ht="57.75" thickBot="1">
       <c r="A13" s="43" t="s">
         <v>801</v>
       </c>
@@ -12098,7 +14519,7 @@
       <c r="J13" s="43"/>
       <c r="K13" s="43"/>
     </row>
-    <row r="14" spans="1:11" ht="114.75" thickBot="1">
+    <row r="14" spans="1:11" ht="72" thickBot="1">
       <c r="A14" s="49" t="s">
         <v>806</v>
       </c>
@@ -12123,7 +14544,7 @@
       <c r="J14" s="49"/>
       <c r="K14" s="49"/>
     </row>
-    <row r="15" spans="1:11" ht="86.25" thickBot="1">
+    <row r="15" spans="1:11" ht="57.75" thickBot="1">
       <c r="A15" s="43" t="s">
         <v>811</v>
       </c>
@@ -12148,7 +14569,7 @@
       <c r="J15" s="43"/>
       <c r="K15" s="43"/>
     </row>
-    <row r="16" spans="1:11" ht="86.25" thickBot="1">
+    <row r="16" spans="1:11" ht="57.75" thickBot="1">
       <c r="A16" s="49" t="s">
         <v>816</v>
       </c>
@@ -12173,7 +14594,7 @@
       <c r="J16" s="49"/>
       <c r="K16" s="49"/>
     </row>
-    <row r="17" spans="1:11" ht="86.25" thickBot="1">
+    <row r="17" spans="1:11" ht="72" thickBot="1">
       <c r="A17" s="43" t="s">
         <v>821</v>
       </c>
@@ -12198,7 +14619,7 @@
       <c r="J17" s="43"/>
       <c r="K17" s="43"/>
     </row>
-    <row r="18" spans="1:11" ht="86.25" thickBot="1">
+    <row r="18" spans="1:11" ht="57.75" thickBot="1">
       <c r="A18" s="49" t="s">
         <v>826</v>
       </c>
@@ -12223,7 +14644,7 @@
       <c r="J18" s="49"/>
       <c r="K18" s="49"/>
     </row>
-    <row r="19" spans="1:11" ht="86.25" thickBot="1">
+    <row r="19" spans="1:11" ht="43.5" thickBot="1">
       <c r="A19" s="43" t="s">
         <v>830</v>
       </c>
@@ -12248,7 +14669,7 @@
       <c r="J19" s="43"/>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="1:11" ht="72" thickBot="1">
+    <row r="20" spans="1:11" ht="43.5" thickBot="1">
       <c r="A20" s="49" t="s">
         <v>834</v>
       </c>
@@ -12273,7 +14694,7 @@
       <c r="J20" s="49"/>
       <c r="K20" s="49"/>
     </row>
-    <row r="21" spans="1:11" ht="72" thickBot="1">
+    <row r="21" spans="1:11" ht="43.5" thickBot="1">
       <c r="A21" s="43" t="s">
         <v>838</v>
       </c>
@@ -12298,7 +14719,7 @@
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
     </row>
-    <row r="22" spans="1:11" ht="86.25" thickBot="1">
+    <row r="22" spans="1:11" ht="43.5" thickBot="1">
       <c r="A22" s="49" t="s">
         <v>842</v>
       </c>
@@ -12323,7 +14744,7 @@
       <c r="J22" s="49"/>
       <c r="K22" s="49"/>
     </row>
-    <row r="23" spans="1:11" ht="100.5" thickBot="1">
+    <row r="23" spans="1:11" ht="57.75" thickBot="1">
       <c r="A23" s="43" t="s">
         <v>847</v>
       </c>
@@ -12348,7 +14769,7 @@
       <c r="J23" s="43"/>
       <c r="K23" s="43"/>
     </row>
-    <row r="24" spans="1:11" ht="100.5" thickBot="1">
+    <row r="24" spans="1:11" ht="72" thickBot="1">
       <c r="A24" s="49" t="s">
         <v>851</v>
       </c>
@@ -12373,7 +14794,7 @@
       <c r="J24" s="49"/>
       <c r="K24" s="49"/>
     </row>
-    <row r="25" spans="1:11" ht="86.25" thickBot="1">
+    <row r="25" spans="1:11" ht="57.75" thickBot="1">
       <c r="A25" s="43" t="s">
         <v>855</v>
       </c>
@@ -12398,7 +14819,7 @@
       <c r="J25" s="43"/>
       <c r="K25" s="43"/>
     </row>
-    <row r="26" spans="1:11" ht="100.5" thickBot="1">
+    <row r="26" spans="1:11" ht="72" thickBot="1">
       <c r="A26" s="49" t="s">
         <v>859</v>
       </c>
@@ -12423,7 +14844,7 @@
       <c r="J26" s="49"/>
       <c r="K26" s="49"/>
     </row>
-    <row r="27" spans="1:11" ht="57.75" thickBot="1">
+    <row r="27" spans="1:11" ht="43.5" thickBot="1">
       <c r="A27" s="43" t="s">
         <v>864</v>
       </c>
@@ -12448,7 +14869,7 @@
       <c r="J27" s="43"/>
       <c r="K27" s="43"/>
     </row>
-    <row r="28" spans="1:11" ht="99.75">
+    <row r="28" spans="1:11" ht="71.25">
       <c r="A28" s="51" t="s">
         <v>869</v>
       </c>
@@ -12486,7 +14907,7 @@
       <c r="J29" s="43"/>
       <c r="K29" s="43"/>
     </row>
-    <row r="30" spans="1:11" ht="100.5" thickBot="1">
+    <row r="30" spans="1:11" ht="57.75" thickBot="1">
       <c r="A30" s="44"/>
       <c r="B30" s="44"/>
       <c r="C30" s="44"/>
@@ -12501,7 +14922,7 @@
       <c r="J30" s="44"/>
       <c r="K30" s="44"/>
     </row>
-    <row r="31" spans="1:11" ht="57">
+    <row r="31" spans="1:11" ht="42.75">
       <c r="A31" s="43" t="s">
         <v>873</v>
       </c>
@@ -12539,7 +14960,7 @@
       <c r="J32" s="43"/>
       <c r="K32" s="43"/>
     </row>
-    <row r="33" spans="1:11" ht="57.75" thickBot="1">
+    <row r="33" spans="1:11" ht="29.25" thickBot="1">
       <c r="A33" s="43"/>
       <c r="B33" s="43"/>
       <c r="C33" s="43"/>
@@ -12554,7 +14975,7 @@
       <c r="J33" s="43"/>
       <c r="K33" s="43"/>
     </row>
-    <row r="34" spans="1:11" ht="57">
+    <row r="34" spans="1:11" ht="42.75">
       <c r="A34" s="51" t="s">
         <v>877</v>
       </c>
@@ -12592,7 +15013,7 @@
       <c r="J35" s="43"/>
       <c r="K35" s="43"/>
     </row>
-    <row r="36" spans="1:11" ht="57.75" thickBot="1">
+    <row r="36" spans="1:11" ht="29.25" thickBot="1">
       <c r="A36" s="44"/>
       <c r="B36" s="44"/>
       <c r="C36" s="44"/>
@@ -12607,7 +15028,7 @@
       <c r="J36" s="44"/>
       <c r="K36" s="44"/>
     </row>
-    <row r="37" spans="1:11" ht="71.25">
+    <row r="37" spans="1:11" ht="57">
       <c r="A37" s="43" t="s">
         <v>881</v>
       </c>
@@ -12645,7 +15066,7 @@
       <c r="J38" s="43"/>
       <c r="K38" s="43"/>
     </row>
-    <row r="39" spans="1:11" ht="43.5" thickBot="1">
+    <row r="39" spans="1:11" ht="29.25" thickBot="1">
       <c r="A39" s="43"/>
       <c r="B39" s="43"/>
       <c r="C39" s="43"/>
@@ -12660,7 +15081,7 @@
       <c r="J39" s="43"/>
       <c r="K39" s="43"/>
     </row>
-    <row r="40" spans="1:11" ht="72" thickBot="1">
+    <row r="40" spans="1:11" ht="57.75" thickBot="1">
       <c r="A40" s="49" t="s">
         <v>885</v>
       </c>
@@ -12685,7 +15106,7 @@
       <c r="J40" s="49"/>
       <c r="K40" s="49"/>
     </row>
-    <row r="41" spans="1:11" ht="72" thickBot="1">
+    <row r="41" spans="1:11" ht="57.75" thickBot="1">
       <c r="A41" s="43" t="s">
         <v>889</v>
       </c>
@@ -12748,7 +15169,7 @@
       <c r="J43" s="43"/>
       <c r="K43" s="43"/>
     </row>
-    <row r="44" spans="1:11" ht="57.75" thickBot="1">
+    <row r="44" spans="1:11" ht="43.5" thickBot="1">
       <c r="A44" s="44"/>
       <c r="B44" s="44"/>
       <c r="C44" s="44"/>
@@ -12763,7 +15184,7 @@
       <c r="J44" s="44"/>
       <c r="K44" s="44"/>
     </row>
-    <row r="45" spans="1:11" ht="171.75" thickBot="1">
+    <row r="45" spans="1:11" ht="100.5" thickBot="1">
       <c r="A45" s="43" t="s">
         <v>895</v>
       </c>
@@ -12788,7 +15209,7 @@
       <c r="J45" s="43"/>
       <c r="K45" s="43"/>
     </row>
-    <row r="46" spans="1:11" ht="72" thickBot="1">
+    <row r="46" spans="1:11" ht="57.75" thickBot="1">
       <c r="A46" s="49" t="s">
         <v>900</v>
       </c>
@@ -12813,7 +15234,7 @@
       <c r="J46" s="49"/>
       <c r="K46" s="49"/>
     </row>
-    <row r="47" spans="1:11" ht="99.75">
+    <row r="47" spans="1:11" ht="71.25">
       <c r="A47" s="51" t="s">
         <v>905</v>
       </c>
@@ -12851,7 +15272,7 @@
       <c r="J48" s="43"/>
       <c r="K48" s="43"/>
     </row>
-    <row r="49" spans="1:11" ht="86.25" thickBot="1">
+    <row r="49" spans="1:11" ht="43.5" thickBot="1">
       <c r="A49" s="44"/>
       <c r="B49" s="44"/>
       <c r="C49" s="44"/>
@@ -12939,7 +15360,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="85.5">
+    <row r="8" spans="1:11" ht="57">
       <c r="A8" s="51" t="s">
         <v>907</v>
       </c>
@@ -12977,7 +15398,7 @@
       <c r="J9" s="43"/>
       <c r="K9" s="43"/>
     </row>
-    <row r="10" spans="1:11" ht="57.75" thickBot="1">
+    <row r="10" spans="1:11" ht="29.25" thickBot="1">
       <c r="A10" s="44"/>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -12992,7 +15413,7 @@
       <c r="J10" s="44"/>
       <c r="K10" s="44"/>
     </row>
-    <row r="11" spans="1:11" ht="85.5">
+    <row r="11" spans="1:11" ht="57">
       <c r="A11" s="43" t="s">
         <v>913</v>
       </c>
@@ -13045,7 +15466,7 @@
       <c r="J13" s="43"/>
       <c r="K13" s="43"/>
     </row>
-    <row r="14" spans="1:11" ht="57">
+    <row r="14" spans="1:11" ht="42.75">
       <c r="A14" s="51" t="s">
         <v>918</v>
       </c>
@@ -13083,7 +15504,7 @@
       <c r="J15" s="43"/>
       <c r="K15" s="43"/>
     </row>
-    <row r="16" spans="1:11" ht="57.75" thickBot="1">
+    <row r="16" spans="1:11" ht="29.25" thickBot="1">
       <c r="A16" s="44"/>
       <c r="B16" s="44"/>
       <c r="C16" s="44"/>
@@ -13098,7 +15519,7 @@
       <c r="J16" s="44"/>
       <c r="K16" s="44"/>
     </row>
-    <row r="17" spans="1:11" ht="71.25">
+    <row r="17" spans="1:11" ht="42.75">
       <c r="A17" s="43" t="s">
         <v>922</v>
       </c>
@@ -13136,7 +15557,7 @@
       <c r="J18" s="43"/>
       <c r="K18" s="43"/>
     </row>
-    <row r="19" spans="1:11" ht="57.75" thickBot="1">
+    <row r="19" spans="1:11" ht="29.25" thickBot="1">
       <c r="A19" s="43"/>
       <c r="B19" s="43"/>
       <c r="C19" s="43"/>
@@ -13151,7 +15572,7 @@
       <c r="J19" s="43"/>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="1:11" ht="143.25" thickBot="1">
+    <row r="20" spans="1:11" ht="72" thickBot="1">
       <c r="A20" s="49" t="s">
         <v>925</v>
       </c>
@@ -13176,7 +15597,7 @@
       <c r="J20" s="49"/>
       <c r="K20" s="49"/>
     </row>
-    <row r="21" spans="1:11" ht="100.5" thickBot="1">
+    <row r="21" spans="1:11" ht="57.75" thickBot="1">
       <c r="A21" s="43" t="s">
         <v>930</v>
       </c>
@@ -13201,7 +15622,7 @@
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
     </row>
-    <row r="22" spans="1:11" ht="86.25" thickBot="1">
+    <row r="22" spans="1:11" ht="43.5" thickBot="1">
       <c r="A22" s="49" t="s">
         <v>935</v>
       </c>
@@ -13264,7 +15685,7 @@
       <c r="J24" s="43"/>
       <c r="K24" s="43"/>
     </row>
-    <row r="25" spans="1:11" ht="57.75" thickBot="1">
+    <row r="25" spans="1:11" ht="29.25" thickBot="1">
       <c r="A25" s="43"/>
       <c r="B25" s="43"/>
       <c r="C25" s="43"/>
@@ -13279,7 +15700,7 @@
       <c r="J25" s="43"/>
       <c r="K25" s="43"/>
     </row>
-    <row r="26" spans="1:11" ht="85.5">
+    <row r="26" spans="1:11" ht="42.75">
       <c r="A26" s="51" t="s">
         <v>946</v>
       </c>
@@ -13317,7 +15738,7 @@
       <c r="J27" s="43"/>
       <c r="K27" s="43"/>
     </row>
-    <row r="28" spans="1:11" ht="57.75" thickBot="1">
+    <row r="28" spans="1:11" ht="29.25" thickBot="1">
       <c r="A28" s="44"/>
       <c r="B28" s="44"/>
       <c r="C28" s="44"/>
@@ -13332,7 +15753,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44"/>
     </row>
-    <row r="29" spans="1:11" ht="114.75" thickBot="1">
+    <row r="29" spans="1:11" ht="72" thickBot="1">
       <c r="A29" s="43" t="s">
         <v>952</v>
       </c>
@@ -13357,7 +15778,7 @@
       <c r="J29" s="43"/>
       <c r="K29" s="43"/>
     </row>
-    <row r="30" spans="1:11" ht="114.75" thickBot="1">
+    <row r="30" spans="1:11" ht="72" thickBot="1">
       <c r="A30" s="49" t="s">
         <v>957</v>
       </c>
@@ -13382,7 +15803,7 @@
       <c r="J30" s="49"/>
       <c r="K30" s="49"/>
     </row>
-    <row r="31" spans="1:11" ht="129" thickBot="1">
+    <row r="31" spans="1:11" ht="57.75" thickBot="1">
       <c r="A31" s="43" t="s">
         <v>962</v>
       </c>
@@ -13407,7 +15828,7 @@
       <c r="J31" s="43"/>
       <c r="K31" s="43"/>
     </row>
-    <row r="32" spans="1:11" ht="99.75">
+    <row r="32" spans="1:11" ht="71.25">
       <c r="A32" s="51" t="s">
         <v>967</v>
       </c>
@@ -13445,7 +15866,7 @@
       <c r="J33" s="43"/>
       <c r="K33" s="43"/>
     </row>
-    <row r="34" spans="1:11" ht="43.5" thickBot="1">
+    <row r="34" spans="1:11" ht="29.25" thickBot="1">
       <c r="A34" s="44"/>
       <c r="B34" s="44"/>
       <c r="C34" s="44"/>
@@ -13460,7 +15881,7 @@
       <c r="J34" s="44"/>
       <c r="K34" s="44"/>
     </row>
-    <row r="35" spans="1:11" ht="114.75" thickBot="1">
+    <row r="35" spans="1:11" ht="57.75" thickBot="1">
       <c r="A35" s="43" t="s">
         <v>973</v>
       </c>
@@ -13485,7 +15906,7 @@
       <c r="J35" s="43"/>
       <c r="K35" s="43"/>
     </row>
-    <row r="36" spans="1:11" ht="85.5">
+    <row r="36" spans="1:11" ht="57">
       <c r="A36" s="51" t="s">
         <v>978</v>
       </c>
@@ -13523,7 +15944,7 @@
       <c r="J37" s="43"/>
       <c r="K37" s="43"/>
     </row>
-    <row r="38" spans="1:11" ht="72" thickBot="1">
+    <row r="38" spans="1:11" ht="29.25" thickBot="1">
       <c r="A38" s="44"/>
       <c r="B38" s="44"/>
       <c r="C38" s="44"/>
@@ -13538,7 +15959,7 @@
       <c r="J38" s="44"/>
       <c r="K38" s="44"/>
     </row>
-    <row r="39" spans="1:11" ht="100.5" thickBot="1">
+    <row r="39" spans="1:11" ht="57.75" thickBot="1">
       <c r="A39" s="43" t="s">
         <v>984</v>
       </c>
@@ -13563,7 +15984,7 @@
       <c r="J39" s="43"/>
       <c r="K39" s="43"/>
     </row>
-    <row r="40" spans="1:11" ht="114.75" thickBot="1">
+    <row r="40" spans="1:11" ht="72" thickBot="1">
       <c r="A40" s="49" t="s">
         <v>989</v>
       </c>
@@ -13588,7 +16009,7 @@
       <c r="J40" s="49"/>
       <c r="K40" s="49"/>
     </row>
-    <row r="41" spans="1:11" ht="114.75" thickBot="1">
+    <row r="41" spans="1:11" ht="57.75" thickBot="1">
       <c r="A41" s="43" t="s">
         <v>993</v>
       </c>
@@ -13613,7 +16034,7 @@
       <c r="J41" s="43"/>
       <c r="K41" s="43"/>
     </row>
-    <row r="42" spans="1:11" ht="86.25" thickBot="1">
+    <row r="42" spans="1:11" ht="43.5" thickBot="1">
       <c r="A42" s="49" t="s">
         <v>997</v>
       </c>
@@ -13638,7 +16059,7 @@
       <c r="J42" s="49"/>
       <c r="K42" s="49"/>
     </row>
-    <row r="43" spans="1:11" ht="100.5" thickBot="1">
+    <row r="43" spans="1:11" ht="43.5" thickBot="1">
       <c r="A43" s="43" t="s">
         <v>1000</v>
       </c>
@@ -13663,7 +16084,7 @@
       <c r="J43" s="43"/>
       <c r="K43" s="43"/>
     </row>
-    <row r="44" spans="1:11" ht="114.75" thickBot="1">
+    <row r="44" spans="1:11" ht="86.25" thickBot="1">
       <c r="A44" s="49" t="s">
         <v>1002</v>
       </c>
@@ -13688,7 +16109,7 @@
       <c r="J44" s="49"/>
       <c r="K44" s="49"/>
     </row>
-    <row r="45" spans="1:11" ht="100.5" thickBot="1">
+    <row r="45" spans="1:11" ht="57.75" thickBot="1">
       <c r="A45" s="43" t="s">
         <v>1006</v>
       </c>
@@ -13713,7 +16134,7 @@
       <c r="J45" s="43"/>
       <c r="K45" s="43"/>
     </row>
-    <row r="46" spans="1:11" ht="71.25">
+    <row r="46" spans="1:11" ht="57">
       <c r="A46" s="51" t="s">
         <v>1011</v>
       </c>
@@ -13751,7 +16172,7 @@
       <c r="J47" s="43"/>
       <c r="K47" s="43"/>
     </row>
-    <row r="48" spans="1:11" ht="71.25">
+    <row r="48" spans="1:11" ht="42.75">
       <c r="A48" s="43"/>
       <c r="B48" s="43"/>
       <c r="C48" s="43"/>
@@ -13779,7 +16200,7 @@
       <c r="J49" s="43"/>
       <c r="K49" s="43"/>
     </row>
-    <row r="50" spans="1:11" ht="43.5" thickBot="1">
+    <row r="50" spans="1:11" ht="29.25" thickBot="1">
       <c r="A50" s="44"/>
       <c r="B50" s="44"/>
       <c r="C50" s="44"/>
@@ -13794,7 +16215,7 @@
       <c r="J50" s="44"/>
       <c r="K50" s="44"/>
     </row>
-    <row r="51" spans="1:11" ht="114">
+    <row r="51" spans="1:11" ht="71.25">
       <c r="A51" s="51" t="s">
         <v>1018</v>
       </c>
@@ -13832,7 +16253,7 @@
       <c r="J52" s="43"/>
       <c r="K52" s="43"/>
     </row>
-    <row r="53" spans="1:11" ht="42.75">
+    <row r="53" spans="1:11" ht="28.5">
       <c r="A53" s="43"/>
       <c r="B53" s="43"/>
       <c r="C53" s="43"/>
@@ -13860,7 +16281,7 @@
       <c r="J54" s="43"/>
       <c r="K54" s="43"/>
     </row>
-    <row r="55" spans="1:11" ht="43.5" thickBot="1">
+    <row r="55" spans="1:11" ht="29.25" thickBot="1">
       <c r="A55" s="44"/>
       <c r="B55" s="44"/>
       <c r="C55" s="44"/>
@@ -13913,7 +16334,7 @@
       </c>
       <c r="B2" s="29"/>
     </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+    <row r="7" spans="1:11" ht="30.75" thickBot="1">
       <c r="A7" s="7" t="s">
         <v>99</v>
       </c>
@@ -13948,7 +16369,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="72" thickBot="1">
+    <row r="8" spans="1:11" ht="43.5" thickBot="1">
       <c r="A8" s="49" t="s">
         <v>1024</v>
       </c>
@@ -14011,7 +16432,7 @@
       <c r="J10" s="43"/>
       <c r="K10" s="43"/>
     </row>
-    <row r="11" spans="1:11" ht="72" thickBot="1">
+    <row r="11" spans="1:11" ht="43.5" thickBot="1">
       <c r="A11" s="43"/>
       <c r="B11" s="43"/>
       <c r="C11" s="43"/>
@@ -14026,7 +16447,7 @@
       <c r="J11" s="43"/>
       <c r="K11" s="43"/>
     </row>
-    <row r="12" spans="1:11" ht="86.25" thickBot="1">
+    <row r="12" spans="1:11" ht="43.5" thickBot="1">
       <c r="A12" s="49" t="s">
         <v>1035</v>
       </c>
@@ -14051,7 +16472,7 @@
       <c r="J12" s="49"/>
       <c r="K12" s="49"/>
     </row>
-    <row r="13" spans="1:11" ht="86.25" thickBot="1">
+    <row r="13" spans="1:11" ht="43.5" thickBot="1">
       <c r="A13" s="43" t="s">
         <v>1039</v>
       </c>
@@ -14076,7 +16497,7 @@
       <c r="J13" s="43"/>
       <c r="K13" s="43"/>
     </row>
-    <row r="14" spans="1:11" ht="99.75">
+    <row r="14" spans="1:11" ht="42.75">
       <c r="A14" s="51" t="s">
         <v>1043</v>
       </c>
@@ -14114,7 +16535,7 @@
       <c r="J15" s="43"/>
       <c r="K15" s="43"/>
     </row>
-    <row r="16" spans="1:11" ht="29.25" thickBot="1">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1">
       <c r="A16" s="44"/>
       <c r="B16" s="44"/>
       <c r="C16" s="44"/>
@@ -14129,7 +16550,7 @@
       <c r="J16" s="44"/>
       <c r="K16" s="44"/>
     </row>
-    <row r="17" spans="1:11" ht="114.75" thickBot="1">
+    <row r="17" spans="1:11" ht="57.75" thickBot="1">
       <c r="A17" s="43" t="s">
         <v>1049</v>
       </c>
@@ -14154,7 +16575,7 @@
       <c r="J17" s="43"/>
       <c r="K17" s="43"/>
     </row>
-    <row r="18" spans="1:11" ht="85.5">
+    <row r="18" spans="1:11" ht="42.75">
       <c r="A18" s="51" t="s">
         <v>1054</v>
       </c>
@@ -14192,7 +16613,7 @@
       <c r="J19" s="43"/>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="1:11" ht="57.75" thickBot="1">
+    <row r="20" spans="1:11" ht="29.25" thickBot="1">
       <c r="A20" s="44"/>
       <c r="B20" s="44"/>
       <c r="C20" s="44"/>
@@ -14207,7 +16628,7 @@
       <c r="J20" s="44"/>
       <c r="K20" s="44"/>
     </row>
-    <row r="21" spans="1:11" ht="86.25" thickBot="1">
+    <row r="21" spans="1:11" ht="43.5" thickBot="1">
       <c r="A21" s="43" t="s">
         <v>1059</v>
       </c>
@@ -14232,7 +16653,7 @@
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
     </row>
-    <row r="22" spans="1:11" ht="72" thickBot="1">
+    <row r="22" spans="1:11" ht="43.5" thickBot="1">
       <c r="A22" s="49" t="s">
         <v>1063</v>
       </c>
@@ -14257,7 +16678,7 @@
       <c r="J22" s="49"/>
       <c r="K22" s="49"/>
     </row>
-    <row r="23" spans="1:11" ht="72" thickBot="1">
+    <row r="23" spans="1:11" ht="29.25" thickBot="1">
       <c r="A23" s="43" t="s">
         <v>1068</v>
       </c>
@@ -14282,7 +16703,7 @@
       <c r="J23" s="43"/>
       <c r="K23" s="43"/>
     </row>
-    <row r="24" spans="1:11" ht="72" thickBot="1">
+    <row r="24" spans="1:11" ht="29.25" thickBot="1">
       <c r="A24" s="49" t="s">
         <v>1073</v>
       </c>
@@ -14307,7 +16728,7 @@
       <c r="J24" s="49"/>
       <c r="K24" s="49"/>
     </row>
-    <row r="25" spans="1:11" ht="72" thickBot="1">
+    <row r="25" spans="1:11" ht="29.25" thickBot="1">
       <c r="A25" s="43" t="s">
         <v>1077</v>
       </c>
@@ -14332,7 +16753,7 @@
       <c r="J25" s="43"/>
       <c r="K25" s="43"/>
     </row>
-    <row r="26" spans="1:11" ht="129" thickBot="1">
+    <row r="26" spans="1:11" ht="57.75" thickBot="1">
       <c r="A26" s="49" t="s">
         <v>1081</v>
       </c>
@@ -14357,7 +16778,7 @@
       <c r="J26" s="49"/>
       <c r="K26" s="49"/>
     </row>
-    <row r="27" spans="1:11" ht="86.25" thickBot="1">
+    <row r="27" spans="1:11" ht="43.5" thickBot="1">
       <c r="A27" s="43" t="s">
         <v>1085</v>
       </c>
@@ -14382,7 +16803,7 @@
       <c r="J27" s="43"/>
       <c r="K27" s="43"/>
     </row>
-    <row r="28" spans="1:11" ht="72" thickBot="1">
+    <row r="28" spans="1:11" ht="43.5" thickBot="1">
       <c r="A28" s="49" t="s">
         <v>1090</v>
       </c>
@@ -14407,7 +16828,7 @@
       <c r="J28" s="49"/>
       <c r="K28" s="49"/>
     </row>
-    <row r="29" spans="1:11" ht="86.25" thickBot="1">
+    <row r="29" spans="1:11" ht="43.5" thickBot="1">
       <c r="A29" s="43" t="s">
         <v>1095</v>
       </c>
@@ -14432,7 +16853,7 @@
       <c r="J29" s="43"/>
       <c r="K29" s="43"/>
     </row>
-    <row r="30" spans="1:11" ht="86.25" thickBot="1">
+    <row r="30" spans="1:11" ht="43.5" thickBot="1">
       <c r="A30" s="49" t="s">
         <v>1100</v>
       </c>
@@ -14457,7 +16878,7 @@
       <c r="J30" s="49"/>
       <c r="K30" s="49"/>
     </row>
-    <row r="31" spans="1:11" ht="86.25" thickBot="1">
+    <row r="31" spans="1:11" ht="43.5" thickBot="1">
       <c r="A31" s="43" t="s">
         <v>1105</v>
       </c>
@@ -14482,7 +16903,7 @@
       <c r="J31" s="43"/>
       <c r="K31" s="43"/>
     </row>
-    <row r="32" spans="1:11" ht="100.5" thickBot="1">
+    <row r="32" spans="1:11" ht="43.5" thickBot="1">
       <c r="A32" s="49" t="s">
         <v>1110</v>
       </c>
@@ -14507,7 +16928,7 @@
       <c r="J32" s="49"/>
       <c r="K32" s="49"/>
     </row>
-    <row r="33" spans="1:11" ht="100.5" thickBot="1">
+    <row r="33" spans="1:11" ht="57.75" thickBot="1">
       <c r="A33" s="43" t="s">
         <v>1115</v>
       </c>
@@ -14532,7 +16953,7 @@
       <c r="J33" s="43"/>
       <c r="K33" s="43"/>
     </row>
-    <row r="34" spans="1:11" ht="71.25">
+    <row r="34" spans="1:11" ht="42.75">
       <c r="A34" s="51" t="s">
         <v>1120</v>
       </c>
@@ -14570,7 +16991,7 @@
       <c r="J35" s="43"/>
       <c r="K35" s="43"/>
     </row>
-    <row r="36" spans="1:11" ht="57.75" thickBot="1">
+    <row r="36" spans="1:11" ht="29.25" thickBot="1">
       <c r="A36" s="44"/>
       <c r="B36" s="44"/>
       <c r="C36" s="44"/>
@@ -14585,7 +17006,7 @@
       <c r="J36" s="44"/>
       <c r="K36" s="44"/>
     </row>
-    <row r="37" spans="1:11" ht="72" thickBot="1">
+    <row r="37" spans="1:11" ht="43.5" thickBot="1">
       <c r="A37" s="43" t="s">
         <v>1126</v>
       </c>
@@ -14610,7 +17031,7 @@
       <c r="J37" s="43"/>
       <c r="K37" s="43"/>
     </row>
-    <row r="38" spans="1:11" ht="71.25">
+    <row r="38" spans="1:11" ht="42.75">
       <c r="A38" s="51" t="s">
         <v>1131</v>
       </c>
@@ -14648,7 +17069,7 @@
       <c r="J39" s="43"/>
       <c r="K39" s="43"/>
     </row>
-    <row r="40" spans="1:11" ht="29.25" thickBot="1">
+    <row r="40" spans="1:11" ht="15.75" thickBot="1">
       <c r="A40" s="44"/>
       <c r="B40" s="44"/>
       <c r="C40" s="44"/>
@@ -14663,7 +17084,7 @@
       <c r="J40" s="44"/>
       <c r="K40" s="44"/>
     </row>
-    <row r="41" spans="1:11" ht="100.5" thickBot="1">
+    <row r="41" spans="1:11" ht="57.75" thickBot="1">
       <c r="A41" s="43" t="s">
         <v>1137</v>
       </c>
@@ -14688,7 +17109,7 @@
       <c r="J41" s="43"/>
       <c r="K41" s="43"/>
     </row>
-    <row r="42" spans="1:11" ht="72" thickBot="1">
+    <row r="42" spans="1:11" ht="29.25" thickBot="1">
       <c r="A42" s="49" t="s">
         <v>1142</v>
       </c>
@@ -14713,7 +17134,7 @@
       <c r="J42" s="49"/>
       <c r="K42" s="49"/>
     </row>
-    <row r="43" spans="1:11" ht="57">
+    <row r="43" spans="1:11" ht="28.5">
       <c r="A43" s="43" t="s">
         <v>1147</v>
       </c>
@@ -14751,7 +17172,7 @@
       <c r="J44" s="43"/>
       <c r="K44" s="43"/>
     </row>
-    <row r="45" spans="1:11" ht="29.25" thickBot="1">
+    <row r="45" spans="1:11" ht="15.75" thickBot="1">
       <c r="A45" s="43"/>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -14804,7 +17225,7 @@
       <c r="J47" s="43"/>
       <c r="K47" s="43"/>
     </row>
-    <row r="48" spans="1:11" ht="29.25" thickBot="1">
+    <row r="48" spans="1:11" ht="15.75" thickBot="1">
       <c r="A48" s="44"/>
       <c r="B48" s="44"/>
       <c r="C48" s="44"/>
@@ -14857,7 +17278,7 @@
       <c r="J50" s="43"/>
       <c r="K50" s="43"/>
     </row>
-    <row r="51" spans="1:11" ht="29.25" thickBot="1">
+    <row r="51" spans="1:11" ht="15.75" thickBot="1">
       <c r="A51" s="43"/>
       <c r="B51" s="43"/>
       <c r="C51" s="43"/>
@@ -14872,7 +17293,7 @@
       <c r="J51" s="43"/>
       <c r="K51" s="43"/>
     </row>
-    <row r="52" spans="1:11" ht="71.25">
+    <row r="52" spans="1:11" ht="42.75">
       <c r="A52" s="51" t="s">
         <v>1160</v>
       </c>
@@ -14910,7 +17331,7 @@
       <c r="J53" s="43"/>
       <c r="K53" s="43"/>
     </row>
-    <row r="54" spans="1:11" ht="57.75" thickBot="1">
+    <row r="54" spans="1:11" ht="29.25" thickBot="1">
       <c r="A54" s="44"/>
       <c r="B54" s="44"/>
       <c r="C54" s="44"/>
@@ -14925,7 +17346,7 @@
       <c r="J54" s="44"/>
       <c r="K54" s="44"/>
     </row>
-    <row r="55" spans="1:11" ht="72" thickBot="1">
+    <row r="55" spans="1:11" ht="43.5" thickBot="1">
       <c r="A55" s="43" t="s">
         <v>1165</v>
       </c>
@@ -14950,7 +17371,7 @@
       <c r="J55" s="43"/>
       <c r="K55" s="43"/>
     </row>
-    <row r="56" spans="1:11" ht="57.75" thickBot="1">
+    <row r="56" spans="1:11" ht="43.5" thickBot="1">
       <c r="A56" s="49" t="s">
         <v>1170</v>
       </c>
@@ -14975,7 +17396,7 @@
       <c r="J56" s="49"/>
       <c r="K56" s="49"/>
     </row>
-    <row r="57" spans="1:11" ht="86.25" thickBot="1">
+    <row r="57" spans="1:11" ht="43.5" thickBot="1">
       <c r="A57" s="43" t="s">
         <v>1175</v>
       </c>
@@ -15000,7 +17421,7 @@
       <c r="J57" s="43"/>
       <c r="K57" s="43"/>
     </row>
-    <row r="58" spans="1:11" ht="86.25" thickBot="1">
+    <row r="58" spans="1:11" ht="43.5" thickBot="1">
       <c r="A58" s="49" t="s">
         <v>1179</v>
       </c>
@@ -15025,7 +17446,7 @@
       <c r="J58" s="49"/>
       <c r="K58" s="49"/>
     </row>
-    <row r="59" spans="1:11" ht="86.25" thickBot="1">
+    <row r="59" spans="1:11" ht="43.5" thickBot="1">
       <c r="A59" s="43" t="s">
         <v>1183</v>
       </c>
@@ -15050,7 +17471,7 @@
       <c r="J59" s="43"/>
       <c r="K59" s="43"/>
     </row>
-    <row r="60" spans="1:11" ht="72" thickBot="1">
+    <row r="60" spans="1:11" ht="43.5" thickBot="1">
       <c r="A60" s="49" t="s">
         <v>1188</v>
       </c>
@@ -15075,7 +17496,7 @@
       <c r="J60" s="49"/>
       <c r="K60" s="49"/>
     </row>
-    <row r="61" spans="1:11" ht="57.75" thickBot="1">
+    <row r="61" spans="1:11" ht="29.25" thickBot="1">
       <c r="A61" s="43" t="s">
         <v>1193</v>
       </c>
@@ -15100,7 +17521,7 @@
       <c r="J61" s="43"/>
       <c r="K61" s="43"/>
     </row>
-    <row r="62" spans="1:11" ht="72" thickBot="1">
+    <row r="62" spans="1:11" ht="29.25" thickBot="1">
       <c r="A62" s="49" t="s">
         <v>1198</v>
       </c>
@@ -15236,7 +17657,7 @@
       <c r="J9" s="43"/>
       <c r="K9" s="43"/>
     </row>
-    <row r="10" spans="1:11" ht="57.75" thickBot="1">
+    <row r="10" spans="1:11" ht="29.25" thickBot="1">
       <c r="A10" s="44"/>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -15251,7 +17672,7 @@
       <c r="J10" s="44"/>
       <c r="K10" s="44"/>
     </row>
-    <row r="11" spans="1:11" ht="128.25">
+    <row r="11" spans="1:11" ht="57">
       <c r="A11" s="43" t="s">
         <v>1208</v>
       </c>
@@ -15289,7 +17710,7 @@
       <c r="J12" s="43"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:11" ht="85.5">
+    <row r="13" spans="1:11" ht="28.5">
       <c r="A13" s="43"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43"/>
@@ -15317,7 +17738,7 @@
       <c r="J14" s="43"/>
       <c r="K14" s="43"/>
     </row>
-    <row r="15" spans="1:11" ht="42.75">
+    <row r="15" spans="1:11">
       <c r="A15" s="43"/>
       <c r="B15" s="43"/>
       <c r="C15" s="43"/>
@@ -15345,7 +17766,7 @@
       <c r="J16" s="43"/>
       <c r="K16" s="43"/>
     </row>
-    <row r="17" spans="1:11" ht="29.25" thickBot="1">
+    <row r="17" spans="1:11" ht="15.75" thickBot="1">
       <c r="A17" s="43"/>
       <c r="B17" s="43"/>
       <c r="C17" s="43"/>
@@ -15360,7 +17781,7 @@
       <c r="J17" s="43"/>
       <c r="K17" s="43"/>
     </row>
-    <row r="18" spans="1:11" ht="85.5">
+    <row r="18" spans="1:11" ht="42.75">
       <c r="A18" s="51" t="s">
         <v>1216</v>
       </c>
@@ -15398,7 +17819,7 @@
       <c r="J19" s="43"/>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="1:11" ht="57">
+    <row r="20" spans="1:11" ht="28.5">
       <c r="A20" s="43"/>
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
@@ -15426,7 +17847,7 @@
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
     </row>
-    <row r="22" spans="1:11" ht="29.25" thickBot="1">
+    <row r="22" spans="1:11" ht="15.75" thickBot="1">
       <c r="A22" s="44"/>
       <c r="B22" s="44"/>
       <c r="C22" s="44"/>
@@ -15441,7 +17862,7 @@
       <c r="J22" s="44"/>
       <c r="K22" s="44"/>
     </row>
-    <row r="23" spans="1:11" ht="85.5">
+    <row r="23" spans="1:11" ht="42.75">
       <c r="A23" s="43" t="s">
         <v>1222</v>
       </c>
@@ -15479,7 +17900,7 @@
       <c r="J24" s="43"/>
       <c r="K24" s="43"/>
     </row>
-    <row r="25" spans="1:11" ht="57">
+    <row r="25" spans="1:11" ht="28.5">
       <c r="A25" s="43"/>
       <c r="B25" s="43"/>
       <c r="C25" s="43"/>
@@ -15507,7 +17928,7 @@
       <c r="J26" s="43"/>
       <c r="K26" s="43"/>
     </row>
-    <row r="27" spans="1:11" ht="29.25" thickBot="1">
+    <row r="27" spans="1:11" ht="15.75" thickBot="1">
       <c r="A27" s="43"/>
       <c r="B27" s="43"/>
       <c r="C27" s="43"/>
@@ -15522,7 +17943,7 @@
       <c r="J27" s="43"/>
       <c r="K27" s="43"/>
     </row>
-    <row r="28" spans="1:11" ht="85.5">
+    <row r="28" spans="1:11" ht="42.75">
       <c r="A28" s="51" t="s">
         <v>1225</v>
       </c>
@@ -15560,7 +17981,7 @@
       <c r="J29" s="43"/>
       <c r="K29" s="43"/>
     </row>
-    <row r="30" spans="1:11" ht="57">
+    <row r="30" spans="1:11" ht="28.5">
       <c r="A30" s="43"/>
       <c r="B30" s="43"/>
       <c r="C30" s="43"/>
@@ -15588,7 +18009,7 @@
       <c r="J31" s="43"/>
       <c r="K31" s="43"/>
     </row>
-    <row r="32" spans="1:11" ht="29.25" thickBot="1">
+    <row r="32" spans="1:11" ht="15.75" thickBot="1">
       <c r="A32" s="44"/>
       <c r="B32" s="44"/>
       <c r="C32" s="44"/>
@@ -15603,7 +18024,7 @@
       <c r="J32" s="44"/>
       <c r="K32" s="44"/>
     </row>
-    <row r="33" spans="1:11" ht="85.5">
+    <row r="33" spans="1:11" ht="42.75">
       <c r="A33" s="43" t="s">
         <v>1228</v>
       </c>
@@ -15641,7 +18062,7 @@
       <c r="J34" s="43"/>
       <c r="K34" s="43"/>
     </row>
-    <row r="35" spans="1:11" ht="57">
+    <row r="35" spans="1:11" ht="28.5">
       <c r="A35" s="43"/>
       <c r="B35" s="43"/>
       <c r="C35" s="43"/>
@@ -15669,7 +18090,7 @@
       <c r="J36" s="43"/>
       <c r="K36" s="43"/>
     </row>
-    <row r="37" spans="1:11" ht="28.5">
+    <row r="37" spans="1:11">
       <c r="A37" s="43"/>
       <c r="B37" s="43"/>
       <c r="C37" s="43"/>
@@ -15697,7 +18118,7 @@
       <c r="J38" s="43"/>
       <c r="K38" s="43"/>
     </row>
-    <row r="39" spans="1:11" ht="29.25" thickBot="1">
+    <row r="39" spans="1:11" ht="15.75" thickBot="1">
       <c r="A39" s="43"/>
       <c r="B39" s="43"/>
       <c r="C39" s="43"/>
@@ -15712,7 +18133,7 @@
       <c r="J39" s="43"/>
       <c r="K39" s="43"/>
     </row>
-    <row r="40" spans="1:11" ht="85.5">
+    <row r="40" spans="1:11" ht="42.75">
       <c r="A40" s="51" t="s">
         <v>1234</v>
       </c>
@@ -15750,7 +18171,7 @@
       <c r="J41" s="43"/>
       <c r="K41" s="43"/>
     </row>
-    <row r="42" spans="1:11" ht="57">
+    <row r="42" spans="1:11" ht="28.5">
       <c r="A42" s="43"/>
       <c r="B42" s="43"/>
       <c r="C42" s="43"/>
@@ -15778,7 +18199,7 @@
       <c r="J43" s="43"/>
       <c r="K43" s="43"/>
     </row>
-    <row r="44" spans="1:11" ht="28.5">
+    <row r="44" spans="1:11">
       <c r="A44" s="43"/>
       <c r="B44" s="43"/>
       <c r="C44" s="43"/>
@@ -15806,7 +18227,7 @@
       <c r="J45" s="43"/>
       <c r="K45" s="43"/>
     </row>
-    <row r="46" spans="1:11" ht="29.25" thickBot="1">
+    <row r="46" spans="1:11" ht="15.75" thickBot="1">
       <c r="A46" s="44"/>
       <c r="B46" s="44"/>
       <c r="C46" s="44"/>
@@ -15821,7 +18242,7 @@
       <c r="J46" s="44"/>
       <c r="K46" s="44"/>
     </row>
-    <row r="47" spans="1:11" ht="85.5">
+    <row r="47" spans="1:11" ht="42.75">
       <c r="A47" s="43" t="s">
         <v>1237</v>
       </c>
@@ -15859,7 +18280,7 @@
       <c r="J48" s="43"/>
       <c r="K48" s="43"/>
     </row>
-    <row r="49" spans="1:11" ht="71.25">
+    <row r="49" spans="1:11" ht="28.5">
       <c r="A49" s="43"/>
       <c r="B49" s="43"/>
       <c r="C49" s="43"/>
@@ -15887,7 +18308,7 @@
       <c r="J50" s="43"/>
       <c r="K50" s="43"/>
     </row>
-    <row r="51" spans="1:11" ht="28.5">
+    <row r="51" spans="1:11">
       <c r="A51" s="43"/>
       <c r="B51" s="43"/>
       <c r="C51" s="43"/>
@@ -15915,7 +18336,7 @@
       <c r="J52" s="43"/>
       <c r="K52" s="43"/>
     </row>
-    <row r="53" spans="1:11" ht="29.25" thickBot="1">
+    <row r="53" spans="1:11" ht="15.75" thickBot="1">
       <c r="A53" s="43"/>
       <c r="B53" s="43"/>
       <c r="C53" s="43"/>
@@ -15930,7 +18351,7 @@
       <c r="J53" s="43"/>
       <c r="K53" s="43"/>
     </row>
-    <row r="54" spans="1:11" ht="57">
+    <row r="54" spans="1:11" ht="28.5">
       <c r="A54" s="51" t="s">
         <v>1240</v>
       </c>
@@ -15968,7 +18389,7 @@
       <c r="J55" s="43"/>
       <c r="K55" s="43"/>
     </row>
-    <row r="56" spans="1:11" ht="57">
+    <row r="56" spans="1:11" ht="28.5">
       <c r="A56" s="43"/>
       <c r="B56" s="43"/>
       <c r="C56" s="43"/>
@@ -15996,7 +18417,7 @@
       <c r="J57" s="43"/>
       <c r="K57" s="43"/>
     </row>
-    <row r="58" spans="1:11" ht="57">
+    <row r="58" spans="1:11" ht="28.5">
       <c r="A58" s="43"/>
       <c r="B58" s="43"/>
       <c r="C58" s="43"/>
@@ -16024,7 +18445,7 @@
       <c r="J59" s="43"/>
       <c r="K59" s="43"/>
     </row>
-    <row r="60" spans="1:11" ht="29.25" thickBot="1">
+    <row r="60" spans="1:11" ht="15.75" thickBot="1">
       <c r="A60" s="44"/>
       <c r="B60" s="44"/>
       <c r="C60" s="44"/>
@@ -16039,7 +18460,7 @@
       <c r="J60" s="44"/>
       <c r="K60" s="44"/>
     </row>
-    <row r="61" spans="1:11" ht="85.5">
+    <row r="61" spans="1:11" ht="42.75">
       <c r="A61" s="43" t="s">
         <v>1245</v>
       </c>
@@ -16077,7 +18498,7 @@
       <c r="J62" s="43"/>
       <c r="K62" s="43"/>
     </row>
-    <row r="63" spans="1:11" ht="57">
+    <row r="63" spans="1:11" ht="28.5">
       <c r="A63" s="43"/>
       <c r="B63" s="43"/>
       <c r="C63" s="43"/>
@@ -16105,7 +18526,7 @@
       <c r="J64" s="43"/>
       <c r="K64" s="43"/>
     </row>
-    <row r="65" spans="1:11" ht="29.25" thickBot="1">
+    <row r="65" spans="1:11" ht="15.75" thickBot="1">
       <c r="A65" s="43"/>
       <c r="B65" s="43"/>
       <c r="C65" s="43"/>
@@ -16120,7 +18541,7 @@
       <c r="J65" s="43"/>
       <c r="K65" s="43"/>
     </row>
-    <row r="66" spans="1:11" ht="85.5">
+    <row r="66" spans="1:11" ht="42.75">
       <c r="A66" s="51" t="s">
         <v>1251</v>
       </c>
@@ -16158,7 +18579,7 @@
       <c r="J67" s="43"/>
       <c r="K67" s="43"/>
     </row>
-    <row r="68" spans="1:11" ht="85.5">
+    <row r="68" spans="1:11" ht="28.5">
       <c r="A68" s="43"/>
       <c r="B68" s="43"/>
       <c r="C68" s="43"/>
@@ -16186,7 +18607,7 @@
       <c r="J69" s="43"/>
       <c r="K69" s="43"/>
     </row>
-    <row r="70" spans="1:11" ht="29.25" thickBot="1">
+    <row r="70" spans="1:11" ht="15.75" thickBot="1">
       <c r="A70" s="44"/>
       <c r="B70" s="44"/>
       <c r="C70" s="44"/>
@@ -16239,7 +18660,7 @@
       <c r="J72" s="43"/>
       <c r="K72" s="43"/>
     </row>
-    <row r="73" spans="1:11" ht="43.5" thickBot="1">
+    <row r="73" spans="1:11" ht="15.75" thickBot="1">
       <c r="A73" s="43"/>
       <c r="B73" s="43"/>
       <c r="C73" s="43"/>
@@ -16292,7 +18713,7 @@
       <c r="J75" s="43"/>
       <c r="K75" s="43"/>
     </row>
-    <row r="76" spans="1:11" ht="43.5" thickBot="1">
+    <row r="76" spans="1:11" ht="15.75" thickBot="1">
       <c r="A76" s="44"/>
       <c r="B76" s="44"/>
       <c r="C76" s="44"/>
@@ -16307,7 +18728,7 @@
       <c r="J76" s="44"/>
       <c r="K76" s="44"/>
     </row>
-    <row r="77" spans="1:11" ht="99.75">
+    <row r="77" spans="1:11" ht="42.75">
       <c r="A77" s="43" t="s">
         <v>1266</v>
       </c>
@@ -16345,7 +18766,7 @@
       <c r="J78" s="43"/>
       <c r="K78" s="43"/>
     </row>
-    <row r="79" spans="1:11" ht="72" thickBot="1">
+    <row r="79" spans="1:11" ht="29.25" thickBot="1">
       <c r="A79" s="43"/>
       <c r="B79" s="43"/>
       <c r="C79" s="43"/>
@@ -16360,7 +18781,7 @@
       <c r="J79" s="43"/>
       <c r="K79" s="43"/>
     </row>
-    <row r="80" spans="1:11" ht="114">
+    <row r="80" spans="1:11" ht="57">
       <c r="A80" s="51" t="s">
         <v>1272</v>
       </c>
@@ -16398,7 +18819,7 @@
       <c r="J81" s="43"/>
       <c r="K81" s="43"/>
     </row>
-    <row r="82" spans="1:11" ht="42.75">
+    <row r="82" spans="1:11">
       <c r="A82" s="43"/>
       <c r="B82" s="43"/>
       <c r="C82" s="43"/>
@@ -16426,7 +18847,7 @@
       <c r="J83" s="43"/>
       <c r="K83" s="43"/>
     </row>
-    <row r="84" spans="1:11" ht="43.5" thickBot="1">
+    <row r="84" spans="1:11" ht="15.75" thickBot="1">
       <c r="A84" s="44"/>
       <c r="B84" s="44"/>
       <c r="C84" s="44"/>
@@ -16552,7 +18973,7 @@
       <c r="J9" s="43"/>
       <c r="K9" s="43"/>
     </row>
-    <row r="10" spans="1:11" ht="43.5" thickBot="1">
+    <row r="10" spans="1:11" ht="29.25" thickBot="1">
       <c r="A10" s="43"/>
       <c r="B10" s="43"/>
       <c r="C10" s="43"/>
@@ -16605,7 +19026,7 @@
       <c r="J12" s="43"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:11" ht="43.5" thickBot="1">
+    <row r="13" spans="1:11" ht="29.25" thickBot="1">
       <c r="A13" s="44"/>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -16620,7 +19041,7 @@
       <c r="J13" s="44"/>
       <c r="K13" s="44"/>
     </row>
-    <row r="14" spans="1:11" ht="85.5">
+    <row r="14" spans="1:11" ht="57">
       <c r="A14" s="43" t="s">
         <v>1289</v>
       </c>
@@ -16658,7 +19079,7 @@
       <c r="J15" s="43"/>
       <c r="K15" s="43"/>
     </row>
-    <row r="16" spans="1:11" ht="43.5" thickBot="1">
+    <row r="16" spans="1:11" ht="29.25" thickBot="1">
       <c r="A16" s="43"/>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
@@ -16673,7 +19094,7 @@
       <c r="J16" s="43"/>
       <c r="K16" s="43"/>
     </row>
-    <row r="17" spans="1:11" ht="85.5">
+    <row r="17" spans="1:11" ht="57">
       <c r="A17" s="51" t="s">
         <v>1294</v>
       </c>
@@ -16711,7 +19132,7 @@
       <c r="J18" s="43"/>
       <c r="K18" s="43"/>
     </row>
-    <row r="19" spans="1:11" ht="72" thickBot="1">
+    <row r="19" spans="1:11" ht="43.5" thickBot="1">
       <c r="A19" s="44"/>
       <c r="B19" s="44"/>
       <c r="C19" s="44"/>
@@ -16726,7 +19147,7 @@
       <c r="J19" s="44"/>
       <c r="K19" s="44"/>
     </row>
-    <row r="20" spans="1:11" ht="114">
+    <row r="20" spans="1:11" ht="71.25">
       <c r="A20" s="43" t="s">
         <v>1299</v>
       </c>
@@ -16764,7 +19185,7 @@
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
     </row>
-    <row r="22" spans="1:11" ht="72" thickBot="1">
+    <row r="22" spans="1:11" ht="43.5" thickBot="1">
       <c r="A22" s="43"/>
       <c r="B22" s="43"/>
       <c r="C22" s="43"/>
@@ -16779,7 +19200,7 @@
       <c r="J22" s="43"/>
       <c r="K22" s="43"/>
     </row>
-    <row r="23" spans="1:11" ht="129" thickBot="1">
+    <row r="23" spans="1:11" ht="86.25" thickBot="1">
       <c r="A23" s="49" t="s">
         <v>1303</v>
       </c>
@@ -16842,7 +19263,7 @@
       <c r="J25" s="43"/>
       <c r="K25" s="43"/>
     </row>
-    <row r="26" spans="1:11" ht="43.5" thickBot="1">
+    <row r="26" spans="1:11" ht="29.25" thickBot="1">
       <c r="A26" s="43"/>
       <c r="B26" s="43"/>
       <c r="C26" s="43"/>
@@ -16895,7 +19316,7 @@
       <c r="J28" s="43"/>
       <c r="K28" s="43"/>
     </row>
-    <row r="29" spans="1:11" ht="43.5" thickBot="1">
+    <row r="29" spans="1:11" ht="29.25" thickBot="1">
       <c r="A29" s="44"/>
       <c r="B29" s="44"/>
       <c r="C29" s="44"/>
@@ -16910,7 +19331,7 @@
       <c r="J29" s="44"/>
       <c r="K29" s="44"/>
     </row>
-    <row r="30" spans="1:11" ht="114">
+    <row r="30" spans="1:11" ht="71.25">
       <c r="A30" s="51" t="s">
         <v>1319</v>
       </c>
@@ -16948,7 +19369,7 @@
       <c r="J31" s="43"/>
       <c r="K31" s="43"/>
     </row>
-    <row r="32" spans="1:11" ht="29.25" thickBot="1">
+    <row r="32" spans="1:11" ht="15.75" thickBot="1">
       <c r="A32" s="44"/>
       <c r="B32" s="44"/>
       <c r="C32" s="44"/>
@@ -16973,11 +19394,3317 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD21624-4E0C-4A0B-B299-8A13E9DE85D8}">
+  <dimension ref="A1:K48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="22.140625" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="11" max="11" width="23.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="71.25">
+      <c r="A8" s="51" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>910</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+    </row>
+    <row r="11" spans="1:11" ht="71.25">
+      <c r="A11" s="43" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43" t="s">
+        <v>917</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" ht="57">
+      <c r="A14" s="51" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>772</v>
+      </c>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51" t="s">
+        <v>921</v>
+      </c>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+    </row>
+    <row r="17" spans="1:11" ht="71.25">
+      <c r="A17" s="43" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>924</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43" t="s">
+        <v>921</v>
+      </c>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A20" s="49" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49" t="s">
+        <v>1342</v>
+      </c>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+    </row>
+    <row r="21" spans="1:11" ht="85.5">
+      <c r="A21" s="43" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>334</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43" t="s">
+        <v>929</v>
+      </c>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A24" s="49" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>931</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49" t="s">
+        <v>1350</v>
+      </c>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+    </row>
+    <row r="25" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A25" s="43" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>334</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="57">
+      <c r="A26" s="51" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
+    </row>
+    <row r="29" spans="1:11" ht="57">
+      <c r="A29" s="43" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A32" s="49" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B32" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="49" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D32" s="49" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F32" s="49"/>
+      <c r="G32" s="49" t="s">
+        <v>1368</v>
+      </c>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+    </row>
+    <row r="33" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A33" s="43" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A34" s="49" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B34" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="49" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D34" s="49" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49" t="s">
+        <v>1377</v>
+      </c>
+      <c r="H34" s="49"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
+      <c r="K34" s="49"/>
+    </row>
+    <row r="35" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A35" s="43" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43" t="s">
+        <v>996</v>
+      </c>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11" ht="72" thickBot="1">
+      <c r="A36" s="49" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B36" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="49" t="s">
+        <v>886</v>
+      </c>
+      <c r="D36" s="49" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E36" s="49" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49" t="s">
+        <v>999</v>
+      </c>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="49"/>
+      <c r="K36" s="49"/>
+    </row>
+    <row r="37" spans="1:11" ht="72" thickBot="1">
+      <c r="A37" s="43" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B37" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>890</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43" t="s">
+        <v>999</v>
+      </c>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A38" s="49" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B38" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="49" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D38" s="49" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E38" s="49" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
+      <c r="K38" s="49"/>
+    </row>
+    <row r="39" spans="1:11" ht="72" thickBot="1">
+      <c r="A39" s="43" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B39" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43" t="s">
+        <v>1394</v>
+      </c>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" spans="1:11" ht="155.25" customHeight="1">
+      <c r="A40" s="51" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>941</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>943</v>
+      </c>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="51"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A42" s="44"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="44"/>
+    </row>
+    <row r="43" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A43" s="43" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B43" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+    </row>
+    <row r="44" spans="1:11" ht="85.5">
+      <c r="A44" s="51" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B44" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="51" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D44" s="51" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E44" s="51" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
+      <c r="K44" s="51"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:11" ht="57">
+      <c r="A46" s="43"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B3A96C4-6EE9-4A3B-985E-1276DEE69391}">
+  <dimension ref="A1:K72"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="59" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A8" s="60" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D8" s="60" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E8" s="60" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+    </row>
+    <row r="9" spans="1:11" ht="57">
+      <c r="A9" s="55" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E9" s="55" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+    </row>
+    <row r="12" spans="1:11" ht="57">
+      <c r="A12" s="55" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A14" s="54"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+    </row>
+    <row r="15" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A15" s="56" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B15" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D15" s="56" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E15" s="56" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+    </row>
+    <row r="16" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A16" s="56" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B16" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D16" s="56" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E16" s="56" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+    </row>
+    <row r="17" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A17" s="56" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B17" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D17" s="56" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E17" s="56" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="56"/>
+    </row>
+    <row r="18" spans="1:11" ht="72" thickBot="1">
+      <c r="A18" s="56" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D18" s="56" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E18" s="56" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="56"/>
+    </row>
+    <row r="19" spans="1:11" ht="72" thickBot="1">
+      <c r="A19" s="56" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B19" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>886</v>
+      </c>
+      <c r="D19" s="56" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E19" s="56" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
+    </row>
+    <row r="20" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A20" s="56" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D20" s="56" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E20" s="56" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
+    </row>
+    <row r="21" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A21" s="56" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D21" s="56" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E21" s="56" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56" t="s">
+        <v>1451</v>
+      </c>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+    </row>
+    <row r="22" spans="1:11" ht="72" thickBot="1">
+      <c r="A22" s="56" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B22" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="56" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D22" s="56" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E22" s="56" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56" t="s">
+        <v>1456</v>
+      </c>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+    </row>
+    <row r="23" spans="1:11" ht="85.5">
+      <c r="A23" s="55" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B23" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="55" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D23" s="55" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E23" s="55" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="72" thickBot="1">
+      <c r="A25" s="54"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="54"/>
+    </row>
+    <row r="26" spans="1:11" ht="85.5">
+      <c r="A26" s="55" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B26" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="55" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D26" s="55" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E26" s="55" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55" t="s">
+        <v>1467</v>
+      </c>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="55"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A28" s="54"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="54"/>
+    </row>
+    <row r="29" spans="1:11" ht="71.25">
+      <c r="A29" s="55" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B29" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D29" s="55" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E29" s="55" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11" ht="28.5">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A33" s="54"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="54"/>
+    </row>
+    <row r="34" spans="1:11" ht="42.75">
+      <c r="A34" s="55" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B34" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="55" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D34" s="55" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E34" s="55" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55" t="s">
+        <v>1477</v>
+      </c>
+      <c r="H34" s="55"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="55"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A36" s="54"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="54"/>
+    </row>
+    <row r="37" spans="1:11" ht="112.5" customHeight="1">
+      <c r="A37" s="55" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B37" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="55" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D37" s="55" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E37" s="55" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55" t="s">
+        <v>1481</v>
+      </c>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="55"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A39" s="54"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54"/>
+    </row>
+    <row r="40" spans="1:11" ht="85.5">
+      <c r="A40" s="55" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B40" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="55" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D40" s="55" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E40" s="55" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A42" s="54"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="54"/>
+    </row>
+    <row r="43" spans="1:11" ht="85.5">
+      <c r="A43" s="55" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B43" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="55" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D43" s="55" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E43" s="55" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55" t="s">
+        <v>1490</v>
+      </c>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="55"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="43"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="54"/>
+    </row>
+    <row r="46" spans="1:11" ht="141" customHeight="1">
+      <c r="A46" s="55" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B46" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="55" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D46" s="55" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E46" s="55" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55" t="s">
+        <v>1495</v>
+      </c>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="55"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+    </row>
+    <row r="49" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A49" s="56" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B49" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="56" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D49" s="56" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E49" s="56" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56" t="s">
+        <v>1500</v>
+      </c>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="56"/>
+    </row>
+    <row r="50" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A50" s="56" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B50" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="56" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D50" s="56" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E50" s="56" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F50" s="56"/>
+      <c r="G50" s="56" t="s">
+        <v>1505</v>
+      </c>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="56"/>
+      <c r="K50" s="56"/>
+    </row>
+    <row r="51" spans="1:11" ht="72" thickBot="1">
+      <c r="A51" s="56" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B51" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" s="56" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D51" s="56" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E51" s="56" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56" t="s">
+        <v>1510</v>
+      </c>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="56"/>
+      <c r="K51" s="56"/>
+    </row>
+    <row r="52" spans="1:11" ht="72" thickBot="1">
+      <c r="A52" s="56" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B52" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="56" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D52" s="56" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E52" s="56" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F52" s="56"/>
+      <c r="G52" s="56" t="s">
+        <v>1515</v>
+      </c>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="56"/>
+      <c r="K52" s="56"/>
+    </row>
+    <row r="53" spans="1:11" ht="71.25">
+      <c r="A53" s="55" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B53" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="55" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D53" s="55" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E53" s="55" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F53" s="55"/>
+      <c r="G53" s="55" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H53" s="55"/>
+      <c r="I53" s="55"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="55"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="43"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+    </row>
+    <row r="55" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A55" s="54"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+    </row>
+    <row r="56" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A56" s="56" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B56" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" s="56" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D56" s="56" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E56" s="56" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56" t="s">
+        <v>1526</v>
+      </c>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="56"/>
+      <c r="K56" s="56"/>
+    </row>
+    <row r="57" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A57" s="56" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B57" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" s="56" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D57" s="56" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E57" s="56" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F57" s="56"/>
+      <c r="G57" s="56" t="s">
+        <v>1531</v>
+      </c>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56"/>
+      <c r="J57" s="56"/>
+      <c r="K57" s="56"/>
+    </row>
+    <row r="58" spans="1:11" ht="72" thickBot="1">
+      <c r="A58" s="56" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B58" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" s="56" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D58" s="56" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E58" s="56" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F58" s="56"/>
+      <c r="G58" s="56" t="s">
+        <v>1536</v>
+      </c>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
+      <c r="J58" s="56"/>
+      <c r="K58" s="56"/>
+    </row>
+    <row r="59" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A59" s="56" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B59" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" s="56" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D59" s="56" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E59" s="56" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F59" s="56"/>
+      <c r="G59" s="56" t="s">
+        <v>1540</v>
+      </c>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56"/>
+      <c r="J59" s="56"/>
+      <c r="K59" s="56"/>
+    </row>
+    <row r="60" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A60" s="56" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B60" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="56" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D60" s="56" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E60" s="56" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F60" s="56"/>
+      <c r="G60" s="56" t="s">
+        <v>1536</v>
+      </c>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="56"/>
+      <c r="K60" s="56"/>
+    </row>
+    <row r="61" spans="1:11" ht="72" thickBot="1">
+      <c r="A61" s="56" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B61" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C61" s="56" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D61" s="56" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E61" s="56" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="56"/>
+      <c r="K61" s="56"/>
+    </row>
+    <row r="62" spans="1:11" ht="128.25">
+      <c r="A62" s="55" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B62" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="55" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D62" s="55" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E62" s="55" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F62" s="55"/>
+      <c r="G62" s="55" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H62" s="55"/>
+      <c r="I62" s="55"/>
+      <c r="J62" s="55"/>
+      <c r="K62" s="55"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="43"/>
+      <c r="I63" s="43"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+    </row>
+    <row r="64" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A64" s="54"/>
+      <c r="B64" s="54"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="54" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="54"/>
+      <c r="I64" s="54"/>
+      <c r="J64" s="54"/>
+      <c r="K64" s="54"/>
+    </row>
+    <row r="65" spans="1:11" ht="71.25">
+      <c r="A65" s="55" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B65" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="55" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D65" s="55" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E65" s="55" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F65" s="55"/>
+      <c r="G65" s="55" t="s">
+        <v>1560</v>
+      </c>
+      <c r="H65" s="55"/>
+      <c r="I65" s="55"/>
+      <c r="J65" s="55"/>
+      <c r="K65" s="55"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="43"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="43"/>
+    </row>
+    <row r="67" spans="1:11" ht="72" thickBot="1">
+      <c r="A67" s="54"/>
+      <c r="B67" s="54"/>
+      <c r="C67" s="54"/>
+      <c r="D67" s="54"/>
+      <c r="E67" s="54" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F67" s="54"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="54"/>
+      <c r="I67" s="54"/>
+      <c r="J67" s="54"/>
+      <c r="K67" s="54"/>
+    </row>
+    <row r="68" spans="1:11" ht="99.75">
+      <c r="A68" s="55" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B68" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" s="55" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D68" s="55" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E68" s="55" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F68" s="55"/>
+      <c r="G68" s="55" t="s">
+        <v>1567</v>
+      </c>
+      <c r="H68" s="55"/>
+      <c r="I68" s="55"/>
+      <c r="J68" s="55"/>
+      <c r="K68" s="55"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="43"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
+      <c r="H69" s="43"/>
+      <c r="I69" s="43"/>
+      <c r="J69" s="43"/>
+      <c r="K69" s="43"/>
+    </row>
+    <row r="70" spans="1:11" ht="57">
+      <c r="A70" s="43"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="43"/>
+      <c r="D70" s="43"/>
+      <c r="E70" s="43" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F70" s="43"/>
+      <c r="G70" s="43"/>
+      <c r="H70" s="43"/>
+      <c r="I70" s="43"/>
+      <c r="J70" s="43"/>
+      <c r="K70" s="43"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="43"/>
+      <c r="B71" s="43"/>
+      <c r="C71" s="43"/>
+      <c r="D71" s="43"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="43"/>
+      <c r="G71" s="43"/>
+      <c r="H71" s="43"/>
+      <c r="I71" s="43"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+    </row>
+    <row r="72" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A72" s="44"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="44"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="44" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
+      <c r="I72" s="44"/>
+      <c r="J72" s="44"/>
+      <c r="K72" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF20DEB2-9AA1-4554-9E7F-130EFC4D1850}">
+  <dimension ref="A1:K65"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="7" max="7" width="34.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="59" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="85.5">
+      <c r="A8" s="51" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="71.25">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+    </row>
+    <row r="12" spans="1:11" ht="57">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+    </row>
+    <row r="15" spans="1:11" ht="99.75">
+      <c r="A15" s="43" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11" ht="57">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="71.25">
+      <c r="A20" s="51" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51" t="s">
+        <v>1585</v>
+      </c>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="57">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+    </row>
+    <row r="25" spans="1:11" ht="71.25">
+      <c r="A25" s="43" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="71.25">
+      <c r="A28" s="51" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51" t="s">
+        <v>1594</v>
+      </c>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+    </row>
+    <row r="31" spans="1:11" ht="99.75">
+      <c r="A31" s="43" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43" t="s">
+        <v>1599</v>
+      </c>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A33" s="43"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11" ht="99.75">
+      <c r="A34" s="51" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51" t="s">
+        <v>1604</v>
+      </c>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="51"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A36" s="44"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44"/>
+    </row>
+    <row r="37" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A37" s="43" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B37" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>1608</v>
+      </c>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43" t="s">
+        <v>1609</v>
+      </c>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A38" s="49" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B38" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="49" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D38" s="49" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E38" s="49" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49" t="s">
+        <v>1613</v>
+      </c>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
+      <c r="K38" s="49"/>
+    </row>
+    <row r="39" spans="1:11" ht="114">
+      <c r="A39" s="43" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B39" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43" t="s">
+        <v>1619</v>
+      </c>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="43"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+    </row>
+    <row r="41" spans="1:11" ht="72" thickBot="1">
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11" ht="85.5">
+      <c r="A42" s="51" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B42" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51" t="s">
+        <v>1626</v>
+      </c>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="51"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="43"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+    </row>
+    <row r="44" spans="1:11" ht="57">
+      <c r="A44" s="43"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+    </row>
+    <row r="47" spans="1:11" ht="99.75">
+      <c r="A47" s="43" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B47" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="43" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D47" s="43" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E47" s="43" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="43"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" spans="1:11" ht="57">
+      <c r="A49" s="43"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+    </row>
+    <row r="51" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A51" s="43"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+    </row>
+    <row r="52" spans="1:11" ht="71.25">
+      <c r="A52" s="51" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B52" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="51" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D52" s="51" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E52" s="51" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F52" s="51"/>
+      <c r="G52" s="51" t="s">
+        <v>1634</v>
+      </c>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
+      <c r="J52" s="51"/>
+      <c r="K52" s="51"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="43"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+    </row>
+    <row r="54" spans="1:11" ht="42.75">
+      <c r="A54" s="43"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="43"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43"/>
+    </row>
+    <row r="56" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A56" s="44"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="44"/>
+    </row>
+    <row r="57" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A57" s="43" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B57" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E57" s="43" t="s">
+        <v>1638</v>
+      </c>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H57" s="43"/>
+      <c r="I57" s="43"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="43"/>
+    </row>
+    <row r="58" spans="1:11" ht="85.5">
+      <c r="A58" s="51" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B58" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="51" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D58" s="51" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E58" s="51" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F58" s="51"/>
+      <c r="G58" s="51" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H58" s="51"/>
+      <c r="I58" s="51"/>
+      <c r="J58" s="51"/>
+      <c r="K58" s="51"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="43"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="43"/>
+    </row>
+    <row r="60" spans="1:11" ht="72" thickBot="1">
+      <c r="A60" s="44"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="44"/>
+      <c r="J60" s="44"/>
+      <c r="K60" s="44"/>
+    </row>
+    <row r="61" spans="1:11" ht="128.25">
+      <c r="A61" s="43" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B61" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="43" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F61" s="43"/>
+      <c r="G61" s="43" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H61" s="43"/>
+      <c r="I61" s="43"/>
+      <c r="J61" s="43"/>
+      <c r="K61" s="43"/>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="43"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="43"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="43"/>
+      <c r="G62" s="43"/>
+      <c r="H62" s="43"/>
+      <c r="I62" s="43"/>
+      <c r="J62" s="43"/>
+      <c r="K62" s="43"/>
+    </row>
+    <row r="63" spans="1:11" ht="57">
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="43" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="43"/>
+      <c r="I63" s="43"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="43"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="45"/>
+      <c r="F64" s="43"/>
+      <c r="G64" s="43"/>
+      <c r="H64" s="43"/>
+      <c r="I64" s="43"/>
+      <c r="J64" s="43"/>
+      <c r="K64" s="43"/>
+    </row>
+    <row r="65" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A65" s="44"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="44"/>
+      <c r="K65" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC62C0B2-BA3F-4506-A1CE-7D714441A411}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDEA6F1-B543-4F25-B30C-45D0356F1F68}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" thickBot="1">
       <c r="A1" s="31" t="s">
@@ -18985,6 +24712,50 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E932FD0D-9602-46DA-B200-F81F31FA9698}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C797F785-D62A-4425-9C57-4E05A11FB1F1}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F5A661-7A83-4175-A457-C5B1190A0FD9}">
   <dimension ref="A1:K99"/>
@@ -24581,7 +30352,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="71.25">
+    <row r="8" spans="1:11" ht="57">
       <c r="A8" s="51" t="s">
         <v>668</v>
       </c>
@@ -24619,7 +30390,7 @@
       <c r="J9" s="43"/>
       <c r="K9" s="43"/>
     </row>
-    <row r="10" spans="1:11" ht="43.5" thickBot="1">
+    <row r="10" spans="1:11" ht="29.25" thickBot="1">
       <c r="A10" s="44"/>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -24634,7 +30405,7 @@
       <c r="J10" s="44"/>
       <c r="K10" s="44"/>
     </row>
-    <row r="11" spans="1:11" ht="71.25">
+    <row r="11" spans="1:11" ht="57">
       <c r="A11" s="43" t="s">
         <v>567</v>
       </c>
@@ -24672,7 +30443,7 @@
       <c r="J12" s="43"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:11" ht="29.25" thickBot="1">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1">
       <c r="A13" s="43"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43"/>
@@ -24687,7 +30458,7 @@
       <c r="J13" s="43"/>
       <c r="K13" s="43"/>
     </row>
-    <row r="14" spans="1:11" ht="85.5">
+    <row r="14" spans="1:11" ht="71.25">
       <c r="A14" s="51" t="s">
         <v>677</v>
       </c>
@@ -24725,7 +30496,7 @@
       <c r="J15" s="43"/>
       <c r="K15" s="43"/>
     </row>
-    <row r="16" spans="1:11" ht="29.25" thickBot="1">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1">
       <c r="A16" s="44"/>
       <c r="B16" s="44"/>
       <c r="C16" s="44"/>
@@ -24778,7 +30549,7 @@
       <c r="J18" s="43"/>
       <c r="K18" s="43"/>
     </row>
-    <row r="19" spans="1:11" ht="29.25" thickBot="1">
+    <row r="19" spans="1:11" ht="15.75" thickBot="1">
       <c r="A19" s="43"/>
       <c r="B19" s="43"/>
       <c r="C19" s="43"/>
@@ -24793,7 +30564,7 @@
       <c r="J19" s="43"/>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="1:11" ht="85.5">
+    <row r="20" spans="1:11" ht="57">
       <c r="A20" s="51" t="s">
         <v>685</v>
       </c>
@@ -24831,7 +30602,7 @@
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
     </row>
-    <row r="22" spans="1:11" ht="43.5" thickBot="1">
+    <row r="22" spans="1:11" ht="29.25" thickBot="1">
       <c r="A22" s="44"/>
       <c r="B22" s="44"/>
       <c r="C22" s="44"/>
@@ -24846,7 +30617,7 @@
       <c r="J22" s="44"/>
       <c r="K22" s="44"/>
     </row>
-    <row r="23" spans="1:11" ht="99.75">
+    <row r="23" spans="1:11" ht="57">
       <c r="A23" s="43" t="s">
         <v>689</v>
       </c>
@@ -24884,7 +30655,7 @@
       <c r="J24" s="43"/>
       <c r="K24" s="43"/>
     </row>
-    <row r="25" spans="1:11" ht="29.25" thickBot="1">
+    <row r="25" spans="1:11" ht="15.75" thickBot="1">
       <c r="A25" s="43"/>
       <c r="B25" s="43"/>
       <c r="C25" s="43"/>
@@ -24899,7 +30670,7 @@
       <c r="J25" s="43"/>
       <c r="K25" s="43"/>
     </row>
-    <row r="26" spans="1:11" ht="85.5">
+    <row r="26" spans="1:11" ht="57">
       <c r="A26" s="51" t="s">
         <v>693</v>
       </c>
@@ -24937,7 +30708,7 @@
       <c r="J27" s="43"/>
       <c r="K27" s="43"/>
     </row>
-    <row r="28" spans="1:11" ht="29.25" thickBot="1">
+    <row r="28" spans="1:11" ht="15.75" thickBot="1">
       <c r="A28" s="44"/>
       <c r="B28" s="44"/>
       <c r="C28" s="44"/>
@@ -24990,7 +30761,7 @@
       <c r="J30" s="43"/>
       <c r="K30" s="43"/>
     </row>
-    <row r="31" spans="1:11" ht="29.25" thickBot="1">
+    <row r="31" spans="1:11" ht="15.75" thickBot="1">
       <c r="A31" s="43"/>
       <c r="B31" s="43"/>
       <c r="C31" s="43"/>
@@ -25005,7 +30776,7 @@
       <c r="J31" s="43"/>
       <c r="K31" s="43"/>
     </row>
-    <row r="32" spans="1:11" ht="85.5">
+    <row r="32" spans="1:11" ht="57">
       <c r="A32" s="51" t="s">
         <v>701</v>
       </c>
@@ -25043,7 +30814,7 @@
       <c r="J33" s="43"/>
       <c r="K33" s="43"/>
     </row>
-    <row r="34" spans="1:11" ht="29.25" thickBot="1">
+    <row r="34" spans="1:11" ht="15.75" thickBot="1">
       <c r="A34" s="44"/>
       <c r="B34" s="44"/>
       <c r="C34" s="44"/>
@@ -25058,7 +30829,7 @@
       <c r="J34" s="44"/>
       <c r="K34" s="44"/>
     </row>
-    <row r="35" spans="1:11" ht="99.75">
+    <row r="35" spans="1:11" ht="71.25">
       <c r="A35" s="43" t="s">
         <v>705</v>
       </c>
@@ -25096,7 +30867,7 @@
       <c r="J36" s="43"/>
       <c r="K36" s="43"/>
     </row>
-    <row r="37" spans="1:11" ht="29.25" thickBot="1">
+    <row r="37" spans="1:11" ht="15.75" thickBot="1">
       <c r="A37" s="43"/>
       <c r="B37" s="43"/>
       <c r="C37" s="43"/>
@@ -25111,7 +30882,7 @@
       <c r="J37" s="43"/>
       <c r="K37" s="43"/>
     </row>
-    <row r="38" spans="1:11" ht="85.5">
+    <row r="38" spans="1:11" ht="57">
       <c r="A38" s="51" t="s">
         <v>709</v>
       </c>
@@ -25149,7 +30920,7 @@
       <c r="J39" s="43"/>
       <c r="K39" s="43"/>
     </row>
-    <row r="40" spans="1:11" ht="29.25" thickBot="1">
+    <row r="40" spans="1:11" ht="15.75" thickBot="1">
       <c r="A40" s="44"/>
       <c r="B40" s="44"/>
       <c r="C40" s="44"/>
@@ -25164,7 +30935,7 @@
       <c r="J40" s="44"/>
       <c r="K40" s="44"/>
     </row>
-    <row r="41" spans="1:11" ht="71.25">
+    <row r="41" spans="1:11" ht="57">
       <c r="A41" s="43" t="s">
         <v>713</v>
       </c>
@@ -25202,7 +30973,7 @@
       <c r="J42" s="43"/>
       <c r="K42" s="43"/>
     </row>
-    <row r="43" spans="1:11" ht="29.25" thickBot="1">
+    <row r="43" spans="1:11" ht="15.75" thickBot="1">
       <c r="A43" s="43"/>
       <c r="B43" s="43"/>
       <c r="C43" s="43"/>
@@ -25255,7 +31026,7 @@
       <c r="J45" s="43"/>
       <c r="K45" s="43"/>
     </row>
-    <row r="46" spans="1:11" ht="57">
+    <row r="46" spans="1:11" ht="28.5">
       <c r="A46" s="43"/>
       <c r="B46" s="43"/>
       <c r="C46" s="43"/>
@@ -25283,7 +31054,7 @@
       <c r="J47" s="43"/>
       <c r="K47" s="43"/>
     </row>
-    <row r="48" spans="1:11" ht="43.5" thickBot="1">
+    <row r="48" spans="1:11" ht="29.25" thickBot="1">
       <c r="A48" s="44"/>
       <c r="B48" s="44"/>
       <c r="C48" s="44"/>
@@ -25298,7 +31069,7 @@
       <c r="J48" s="44"/>
       <c r="K48" s="44"/>
     </row>
-    <row r="49" spans="1:11" ht="85.5">
+    <row r="49" spans="1:11" ht="71.25">
       <c r="A49" s="43" t="s">
         <v>724</v>
       </c>
@@ -25336,7 +31107,7 @@
       <c r="J50" s="43"/>
       <c r="K50" s="43"/>
     </row>
-    <row r="51" spans="1:11" ht="57">
+    <row r="51" spans="1:11" ht="42.75">
       <c r="A51" s="43"/>
       <c r="B51" s="43"/>
       <c r="C51" s="43"/>
@@ -25379,7 +31150,7 @@
       <c r="J53" s="43"/>
       <c r="K53" s="43"/>
     </row>
-    <row r="54" spans="1:11" ht="85.5">
+    <row r="54" spans="1:11" ht="57">
       <c r="A54" s="51" t="s">
         <v>730</v>
       </c>
@@ -25417,7 +31188,7 @@
       <c r="J55" s="43"/>
       <c r="K55" s="43"/>
     </row>
-    <row r="56" spans="1:11" ht="28.5">
+    <row r="56" spans="1:11">
       <c r="A56" s="43"/>
       <c r="B56" s="43"/>
       <c r="C56" s="43"/>
@@ -25445,7 +31216,7 @@
       <c r="J57" s="43"/>
       <c r="K57" s="43"/>
     </row>
-    <row r="58" spans="1:11" ht="57">
+    <row r="58" spans="1:11" ht="28.5">
       <c r="A58" s="43"/>
       <c r="B58" s="43"/>
       <c r="C58" s="43"/>
@@ -25488,7 +31259,7 @@
       <c r="J60" s="44"/>
       <c r="K60" s="44"/>
     </row>
-    <row r="61" spans="1:11" ht="71.25">
+    <row r="61" spans="1:11" ht="57">
       <c r="A61" s="43" t="s">
         <v>737</v>
       </c>
@@ -25541,7 +31312,7 @@
       <c r="J63" s="43"/>
       <c r="K63" s="43"/>
     </row>
-    <row r="64" spans="1:11" ht="71.25">
+    <row r="64" spans="1:11" ht="57">
       <c r="A64" s="51" t="s">
         <v>742</v>
       </c>
@@ -25579,7 +31350,7 @@
       <c r="J65" s="43"/>
       <c r="K65" s="43"/>
     </row>
-    <row r="66" spans="1:11" ht="29.25" thickBot="1">
+    <row r="66" spans="1:11" ht="15.75" thickBot="1">
       <c r="A66" s="44"/>
       <c r="B66" s="44"/>
       <c r="C66" s="44"/>
@@ -25594,7 +31365,7 @@
       <c r="J66" s="44"/>
       <c r="K66" s="44"/>
     </row>
-    <row r="67" spans="1:11" ht="85.5">
+    <row r="67" spans="1:11" ht="57">
       <c r="A67" s="43" t="s">
         <v>748</v>
       </c>
@@ -25632,7 +31403,7 @@
       <c r="J68" s="43"/>
       <c r="K68" s="43"/>
     </row>
-    <row r="69" spans="1:11" ht="29.25" thickBot="1">
+    <row r="69" spans="1:11" ht="15.75" thickBot="1">
       <c r="A69" s="43"/>
       <c r="B69" s="43"/>
       <c r="C69" s="43"/>
@@ -25685,7 +31456,7 @@
       <c r="J71" s="43"/>
       <c r="K71" s="43"/>
     </row>
-    <row r="72" spans="1:11" ht="43.5" thickBot="1">
+    <row r="72" spans="1:11" ht="29.25" thickBot="1">
       <c r="A72" s="44"/>
       <c r="B72" s="44"/>
       <c r="C72" s="44"/>
@@ -25700,7 +31471,7 @@
       <c r="J72" s="44"/>
       <c r="K72" s="44"/>
     </row>
-    <row r="73" spans="1:11" ht="99.75">
+    <row r="73" spans="1:11" ht="71.25">
       <c r="A73" s="43" t="s">
         <v>760</v>
       </c>
@@ -25738,7 +31509,7 @@
       <c r="J74" s="43"/>
       <c r="K74" s="43"/>
     </row>
-    <row r="75" spans="1:11" ht="29.25" thickBot="1">
+    <row r="75" spans="1:11" ht="15.75" thickBot="1">
       <c r="A75" s="43"/>
       <c r="B75" s="43"/>
       <c r="C75" s="43"/>
@@ -25753,7 +31524,7 @@
       <c r="J75" s="43"/>
       <c r="K75" s="43"/>
     </row>
-    <row r="76" spans="1:11" ht="86.25" thickBot="1">
+    <row r="76" spans="1:11" ht="57.75" thickBot="1">
       <c r="A76" s="49" t="s">
         <v>765</v>
       </c>
@@ -25778,7 +31549,7 @@
       <c r="J76" s="49"/>
       <c r="K76" s="49"/>
     </row>
-    <row r="77" spans="1:11" ht="85.5">
+    <row r="77" spans="1:11" ht="57">
       <c r="A77" s="51" t="s">
         <v>770</v>
       </c>
@@ -25816,7 +31587,7 @@
       <c r="J78" s="43"/>
       <c r="K78" s="43"/>
     </row>
-    <row r="79" spans="1:11" ht="57.75" thickBot="1">
+    <row r="79" spans="1:11" ht="29.25" thickBot="1">
       <c r="A79" s="44"/>
       <c r="B79" s="44"/>
       <c r="C79" s="44"/>

--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD94ABF-F706-4550-9593-768163843099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B77AE1-BA4F-4910-BC26-62C809E5130A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="16" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="18" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -29,8 +29,8 @@
     <sheet name="AddToCart" sheetId="14" r:id="rId14"/>
     <sheet name="WishList" sheetId="15" r:id="rId15"/>
     <sheet name="Cart" sheetId="16" r:id="rId16"/>
-    <sheet name="Sheet2" sheetId="17" r:id="rId17"/>
-    <sheet name="Sheet3" sheetId="18" r:id="rId18"/>
+    <sheet name="Coupon" sheetId="17" r:id="rId17"/>
+    <sheet name="Shipping" sheetId="18" r:id="rId18"/>
     <sheet name="Sheet4" sheetId="19" r:id="rId19"/>
     <sheet name="Sheet5" sheetId="20" r:id="rId20"/>
     <sheet name="Sheet6" sheetId="21" r:id="rId21"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="1652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="1848">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -5409,6 +5409,614 @@
   </si>
   <si>
     <t>Both discounts stack successfully. The Percentage/Fixed coupon applies first, and the Gift Certificate deducts from the remaining total.</t>
+  </si>
+  <si>
+    <t>TC_EST_001</t>
+  </si>
+  <si>
+    <t>Verify expanding the 'Estimate Shipping &amp; Taxes' panel</t>
+  </si>
+  <si>
+    <t>User has an item requiring shipping in the cart</t>
+  </si>
+  <si>
+    <t>2. Click the 'Estimate Shipping &amp; Taxes' accordion header.</t>
+  </si>
+  <si>
+    <t>The panel smoothly expands to reveal the Country, Region / State, and Post Code fields, along with a 'Get Quotes' button.</t>
+  </si>
+  <si>
+    <t>TC_EST_002</t>
+  </si>
+  <si>
+    <t>Verify 'Country' dropdown functionality</t>
+  </si>
+  <si>
+    <t>User has expanded the Estimate Shipping panel</t>
+  </si>
+  <si>
+    <t>1. Click the 'Country' dropdown.</t>
+  </si>
+  <si>
+    <t>2. Select a valid country (e.g., United Kingdom).</t>
+  </si>
+  <si>
+    <t>The dropdown updates to the selected country, and the page dynamically triggers a request to fetch relevant Regions/States.</t>
+  </si>
+  <si>
+    <t>TC_EST_003</t>
+  </si>
+  <si>
+    <t>Verify 'Region / State' dropdown populates dynamically</t>
+  </si>
+  <si>
+    <t>User has selected a Country</t>
+  </si>
+  <si>
+    <t>1. Observe the 'Region / State' dropdown after selecting a Country.</t>
+  </si>
+  <si>
+    <t>The dropdown successfully populates with the correct states, provinces, or counties associated with the selected Country.</t>
+  </si>
+  <si>
+    <t>TC_EST_004</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Country' is left unselected</t>
+  </si>
+  <si>
+    <t>1. Leave the 'Country' dropdown on the default '--- Please Select ---' option.</t>
+  </si>
+  <si>
+    <t>2. Click 'Get Quotes'.</t>
+  </si>
+  <si>
+    <t>The request fails. A validation warning prompts the user to select a country.</t>
+  </si>
+  <si>
+    <t>TC_EST_005</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Region / State' is left unselected</t>
+  </si>
+  <si>
+    <t>1. Select a Country.</t>
+  </si>
+  <si>
+    <t>2. Leave 'Region / State' on '--- Please Select ---'.</t>
+  </si>
+  <si>
+    <t>3. Click 'Get Quotes'.</t>
+  </si>
+  <si>
+    <t>The request fails. A validation warning prompts the user to select a region/state.</t>
+  </si>
+  <si>
+    <t>TC_EST_006</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Post Code' is blank (if required by country)</t>
+  </si>
+  <si>
+    <t>User has selected Country and Region</t>
+  </si>
+  <si>
+    <t>1. Leave the 'Post Code' field empty.</t>
+  </si>
+  <si>
+    <t>If the selected country requires a postcode for shipping calculations, a validation warning is displayed.</t>
+  </si>
+  <si>
+    <t>TC_EST_007</t>
+  </si>
+  <si>
+    <t>Verify fetching quotes with valid destination data</t>
+  </si>
+  <si>
+    <t>User is on the Estimate Shipping panel</t>
+  </si>
+  <si>
+    <t>1. Select a valid Country and Region.</t>
+  </si>
+  <si>
+    <t>2. Enter a valid Post Code.</t>
+  </si>
+  <si>
+    <t>A modal window pops up titled "Please select the preferred shipping method to use on this order."</t>
+  </si>
+  <si>
+    <t>TC_EST_008</t>
+  </si>
+  <si>
+    <t>Verify Shipping Quotes modal UI</t>
+  </si>
+  <si>
+    <t>User has clicked 'Get Quotes' and modal is open</t>
+  </si>
+  <si>
+    <t>1. Observe the contents of the modal.</t>
+  </si>
+  <si>
+    <t>The modal displays available shipping methods (e.g., Flat Rate, Free Shipping) with radio buttons and their respective costs.</t>
+  </si>
+  <si>
+    <t>TC_EST_009</t>
+  </si>
+  <si>
+    <t>Verify successful application of a selected shipping quote</t>
+  </si>
+  <si>
+    <t>User has the Shipping Quotes modal open</t>
+  </si>
+  <si>
+    <t>1. Select a specific shipping method using the radio button.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Apply Shipping' button.</t>
+  </si>
+  <si>
+    <t>The modal closes, a success banner appears ("Success: Your shipping estimate has been applied!"), and the page reloads.</t>
+  </si>
+  <si>
+    <t>TC_EST_010</t>
+  </si>
+  <si>
+    <t>Verify Cart Totals table updates with shipping cost</t>
+  </si>
+  <si>
+    <t>User has successfully applied a shipping quote</t>
+  </si>
+  <si>
+    <t>1. Scroll down to the Totals section at the bottom of the cart.</t>
+  </si>
+  <si>
+    <t>A new line item for the applied shipping method is displayed, and the Final Total accurately includes the shipping cost.</t>
+  </si>
+  <si>
+    <t>TC_EST_011</t>
+  </si>
+  <si>
+    <t>Verify dynamic Tax calculation based on estimated destination</t>
+  </si>
+  <si>
+    <t>User has applied an estimate for a taxable region</t>
+  </si>
+  <si>
+    <t>1. Observe the Tax line items in the Totals section (e.g., State Tax, VAT).</t>
+  </si>
+  <si>
+    <t>The tax rates automatically recalculate and display correctly based on the Country and Region/State provided in the estimate tool.</t>
+  </si>
+  <si>
+    <t>TC_EST_012</t>
+  </si>
+  <si>
+    <t>Verify behavior when no shipping methods are available</t>
+  </si>
+  <si>
+    <t>User is estimating shipping for an unsupported region</t>
+  </si>
+  <si>
+    <t>1. Enter destination details for a country/region the store does not ship to.</t>
+  </si>
+  <si>
+    <t>A warning message is displayed inside the modal or panel stating: "Warning: No Shipping options are available."</t>
+  </si>
+  <si>
+    <t>TC_EST_013</t>
+  </si>
+  <si>
+    <t>Verify 'Cancel' button functionality on the quotes modal</t>
+  </si>
+  <si>
+    <t>1. Click the 'Cancel' button.</t>
+  </si>
+  <si>
+    <t>The modal closes immediately without applying any shipping methods or reloading the page.</t>
+  </si>
+  <si>
+    <t>TC_EST_014</t>
+  </si>
+  <si>
+    <t>Verify updating the estimate with a new destination</t>
+  </si>
+  <si>
+    <t>User has already applied a shipping cost</t>
+  </si>
+  <si>
+    <t>1. Change the Country/Region to a different location.</t>
+  </si>
+  <si>
+    <t>2. Fetch new quotes and apply a different method.</t>
+  </si>
+  <si>
+    <t>The old shipping cost is completely replaced by the new shipping cost in the Totals section.</t>
+  </si>
+  <si>
+    <t>TC_EST_015</t>
+  </si>
+  <si>
+    <t>Verify 'Estimate Shipping' behavior with digital/downloadable products</t>
+  </si>
+  <si>
+    <t>User only has a downloadable product in the cart</t>
+  </si>
+  <si>
+    <t>1. View the Shopping Cart page.</t>
+  </si>
+  <si>
+    <t>The 'Estimate Shipping &amp; Taxes' panel is either hidden completely or disables the shipping components, as digital goods do not require physical shipping.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_001</t>
+  </si>
+  <si>
+    <t>Verify navigation to the Checkout page</t>
+  </si>
+  <si>
+    <t>User has a physical item in the cart</t>
+  </si>
+  <si>
+    <t>2. Click the 'Checkout' button.</t>
+  </si>
+  <si>
+    <t>User is routed to the Checkout page, and "Step 1: Checkout Options" is expanded.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_002</t>
+  </si>
+  <si>
+    <t>Verify 'Guest Checkout' selection</t>
+  </si>
+  <si>
+    <t>User is on Step 1: Checkout Options</t>
+  </si>
+  <si>
+    <t>1. Locate the 'New Customer' section.</t>
+  </si>
+  <si>
+    <t>2. Select the 'Guest Checkout' radio button.</t>
+  </si>
+  <si>
+    <t>"Step 2: Billing Details" expands smoothly, and the Guest details form is displayed.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_003</t>
+  </si>
+  <si>
+    <t>Verify validation for blank mandatory fields in Billing Details</t>
+  </si>
+  <si>
+    <t>User is on Step 2: Billing Details</t>
+  </si>
+  <si>
+    <t>1. Leave all mandatory fields (First Name, Last Name, Email, Telephone, Address 1, City, Postcode, Country, Region) blank.</t>
+  </si>
+  <si>
+    <t>Step 2 does not submit. Validation error messages appear below every required field.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_004</t>
+  </si>
+  <si>
+    <t>Verify validation for invalid Email format in Billing Details</t>
+  </si>
+  <si>
+    <t>Step 2 does not submit. A validation error message is displayed under the E-Mail field.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_005</t>
+  </si>
+  <si>
+    <t>Verify 'My delivery and billing addresses are the same' checked behavior</t>
+  </si>
+  <si>
+    <t>1. Fill all mandatory billing fields with valid data.</t>
+  </si>
+  <si>
+    <t>2. Ensure the "My delivery and billing addresses are the same" checkbox is CHECKED.</t>
+  </si>
+  <si>
+    <t>The system successfully skips Step 3 (Delivery Details) and expands "Step 4: Delivery Method".</t>
+  </si>
+  <si>
+    <t>TC_GUEST_006</t>
+  </si>
+  <si>
+    <t>Verify 'My delivery and billing addresses are the same' unchecked behavior</t>
+  </si>
+  <si>
+    <t>2. UNCHECK the "My delivery and billing addresses are the same" checkbox.</t>
+  </si>
+  <si>
+    <t>The system successfully expands "Step 3: Delivery Details" to require a separate shipping address.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_007</t>
+  </si>
+  <si>
+    <t>Verify validation for blank mandatory fields in Delivery Details</t>
+  </si>
+  <si>
+    <t>User is on Step 3: Delivery Details</t>
+  </si>
+  <si>
+    <t>1. Leave all mandatory fields blank.</t>
+  </si>
+  <si>
+    <t>Step 3 does not submit. Validation error messages appear below every required field.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_008</t>
+  </si>
+  <si>
+    <t>Verify successful completion of Delivery Details</t>
+  </si>
+  <si>
+    <t>1. Fill all mandatory delivery fields with valid destination data.</t>
+  </si>
+  <si>
+    <t>Step 3 submits successfully, and "Step 4: Delivery Method" expands.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_009</t>
+  </si>
+  <si>
+    <t>Verify Delivery Method options are populated</t>
+  </si>
+  <si>
+    <t>User is on Step 4: Delivery Method</t>
+  </si>
+  <si>
+    <t>1. Observe the available shipping options.</t>
+  </si>
+  <si>
+    <t>The system successfully calculates and displays available shipping methods (e.g., Flat Rate) based on the destination address.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_010</t>
+  </si>
+  <si>
+    <t>Verify validation when no Delivery Method is selected</t>
+  </si>
+  <si>
+    <t>1. Ensure no radio button is selected for shipping (if a default is not forced).</t>
+  </si>
+  <si>
+    <t>A warning message states that a shipping method is required.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_011</t>
+  </si>
+  <si>
+    <t>Verify 'Add Comments About Your Order' in Delivery Method</t>
+  </si>
+  <si>
+    <t>1. Type a message in the comments text area (e.g., "Leave at back door").</t>
+  </si>
+  <si>
+    <t>2. Select a shipping method.</t>
+  </si>
+  <si>
+    <t>Step 4 submits successfully, and "Step 5: Payment Method" expands. The comment is saved to the session.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_012</t>
+  </si>
+  <si>
+    <t>Verify Security: XSS injection in Order Comments</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Type </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;script&gt;alert('XSS')&lt;/script&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the comments text area.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4 submits successfully. The script is sanitized and will not execute upon order review or in the admin panel.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_013</t>
+  </si>
+  <si>
+    <t>Verify Payment Method options are populated</t>
+  </si>
+  <si>
+    <t>User is on Step 5: Payment Method</t>
+  </si>
+  <si>
+    <t>1. Observe the available payment options.</t>
+  </si>
+  <si>
+    <t>The system successfully displays available payment methods (e.g., Cash On Delivery, PayPal, Bank Transfer).</t>
+  </si>
+  <si>
+    <t>TC_GUEST_014</t>
+  </si>
+  <si>
+    <t>Verify validation when no Payment Method is selected</t>
+  </si>
+  <si>
+    <t>1. Ensure no radio button is selected for payment.</t>
+  </si>
+  <si>
+    <t>A warning message states that a payment method is required.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_015</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Terms &amp; Conditions' is unchecked</t>
+  </si>
+  <si>
+    <t>1. Select a payment method.</t>
+  </si>
+  <si>
+    <t>2. Leave the "I have read and agree to the Terms &amp; Conditions" checkbox UNCHECKED.</t>
+  </si>
+  <si>
+    <t>Step 5 does not submit. A warning banner states that you must agree to the Terms &amp; Conditions.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_016</t>
+  </si>
+  <si>
+    <t>Verify 'Terms &amp; Conditions' hyperlink opens the policy</t>
+  </si>
+  <si>
+    <t>1. Click on the hyperlinked text for 'Terms &amp; Conditions'.</t>
+  </si>
+  <si>
+    <t>The Terms &amp; Conditions policy text opens successfully in a modal window.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_017</t>
+  </si>
+  <si>
+    <t>Verify successful completion of Payment Method</t>
+  </si>
+  <si>
+    <t>2. Check the Terms &amp; Conditions box.</t>
+  </si>
+  <si>
+    <t>Step 5 submits successfully, and "Step 6: Confirm Order" expands.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_018</t>
+  </si>
+  <si>
+    <t>Verify Order Confirmation Item Details match Cart</t>
+  </si>
+  <si>
+    <t>User is on Step 6: Confirm Order</t>
+  </si>
+  <si>
+    <t>1. Review the items in the confirmation table.</t>
+  </si>
+  <si>
+    <t>Product Name, Model, Quantity, and Unit Price exactly match the items previously added to the shopping cart.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_019</t>
+  </si>
+  <si>
+    <t>Verify Order Confirmation Totals match selected methods</t>
+  </si>
+  <si>
+    <t>1. Review the Totals section (Sub-Total, Shipping, Taxes, Total).</t>
+  </si>
+  <si>
+    <t>The shipping line item matches the cost selected in Step 4, and the Final Total is mathematically accurate.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_020</t>
+  </si>
+  <si>
+    <t>Verify 'Confirm Order' button executes the order (Offline Payment)</t>
+  </si>
+  <si>
+    <t>1. Ensure an offline payment method (e.g., Cash on Delivery) is selected.</t>
+  </si>
+  <si>
+    <t>2. Click 'Confirm Order'.</t>
+  </si>
+  <si>
+    <t>The order processes successfully, and the user is redirected to the "Checkout Success" page.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_021</t>
+  </si>
+  <si>
+    <t>Verify 'Confirm Order' button redirects to Payment Gateway</t>
+  </si>
+  <si>
+    <t>1. Ensure a third-party gateway (e.g., PayPal) is selected.</t>
+  </si>
+  <si>
+    <t>The user is securely redirected to the external payment gateway to complete the transaction.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_022</t>
+  </si>
+  <si>
+    <t>Verify Checkout Success Page UI</t>
+  </si>
+  <si>
+    <t>User has just completed an order</t>
+  </si>
+  <si>
+    <t>1. Observe the Checkout Success page.</t>
+  </si>
+  <si>
+    <t>A success message is displayed ("Your order has been placed!"), along with a 'Continue' button to return to the home page.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_023</t>
+  </si>
+  <si>
+    <t>Verify cart is emptied after successful Guest Checkout</t>
+  </si>
+  <si>
+    <t>User has just reached the Checkout Success page</t>
+  </si>
+  <si>
+    <t>1. Click the 'Shopping Cart' link in the header or mini-cart.</t>
+  </si>
+  <si>
+    <t>The shopping cart is completely empty.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_024</t>
+  </si>
+  <si>
+    <t>Verify Guest Checkout is blocked for Downloadable Products</t>
+  </si>
+  <si>
+    <t>User adds a digital/downloadable product to the cart</t>
+  </si>
+  <si>
+    <t>1. Navigate to Checkout.</t>
+  </si>
+  <si>
+    <t>2. Observe Step 1: Checkout Options.</t>
+  </si>
+  <si>
+    <t>The "Guest Checkout" option is either hidden or disabled, as digital goods require an account to access the download.</t>
+  </si>
+  <si>
+    <t>TC_GUEST_025</t>
+  </si>
+  <si>
+    <t>Verify accordion 'Modify' functionality during checkout</t>
+  </si>
+  <si>
+    <t>1. Click the 'Step 2: Billing Details' header to expand it again.</t>
+  </si>
+  <si>
+    <t>2. Modify the First Name.</t>
+  </si>
+  <si>
+    <t>3. Click Continue through to Step 6.</t>
+  </si>
+  <si>
+    <t>The user can successfully navigate backward through the accordion, modify data, and the session retains the new updates.</t>
   </si>
 </sst>
 </file>
@@ -6204,7 +6812,839 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="254">
+  <dxfs count="284">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -12931,227 +14371,267 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="238">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="268">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="237"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="236"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="267"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="266"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
   <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="130"/>
-    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="129"/>
-    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="127"/>
-    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="126"/>
-    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="125"/>
-    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="124"/>
-    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="123"/>
-    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="122"/>
-    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="121"/>
-    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="157"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="156"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="155"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="154"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="153"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="152"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="151"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
   <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
   <autoFilter ref="A7:K49" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="128"/>
+    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="127"/>
+    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="123"/>
+    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="122"/>
+    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="121"/>
+    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
   <autoFilter ref="A7:K55" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="110"/>
+    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="105"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
   <autoFilter ref="A7:K62" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86">
   <autoFilter ref="A7:K84" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="253" dataDxfId="251" headerRowBorderDxfId="252" tableBorderDxfId="250">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="283" dataDxfId="281" headerRowBorderDxfId="282" tableBorderDxfId="280">
   <autoFilter ref="A7:K32" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="249"/>
-    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="248"/>
-    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="247"/>
-    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="246"/>
-    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="245"/>
-    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="244"/>
-    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="243"/>
-    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="242"/>
-    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="241"/>
-    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="240"/>
-    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="239"/>
+    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="279"/>
+    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="278"/>
+    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="277"/>
+    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="276"/>
+    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="275"/>
+    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="274"/>
+    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="273"/>
+    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="272"/>
+    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="271"/>
+    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="270"/>
+    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="269"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="42" dataDxfId="44" headerRowBorderDxfId="43" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="72" dataDxfId="74" headerRowBorderDxfId="73" tableBorderDxfId="71">
   <autoFilter ref="A7:K48" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="26" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="56" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
   <autoFilter ref="A7:K72" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="11" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="41" dataDxfId="44" headerRowBorderDxfId="42" tableBorderDxfId="43">
   <autoFilter ref="A7:K65" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="235" dataDxfId="233" headerRowBorderDxfId="234" tableBorderDxfId="232" totalsRowBorderDxfId="231">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="265" dataDxfId="263" headerRowBorderDxfId="264" tableBorderDxfId="262" totalsRowBorderDxfId="261">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="230"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="229"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="228"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="227"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="226"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="260"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="259"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="258"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="257"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="256"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}" name="Table20" displayName="Table20" ref="A7:K44" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+  <autoFilter ref="A7:K44" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{E9107AEB-9917-4DCD-999F-23DED7528269}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{4E7F2B0A-9A06-45D9-829D-517139E93FB0}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{09C2C301-9101-42D2-87C5-CF12D84AFDE2}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{4630FF91-0DD6-4E25-827E-20AC0C3327F3}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{6ACC0A37-29EE-49DB-857B-3EF893C5DD7D}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{2AF81478-C083-4718-B4FE-A5FEC39D4683}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{7FDCD6DB-5E88-42AB-9324-CD156B2F76E1}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{8B796E38-6BAF-4EB8-846A-DFC533AC8C87}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{362BE16E-720C-4E90-AFB8-ED627DE3BEF5}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{E7237EFD-FF4D-4C9B-98AD-189BF6BF0535}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{35851930-6F01-4446-835F-13E1EDBAF070}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}" name="Table21" displayName="Table21" ref="A7:K84" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+  <autoFilter ref="A7:K84" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{15029807-7F0E-425A-BB46-0B6DB3C95839}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{7BD8F686-C564-499F-8D06-C85E47BDAB51}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{67E25BA4-3FF0-4F70-B233-F0E251B42D26}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{B181D3E8-3A2C-400F-B359-B20568BAB1D1}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{B58B21E5-45D9-46DC-BFE5-78BDC714CE7C}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{7D364936-A237-464A-A78D-51E3CF7B08EF}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{DD78F72F-2F82-49C0-857B-9230594DFC47}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{DD233399-E0C4-4DCB-918E-551AD68ACB5A}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{8D1587AC-EA15-44E2-A0C1-155707A09C86}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{B82BB21B-0563-40CE-B8DB-5D4ADE46287B}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{B4AF1D65-2623-4B0C-9A46-AAAF78C4F53B}" name="Comments" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -13159,7 +14639,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="225"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="255"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -13167,120 +14647,120 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="220"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="219"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="218"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="217"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="216"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="215"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="214"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="213"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="212"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="211"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="210"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="250"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="249"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="248"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="247"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="246"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="245"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="244"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="243"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="242"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="241"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="240"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="205"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="204"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="203"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="202"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="201"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="200"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="199"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="198"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="197"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="196"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="195"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="235"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="234"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="233"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="232"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="231"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="230"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="229"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="228"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="227"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="226"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="225"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="190"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="189"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="188"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="187"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="186"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="185"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="184"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="183"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="182"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="181"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="180"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="220"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="219"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="218"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="217"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="216"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="215"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="214"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="213"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="212"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="211"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="210"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="173"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="172"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="171"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="170"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="169"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="168"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="167"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="166"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="165"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="205"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="204"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="203"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="202"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="201"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="200"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="199"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="198"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="197"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="196"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="195"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
   <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="160"/>
-    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="159"/>
-    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="158"/>
-    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="157"/>
-    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="156"/>
-    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="155"/>
-    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="154"/>
-    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="153"/>
-    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="152"/>
-    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="151"/>
-    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="150"/>
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="190"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="189"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="188"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="187"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="186"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="185"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="184"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="183"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="182"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="181"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="180"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
   <autoFilter ref="A6:K40" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="142"/>
-    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="140"/>
-    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="139"/>
-    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="138"/>
-    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="137"/>
-    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="136"/>
-    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="135"/>
+    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="174"/>
+    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="173"/>
+    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="172"/>
+    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="171"/>
+    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="170"/>
+    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="169"/>
+    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="168"/>
+    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="167"/>
+    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="166"/>
+    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="165"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -22681,45 +24161,2183 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC62C0B2-BA3F-4506-A1CE-7D714441A411}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="7" width="34.7109375" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
       <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
       <c r="B1" s="28"/>
     </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
       <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
       <c r="B2" s="29"/>
     </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="114">
+      <c r="A8" s="51" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A11" s="51" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+    </row>
+    <row r="14" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A14" s="43" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43" t="s">
+        <v>1667</v>
+      </c>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="99.75">
+      <c r="A15" s="51" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51" t="s">
+        <v>1672</v>
+      </c>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+    </row>
+    <row r="18" spans="1:11" ht="71.25">
+      <c r="A18" s="43" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="71.25">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11" ht="155.25" customHeight="1">
+      <c r="A23" s="51" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>1681</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51" t="s">
+        <v>1683</v>
+      </c>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+    </row>
+    <row r="26" spans="1:11" ht="85.5">
+      <c r="A26" s="43" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43" t="s">
+        <v>1689</v>
+      </c>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="42.75">
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A31" s="49" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D31" s="49" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E31" s="49" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49" t="s">
+        <v>1694</v>
+      </c>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
+    </row>
+    <row r="32" spans="1:11" ht="114">
+      <c r="A32" s="43" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D32" s="43" t="s">
+        <v>1697</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>1698</v>
+      </c>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43" t="s">
+        <v>1700</v>
+      </c>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="43"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A34" s="43"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+    </row>
+    <row r="35" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A35" s="49" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B35" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="49" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49" t="s">
+        <v>1705</v>
+      </c>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
+    </row>
+    <row r="36" spans="1:11" ht="129" thickBot="1">
+      <c r="A36" s="43" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B36" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>1708</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43" t="s">
+        <v>1710</v>
+      </c>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="1:11" ht="114">
+      <c r="A37" s="51" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B37" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>1714</v>
+      </c>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51" t="s">
+        <v>1715</v>
+      </c>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="51"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A39" s="44"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
+    </row>
+    <row r="40" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A40" s="43" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B40" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>1697</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43" t="s">
+        <v>1719</v>
+      </c>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+    </row>
+    <row r="41" spans="1:11" ht="85.5">
+      <c r="A41" s="51" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B41" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51" t="s">
+        <v>1725</v>
+      </c>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="51"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+    </row>
+    <row r="43" spans="1:11" ht="72" thickBot="1">
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+    </row>
+    <row r="44" spans="1:11" ht="143.25" thickBot="1">
+      <c r="A44" s="44" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B44" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D44" s="44" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E44" s="44" t="s">
+        <v>1729</v>
+      </c>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDEA6F1-B543-4F25-B30C-45D0356F1F68}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
       <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
       <c r="B1" s="28"/>
     </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
       <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
       <c r="B2" s="29"/>
     </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="98.25" customHeight="1">
+      <c r="A8" s="51" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>1735</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="71.25">
+      <c r="A11" s="51" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>1739</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51" t="s">
+        <v>1741</v>
+      </c>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="57">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+    </row>
+    <row r="16" spans="1:11" ht="185.25">
+      <c r="A16" s="43" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>1745</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11" ht="71.25">
+      <c r="A19" s="51" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51" t="s">
+        <v>1749</v>
+      </c>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11" ht="57">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+    </row>
+    <row r="24" spans="1:11" ht="85.5">
+      <c r="A24" s="43" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43" t="s">
+        <v>1754</v>
+      </c>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="114">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11" ht="85.5">
+      <c r="A29" s="51" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B29" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51" t="s">
+        <v>1758</v>
+      </c>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="51"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11" ht="128.25">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A33" s="44"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
+    </row>
+    <row r="34" spans="1:11" ht="112.5" customHeight="1">
+      <c r="A34" s="43" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B34" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>1761</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43" t="s">
+        <v>1763</v>
+      </c>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A36" s="43"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="1:11" ht="85.5">
+      <c r="A37" s="51" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B37" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>1761</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51" t="s">
+        <v>1767</v>
+      </c>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="51"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A39" s="44"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
+    </row>
+    <row r="40" spans="1:11" ht="129" thickBot="1">
+      <c r="A40" s="43" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B40" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43" t="s">
+        <v>1772</v>
+      </c>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+    </row>
+    <row r="41" spans="1:11" ht="85.5">
+      <c r="A41" s="51" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B41" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>1775</v>
+      </c>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="51"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+    </row>
+    <row r="43" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+    </row>
+    <row r="44" spans="1:11" ht="114">
+      <c r="A44" s="43" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B44" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43" t="s">
+        <v>1781</v>
+      </c>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:11" ht="42.75">
+      <c r="A46" s="43"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A48" s="43"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" spans="1:11" ht="155.25" customHeight="1">
+      <c r="A49" s="51" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B49" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="51" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D49" s="51" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E49" s="51" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F49" s="51"/>
+      <c r="G49" s="51" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H49" s="51"/>
+      <c r="I49" s="51"/>
+      <c r="J49" s="51"/>
+      <c r="K49" s="51"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+    </row>
+    <row r="51" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A51" s="44"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+    </row>
+    <row r="52" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A52" s="43" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B52" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D52" s="43" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43" t="s">
+        <v>1790</v>
+      </c>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+    </row>
+    <row r="53" spans="1:11" ht="57">
+      <c r="A53" s="51" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B53" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="51" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D53" s="51" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E53" s="51" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F53" s="51"/>
+      <c r="G53" s="51" t="s">
+        <v>1794</v>
+      </c>
+      <c r="H53" s="51"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="51"/>
+      <c r="K53" s="51"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="43"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+    </row>
+    <row r="55" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A55" s="44"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
+    </row>
+    <row r="56" spans="1:11" ht="85.5">
+      <c r="A56" s="43" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B56" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C56" s="43" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D56" s="43" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E56" s="43" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43" t="s">
+        <v>1799</v>
+      </c>
+      <c r="H56" s="43"/>
+      <c r="I56" s="43"/>
+      <c r="J56" s="43"/>
+      <c r="K56" s="43"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="43"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="43"/>
+      <c r="I57" s="43"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="43"/>
+    </row>
+    <row r="58" spans="1:11" ht="114">
+      <c r="A58" s="43"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43" t="s">
+        <v>1798</v>
+      </c>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="43"/>
+      <c r="J58" s="43"/>
+      <c r="K58" s="43"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="43"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="43"/>
+    </row>
+    <row r="60" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A60" s="43"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F60" s="43"/>
+      <c r="G60" s="43"/>
+      <c r="H60" s="43"/>
+      <c r="I60" s="43"/>
+      <c r="J60" s="43"/>
+      <c r="K60" s="43"/>
+    </row>
+    <row r="61" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A61" s="49" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B61" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61" s="49" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D61" s="49" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E61" s="49" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F61" s="49"/>
+      <c r="G61" s="49" t="s">
+        <v>1803</v>
+      </c>
+      <c r="H61" s="49"/>
+      <c r="I61" s="49"/>
+      <c r="J61" s="49"/>
+      <c r="K61" s="49"/>
+    </row>
+    <row r="62" spans="1:11" ht="57">
+      <c r="A62" s="43" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B62" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="43" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D62" s="43" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E62" s="43" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F62" s="43"/>
+      <c r="G62" s="43" t="s">
+        <v>1807</v>
+      </c>
+      <c r="H62" s="43"/>
+      <c r="I62" s="43"/>
+      <c r="J62" s="43"/>
+      <c r="K62" s="43"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="43"/>
+      <c r="I63" s="43"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+    </row>
+    <row r="64" spans="1:11" ht="57">
+      <c r="A64" s="43"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="43" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F64" s="43"/>
+      <c r="G64" s="43"/>
+      <c r="H64" s="43"/>
+      <c r="I64" s="43"/>
+      <c r="J64" s="43"/>
+      <c r="K64" s="43"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="43"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="43"/>
+      <c r="G65" s="43"/>
+      <c r="H65" s="43"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+    </row>
+    <row r="66" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A66" s="43"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="43"/>
+    </row>
+    <row r="67" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A67" s="49" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B67" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F67" s="49"/>
+      <c r="G67" s="49" t="s">
+        <v>1812</v>
+      </c>
+      <c r="H67" s="49"/>
+      <c r="I67" s="49"/>
+      <c r="J67" s="49"/>
+      <c r="K67" s="49"/>
+    </row>
+    <row r="68" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A68" s="43" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B68" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68" s="43" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D68" s="43" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E68" s="43" t="s">
+        <v>1815</v>
+      </c>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="43"/>
+    </row>
+    <row r="69" spans="1:11" ht="99.75">
+      <c r="A69" s="51" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B69" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C69" s="51" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D69" s="51" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E69" s="51" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51" t="s">
+        <v>1821</v>
+      </c>
+      <c r="H69" s="51"/>
+      <c r="I69" s="51"/>
+      <c r="J69" s="51"/>
+      <c r="K69" s="51"/>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="43"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="43"/>
+      <c r="D70" s="43"/>
+      <c r="E70" s="45"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="43"/>
+      <c r="H70" s="43"/>
+      <c r="I70" s="43"/>
+      <c r="J70" s="43"/>
+      <c r="K70" s="43"/>
+    </row>
+    <row r="71" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A71" s="44"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="44"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="44" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F71" s="44"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="44"/>
+      <c r="I71" s="44"/>
+      <c r="J71" s="44"/>
+      <c r="K71" s="44"/>
+    </row>
+    <row r="72" spans="1:11" ht="85.5">
+      <c r="A72" s="43" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B72" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C72" s="43" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D72" s="43" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E72" s="43" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43" t="s">
+        <v>1825</v>
+      </c>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="43"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="45"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="43"/>
+      <c r="H73" s="43"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="43"/>
+      <c r="K73" s="43"/>
+    </row>
+    <row r="74" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A74" s="43"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="43"/>
+      <c r="E74" s="43" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F74" s="43"/>
+      <c r="G74" s="43"/>
+      <c r="H74" s="43"/>
+      <c r="I74" s="43"/>
+      <c r="J74" s="43"/>
+      <c r="K74" s="43"/>
+    </row>
+    <row r="75" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A75" s="49" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B75" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="49" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D75" s="49" t="s">
+        <v>1828</v>
+      </c>
+      <c r="E75" s="49" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
+      <c r="J75" s="49"/>
+      <c r="K75" s="49"/>
+    </row>
+    <row r="76" spans="1:11" ht="72" thickBot="1">
+      <c r="A76" s="43" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B76" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" s="43" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D76" s="43" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E76" s="43" t="s">
+        <v>1834</v>
+      </c>
+      <c r="F76" s="43"/>
+      <c r="G76" s="43" t="s">
+        <v>1835</v>
+      </c>
+      <c r="H76" s="43"/>
+      <c r="I76" s="43"/>
+      <c r="J76" s="43"/>
+      <c r="K76" s="43"/>
+    </row>
+    <row r="77" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A77" s="51" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B77" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77" s="51" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D77" s="51" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E77" s="51" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F77" s="51"/>
+      <c r="G77" s="51" t="s">
+        <v>1841</v>
+      </c>
+      <c r="H77" s="51"/>
+      <c r="I77" s="51"/>
+      <c r="J77" s="51"/>
+      <c r="K77" s="51"/>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="43"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="43"/>
+      <c r="D78" s="43"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="43"/>
+      <c r="G78" s="43"/>
+      <c r="H78" s="43"/>
+      <c r="I78" s="43"/>
+      <c r="J78" s="43"/>
+      <c r="K78" s="43"/>
+    </row>
+    <row r="79" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A79" s="44"/>
+      <c r="B79" s="44"/>
+      <c r="C79" s="44"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="44" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="44"/>
+      <c r="J79" s="44"/>
+      <c r="K79" s="44"/>
+    </row>
+    <row r="80" spans="1:11" ht="114">
+      <c r="A80" s="43" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B80" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C80" s="43" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D80" s="43" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E80" s="43" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F80" s="43"/>
+      <c r="G80" s="43" t="s">
+        <v>1847</v>
+      </c>
+      <c r="H80" s="43"/>
+      <c r="I80" s="43"/>
+      <c r="J80" s="43"/>
+      <c r="K80" s="43"/>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="43"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="43"/>
+      <c r="D81" s="43"/>
+      <c r="E81" s="45"/>
+      <c r="F81" s="43"/>
+      <c r="G81" s="43"/>
+      <c r="H81" s="43"/>
+      <c r="I81" s="43"/>
+      <c r="J81" s="43"/>
+      <c r="K81" s="43"/>
+    </row>
+    <row r="82" spans="1:11" ht="28.5">
+      <c r="A82" s="43"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="43"/>
+      <c r="D82" s="43"/>
+      <c r="E82" s="43" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F82" s="43"/>
+      <c r="G82" s="43"/>
+      <c r="H82" s="43"/>
+      <c r="I82" s="43"/>
+      <c r="J82" s="43"/>
+      <c r="K82" s="43"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="43"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="43"/>
+      <c r="D83" s="43"/>
+      <c r="E83" s="45"/>
+      <c r="F83" s="43"/>
+      <c r="G83" s="43"/>
+      <c r="H83" s="43"/>
+      <c r="I83" s="43"/>
+      <c r="J83" s="43"/>
+      <c r="K83" s="43"/>
+    </row>
+    <row r="84" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A84" s="44"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44" t="s">
+        <v>1846</v>
+      </c>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="44"/>
+      <c r="J84" s="44"/>
+      <c r="K84" s="44"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B77AE1-BA4F-4910-BC26-62C809E5130A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55E063F-7F16-4D8C-BBCA-DDBA0916BB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="18" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="11" activeTab="19" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,8 @@
     <sheet name="Cart" sheetId="16" r:id="rId16"/>
     <sheet name="Coupon" sheetId="17" r:id="rId17"/>
     <sheet name="Shipping" sheetId="18" r:id="rId18"/>
-    <sheet name="Sheet4" sheetId="19" r:id="rId19"/>
-    <sheet name="Sheet5" sheetId="20" r:id="rId20"/>
+    <sheet name="GuestCheckout" sheetId="19" r:id="rId19"/>
+    <sheet name="RegisteredAccCheckout" sheetId="20" r:id="rId20"/>
     <sheet name="Sheet6" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="1848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3074" uniqueCount="1914">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -6017,6 +6017,204 @@
   </si>
   <si>
     <t>The user can successfully navigate backward through the accordion, modify data, and the session retains the new updates.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_001</t>
+  </si>
+  <si>
+    <t>Verify navigation to Checkout for a logged-in user</t>
+  </si>
+  <si>
+    <t>User is logged in and has a physical item in the cart</t>
+  </si>
+  <si>
+    <t>User is routed to the Checkout page. "Step 1: Checkout Options" is bypassed automatically, and "Step 2: Billing Details" is expanded.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_002</t>
+  </si>
+  <si>
+    <t>Verify Billing Details using an 'Existing Address'</t>
+  </si>
+  <si>
+    <t>User is on Step 2: Billing Details and has a saved address</t>
+  </si>
+  <si>
+    <t>1. Select the "I want to use an existing billing address" radio button.</t>
+  </si>
+  <si>
+    <t>2. Select an address from the dropdown.</t>
+  </si>
+  <si>
+    <t>Step 2 submits successfully, and "Step 3: Delivery Details" expands.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_003</t>
+  </si>
+  <si>
+    <t>Verify Billing Details adding a 'New Address' with valid data</t>
+  </si>
+  <si>
+    <t>1. Select the "I want to use a new billing address" radio button.</t>
+  </si>
+  <si>
+    <t>2. Fill all mandatory fields with valid data.</t>
+  </si>
+  <si>
+    <t>Step 2 submits successfully. The new address is saved to the user's account, and Step 3 expands.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_004</t>
+  </si>
+  <si>
+    <t>Verify validation adding a 'New Address' with missing fields in Billing</t>
+  </si>
+  <si>
+    <t>1. Select "I want to use a new billing address".</t>
+  </si>
+  <si>
+    <t>2. Leave mandatory fields blank.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_005</t>
+  </si>
+  <si>
+    <t>Verify Delivery Details using an 'Existing Address'</t>
+  </si>
+  <si>
+    <t>User is on Step 3: Delivery Details and has a saved address</t>
+  </si>
+  <si>
+    <t>1. Select the "I want to use an existing delivery address" radio button.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_006</t>
+  </si>
+  <si>
+    <t>Verify Delivery Details adding a 'New Address' with valid data</t>
+  </si>
+  <si>
+    <t>1. Select the "I want to use a new delivery address" radio button.</t>
+  </si>
+  <si>
+    <t>Step 3 submits successfully. The new address is saved, and Step 4 expands.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_007</t>
+  </si>
+  <si>
+    <t>Verify validation adding a 'New Address' with missing fields in Delivery</t>
+  </si>
+  <si>
+    <t>1. Select "I want to use a new delivery address".</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_008</t>
+  </si>
+  <si>
+    <t>Verify UI toggle between 'Existing' and 'New' address options</t>
+  </si>
+  <si>
+    <t>User is on Step 2 or Step 3</t>
+  </si>
+  <si>
+    <t>1. Click "I want to use a new address".</t>
+  </si>
+  <si>
+    <t>2. Click "I want to use an existing address".</t>
+  </si>
+  <si>
+    <t>The UI smoothly toggles between showing the blank form fields and showing the saved address dropdown list.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_009</t>
+  </si>
+  <si>
+    <t>Verify Delivery Method options load based on saved address</t>
+  </si>
+  <si>
+    <t>The system successfully calculates and displays available shipping methods based on the specific address selected in Step 3.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_010</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_011</t>
+  </si>
+  <si>
+    <t>Verify 'Add Comments About Your Order' functionality</t>
+  </si>
+  <si>
+    <t>1. Type a message in the comments text area.</t>
+  </si>
+  <si>
+    <t>Step 4 submits successfully, and "Step 5: Payment Method" expands. The comment is saved to the order session.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_012</t>
+  </si>
+  <si>
+    <t>Verify Payment Method options load correctly</t>
+  </si>
+  <si>
+    <t>The system successfully displays all available payment methods configured for registered users in that region.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_013</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_014</t>
+  </si>
+  <si>
+    <t>Step 5 does not submit. A warning banner states that the user must agree to the Terms &amp; Conditions.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_015</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_016</t>
+  </si>
+  <si>
+    <t>Product Name, Model, Quantity, and Unit Price exactly match the items the user added to their shopping cart.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_017</t>
+  </si>
+  <si>
+    <t>Verify Order Confirmation Totals recalculate accurately</t>
+  </si>
+  <si>
+    <t>1. Review the Totals section.</t>
+  </si>
+  <si>
+    <t>The shipping line item matches the cost selected in Step 4, taxes are calculated based on the saved address, and the Final Total is mathematically accurate.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_018</t>
+  </si>
+  <si>
+    <t>1. Ensure an offline payment method is selected.</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_019</t>
+  </si>
+  <si>
+    <t>Verify Order History is updated after successful checkout</t>
+  </si>
+  <si>
+    <t>1. Navigate to My Account &gt; Order History.</t>
+  </si>
+  <si>
+    <t>The newly placed order is immediately visible in the list with a status of 'Pending' (or the configured default status).</t>
+  </si>
+  <si>
+    <t>TC_REGCHK_020</t>
+  </si>
+  <si>
+    <t>Verify cart is emptied after successful registered checkout</t>
+  </si>
+  <si>
+    <t>The shopping cart is completely empty, confirming the session cleared the purchased items.</t>
   </si>
 </sst>
 </file>
@@ -6812,7 +7010,466 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="284">
+  <dxfs count="299">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -14371,265 +15028,285 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="268">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="283">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="267"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="266"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="282"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="281"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
   <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="160"/>
-    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="159"/>
-    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="158"/>
-    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="157"/>
-    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="156"/>
-    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="155"/>
-    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="154"/>
-    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="153"/>
-    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="152"/>
-    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="151"/>
-    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="150"/>
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="174"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="173"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="172"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="171"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="170"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="169"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="168"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="167"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="166"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="165"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
   <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="142"/>
-    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="140"/>
-    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="139"/>
-    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="138"/>
-    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="137"/>
-    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="136"/>
-    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="135"/>
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="157"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="156"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="155"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="154"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="153"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="152"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="151"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
   <autoFilter ref="A7:K49" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="130"/>
-    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="129"/>
-    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="127"/>
-    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="126"/>
-    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="125"/>
-    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="124"/>
-    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="123"/>
-    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="122"/>
-    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="121"/>
-    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
   <autoFilter ref="A7:K55" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="128"/>
+    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="127"/>
+    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="123"/>
+    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="122"/>
+    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="121"/>
+    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
   <autoFilter ref="A7:K62" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="110"/>
+    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="105"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
   <autoFilter ref="A7:K84" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="283" dataDxfId="281" headerRowBorderDxfId="282" tableBorderDxfId="280">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="298" dataDxfId="296" headerRowBorderDxfId="297" tableBorderDxfId="295">
   <autoFilter ref="A7:K32" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="279"/>
-    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="278"/>
-    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="277"/>
-    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="276"/>
-    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="275"/>
-    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="274"/>
-    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="273"/>
-    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="272"/>
-    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="271"/>
-    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="270"/>
-    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="269"/>
+    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="294"/>
+    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="293"/>
+    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="292"/>
+    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="291"/>
+    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="290"/>
+    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="289"/>
+    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="288"/>
+    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="287"/>
+    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="286"/>
+    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="285"/>
+    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="284"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="72" dataDxfId="74" headerRowBorderDxfId="73" tableBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="87" dataDxfId="89" headerRowBorderDxfId="88" tableBorderDxfId="86">
   <autoFilter ref="A7:K48" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="56" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="71" dataDxfId="74" headerRowBorderDxfId="72" tableBorderDxfId="73">
   <autoFilter ref="A7:K72" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="41" dataDxfId="44" headerRowBorderDxfId="42" tableBorderDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="56" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
   <autoFilter ref="A7:K65" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="265" dataDxfId="263" headerRowBorderDxfId="264" tableBorderDxfId="262" totalsRowBorderDxfId="261">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="280" dataDxfId="278" headerRowBorderDxfId="279" tableBorderDxfId="277" totalsRowBorderDxfId="276">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="260"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="259"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="258"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="257"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="256"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="275"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="274"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="273"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="272"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="271"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}" name="Table20" displayName="Table20" ref="A7:K44" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}" name="Table20" displayName="Table20" ref="A7:K44" totalsRowShown="0" headerRowDxfId="41" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
   <autoFilter ref="A7:K44" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E9107AEB-9917-4DCD-999F-23DED7528269}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{4E7F2B0A-9A06-45D9-829D-517139E93FB0}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{09C2C301-9101-42D2-87C5-CF12D84AFDE2}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{4630FF91-0DD6-4E25-827E-20AC0C3327F3}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{6ACC0A37-29EE-49DB-857B-3EF893C5DD7D}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{2AF81478-C083-4718-B4FE-A5FEC39D4683}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{7FDCD6DB-5E88-42AB-9324-CD156B2F76E1}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{8B796E38-6BAF-4EB8-846A-DFC533AC8C87}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{362BE16E-720C-4E90-AFB8-ED627DE3BEF5}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{E7237EFD-FF4D-4C9B-98AD-189BF6BF0535}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{35851930-6F01-4446-835F-13E1EDBAF070}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{E9107AEB-9917-4DCD-999F-23DED7528269}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{4E7F2B0A-9A06-45D9-829D-517139E93FB0}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{09C2C301-9101-42D2-87C5-CF12D84AFDE2}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{4630FF91-0DD6-4E25-827E-20AC0C3327F3}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{6ACC0A37-29EE-49DB-857B-3EF893C5DD7D}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{2AF81478-C083-4718-B4FE-A5FEC39D4683}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{7FDCD6DB-5E88-42AB-9324-CD156B2F76E1}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{8B796E38-6BAF-4EB8-846A-DFC533AC8C87}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{362BE16E-720C-4E90-AFB8-ED627DE3BEF5}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{E7237EFD-FF4D-4C9B-98AD-189BF6BF0535}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{35851930-6F01-4446-835F-13E1EDBAF070}" name="Comments" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}" name="Table21" displayName="Table21" ref="A7:K84" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}" name="Table21" displayName="Table21" ref="A7:K84" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A7:K84" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{15029807-7F0E-425A-BB46-0B6DB3C95839}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{7BD8F686-C564-499F-8D06-C85E47BDAB51}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{67E25BA4-3FF0-4F70-B233-F0E251B42D26}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{B181D3E8-3A2C-400F-B359-B20568BAB1D1}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{B58B21E5-45D9-46DC-BFE5-78BDC714CE7C}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{7D364936-A237-464A-A78D-51E3CF7B08EF}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{DD78F72F-2F82-49C0-857B-9230594DFC47}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{DD233399-E0C4-4DCB-918E-551AD68ACB5A}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{8D1587AC-EA15-44E2-A0C1-155707A09C86}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{B82BB21B-0563-40CE-B8DB-5D4ADE46287B}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{B4AF1D65-2623-4B0C-9A46-AAAF78C4F53B}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{15029807-7F0E-425A-BB46-0B6DB3C95839}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{7BD8F686-C564-499F-8D06-C85E47BDAB51}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{67E25BA4-3FF0-4F70-B233-F0E251B42D26}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{B181D3E8-3A2C-400F-B359-B20568BAB1D1}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{B58B21E5-45D9-46DC-BFE5-78BDC714CE7C}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{7D364936-A237-464A-A78D-51E3CF7B08EF}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{DD78F72F-2F82-49C0-857B-9230594DFC47}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{DD233399-E0C4-4DCB-918E-551AD68ACB5A}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{8D1587AC-EA15-44E2-A0C1-155707A09C86}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{B82BB21B-0563-40CE-B8DB-5D4ADE46287B}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{B4AF1D65-2623-4B0C-9A46-AAAF78C4F53B}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}" name="Table22" displayName="Table22" ref="A7:K73" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+  <autoFilter ref="A7:K73" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{9C094CDF-2D28-4BE3-99E2-FE5BD3E1EFED}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{94350EDF-00E0-425A-8D59-A436A634832D}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{46F08573-9A97-4833-A375-E13614AB1CD1}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{9CAFA43D-2ED9-4B71-B10E-703FE41DF889}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{6B1DCF0A-0BAA-40AF-A30E-7AF7E59D4B32}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{254FF740-551F-44C6-85E3-0201E5C78A60}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{37BC01A3-6D35-4AC9-B6E3-D024ABF0F7F6}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{490207E0-C5D6-4F92-A004-D0982BA6E84D}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{2D195591-BB51-4C69-8149-6B4BCC5DCE19}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{D3EB2765-8091-404B-AF58-2635762A163C}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{EA1CCBEC-876B-40ED-8BDE-8E73CB5ABE7B}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14639,7 +15316,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="255"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="270"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14647,120 +15324,120 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="269" dataDxfId="267" headerRowBorderDxfId="268" tableBorderDxfId="266">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="250"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="249"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="248"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="247"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="246"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="245"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="244"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="243"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="242"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="241"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="240"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="265"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="264"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="263"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="262"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="261"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="260"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="259"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="258"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="257"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="256"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="255"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="235"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="234"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="233"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="232"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="231"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="230"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="229"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="228"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="227"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="226"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="225"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="250"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="249"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="248"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="247"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="246"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="245"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="244"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="243"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="242"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="241"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="240"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="220"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="219"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="218"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="217"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="216"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="215"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="214"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="213"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="212"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="211"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="210"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="235"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="234"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="233"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="232"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="231"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="230"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="229"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="228"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="227"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="226"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="225"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="205"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="204"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="203"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="202"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="201"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="200"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="199"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="198"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="197"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="196"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="195"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="220"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="219"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="218"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="217"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="216"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="215"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="214"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="213"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="212"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="211"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="210"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
   <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="190"/>
-    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="189"/>
-    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="188"/>
-    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="187"/>
-    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="186"/>
-    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="185"/>
-    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="184"/>
-    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="183"/>
-    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="182"/>
-    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="181"/>
-    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="180"/>
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="205"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="204"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="203"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="202"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="201"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="200"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="199"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="198"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="197"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="196"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="195"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
   <autoFilter ref="A6:K40" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="173"/>
-    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="172"/>
-    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="171"/>
-    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="170"/>
-    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="169"/>
-    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="168"/>
-    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="167"/>
-    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="166"/>
-    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="165"/>
+    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="190"/>
+    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="189"/>
+    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="188"/>
+    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="187"/>
+    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="186"/>
+    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="185"/>
+    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="184"/>
+    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="183"/>
+    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="182"/>
+    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="181"/>
+    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="180"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -28332,23 +29009,1218 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E932FD0D-9602-46DA-B200-F81F31FA9698}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" customWidth="1"/>
+    <col min="7" max="7" width="33.5703125" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="23.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
       <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
       <c r="B1" s="28"/>
     </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
       <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
       <c r="B2" s="29"/>
     </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="212.25" customHeight="1">
+      <c r="A8" s="51" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>1851</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="85.5">
+      <c r="A11" s="51" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>1855</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51" t="s">
+        <v>1857</v>
+      </c>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="57">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+    </row>
+    <row r="16" spans="1:11" ht="85.5">
+      <c r="A16" s="43" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>1860</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="57">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11" ht="71.25">
+      <c r="A21" s="51" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11" ht="42.75">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43" t="s">
+        <v>1866</v>
+      </c>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+    </row>
+    <row r="26" spans="1:11" ht="85.5">
+      <c r="A26" s="43" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>1870</v>
+      </c>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43" t="s">
+        <v>1767</v>
+      </c>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="57">
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11" ht="85.5">
+      <c r="A31" s="51" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B31" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>1761</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51" t="s">
+        <v>1874</v>
+      </c>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11" ht="57">
+      <c r="A33" s="43"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="43"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+    </row>
+    <row r="35" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
+    </row>
+    <row r="36" spans="1:11" ht="71.25">
+      <c r="A36" s="43" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B36" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>1761</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43" t="s">
+        <v>1763</v>
+      </c>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="42.75">
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43" t="s">
+        <v>1866</v>
+      </c>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A40" s="43"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+    </row>
+    <row r="41" spans="1:11" ht="99.75">
+      <c r="A41" s="51" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B41" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51" t="s">
+        <v>1883</v>
+      </c>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="51"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+    </row>
+    <row r="43" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44" t="s">
+        <v>1882</v>
+      </c>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+    </row>
+    <row r="44" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A44" s="43" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B44" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43" t="s">
+        <v>1886</v>
+      </c>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" spans="1:11" ht="85.5">
+      <c r="A45" s="51" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B45" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="51" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D45" s="51" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E45" s="51" t="s">
+        <v>1775</v>
+      </c>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
+      <c r="K45" s="51"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="43"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+    </row>
+    <row r="47" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+    </row>
+    <row r="48" spans="1:11" ht="99.75">
+      <c r="A48" s="43" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B48" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E48" s="43" t="s">
+        <v>1890</v>
+      </c>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43" t="s">
+        <v>1891</v>
+      </c>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="43"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+    </row>
+    <row r="50" spans="1:11" ht="42.75">
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="43"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+    </row>
+    <row r="52" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A52" s="43"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+    </row>
+    <row r="53" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A53" s="49" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B53" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" s="49" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D53" s="49" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E53" s="49" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F53" s="49"/>
+      <c r="G53" s="49" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H53" s="49"/>
+      <c r="I53" s="49"/>
+      <c r="J53" s="49"/>
+      <c r="K53" s="49"/>
+    </row>
+    <row r="54" spans="1:11" ht="57">
+      <c r="A54" s="43" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B54" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" s="43" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D54" s="43" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E54" s="43" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43" t="s">
+        <v>1794</v>
+      </c>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="43"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43"/>
+    </row>
+    <row r="56" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A56" s="43"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="43"/>
+      <c r="J56" s="43"/>
+      <c r="K56" s="43"/>
+    </row>
+    <row r="57" spans="1:11" ht="85.5">
+      <c r="A57" s="51" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B57" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C57" s="51" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D57" s="51" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E57" s="51" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F57" s="51"/>
+      <c r="G57" s="51" t="s">
+        <v>1897</v>
+      </c>
+      <c r="H57" s="51"/>
+      <c r="I57" s="51"/>
+      <c r="J57" s="51"/>
+      <c r="K57" s="51"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="43"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="45"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="43"/>
+      <c r="J58" s="43"/>
+      <c r="K58" s="43"/>
+    </row>
+    <row r="59" spans="1:11" ht="114">
+      <c r="A59" s="43"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="43" t="s">
+        <v>1798</v>
+      </c>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="43"/>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="43"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="45"/>
+      <c r="F60" s="43"/>
+      <c r="G60" s="43"/>
+      <c r="H60" s="43"/>
+      <c r="I60" s="43"/>
+      <c r="J60" s="43"/>
+      <c r="K60" s="43"/>
+    </row>
+    <row r="61" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A61" s="44"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="44"/>
+      <c r="J61" s="44"/>
+      <c r="K61" s="44"/>
+    </row>
+    <row r="62" spans="1:11" ht="57">
+      <c r="A62" s="43" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B62" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="43" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D62" s="43" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E62" s="43" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F62" s="43"/>
+      <c r="G62" s="43" t="s">
+        <v>1807</v>
+      </c>
+      <c r="H62" s="43"/>
+      <c r="I62" s="43"/>
+      <c r="J62" s="43"/>
+      <c r="K62" s="43"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="43"/>
+      <c r="I63" s="43"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+    </row>
+    <row r="64" spans="1:11" ht="57">
+      <c r="A64" s="43"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="43" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F64" s="43"/>
+      <c r="G64" s="43"/>
+      <c r="H64" s="43"/>
+      <c r="I64" s="43"/>
+      <c r="J64" s="43"/>
+      <c r="K64" s="43"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="43"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="43"/>
+      <c r="G65" s="43"/>
+      <c r="H65" s="43"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+    </row>
+    <row r="66" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A66" s="43"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="43"/>
+    </row>
+    <row r="67" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A67" s="49" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B67" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F67" s="49"/>
+      <c r="G67" s="49" t="s">
+        <v>1900</v>
+      </c>
+      <c r="H67" s="49"/>
+      <c r="I67" s="49"/>
+      <c r="J67" s="49"/>
+      <c r="K67" s="49"/>
+    </row>
+    <row r="68" spans="1:11" ht="143.25" thickBot="1">
+      <c r="A68" s="43" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B68" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" s="43" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D68" s="43" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E68" s="43" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43" t="s">
+        <v>1904</v>
+      </c>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="43"/>
+    </row>
+    <row r="69" spans="1:11" ht="99.75">
+      <c r="A69" s="51" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B69" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" s="51" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D69" s="51" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E69" s="51" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51" t="s">
+        <v>1821</v>
+      </c>
+      <c r="H69" s="51"/>
+      <c r="I69" s="51"/>
+      <c r="J69" s="51"/>
+      <c r="K69" s="51"/>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="43"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="43"/>
+      <c r="D70" s="43"/>
+      <c r="E70" s="45"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="43"/>
+      <c r="H70" s="43"/>
+      <c r="I70" s="43"/>
+      <c r="J70" s="43"/>
+      <c r="K70" s="43"/>
+    </row>
+    <row r="71" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A71" s="44"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="44"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="44" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F71" s="44"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="44"/>
+      <c r="I71" s="44"/>
+      <c r="J71" s="44"/>
+      <c r="K71" s="44"/>
+    </row>
+    <row r="72" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A72" s="43" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B72" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C72" s="43" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D72" s="43" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E72" s="43" t="s">
+        <v>1909</v>
+      </c>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+    </row>
+    <row r="73" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A73" s="49" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B73" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="49" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D73" s="49" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E73" s="49" t="s">
+        <v>1834</v>
+      </c>
+      <c r="F73" s="49"/>
+      <c r="G73" s="49" t="s">
+        <v>1913</v>
+      </c>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49"/>
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55E063F-7F16-4D8C-BBCA-DDBA0916BB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1613D0A3-1A32-45E8-ACCE-32F126F0F8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="11" activeTab="19" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="14" activeTab="21" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,11 @@
     <sheet name="Shipping" sheetId="18" r:id="rId18"/>
     <sheet name="GuestCheckout" sheetId="19" r:id="rId19"/>
     <sheet name="RegisteredAccCheckout" sheetId="20" r:id="rId20"/>
-    <sheet name="Sheet6" sheetId="21" r:id="rId21"/>
+    <sheet name="PaymentGateway" sheetId="21" r:id="rId21"/>
+    <sheet name="MyAccDashboard" sheetId="22" r:id="rId22"/>
+    <sheet name="Sheet8" sheetId="23" r:id="rId23"/>
+    <sheet name="Sheet9" sheetId="24" r:id="rId24"/>
+    <sheet name="Sheet10" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3074" uniqueCount="1914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="2043">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -6215,6 +6219,393 @@
   </si>
   <si>
     <t>The shopping cart is completely empty, confirming the session cleared the purchased items.</t>
+  </si>
+  <si>
+    <t>TC_PAY_001</t>
+  </si>
+  <si>
+    <t>Verify successful order completion using Cash On Delivery (COD)</t>
+  </si>
+  <si>
+    <t>User is on Step 6: Confirm Order with COD selected</t>
+  </si>
+  <si>
+    <t>1. Click 'Confirm Order'.</t>
+  </si>
+  <si>
+    <t>The order processes immediately without external redirection, and the user is routed to the Checkout Success page.</t>
+  </si>
+  <si>
+    <t>TC_PAY_002</t>
+  </si>
+  <si>
+    <t>Verify successful order completion using Bank Transfer</t>
+  </si>
+  <si>
+    <t>User is on Step 6: Confirm Order with Bank Transfer selected</t>
+  </si>
+  <si>
+    <t>The order processes immediately. The user is routed to the Checkout Success page, and bank transfer instructions are displayed or emailed.</t>
+  </si>
+  <si>
+    <t>TC_PAY_003</t>
+  </si>
+  <si>
+    <t>Verify redirection to an external Payment Gateway (e.g., PayPal Standard)</t>
+  </si>
+  <si>
+    <t>User is on Step 6: Confirm Order with PayPal selected</t>
+  </si>
+  <si>
+    <t>The user is securely redirected away from the store to the external PayPal login/payment page.</t>
+  </si>
+  <si>
+    <t>TC_PAY_004</t>
+  </si>
+  <si>
+    <t>Verify successful payment via external Gateway redirects to Success Page</t>
+  </si>
+  <si>
+    <t>User is on the external PayPal payment page</t>
+  </si>
+  <si>
+    <t>1. Complete the payment using valid sandbox/test credentials.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Return to Merchant' button (if not auto-redirected).</t>
+  </si>
+  <si>
+    <t>The user is routed securely back to the OpenCart Checkout Success page.</t>
+  </si>
+  <si>
+    <t>TC_PAY_005</t>
+  </si>
+  <si>
+    <t>Verify canceling payment at external Gateway</t>
+  </si>
+  <si>
+    <t>1. Click the 'Cancel and return to [Store Name]' link on the gateway page.</t>
+  </si>
+  <si>
+    <t>The user is routed back to the OpenCart Shopping Cart or Checkout page. The order is NOT completed, and the cart remains intact.</t>
+  </si>
+  <si>
+    <t>TC_PAY_006</t>
+  </si>
+  <si>
+    <t>Verify validation for blank fields on inline Credit Card forms (e.g., Stripe/Authorize.Net)</t>
+  </si>
+  <si>
+    <t>User is on Step 6 with an inline CC method selected</t>
+  </si>
+  <si>
+    <t>1. Leave the Card Number, Expiry, and CVV fields blank.</t>
+  </si>
+  <si>
+    <t>The order does not process. Validation error messages appear prompting the user to enter card details.</t>
+  </si>
+  <si>
+    <t>TC_PAY_007</t>
+  </si>
+  <si>
+    <t>Verify validation for invalid Credit Card format</t>
+  </si>
+  <si>
+    <t>1. Enter an invalid card number format (e.g., too few digits or letters).</t>
+  </si>
+  <si>
+    <t>2. Fill Expiry and CVV.</t>
+  </si>
+  <si>
+    <t>3. Click 'Confirm Order'.</t>
+  </si>
+  <si>
+    <t>The gateway rejects the input, and a validation warning is displayed to the user.</t>
+  </si>
+  <si>
+    <t>TC_PAY_008</t>
+  </si>
+  <si>
+    <t>Verify validation for an expired Credit Card</t>
+  </si>
+  <si>
+    <t>1. Enter a valid test card number.</t>
+  </si>
+  <si>
+    <t>2. Enter an Expiry date that is in the past.</t>
+  </si>
+  <si>
+    <t>The gateway rejects the input, and an "Expired Card" validation warning is displayed.</t>
+  </si>
+  <si>
+    <t>TC_PAY_009</t>
+  </si>
+  <si>
+    <t>Verify validation for an incorrect CVV</t>
+  </si>
+  <si>
+    <t>1. Enter a valid test card number and expiry.</t>
+  </si>
+  <si>
+    <t>2. Enter a deliberately incorrect/invalid CVV code.</t>
+  </si>
+  <si>
+    <t>The gateway declines the transaction, and an error message regarding the CVV is displayed.</t>
+  </si>
+  <si>
+    <t>TC_PAY_010</t>
+  </si>
+  <si>
+    <t>Verify declined transaction handling (e.g., insufficient funds)</t>
+  </si>
+  <si>
+    <t>1. Enter a test card number specifically configured to simulate a bank decline.</t>
+  </si>
+  <si>
+    <t>The transaction is declined by the bank/gateway. An error message is displayed (e.g., "Card Declined"), and the order is not finalized.</t>
+  </si>
+  <si>
+    <t>TC_PAY_011</t>
+  </si>
+  <si>
+    <t>Verify successful order completion via inline Credit Card</t>
+  </si>
+  <si>
+    <t>1. Enter valid test card details (Number, Expiry, CVV).</t>
+  </si>
+  <si>
+    <t>The transaction is approved by the gateway, and the user is routed to the Checkout Success page.</t>
+  </si>
+  <si>
+    <t>TC_PAY_012</t>
+  </si>
+  <si>
+    <t>Verify Order Status update via IPN/Webhook</t>
+  </si>
+  <si>
+    <t>A successful external payment (e.g., PayPal) has just been completed</t>
+  </si>
+  <si>
+    <t>1. Log into the OpenCart Admin Panel.</t>
+  </si>
+  <si>
+    <t>2. Navigate to Sales &gt; Orders.</t>
+  </si>
+  <si>
+    <t>3. Check the status of the newly created order.</t>
+  </si>
+  <si>
+    <t>The gateway's Instant Payment Notification (IPN) successfully communicated with OpenCart, automatically updating the order status to 'Processing' or 'Complete'.</t>
+  </si>
+  <si>
+    <t>TC_PAY_013</t>
+  </si>
+  <si>
+    <t>Verify Order Confirmation Email is sent to the Customer</t>
+  </si>
+  <si>
+    <t>1. Open the inbox of the email address used during checkout.</t>
+  </si>
+  <si>
+    <t>An "Order Confirmation" email containing the order number, itemized receipt, totals, and billing/shipping details is received.</t>
+  </si>
+  <si>
+    <t>TC_PAY_014</t>
+  </si>
+  <si>
+    <t>Verify New Order Alert Email is sent to the Store Admin</t>
+  </si>
+  <si>
+    <t>1. Open the inbox of the Store Admin email address.</t>
+  </si>
+  <si>
+    <t>An alert email notifying the admin of a new order, including order details, is received (if alerts are enabled in settings).</t>
+  </si>
+  <si>
+    <t>TC_PAY_015</t>
+  </si>
+  <si>
+    <t>Verify inventory stock is deducted upon successful order</t>
+  </si>
+  <si>
+    <t>User has just completed an order for an item</t>
+  </si>
+  <si>
+    <t>1. Navigate to the Product Display Page of the purchased item, or check the Admin Catalog.</t>
+  </si>
+  <si>
+    <t>2. Check the current stock quantity.</t>
+  </si>
+  <si>
+    <t>The inventory quantity is accurately decremented by the exact amount purchased in the order.</t>
+  </si>
+  <si>
+    <t>TC_PAY_016</t>
+  </si>
+  <si>
+    <t>Verify 'Subtract Stock' configuration is respected</t>
+  </si>
+  <si>
+    <t>User buys an item where 'Subtract Stock' is set to 'No'</t>
+  </si>
+  <si>
+    <t>1. Complete the order.</t>
+  </si>
+  <si>
+    <t>2. Check the inventory quantity of the item.</t>
+  </si>
+  <si>
+    <t>The inventory quantity remains completely unchanged, respecting the backend configuration.</t>
+  </si>
+  <si>
+    <t>TC_PAY_017</t>
+  </si>
+  <si>
+    <t>Verify Coupon/Voucher usage limits update upon successful order</t>
+  </si>
+  <si>
+    <t>User completes an order using a coupon with a usage limit</t>
+  </si>
+  <si>
+    <t>1. Attempt to use the exact same coupon on a new order.</t>
+  </si>
+  <si>
+    <t>2. (Or check the admin coupon usage history).</t>
+  </si>
+  <si>
+    <t>The coupon is marked as used, and if its maximum usage limit was reached, it is correctly invalidated for future transactions.</t>
+  </si>
+  <si>
+    <t>TC_PAY_018</t>
+  </si>
+  <si>
+    <t>Verify shopping cart is cleared upon successful order completion</t>
+  </si>
+  <si>
+    <t>1. Click on the Shopping Cart link or the mini-cart icon in the header.</t>
+  </si>
+  <si>
+    <t>The shopping cart is completely empty, ensuring the user does not accidentally repurchase the same items.</t>
+  </si>
+  <si>
+    <t>TC_ACC_001</t>
+  </si>
+  <si>
+    <t>Verify successful navigation to My Account dashboard</t>
+  </si>
+  <si>
+    <t>User is successfully logged in</t>
+  </si>
+  <si>
+    <t>1. Click the 'My Account' link in the top global header.</t>
+  </si>
+  <si>
+    <t>2. Select 'My Account' from the dropdown.</t>
+  </si>
+  <si>
+    <t>User is routed to the My Account dashboard page displaying all account management options.</t>
+  </si>
+  <si>
+    <t>TC_ACC_002</t>
+  </si>
+  <si>
+    <t>Verify dashboard access is restricted for guest users</t>
+  </si>
+  <si>
+    <t>User is logged out (Guest)</t>
+  </si>
+  <si>
+    <t>1. Attempt to access the My Account page via direct URL or header link.</t>
+  </si>
+  <si>
+    <t>Access is denied. User is automatically redirected to the Login/Register page.</t>
+  </si>
+  <si>
+    <t>TC_ACC_003</t>
+  </si>
+  <si>
+    <t>Verify UI and sections of the My Account dashboard</t>
+  </si>
+  <si>
+    <t>User is on the My Account dashboard</t>
+  </si>
+  <si>
+    <t>1. Observe the main content area of the page.</t>
+  </si>
+  <si>
+    <t>The page is logically divided into sections: 'My Account', 'My Orders', 'My Affiliate Account', and 'Newsletter'.</t>
+  </si>
+  <si>
+    <t>TC_ACC_004</t>
+  </si>
+  <si>
+    <t>Verify navigation to 'Edit your account information'</t>
+  </si>
+  <si>
+    <t>1. Locate the 'My Account' section.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Edit your account information' link.</t>
+  </si>
+  <si>
+    <t>User is routed to the Account Information form where First Name, Last Name, Email, and Telephone can be edited.</t>
+  </si>
+  <si>
+    <t>TC_ACC_005</t>
+  </si>
+  <si>
+    <t>Verify navigation to 'Change your password'</t>
+  </si>
+  <si>
+    <t>2. Click the 'Change your password' link.</t>
+  </si>
+  <si>
+    <t>User is routed to the Change Password form.</t>
+  </si>
+  <si>
+    <t>TC_ACC_006</t>
+  </si>
+  <si>
+    <t>Verify navigation to 'Modify your address book entries'</t>
+  </si>
+  <si>
+    <t>2. Click the 'Modify your address book entries' link.</t>
+  </si>
+  <si>
+    <t>User is routed to the Address Book Entries list.</t>
+  </si>
+  <si>
+    <t>TC_ACC_007</t>
+  </si>
+  <si>
+    <t>Verify navigation to 'Modify your wish list'</t>
+  </si>
+  <si>
+    <t>TC_ACC_008</t>
+  </si>
+  <si>
+    <t>Verify navigation to 'View your order history'</t>
+  </si>
+  <si>
+    <t>2. Click the 'View your order history' link.</t>
+  </si>
+  <si>
+    <t>User is routed to the Order History list showing all past orders.</t>
+  </si>
+  <si>
+    <t>TC_ACC_009</t>
+  </si>
+  <si>
+    <t>Verify Right Column menu synchronization</t>
+  </si>
+  <si>
+    <t>1. Observe the links in the right-hand column menu.</t>
+  </si>
+  <si>
+    <t>2. Compare them to the central page links.</t>
+  </si>
+  <si>
+    <t>The right column menu accurately reflects and provides duplicate quick-access links to all the sections available on the main dashboard layout.</t>
   </si>
 </sst>
 </file>
@@ -6835,7 +7226,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7005,12 +7396,826 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="299">
+  <dxfs count="329">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -15028,285 +16233,325 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="283">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="313">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="282"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="281"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="312"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="311"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
   <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="173"/>
-    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="172"/>
-    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="171"/>
-    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="170"/>
-    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="169"/>
-    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="168"/>
-    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="167"/>
-    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="166"/>
-    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="165"/>
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="205"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="204"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="203"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="202"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="201"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="200"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="199"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="198"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="197"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="196"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="195"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
   <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="160"/>
-    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="159"/>
-    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="158"/>
-    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="157"/>
-    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="156"/>
-    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="155"/>
-    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="154"/>
-    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="153"/>
-    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="152"/>
-    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="151"/>
-    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="150"/>
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="190"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="189"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="188"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="187"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="186"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="185"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="184"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="183"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="182"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="181"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="180"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
   <autoFilter ref="A7:K49" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="142"/>
-    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="140"/>
-    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="139"/>
-    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="138"/>
-    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="137"/>
-    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="136"/>
-    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="135"/>
+    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="174"/>
+    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="173"/>
+    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="172"/>
+    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="171"/>
+    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="170"/>
+    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="169"/>
+    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="168"/>
+    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="167"/>
+    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="166"/>
+    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="165"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
   <autoFilter ref="A7:K55" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="130"/>
-    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="129"/>
-    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="127"/>
-    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="126"/>
-    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="125"/>
-    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="124"/>
-    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="123"/>
-    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="122"/>
-    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="121"/>
-    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="157"/>
+    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="156"/>
+    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="155"/>
+    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="154"/>
+    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="153"/>
+    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="152"/>
+    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="151"/>
+    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
   <autoFilter ref="A7:K62" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
   <autoFilter ref="A7:K84" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="128"/>
+    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="127"/>
+    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="123"/>
+    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="122"/>
+    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="121"/>
+    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="298" dataDxfId="296" headerRowBorderDxfId="297" tableBorderDxfId="295">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="328" dataDxfId="326" headerRowBorderDxfId="327" tableBorderDxfId="325">
   <autoFilter ref="A7:K32" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="294"/>
-    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="293"/>
-    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="292"/>
-    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="291"/>
-    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="290"/>
-    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="289"/>
-    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="288"/>
-    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="287"/>
-    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="286"/>
-    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="285"/>
-    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="284"/>
+    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="324"/>
+    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="323"/>
+    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="322"/>
+    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="321"/>
+    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="320"/>
+    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="319"/>
+    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="318"/>
+    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="317"/>
+    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="316"/>
+    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="315"/>
+    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="314"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="87" dataDxfId="89" headerRowBorderDxfId="88" tableBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="117" dataDxfId="119" headerRowBorderDxfId="118" tableBorderDxfId="116">
   <autoFilter ref="A7:K48" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="110"/>
+    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="105"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="71" dataDxfId="74" headerRowBorderDxfId="72" tableBorderDxfId="73">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="101" dataDxfId="104" headerRowBorderDxfId="102" tableBorderDxfId="103">
   <autoFilter ref="A7:K72" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="56" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="86" dataDxfId="89" headerRowBorderDxfId="87" tableBorderDxfId="88">
   <autoFilter ref="A7:K65" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="280" dataDxfId="278" headerRowBorderDxfId="279" tableBorderDxfId="277" totalsRowBorderDxfId="276">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="310" dataDxfId="308" headerRowBorderDxfId="309" tableBorderDxfId="307" totalsRowBorderDxfId="306">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="275"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="274"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="273"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="272"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="271"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="305"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="304"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="303"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="302"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="301"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}" name="Table20" displayName="Table20" ref="A7:K44" totalsRowShown="0" headerRowDxfId="41" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}" name="Table20" displayName="Table20" ref="A7:K44" totalsRowShown="0" headerRowDxfId="71" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72">
   <autoFilter ref="A7:K44" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E9107AEB-9917-4DCD-999F-23DED7528269}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{4E7F2B0A-9A06-45D9-829D-517139E93FB0}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{09C2C301-9101-42D2-87C5-CF12D84AFDE2}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{4630FF91-0DD6-4E25-827E-20AC0C3327F3}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{6ACC0A37-29EE-49DB-857B-3EF893C5DD7D}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{2AF81478-C083-4718-B4FE-A5FEC39D4683}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{7FDCD6DB-5E88-42AB-9324-CD156B2F76E1}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{8B796E38-6BAF-4EB8-846A-DFC533AC8C87}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{362BE16E-720C-4E90-AFB8-ED627DE3BEF5}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{E7237EFD-FF4D-4C9B-98AD-189BF6BF0535}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{35851930-6F01-4446-835F-13E1EDBAF070}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{E9107AEB-9917-4DCD-999F-23DED7528269}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{4E7F2B0A-9A06-45D9-829D-517139E93FB0}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{09C2C301-9101-42D2-87C5-CF12D84AFDE2}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{4630FF91-0DD6-4E25-827E-20AC0C3327F3}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{6ACC0A37-29EE-49DB-857B-3EF893C5DD7D}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{2AF81478-C083-4718-B4FE-A5FEC39D4683}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{7FDCD6DB-5E88-42AB-9324-CD156B2F76E1}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{8B796E38-6BAF-4EB8-846A-DFC533AC8C87}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{362BE16E-720C-4E90-AFB8-ED627DE3BEF5}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{E7237EFD-FF4D-4C9B-98AD-189BF6BF0535}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{35851930-6F01-4446-835F-13E1EDBAF070}" name="Comments" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}" name="Table21" displayName="Table21" ref="A7:K84" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}" name="Table21" displayName="Table21" ref="A7:K84" totalsRowShown="0" headerRowDxfId="56" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A7:K84" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{15029807-7F0E-425A-BB46-0B6DB3C95839}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{7BD8F686-C564-499F-8D06-C85E47BDAB51}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{67E25BA4-3FF0-4F70-B233-F0E251B42D26}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{B181D3E8-3A2C-400F-B359-B20568BAB1D1}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{B58B21E5-45D9-46DC-BFE5-78BDC714CE7C}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{7D364936-A237-464A-A78D-51E3CF7B08EF}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{DD78F72F-2F82-49C0-857B-9230594DFC47}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{DD233399-E0C4-4DCB-918E-551AD68ACB5A}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{8D1587AC-EA15-44E2-A0C1-155707A09C86}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{B82BB21B-0563-40CE-B8DB-5D4ADE46287B}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{B4AF1D65-2623-4B0C-9A46-AAAF78C4F53B}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{15029807-7F0E-425A-BB46-0B6DB3C95839}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{7BD8F686-C564-499F-8D06-C85E47BDAB51}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{67E25BA4-3FF0-4F70-B233-F0E251B42D26}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{B181D3E8-3A2C-400F-B359-B20568BAB1D1}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{B58B21E5-45D9-46DC-BFE5-78BDC714CE7C}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{7D364936-A237-464A-A78D-51E3CF7B08EF}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{DD78F72F-2F82-49C0-857B-9230594DFC47}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{DD233399-E0C4-4DCB-918E-551AD68ACB5A}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{8D1587AC-EA15-44E2-A0C1-155707A09C86}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{B82BB21B-0563-40CE-B8DB-5D4ADE46287B}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{B4AF1D65-2623-4B0C-9A46-AAAF78C4F53B}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}" name="Table22" displayName="Table22" ref="A7:K73" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}" name="Table22" displayName="Table22" ref="A7:K73" totalsRowShown="0" headerRowDxfId="41" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
   <autoFilter ref="A7:K73" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{9C094CDF-2D28-4BE3-99E2-FE5BD3E1EFED}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{94350EDF-00E0-425A-8D59-A436A634832D}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{46F08573-9A97-4833-A375-E13614AB1CD1}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{9CAFA43D-2ED9-4B71-B10E-703FE41DF889}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{6B1DCF0A-0BAA-40AF-A30E-7AF7E59D4B32}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{254FF740-551F-44C6-85E3-0201E5C78A60}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{37BC01A3-6D35-4AC9-B6E3-D024ABF0F7F6}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{490207E0-C5D6-4F92-A004-D0982BA6E84D}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{2D195591-BB51-4C69-8149-6B4BCC5DCE19}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{D3EB2765-8091-404B-AF58-2635762A163C}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{EA1CCBEC-876B-40ED-8BDE-8E73CB5ABE7B}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{9C094CDF-2D28-4BE3-99E2-FE5BD3E1EFED}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{94350EDF-00E0-425A-8D59-A436A634832D}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{46F08573-9A97-4833-A375-E13614AB1CD1}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{9CAFA43D-2ED9-4B71-B10E-703FE41DF889}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{6B1DCF0A-0BAA-40AF-A30E-7AF7E59D4B32}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{254FF740-551F-44C6-85E3-0201E5C78A60}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{37BC01A3-6D35-4AC9-B6E3-D024ABF0F7F6}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{490207E0-C5D6-4F92-A004-D0982BA6E84D}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{2D195591-BB51-4C69-8149-6B4BCC5DCE19}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{D3EB2765-8091-404B-AF58-2635762A163C}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{EA1CCBEC-876B-40ED-8BDE-8E73CB5ABE7B}" name="Comments" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{68D33CEF-CA71-4D05-A22F-64AD7D766BFE}" name="Table23" displayName="Table23" ref="A7:K55" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+  <autoFilter ref="A7:K55" xr:uid="{68D33CEF-CA71-4D05-A22F-64AD7D766BFE}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{EB45F800-5532-41CB-89BE-F74E48473DD0}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{9232284E-5738-40E3-8919-775C400215EA}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{4EA3B8D0-97A9-4985-A57D-5A2E04A4A859}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{5E1AF50A-9662-4A96-86EC-03FD3FAF1123}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{BB4ACB27-08A2-4080-9E28-9896A36E30AC}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{B0EEDF0B-BB67-49EC-9A2B-CB5DC44066E8}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{B0FFBE88-FEFB-4A88-A24F-378B78A83254}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{4817BD8B-4FE8-4DD9-B2F3-B7DA04D2A3E0}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{7997A220-EC1A-4430-84A8-C8531D74BB13}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{D3D577BF-5FF1-4EFF-822F-E65604ACFCA3}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{46BB6195-AF8F-4AE9-A591-5A814E6FDA36}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{FD17F5D9-1665-4980-BBDA-726FB1A23CA2}" name="Table24" displayName="Table24" ref="A7:K30" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+  <autoFilter ref="A7:K30" xr:uid="{FD17F5D9-1665-4980-BBDA-726FB1A23CA2}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{235EDE94-026F-4F64-98C8-5E31B6DE7F8E}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{66B07AAE-FBBF-40DE-ACF7-ED15C3FDC7D1}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{9103F5B9-0E85-4065-9EB6-5AA8C473300D}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{245EF63E-50D3-4405-838D-07A0E174322A}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{1F0C6C54-8F91-4158-9226-0735A26CCDF1}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{51104F2E-6E22-4719-8062-90335CF6F7DF}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{AC76E163-1681-4CAD-8433-B5CC48CE5313}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{9BA700C1-6164-4AF4-85D8-8954E78872A2}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{199390DA-0C6B-4789-984B-A089DE51DFDD}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{4649A77B-C6C4-4D9F-B175-B39CCF8E9ECD}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{E5E9D353-22FE-4C44-A295-0D119BC404B8}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15316,7 +16561,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="270"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="300"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -15324,120 +16569,120 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="269" dataDxfId="267" headerRowBorderDxfId="268" tableBorderDxfId="266">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="299" dataDxfId="297" headerRowBorderDxfId="298" tableBorderDxfId="296">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="265"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="264"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="263"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="262"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="261"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="260"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="259"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="258"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="257"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="256"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="255"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="295"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="294"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="293"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="292"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="291"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="290"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="289"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="288"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="287"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="286"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="285"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="284" dataDxfId="282" headerRowBorderDxfId="283" tableBorderDxfId="281">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="250"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="249"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="248"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="247"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="246"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="245"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="244"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="243"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="242"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="241"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="240"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="280"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="279"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="278"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="277"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="276"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="275"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="274"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="273"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="272"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="271"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="270"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="269" dataDxfId="267" headerRowBorderDxfId="268" tableBorderDxfId="266">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="235"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="234"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="233"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="232"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="231"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="230"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="229"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="228"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="227"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="226"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="225"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="265"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="264"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="263"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="262"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="261"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="260"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="259"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="258"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="257"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="256"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="255"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="220"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="219"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="218"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="217"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="216"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="215"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="214"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="213"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="212"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="211"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="210"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="250"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="249"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="248"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="247"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="246"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="245"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="244"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="243"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="242"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="241"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="240"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
   <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="205"/>
-    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="204"/>
-    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="203"/>
-    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="202"/>
-    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="201"/>
-    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="200"/>
-    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="199"/>
-    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="198"/>
-    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="197"/>
-    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="196"/>
-    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="195"/>
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="235"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="234"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="233"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="232"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="231"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="230"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="229"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="228"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="227"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="226"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="225"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
   <autoFilter ref="A6:K40" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="190"/>
-    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="189"/>
-    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="188"/>
-    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="187"/>
-    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="186"/>
-    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="185"/>
-    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="184"/>
-    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="183"/>
-    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="182"/>
-    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="181"/>
-    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="180"/>
+    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="220"/>
+    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="219"/>
+    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="218"/>
+    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="217"/>
+    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="216"/>
+    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="215"/>
+    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="214"/>
+    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="213"/>
+    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="212"/>
+    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="211"/>
+    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="210"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -30226,6 +31471,1487 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C797F785-D62A-4425-9C57-4E05A11FB1F1}">
+  <dimension ref="A1:K55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="61"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="64" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="62"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A8" s="51" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11" ht="143.25" thickBot="1">
+      <c r="A9" s="49" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+    </row>
+    <row r="10" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A10" s="43" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43" t="s">
+        <v>1926</v>
+      </c>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="71.25">
+      <c r="A11" s="51" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>1929</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>1930</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51" t="s">
+        <v>1932</v>
+      </c>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44" t="s">
+        <v>1931</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+    </row>
+    <row r="14" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A14" s="43" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>1929</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>1935</v>
+      </c>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43" t="s">
+        <v>1936</v>
+      </c>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="85.5">
+      <c r="A15" s="51" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>1940</v>
+      </c>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51" t="s">
+        <v>1941</v>
+      </c>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+    </row>
+    <row r="18" spans="1:11" ht="85.5">
+      <c r="A18" s="43" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>1944</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43" t="s">
+        <v>1947</v>
+      </c>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="28.5">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43" t="s">
+        <v>1945</v>
+      </c>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11" ht="85.5">
+      <c r="A23" s="51" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51" t="s">
+        <v>1952</v>
+      </c>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="57">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43" t="s">
+        <v>1951</v>
+      </c>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+    </row>
+    <row r="28" spans="1:11" ht="85.5">
+      <c r="A28" s="43" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="57">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11" ht="114">
+      <c r="A33" s="51" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B33" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51" t="s">
+        <v>1961</v>
+      </c>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="43"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+    </row>
+    <row r="35" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
+    </row>
+    <row r="36" spans="1:11" ht="85.5">
+      <c r="A36" s="43" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B36" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43" t="s">
+        <v>1965</v>
+      </c>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" spans="1:11" ht="156.75">
+      <c r="A39" s="51" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
+      <c r="K39" s="51"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="43"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+    </row>
+    <row r="41" spans="1:11" ht="42.75">
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+    </row>
+    <row r="43" spans="1:11" ht="72" thickBot="1">
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+    </row>
+    <row r="44" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A44" s="43" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B44" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>1975</v>
+      </c>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43" t="s">
+        <v>1976</v>
+      </c>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A45" s="49" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B45" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="49" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D45" s="49" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E45" s="49" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H45" s="49"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="49"/>
+      <c r="K45" s="49"/>
+    </row>
+    <row r="46" spans="1:11" ht="142.5">
+      <c r="A46" s="43" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B46" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="43" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D46" s="43" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E46" s="43" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43" t="s">
+        <v>1986</v>
+      </c>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A48" s="43"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" spans="1:11" ht="99.75">
+      <c r="A49" s="51" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B49" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49" s="51" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D49" s="51" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E49" s="51" t="s">
+        <v>1990</v>
+      </c>
+      <c r="F49" s="51"/>
+      <c r="G49" s="51" t="s">
+        <v>1992</v>
+      </c>
+      <c r="H49" s="51"/>
+      <c r="I49" s="51"/>
+      <c r="J49" s="51"/>
+      <c r="K49" s="51"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+    </row>
+    <row r="51" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A51" s="44"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44" t="s">
+        <v>1991</v>
+      </c>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+    </row>
+    <row r="52" spans="1:11" ht="114">
+      <c r="A52" s="43" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B52" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D52" s="43" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>1996</v>
+      </c>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43" t="s">
+        <v>1998</v>
+      </c>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="43"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+    </row>
+    <row r="54" spans="1:11" ht="72" thickBot="1">
+      <c r="A54" s="43"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43" t="s">
+        <v>1997</v>
+      </c>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+    </row>
+    <row r="55" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A55" s="49" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B55" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" s="49" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D55" s="49" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E55" s="49" t="s">
+        <v>2001</v>
+      </c>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49" t="s">
+        <v>2002</v>
+      </c>
+      <c r="H55" s="49"/>
+      <c r="I55" s="49"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="49"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8403BCF2-81FC-4F00-88C7-07588ED122FD}">
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="11" max="11" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="99.75">
+      <c r="A8" s="51" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>2005</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>2008</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>2007</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A11" s="49" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>2011</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>2012</v>
+      </c>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49" t="s">
+        <v>2013</v>
+      </c>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+    </row>
+    <row r="12" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A12" s="43" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>2017</v>
+      </c>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43" t="s">
+        <v>2018</v>
+      </c>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="99.75">
+      <c r="A13" s="51" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51" t="s">
+        <v>2023</v>
+      </c>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="72" thickBot="1">
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+    </row>
+    <row r="16" spans="1:11" ht="42.75">
+      <c r="A16" s="43" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>2025</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43" t="s">
+        <v>2027</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11" ht="57">
+      <c r="A19" s="51" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51" t="s">
+        <v>2031</v>
+      </c>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11" ht="72" thickBot="1">
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44" t="s">
+        <v>2030</v>
+      </c>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+    </row>
+    <row r="22" spans="1:11" ht="42.75">
+      <c r="A22" s="43" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="57">
+      <c r="A25" s="51" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51" t="s">
+        <v>2037</v>
+      </c>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44" t="s">
+        <v>2036</v>
+      </c>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+    </row>
+    <row r="28" spans="1:11" ht="141" customHeight="1">
+      <c r="A28" s="43" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>2040</v>
+      </c>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43" t="s">
+        <v>2042</v>
+      </c>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E21061-D0D2-4A74-9CDD-1B03CA6F95CB}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C1422E-4919-4218-8ECF-B481DD17EC8F}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D27E5CC-CD82-49DD-9D25-77978C556157}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1613D0A3-1A32-45E8-ACCE-32F126F0F8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBF6F0A-60DD-4536-93AC-EBD3E7ED31AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="14" activeTab="21" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="16" activeTab="23" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,8 @@
     <sheet name="RegisteredAccCheckout" sheetId="20" r:id="rId20"/>
     <sheet name="PaymentGateway" sheetId="21" r:id="rId21"/>
     <sheet name="MyAccDashboard" sheetId="22" r:id="rId22"/>
-    <sheet name="Sheet8" sheetId="23" r:id="rId23"/>
-    <sheet name="Sheet9" sheetId="24" r:id="rId24"/>
+    <sheet name="AccInfo" sheetId="23" r:id="rId23"/>
+    <sheet name="ChangePassword" sheetId="24" r:id="rId24"/>
     <sheet name="Sheet10" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="2043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3493" uniqueCount="2145">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -6607,12 +6607,380 @@
   <si>
     <t>The right column menu accurately reflects and provides duplicate quick-access links to all the sections available on the main dashboard layout.</t>
   </si>
+  <si>
+    <t>TC_ACCINFO_001</t>
+  </si>
+  <si>
+    <t>Verify pre-population of existing user data</t>
+  </si>
+  <si>
+    <t>User is logged in and navigates to 'Edit Account'</t>
+  </si>
+  <si>
+    <t>1. Observe the input fields (First Name, Last Name, E-Mail, Telephone).</t>
+  </si>
+  <si>
+    <t>All fields are automatically pre-populated with the user's currently saved account data.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_002</t>
+  </si>
+  <si>
+    <t>Verify successful update of all fields with valid data</t>
+  </si>
+  <si>
+    <t>User is on the Edit Account Information page</t>
+  </si>
+  <si>
+    <t>1. Modify the First Name, Last Name, E-Mail, and Telephone fields with new valid data.</t>
+  </si>
+  <si>
+    <t>A success banner appears ("Success: Your account has been successfully updated."), and user is routed back to the My Account dashboard.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_003</t>
+  </si>
+  <si>
+    <t>Verify validation when First Name is left blank</t>
+  </si>
+  <si>
+    <t>1. Clear the First Name field.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error message is displayed under the First Name field.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_004</t>
+  </si>
+  <si>
+    <t>Verify validation when Last Name is left blank</t>
+  </si>
+  <si>
+    <t>1. Clear the Last Name field.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error message is displayed under the Last Name field.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_005</t>
+  </si>
+  <si>
+    <t>Verify validation when E-Mail is left blank</t>
+  </si>
+  <si>
+    <t>1. Clear the E-Mail field.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error message is displayed under the E-Mail field.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_006</t>
+  </si>
+  <si>
+    <t>Verify validation when Telephone is left blank</t>
+  </si>
+  <si>
+    <t>1. Clear the Telephone field.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error message is displayed under the Telephone field.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_007</t>
+  </si>
+  <si>
+    <t>Verify validation with an invalid E-Mail format (missing '@')</t>
+  </si>
+  <si>
+    <t>Form submission fails. An invalid email format error message is displayed.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_008</t>
+  </si>
+  <si>
+    <t>Verify validation when updating E-Mail to one already in use</t>
+  </si>
+  <si>
+    <t>1. Change the E-Mail to an address that is already registered to a different user in the database.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A warning banner states that the E-Mail Address is already registered.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_009</t>
+  </si>
+  <si>
+    <t>Verify First Name accepts the minimum character limit</t>
+  </si>
+  <si>
+    <t>1. Enter exactly 1 character in the First Name field.</t>
+  </si>
+  <si>
+    <t>The account information is updated successfully.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_010</t>
+  </si>
+  <si>
+    <t>1. Enter a string exceeding the maximum limit (e.g., 33 characters) in the First Name field.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error states the First Name must be between 1 and 32 characters.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_011</t>
+  </si>
+  <si>
+    <t>1. Add space characters before and after the text in the E-Mail field.</t>
+  </si>
+  <si>
+    <t>The update is successful. The system automatically trims the whitespaces from the database entry.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_012</t>
+  </si>
+  <si>
+    <t>1. Click the 'Back' button at the bottom left of the form.</t>
+  </si>
+  <si>
+    <t>Any unsaved changes are discarded, and the user is navigated back to the My Account dashboard.</t>
+  </si>
+  <si>
+    <t>TC_ACCINFO_013</t>
+  </si>
+  <si>
+    <t>Verify Security: XSS injection attempt in input fields</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;script&gt;alert('XSS')&lt;/script&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> into the First Name field.</t>
+    </r>
+  </si>
+  <si>
+    <t>Script is not executed. The input is sanitized or rejected with a validation error.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_001</t>
+  </si>
+  <si>
+    <t>Verify successful password change with valid matching data</t>
+  </si>
+  <si>
+    <t>User is on the Change Password page</t>
+  </si>
+  <si>
+    <t>1. Enter a valid new password in the 'Password' field.</t>
+  </si>
+  <si>
+    <t>2. Enter the exact same password in the 'Password Confirm' field.</t>
+  </si>
+  <si>
+    <t>A success banner appears ("Success: Your password has been successfully updated."), and user is routed back to the My Account dashboard.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_002</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Password' is left blank</t>
+  </si>
+  <si>
+    <t>1. Leave the 'Password' field blank.</t>
+  </si>
+  <si>
+    <t>2. Leave 'Password Confirm' blank.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error message is displayed under the Password field.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_003</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Password Confirm' is left blank</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error states that the password confirmation does not match.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_004</t>
+  </si>
+  <si>
+    <t>Verify validation when Passwords do not match</t>
+  </si>
+  <si>
+    <t>1. Enter a valid new password in 'Password'.</t>
+  </si>
+  <si>
+    <t>2. Enter a different string in 'Password Confirm'.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error states that the password confirmation does not match password.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_005</t>
+  </si>
+  <si>
+    <t>Verify validation when Password is below minimum length</t>
+  </si>
+  <si>
+    <t>1. Enter a 3-character password in both fields.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error states the Password must be between 4 and 20 characters.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_006</t>
+  </si>
+  <si>
+    <t>Verify validation when Password exceeds maximum length</t>
+  </si>
+  <si>
+    <t>1. Enter a 21-character password in both fields.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_007</t>
+  </si>
+  <si>
+    <t>Verify characters entered in password fields are masked</t>
+  </si>
+  <si>
+    <t>1. Type alphanumeric characters into the 'Password' and 'Password Confirm' fields.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_008</t>
+  </si>
+  <si>
+    <t>Any typed data is discarded, the password is not changed, and the user is navigated back to the My Account dashboard.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_009</t>
+  </si>
+  <si>
+    <t>Verify successful login using the newly changed password</t>
+  </si>
+  <si>
+    <t>User has just successfully changed their password</t>
+  </si>
+  <si>
+    <t>2. Navigate to the Login page.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Attempt to login with the Email and the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Password.</t>
+    </r>
+  </si>
+  <si>
+    <t>Login is successful, and the user is routed to the My Account dashboard.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_010</t>
+  </si>
+  <si>
+    <t>Verify login fails when using the old password</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Attempt to login with the Email and the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>old</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Password.</t>
+    </r>
+  </si>
+  <si>
+    <t>TC_CHGPWD_011</t>
+  </si>
+  <si>
+    <t>1. Enter matching passwords in both fields.</t>
+  </si>
+  <si>
+    <t>The form submits successfully, identical to clicking the 'Continue' button.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_012</t>
+  </si>
+  <si>
+    <t>User has successfully changed their password to include uppercase letters</t>
+  </si>
+  <si>
+    <t>2. Attempt to login using the new password, but typed entirely in lowercase.</t>
+  </si>
+  <si>
+    <t>Login fails due to case mismatch, proving the new password was saved with case sensitivity.</t>
+  </si>
+  <si>
+    <t>TC_CHGPWD_013</t>
+  </si>
+  <si>
+    <t>Verify session remains active post-change</t>
+  </si>
+  <si>
+    <t>User has just clicked 'Continue' to change their password</t>
+  </si>
+  <si>
+    <t>1. Observe the user state upon redirect to the My Account dashboard.</t>
+  </si>
+  <si>
+    <t>The user remains securely logged in and is not forced to re-authenticate immediately after the change.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6688,6 +7056,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -6709,7 +7084,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -7124,6 +7499,28 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color rgb="FFC4C7C5"/>
       </right>
@@ -7226,7 +7623,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7375,37 +7772,846 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="329">
+  <dxfs count="359">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -16233,325 +17439,365 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="313">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="343">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="312"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="311"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="342"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="341"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
   <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="205"/>
-    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="204"/>
-    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="203"/>
-    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="202"/>
-    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="201"/>
-    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="200"/>
-    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="199"/>
-    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="198"/>
-    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="197"/>
-    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="196"/>
-    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="195"/>
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="235"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="234"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="233"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="232"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="231"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="230"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="229"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="228"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="227"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="226"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="225"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
   <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="190"/>
-    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="189"/>
-    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="188"/>
-    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="187"/>
-    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="186"/>
-    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="185"/>
-    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="184"/>
-    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="183"/>
-    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="182"/>
-    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="181"/>
-    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="180"/>
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="220"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="219"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="218"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="217"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="216"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="215"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="214"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="213"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="212"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="211"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="210"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
   <autoFilter ref="A7:K49" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="173"/>
-    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="172"/>
-    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="171"/>
-    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="170"/>
-    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="169"/>
-    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="168"/>
-    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="167"/>
-    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="166"/>
-    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="165"/>
+    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="205"/>
+    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="204"/>
+    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="203"/>
+    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="202"/>
+    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="201"/>
+    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="200"/>
+    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="199"/>
+    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="198"/>
+    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="197"/>
+    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="196"/>
+    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="195"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
   <autoFilter ref="A7:K55" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="160"/>
-    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="159"/>
-    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="158"/>
-    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="157"/>
-    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="156"/>
-    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="155"/>
-    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="154"/>
-    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="153"/>
-    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="152"/>
-    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="151"/>
-    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="150"/>
+    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="190"/>
+    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="189"/>
+    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="188"/>
+    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="187"/>
+    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="186"/>
+    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="185"/>
+    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="184"/>
+    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="183"/>
+    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="182"/>
+    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="181"/>
+    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="180"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
   <autoFilter ref="A7:K62" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="142"/>
-    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="140"/>
-    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="139"/>
-    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="138"/>
-    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="137"/>
-    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="136"/>
-    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="135"/>
+    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="174"/>
+    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="173"/>
+    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="172"/>
+    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="171"/>
+    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="170"/>
+    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="169"/>
+    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="168"/>
+    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="167"/>
+    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="166"/>
+    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="165"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="134" dataDxfId="132" headerRowBorderDxfId="133" tableBorderDxfId="131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
   <autoFilter ref="A7:K84" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="130"/>
-    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="129"/>
-    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="127"/>
-    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="126"/>
-    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="125"/>
-    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="124"/>
-    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="123"/>
-    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="122"/>
-    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="121"/>
-    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="157"/>
+    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="156"/>
+    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="155"/>
+    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="154"/>
+    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="153"/>
+    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="152"/>
+    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="151"/>
+    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="328" dataDxfId="326" headerRowBorderDxfId="327" tableBorderDxfId="325">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="358" dataDxfId="356" headerRowBorderDxfId="357" tableBorderDxfId="355">
   <autoFilter ref="A7:K32" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="324"/>
-    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="323"/>
-    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="322"/>
-    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="321"/>
-    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="320"/>
-    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="319"/>
-    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="318"/>
-    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="317"/>
-    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="316"/>
-    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="315"/>
-    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="314"/>
+    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="354"/>
+    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="353"/>
+    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="352"/>
+    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="351"/>
+    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="350"/>
+    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="349"/>
+    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="348"/>
+    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="347"/>
+    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="346"/>
+    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="345"/>
+    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="344"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="117" dataDxfId="119" headerRowBorderDxfId="118" tableBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="147" dataDxfId="149" headerRowBorderDxfId="148" tableBorderDxfId="146">
   <autoFilter ref="A7:K48" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="101" dataDxfId="104" headerRowBorderDxfId="102" tableBorderDxfId="103">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="131" dataDxfId="134" headerRowBorderDxfId="132" tableBorderDxfId="133">
   <autoFilter ref="A7:K72" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="128"/>
+    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="127"/>
+    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="123"/>
+    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="122"/>
+    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="121"/>
+    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="86" dataDxfId="89" headerRowBorderDxfId="87" tableBorderDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="116" dataDxfId="119" headerRowBorderDxfId="117" tableBorderDxfId="118">
   <autoFilter ref="A7:K65" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="110"/>
+    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="105"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="310" dataDxfId="308" headerRowBorderDxfId="309" tableBorderDxfId="307" totalsRowBorderDxfId="306">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="340" dataDxfId="338" headerRowBorderDxfId="339" tableBorderDxfId="337" totalsRowBorderDxfId="336">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="305"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="304"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="303"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="302"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="301"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="335"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="334"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="333"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="332"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="331"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}" name="Table20" displayName="Table20" ref="A7:K44" totalsRowShown="0" headerRowDxfId="71" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}" name="Table20" displayName="Table20" ref="A7:K44" totalsRowShown="0" headerRowDxfId="101" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102">
   <autoFilter ref="A7:K44" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E9107AEB-9917-4DCD-999F-23DED7528269}" name="testCaseId" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{4E7F2B0A-9A06-45D9-829D-517139E93FB0}" name="TestScenario" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{09C2C301-9101-42D2-87C5-CF12D84AFDE2}" name="TestCaseTitle" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{4630FF91-0DD6-4E25-827E-20AC0C3327F3}" name="Pre-requisites" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{6ACC0A37-29EE-49DB-857B-3EF893C5DD7D}" name="TestSteps" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{2AF81478-C083-4718-B4FE-A5FEC39D4683}" name="TestData" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{7FDCD6DB-5E88-42AB-9324-CD156B2F76E1}" name="ExpectedResult" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{8B796E38-6BAF-4EB8-846A-DFC533AC8C87}" name="actualResult" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{362BE16E-720C-4E90-AFB8-ED627DE3BEF5}" name="priority" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{E7237EFD-FF4D-4C9B-98AD-189BF6BF0535}" name="result" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{35851930-6F01-4446-835F-13E1EDBAF070}" name="Comments" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{E9107AEB-9917-4DCD-999F-23DED7528269}" name="testCaseId" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{4E7F2B0A-9A06-45D9-829D-517139E93FB0}" name="TestScenario" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{09C2C301-9101-42D2-87C5-CF12D84AFDE2}" name="TestCaseTitle" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{4630FF91-0DD6-4E25-827E-20AC0C3327F3}" name="Pre-requisites" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{6ACC0A37-29EE-49DB-857B-3EF893C5DD7D}" name="TestSteps" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{2AF81478-C083-4718-B4FE-A5FEC39D4683}" name="TestData" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{7FDCD6DB-5E88-42AB-9324-CD156B2F76E1}" name="ExpectedResult" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{8B796E38-6BAF-4EB8-846A-DFC533AC8C87}" name="actualResult" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{362BE16E-720C-4E90-AFB8-ED627DE3BEF5}" name="priority" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{E7237EFD-FF4D-4C9B-98AD-189BF6BF0535}" name="result" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{35851930-6F01-4446-835F-13E1EDBAF070}" name="Comments" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}" name="Table21" displayName="Table21" ref="A7:K84" totalsRowShown="0" headerRowDxfId="56" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}" name="Table21" displayName="Table21" ref="A7:K84" totalsRowShown="0" headerRowDxfId="86" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87">
   <autoFilter ref="A7:K84" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{15029807-7F0E-425A-BB46-0B6DB3C95839}" name="testCaseId" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{7BD8F686-C564-499F-8D06-C85E47BDAB51}" name="TestScenario" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{67E25BA4-3FF0-4F70-B233-F0E251B42D26}" name="TestCaseTitle" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{B181D3E8-3A2C-400F-B359-B20568BAB1D1}" name="Pre-requisites" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{B58B21E5-45D9-46DC-BFE5-78BDC714CE7C}" name="TestSteps" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{7D364936-A237-464A-A78D-51E3CF7B08EF}" name="TestData" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{DD78F72F-2F82-49C0-857B-9230594DFC47}" name="ExpectedResult" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{DD233399-E0C4-4DCB-918E-551AD68ACB5A}" name="actualResult" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{8D1587AC-EA15-44E2-A0C1-155707A09C86}" name="priority" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{B82BB21B-0563-40CE-B8DB-5D4ADE46287B}" name="result" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{B4AF1D65-2623-4B0C-9A46-AAAF78C4F53B}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{15029807-7F0E-425A-BB46-0B6DB3C95839}" name="testCaseId" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{7BD8F686-C564-499F-8D06-C85E47BDAB51}" name="TestScenario" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{67E25BA4-3FF0-4F70-B233-F0E251B42D26}" name="TestCaseTitle" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{B181D3E8-3A2C-400F-B359-B20568BAB1D1}" name="Pre-requisites" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{B58B21E5-45D9-46DC-BFE5-78BDC714CE7C}" name="TestSteps" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{7D364936-A237-464A-A78D-51E3CF7B08EF}" name="TestData" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{DD78F72F-2F82-49C0-857B-9230594DFC47}" name="ExpectedResult" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{DD233399-E0C4-4DCB-918E-551AD68ACB5A}" name="actualResult" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{8D1587AC-EA15-44E2-A0C1-155707A09C86}" name="priority" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{B82BB21B-0563-40CE-B8DB-5D4ADE46287B}" name="result" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{B4AF1D65-2623-4B0C-9A46-AAAF78C4F53B}" name="Comments" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}" name="Table22" displayName="Table22" ref="A7:K73" totalsRowShown="0" headerRowDxfId="41" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}" name="Table22" displayName="Table22" ref="A7:K73" totalsRowShown="0" headerRowDxfId="71" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72">
   <autoFilter ref="A7:K73" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{9C094CDF-2D28-4BE3-99E2-FE5BD3E1EFED}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{94350EDF-00E0-425A-8D59-A436A634832D}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{46F08573-9A97-4833-A375-E13614AB1CD1}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{9CAFA43D-2ED9-4B71-B10E-703FE41DF889}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{6B1DCF0A-0BAA-40AF-A30E-7AF7E59D4B32}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{254FF740-551F-44C6-85E3-0201E5C78A60}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{37BC01A3-6D35-4AC9-B6E3-D024ABF0F7F6}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{490207E0-C5D6-4F92-A004-D0982BA6E84D}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{2D195591-BB51-4C69-8149-6B4BCC5DCE19}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{D3EB2765-8091-404B-AF58-2635762A163C}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{EA1CCBEC-876B-40ED-8BDE-8E73CB5ABE7B}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{9C094CDF-2D28-4BE3-99E2-FE5BD3E1EFED}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{94350EDF-00E0-425A-8D59-A436A634832D}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{46F08573-9A97-4833-A375-E13614AB1CD1}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{9CAFA43D-2ED9-4B71-B10E-703FE41DF889}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{6B1DCF0A-0BAA-40AF-A30E-7AF7E59D4B32}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{254FF740-551F-44C6-85E3-0201E5C78A60}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{37BC01A3-6D35-4AC9-B6E3-D024ABF0F7F6}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{490207E0-C5D6-4F92-A004-D0982BA6E84D}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{2D195591-BB51-4C69-8149-6B4BCC5DCE19}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{D3EB2765-8091-404B-AF58-2635762A163C}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{EA1CCBEC-876B-40ED-8BDE-8E73CB5ABE7B}" name="Comments" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{68D33CEF-CA71-4D05-A22F-64AD7D766BFE}" name="Table23" displayName="Table23" ref="A7:K55" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{68D33CEF-CA71-4D05-A22F-64AD7D766BFE}" name="Table23" displayName="Table23" ref="A7:K55" totalsRowShown="0" headerRowDxfId="56" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A7:K55" xr:uid="{68D33CEF-CA71-4D05-A22F-64AD7D766BFE}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{EB45F800-5532-41CB-89BE-F74E48473DD0}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{9232284E-5738-40E3-8919-775C400215EA}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{4EA3B8D0-97A9-4985-A57D-5A2E04A4A859}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{5E1AF50A-9662-4A96-86EC-03FD3FAF1123}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{BB4ACB27-08A2-4080-9E28-9896A36E30AC}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{B0EEDF0B-BB67-49EC-9A2B-CB5DC44066E8}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{B0FFBE88-FEFB-4A88-A24F-378B78A83254}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{4817BD8B-4FE8-4DD9-B2F3-B7DA04D2A3E0}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{7997A220-EC1A-4430-84A8-C8531D74BB13}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{D3D577BF-5FF1-4EFF-822F-E65604ACFCA3}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{46BB6195-AF8F-4AE9-A591-5A814E6FDA36}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{EB45F800-5532-41CB-89BE-F74E48473DD0}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{9232284E-5738-40E3-8919-775C400215EA}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{4EA3B8D0-97A9-4985-A57D-5A2E04A4A859}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{5E1AF50A-9662-4A96-86EC-03FD3FAF1123}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{BB4ACB27-08A2-4080-9E28-9896A36E30AC}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{B0EEDF0B-BB67-49EC-9A2B-CB5DC44066E8}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{B0FFBE88-FEFB-4A88-A24F-378B78A83254}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{4817BD8B-4FE8-4DD9-B2F3-B7DA04D2A3E0}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{7997A220-EC1A-4430-84A8-C8531D74BB13}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{D3D577BF-5FF1-4EFF-822F-E65604ACFCA3}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{46BB6195-AF8F-4AE9-A591-5A814E6FDA36}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{FD17F5D9-1665-4980-BBDA-726FB1A23CA2}" name="Table24" displayName="Table24" ref="A7:K30" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{FD17F5D9-1665-4980-BBDA-726FB1A23CA2}" name="Table24" displayName="Table24" ref="A7:K30" totalsRowShown="0" headerRowDxfId="41" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
   <autoFilter ref="A7:K30" xr:uid="{FD17F5D9-1665-4980-BBDA-726FB1A23CA2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{235EDE94-026F-4F64-98C8-5E31B6DE7F8E}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{66B07AAE-FBBF-40DE-ACF7-ED15C3FDC7D1}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{9103F5B9-0E85-4065-9EB6-5AA8C473300D}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{245EF63E-50D3-4405-838D-07A0E174322A}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{1F0C6C54-8F91-4158-9226-0735A26CCDF1}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{51104F2E-6E22-4719-8062-90335CF6F7DF}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{AC76E163-1681-4CAD-8433-B5CC48CE5313}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{9BA700C1-6164-4AF4-85D8-8954E78872A2}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{199390DA-0C6B-4789-984B-A089DE51DFDD}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{4649A77B-C6C4-4D9F-B175-B39CCF8E9ECD}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{E5E9D353-22FE-4C44-A295-0D119BC404B8}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{235EDE94-026F-4F64-98C8-5E31B6DE7F8E}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{66B07AAE-FBBF-40DE-ACF7-ED15C3FDC7D1}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{9103F5B9-0E85-4065-9EB6-5AA8C473300D}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{245EF63E-50D3-4405-838D-07A0E174322A}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{1F0C6C54-8F91-4158-9226-0735A26CCDF1}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{51104F2E-6E22-4719-8062-90335CF6F7DF}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{AC76E163-1681-4CAD-8433-B5CC48CE5313}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{9BA700C1-6164-4AF4-85D8-8954E78872A2}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{199390DA-0C6B-4789-984B-A089DE51DFDD}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{4649A77B-C6C4-4D9F-B175-B39CCF8E9ECD}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{E5E9D353-22FE-4C44-A295-0D119BC404B8}" name="Comments" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{FB7280D7-BCAD-4FF1-954E-497681E98B01}" name="Table25" displayName="Table25" ref="A7:K42" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+  <autoFilter ref="A7:K42" xr:uid="{FB7280D7-BCAD-4FF1-954E-497681E98B01}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{C34059EB-D8CC-4CB5-B77D-1FEA883D6627}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{4857DF9B-007C-441F-B34D-2E702E256E55}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{BC62CFB1-CF67-4BF5-AD42-6725F64A42EA}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{8D8A7C91-2B26-43A9-93BF-E45E7B561258}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{3F2E406A-A218-4064-93BC-E2634CE28D7C}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{E3F4E357-EBA7-4F65-BC33-AC8439820FCB}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{94056214-A554-4202-9399-B05BE597BDC7}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{40766EFA-F7AD-49AA-B233-B5BC924682CB}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{0165342E-CEF0-4A6B-B205-2C00A198D2F4}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{D50A93B7-0F9E-403B-84D4-C5035A273DF2}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{8524DFEB-A607-444E-8F12-73187F3E1599}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{13186742-473F-4AAA-A23E-2B220DA71B17}" name="Table26" displayName="Table26" ref="A7:K52" totalsRowShown="0" headerRowDxfId="12" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="11">
+  <autoFilter ref="A7:K52" xr:uid="{13186742-473F-4AAA-A23E-2B220DA71B17}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{44D9CBF6-8A4C-4A11-BB7B-0866FE800104}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{1DCAEA68-69A2-46D3-9A8B-0AB366B33F66}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{11A6AC34-7EB4-4A8C-B0C6-6E6FF002A79B}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{93789150-0624-43D7-8091-EDC37A54BE2B}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{FFD1E138-B51A-4AFB-BF12-ADB26A6EF42E}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{34AB9F4E-A1AB-4AF9-A8C3-A1A1AABECE87}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{528D6C6B-AF55-43B1-A3D9-C1FF4522E16B}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{C60DE4FE-D70C-4169-8D1E-BCC0050A0117}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{FAA5324F-E6C6-47F1-BD4F-5602167797DA}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{2161F82E-F261-418B-8F48-5C94CBF8E9CC}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{F70A27B6-2C6B-459F-A595-D26B1E0BBC13}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16561,7 +17807,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="300"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="330"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -16569,120 +17815,120 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="299" dataDxfId="297" headerRowBorderDxfId="298" tableBorderDxfId="296">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="329" dataDxfId="327" headerRowBorderDxfId="328" tableBorderDxfId="326">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="295"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="294"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="293"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="292"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="291"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="290"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="289"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="288"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="287"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="286"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="285"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="325"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="324"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="323"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="322"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="321"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="320"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="319"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="318"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="317"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="316"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="315"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="284" dataDxfId="282" headerRowBorderDxfId="283" tableBorderDxfId="281">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="314" dataDxfId="312" headerRowBorderDxfId="313" tableBorderDxfId="311">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="280"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="279"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="278"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="277"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="276"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="275"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="274"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="273"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="272"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="271"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="270"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="310"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="309"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="308"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="307"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="306"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="305"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="304"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="303"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="302"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="301"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="300"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="269" dataDxfId="267" headerRowBorderDxfId="268" tableBorderDxfId="266">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="299" dataDxfId="297" headerRowBorderDxfId="298" tableBorderDxfId="296">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="265"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="264"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="263"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="262"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="261"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="260"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="259"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="258"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="257"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="256"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="255"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="295"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="294"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="293"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="292"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="291"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="290"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="289"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="288"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="287"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="286"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="285"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="284" dataDxfId="282" headerRowBorderDxfId="283" tableBorderDxfId="281">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="250"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="249"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="248"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="247"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="246"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="245"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="244"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="243"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="242"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="241"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="240"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="280"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="279"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="278"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="277"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="276"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="275"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="274"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="273"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="272"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="271"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="270"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="269" dataDxfId="267" headerRowBorderDxfId="268" tableBorderDxfId="266">
   <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="235"/>
-    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="234"/>
-    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="233"/>
-    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="232"/>
-    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="231"/>
-    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="230"/>
-    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="229"/>
-    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="228"/>
-    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="227"/>
-    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="226"/>
-    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="225"/>
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="265"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="264"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="263"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="262"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="261"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="260"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="259"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="258"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="257"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="256"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="255"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
   <autoFilter ref="A6:K40" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="220"/>
-    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="219"/>
-    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="218"/>
-    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="217"/>
-    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="216"/>
-    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="215"/>
-    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="214"/>
-    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="213"/>
-    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="212"/>
-    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="211"/>
-    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="210"/>
+    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="250"/>
+    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="249"/>
+    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="248"/>
+    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="247"/>
+    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="246"/>
+    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="245"/>
+    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="244"/>
+    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="243"/>
+    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="242"/>
+    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="241"/>
+    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="240"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -32908,45 +34154,1553 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E21061-D0D2-4A74-9CDD-1B03CA6F95CB}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="32.85546875" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
+    <col min="11" max="11" width="21.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
       <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
       <c r="B1" s="28"/>
     </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
       <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
       <c r="B2" s="29"/>
     </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A8" s="51" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>2045</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>2047</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11" ht="128.25">
+      <c r="A9" s="51" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>2051</v>
+      </c>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51" t="s">
+        <v>2052</v>
+      </c>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+    </row>
+    <row r="12" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A12" s="43" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A15" s="51" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>2059</v>
+      </c>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51" t="s">
+        <v>2060</v>
+      </c>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+    </row>
+    <row r="18" spans="1:11" ht="112.5" customHeight="1">
+      <c r="A18" s="43" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43" t="s">
+        <v>2064</v>
+      </c>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11" ht="126.75" customHeight="1">
+      <c r="A21" s="51" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>2067</v>
+      </c>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51" t="s">
+        <v>2068</v>
+      </c>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+    </row>
+    <row r="24" spans="1:11" ht="71.25">
+      <c r="A24" s="43" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43" t="s">
+        <v>2071</v>
+      </c>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="128.25">
+      <c r="A27" s="51" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>2074</v>
+      </c>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51" t="s">
+        <v>2075</v>
+      </c>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+    </row>
+    <row r="30" spans="1:11" ht="71.25">
+      <c r="A30" s="43" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43" t="s">
+        <v>2079</v>
+      </c>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11" ht="128.25">
+      <c r="A33" s="51" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B33" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51" t="s">
+        <v>2082</v>
+      </c>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="43"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+    </row>
+    <row r="35" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
+    </row>
+    <row r="36" spans="1:11" ht="99.75">
+      <c r="A36" s="43" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B36" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>405</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>2084</v>
+      </c>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43" t="s">
+        <v>2085</v>
+      </c>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A39" s="49" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B39" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="49" t="s">
+        <v>409</v>
+      </c>
+      <c r="D39" s="49" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E39" s="49" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49" t="s">
+        <v>2088</v>
+      </c>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
+      <c r="J39" s="49"/>
+      <c r="K39" s="49"/>
+    </row>
+    <row r="40" spans="1:11" ht="71.25">
+      <c r="A40" s="43" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B40" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A42" s="44"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="44"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C1422E-4919-4218-8ECF-B481DD17EC8F}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" customWidth="1"/>
+    <col min="7" max="7" width="31.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="23.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
       <c r="A1" s="31" t="s">
         <v>171</v>
       </c>
       <c r="B1" s="28"/>
     </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
       <c r="A2" s="30" t="s">
         <v>172</v>
       </c>
       <c r="B2" s="29"/>
     </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="128.25">
+      <c r="A8" s="65" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>2096</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>2098</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="66"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="47"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="48"/>
+    </row>
+    <row r="10" spans="1:11" ht="99.75">
+      <c r="A10" s="47"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>2097</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="48"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="47"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="48"/>
+    </row>
+    <row r="12" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A12" s="47"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="48"/>
+    </row>
+    <row r="13" spans="1:11" ht="71.25">
+      <c r="A13" s="51" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51" t="s">
+        <v>2103</v>
+      </c>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="57">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+    </row>
+    <row r="18" spans="1:11" ht="85.5">
+      <c r="A18" s="47" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>2096</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43" t="s">
+        <v>2106</v>
+      </c>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="48"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="47"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="48"/>
+    </row>
+    <row r="20" spans="1:11" ht="57">
+      <c r="A20" s="47"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="48"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="47"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="48"/>
+    </row>
+    <row r="22" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A22" s="47"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="48"/>
+    </row>
+    <row r="23" spans="1:11" ht="99.75">
+      <c r="A23" s="51" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>2109</v>
+      </c>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51" t="s">
+        <v>2111</v>
+      </c>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="71.25">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+    </row>
+    <row r="28" spans="1:11" ht="155.25" customHeight="1">
+      <c r="A28" s="47" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43" t="s">
+        <v>2115</v>
+      </c>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="48"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="47"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="48"/>
+    </row>
+    <row r="30" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A30" s="47"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="48"/>
+    </row>
+    <row r="31" spans="1:11" ht="155.25" customHeight="1">
+      <c r="A31" s="51" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B31" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51" t="s">
+        <v>2115</v>
+      </c>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A33" s="44"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
+    </row>
+    <row r="34" spans="1:11" ht="129" thickBot="1">
+      <c r="A34" s="47" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B34" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>2121</v>
+      </c>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="48"/>
+    </row>
+    <row r="35" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A35" s="49" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B35" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="49" t="s">
+        <v>409</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49" t="s">
+        <v>2123</v>
+      </c>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
+    </row>
+    <row r="36" spans="1:11" ht="71.25">
+      <c r="A36" s="47" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B36" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43" t="s">
+        <v>2129</v>
+      </c>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="48"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="47"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="48"/>
+    </row>
+    <row r="38" spans="1:11" ht="42.75">
+      <c r="A38" s="47"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43" t="s">
+        <v>2127</v>
+      </c>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="48"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="47"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="48"/>
+    </row>
+    <row r="40" spans="1:11" ht="72" thickBot="1">
+      <c r="A40" s="47"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="48"/>
+    </row>
+    <row r="41" spans="1:11" ht="85.5">
+      <c r="A41" s="51" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B41" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="51"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+    </row>
+    <row r="43" spans="1:11" ht="42.75">
+      <c r="A43" s="43"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43" t="s">
+        <v>2127</v>
+      </c>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="43"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" spans="1:11" ht="72" thickBot="1">
+      <c r="A45" s="44"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44" t="s">
+        <v>2132</v>
+      </c>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+    </row>
+    <row r="46" spans="1:11" ht="71.25">
+      <c r="A46" s="47" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B46" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="43" t="s">
+        <v>413</v>
+      </c>
+      <c r="D46" s="43" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E46" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43" t="s">
+        <v>2135</v>
+      </c>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="48"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="47"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="48"/>
+    </row>
+    <row r="48" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A48" s="47"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43" t="s">
+        <v>415</v>
+      </c>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="48"/>
+    </row>
+    <row r="49" spans="1:11" ht="85.5">
+      <c r="A49" s="51" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B49" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="51" t="s">
+        <v>261</v>
+      </c>
+      <c r="D49" s="51" t="s">
+        <v>2137</v>
+      </c>
+      <c r="E49" s="51" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F49" s="51"/>
+      <c r="G49" s="51" t="s">
+        <v>2139</v>
+      </c>
+      <c r="H49" s="51"/>
+      <c r="I49" s="51"/>
+      <c r="J49" s="51"/>
+      <c r="K49" s="51"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+    </row>
+    <row r="51" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A51" s="44"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44" t="s">
+        <v>2138</v>
+      </c>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+    </row>
+    <row r="52" spans="1:11" ht="99.75">
+      <c r="A52" s="47" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B52" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D52" s="43" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43" t="s">
+        <v>2144</v>
+      </c>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="48"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBF6F0A-60DD-4536-93AC-EBD3E7ED31AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0DC078-8521-4742-B6B9-C05E7619B538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="16" activeTab="23" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="19" activeTab="25" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,11 @@
     <sheet name="MyAccDashboard" sheetId="22" r:id="rId22"/>
     <sheet name="AccInfo" sheetId="23" r:id="rId23"/>
     <sheet name="ChangePassword" sheetId="24" r:id="rId24"/>
-    <sheet name="Sheet10" sheetId="25" r:id="rId25"/>
+    <sheet name="AddressBook" sheetId="25" r:id="rId25"/>
+    <sheet name="OrderHistory" sheetId="26" r:id="rId26"/>
+    <sheet name="Sheet12" sheetId="27" r:id="rId27"/>
+    <sheet name="Sheet13" sheetId="28" r:id="rId28"/>
+    <sheet name="Sheet14" sheetId="29" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3493" uniqueCount="2145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3705" uniqueCount="2273">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -6974,6 +6978,430 @@
   </si>
   <si>
     <t>The user remains securely logged in and is not forced to re-authenticate immediately after the change.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_001</t>
+  </si>
+  <si>
+    <t>Verify navigation to Address Book</t>
+  </si>
+  <si>
+    <t>User is logged into their account</t>
+  </si>
+  <si>
+    <t>1. Navigate to the My Account dashboard.</t>
+  </si>
+  <si>
+    <t>2. Click 'Modify your address book entries'.</t>
+  </si>
+  <si>
+    <t>User is routed to the Address Book Entries page, displaying a list of saved addresses.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_002</t>
+  </si>
+  <si>
+    <t>Verify Address Book list UI</t>
+  </si>
+  <si>
+    <t>User has at least one saved address</t>
+  </si>
+  <si>
+    <t>1. Observe the Address Book page layout.</t>
+  </si>
+  <si>
+    <t>Saved addresses are displayed clearly in a list or grid format, with 'Edit' and 'Delete' buttons available for each entry.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_003</t>
+  </si>
+  <si>
+    <t>Verify navigation to 'New Address' form</t>
+  </si>
+  <si>
+    <t>User is on the Address Book page</t>
+  </si>
+  <si>
+    <t>1. Click the 'New Address' button.</t>
+  </si>
+  <si>
+    <t>User is routed to the Add Address form containing fields for First Name, Last Name, Company, Address 1, City, Post Code, Country, and Region.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_004</t>
+  </si>
+  <si>
+    <t>Verify adding a New Address with valid data</t>
+  </si>
+  <si>
+    <t>User is on the Add Address form</t>
+  </si>
+  <si>
+    <t>1. Fill all mandatory fields (First Name, Last Name, Address 1, City, Country, Region/State) with valid data.</t>
+  </si>
+  <si>
+    <t>A success banner appears ("Success: Your address has been successfully added"), and the user is routed back to the Address Book list where the new address is visible.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_005</t>
+  </si>
+  <si>
+    <t>Verify validation when mandatory fields are left blank</t>
+  </si>
+  <si>
+    <t>1. Leave First Name, Last Name, Address 1, and City blank.</t>
+  </si>
+  <si>
+    <t>Form submission fails. Validation error messages appear below every required field indicating they cannot be empty.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_006</t>
+  </si>
+  <si>
+    <t>Verify Country and Region dropdown dependency</t>
+  </si>
+  <si>
+    <t>1. Click the 'Country' dropdown and select a country.</t>
+  </si>
+  <si>
+    <t>2. Observe the 'Region / State' dropdown.</t>
+  </si>
+  <si>
+    <t>The Region / State dropdown dynamically populates with the correct regions associated with the newly selected Country.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_007</t>
+  </si>
+  <si>
+    <t>Verify adding a New Address and setting it as 'Default'</t>
+  </si>
+  <si>
+    <t>1. Fill all mandatory fields.</t>
+  </si>
+  <si>
+    <t>2. Select the 'Yes' radio button for "Default Address".</t>
+  </si>
+  <si>
+    <t>The address is successfully added and is now recognized globally by the system as the user's default billing/shipping address.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_008</t>
+  </si>
+  <si>
+    <t>Verify navigating to 'Edit Address'</t>
+  </si>
+  <si>
+    <t>1. Locate an existing address.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Edit' button for that address.</t>
+  </si>
+  <si>
+    <t>User is routed to the Edit Address form, and all fields are accurately pre-populated with the selected address's data.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_009</t>
+  </si>
+  <si>
+    <t>Verify successful update of an existing Address</t>
+  </si>
+  <si>
+    <t>User is on the Edit Address form</t>
+  </si>
+  <si>
+    <t>1. Modify the 'Address 1' and 'City' fields.</t>
+  </si>
+  <si>
+    <t>A success banner appears ("Success: Your address has been successfully updated"), and the changes are reflected in the Address Book list.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_010</t>
+  </si>
+  <si>
+    <t>Verify successful deletion of a non-default Address</t>
+  </si>
+  <si>
+    <t>User is on the Address Book page with multiple addresses</t>
+  </si>
+  <si>
+    <t>1. Locate an address that is NOT the default.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Delete' button.</t>
+  </si>
+  <si>
+    <t>A success banner appears ("Success: Your address has been successfully deleted"), and the entry disappears from the list.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_011</t>
+  </si>
+  <si>
+    <t>Verify system prevents deletion of the Default Address</t>
+  </si>
+  <si>
+    <t>1. Locate the address currently set as the Default Address.</t>
+  </si>
+  <si>
+    <t>Deletion fails. A warning banner states: "Warning: You can not delete your default address!"</t>
+  </si>
+  <si>
+    <t>TC_ADDR_012</t>
+  </si>
+  <si>
+    <t>Verify Post Code validation based on Country selection</t>
+  </si>
+  <si>
+    <t>1. Select a Country that strictly requires a Post Code (e.g., US or UK).</t>
+  </si>
+  <si>
+    <t>2. Leave the Post Code field blank.</t>
+  </si>
+  <si>
+    <t>Form submission fails. A validation error message appears under the Post Code field stating it is required for the selected country.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_013</t>
+  </si>
+  <si>
+    <t>Verify system trims leading/trailing whitespaces</t>
+  </si>
+  <si>
+    <t>1. Enter an address with heavy whitespace before and after the text (e.g., " 123 Main St ").</t>
+  </si>
+  <si>
+    <t>The address saves successfully, and the system automatically trims the excess whitespace from the database entry.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_014</t>
+  </si>
+  <si>
+    <t>Verify 'Back' button functionality on Address forms</t>
+  </si>
+  <si>
+    <t>User is on the Add Address or Edit Address form</t>
+  </si>
+  <si>
+    <t>1. Click the 'Back' button at the bottom left.</t>
+  </si>
+  <si>
+    <t>Any unsaved changes or inputs are discarded, and the user is safely navigated back to the main Address Book list.</t>
+  </si>
+  <si>
+    <t>TC_ADDR_015</t>
+  </si>
+  <si>
+    <t>Verify Security: XSS injection attempt in Address fields</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;script&gt;alert(1)&lt;/script&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> into the 'Address 1' or 'City' field.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Complete other fields and submit.</t>
+  </si>
+  <si>
+    <t>Script is safely neutralized. The input is sanitized and rendered as harmless plain text when viewing the address list or during checkout.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_001</t>
+  </si>
+  <si>
+    <t>Verify navigation to Order History</t>
+  </si>
+  <si>
+    <t>User is routed to the Order History page displaying a list of past orders.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_002</t>
+  </si>
+  <si>
+    <t>Verify Order History list UI</t>
+  </si>
+  <si>
+    <t>User has placed at least one order</t>
+  </si>
+  <si>
+    <t>1. Observe the Order History page layout.</t>
+  </si>
+  <si>
+    <t>Orders are displayed in a clear list/grid showing Order ID, Status, Date Added, No. of Products, Customer Name, Total, and a 'View' button.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_003</t>
+  </si>
+  <si>
+    <t>Verify empty state for new users</t>
+  </si>
+  <si>
+    <t>User has never placed an order</t>
+  </si>
+  <si>
+    <t>1. Navigate to the Order History page.</t>
+  </si>
+  <si>
+    <t>The page displays the empty state text: "You have not made any previous orders!" with a Continue button.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_004</t>
+  </si>
+  <si>
+    <t>Verify Pagination on Order History</t>
+  </si>
+  <si>
+    <t>User has placed more orders than the default page limit (e.g., &gt;20)</t>
+  </si>
+  <si>
+    <t>1. Scroll to the bottom of the Order History list.</t>
+  </si>
+  <si>
+    <t>2. Click to page '2'.</t>
+  </si>
+  <si>
+    <t>The pagination works correctly, loading the older set of historical orders.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_005</t>
+  </si>
+  <si>
+    <t>Verify navigation to Order Details (View)</t>
+  </si>
+  <si>
+    <t>User is on the Order History page</t>
+  </si>
+  <si>
+    <t>1. Locate a specific order in the list.</t>
+  </si>
+  <si>
+    <t>2. Click the 'View' (eye icon) button.</t>
+  </si>
+  <si>
+    <t>User is routed to the detailed 'Order Information' page for that specific transaction.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_006</t>
+  </si>
+  <si>
+    <t>Verify Order Details UI and Information accuracy</t>
+  </si>
+  <si>
+    <t>User is on the Order Information page</t>
+  </si>
+  <si>
+    <t>1. Review the Order Details, Payment Address, and Shipping Address blocks.</t>
+  </si>
+  <si>
+    <t>All data accurately matches the information provided by the user during that specific checkout session.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_007</t>
+  </si>
+  <si>
+    <t>Verify Itemized Product List accuracy</t>
+  </si>
+  <si>
+    <t>1. Review the table of purchased products.</t>
+  </si>
+  <si>
+    <t>Product Name, Model, Quantity, Unit Price, and Totals accurately match what was purchased.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_008</t>
+  </si>
+  <si>
+    <t>Verify Order History Status Timeline</t>
+  </si>
+  <si>
+    <t>1. Scroll to the 'Order History' table at the bottom.</t>
+  </si>
+  <si>
+    <t>The table accurately displays the chronological timeline of status changes (e.g., Pending -&gt; Processing -&gt; Shipped) with exact dates and admin comments.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_009</t>
+  </si>
+  <si>
+    <t>Verify 'Reorder' functionality</t>
+  </si>
+  <si>
+    <t>1. Locate a specific product in the order table.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Reorder' (shopping cart icon) button.</t>
+  </si>
+  <si>
+    <t>A success banner appears, and the exact product (with its saved options) is instantly added to the user's current active shopping cart.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_010</t>
+  </si>
+  <si>
+    <t>Verify 'Return' functionality routing</t>
+  </si>
+  <si>
+    <t>2. Click the 'Return' (red undo arrow icon) button.</t>
+  </si>
+  <si>
+    <t>User is navigated directly to the 'Product Returns' form, with the Order ID and Product details pre-populated.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_011</t>
+  </si>
+  <si>
+    <t>User is navigated back to the main Order History list.</t>
+  </si>
+  <si>
+    <t>TC_ORDH_012</t>
+  </si>
+  <si>
+    <t>Verify security restriction for accessing other users' orders</t>
+  </si>
+  <si>
+    <t>1. Open the Order Information page for an owned order.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Manipulate the URL parameter (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>order_id=XX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) to an ID belonging to a different customer.</t>
+    </r>
+  </si>
+  <si>
+    <t>Access is denied. The system prevents viewing the order details and redirects the user or shows an error.</t>
   </si>
 </sst>
 </file>
@@ -7084,7 +7512,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -7618,12 +8046,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7803,12 +8289,806 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="359">
+  <dxfs count="389">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -17439,365 +18719,405 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="343">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="373">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="342"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="341"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="372"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="371"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="269" dataDxfId="267" headerRowBorderDxfId="268" tableBorderDxfId="266">
   <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="235"/>
-    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="234"/>
-    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="233"/>
-    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="232"/>
-    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="231"/>
-    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="230"/>
-    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="229"/>
-    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="228"/>
-    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="227"/>
-    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="226"/>
-    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="225"/>
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="265"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="264"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="263"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="262"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="261"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="260"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="259"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="258"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="257"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="256"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="255"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
   <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="220"/>
-    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="219"/>
-    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="218"/>
-    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="217"/>
-    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="216"/>
-    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="215"/>
-    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="214"/>
-    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="213"/>
-    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="212"/>
-    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="211"/>
-    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="210"/>
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="250"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="249"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="248"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="247"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="246"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="245"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="244"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="243"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="242"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="241"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="240"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
   <autoFilter ref="A7:K49" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="205"/>
-    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="204"/>
-    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="203"/>
-    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="202"/>
-    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="201"/>
-    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="200"/>
-    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="199"/>
-    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="198"/>
-    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="197"/>
-    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="196"/>
-    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="195"/>
+    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="235"/>
+    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="234"/>
+    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="233"/>
+    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="232"/>
+    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="231"/>
+    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="230"/>
+    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="229"/>
+    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="228"/>
+    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="227"/>
+    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="226"/>
+    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="225"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDxfId="224" dataDxfId="222" headerRowBorderDxfId="223" tableBorderDxfId="221">
   <autoFilter ref="A7:K55" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="190"/>
-    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="189"/>
-    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="188"/>
-    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="187"/>
-    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="186"/>
-    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="185"/>
-    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="184"/>
-    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="183"/>
-    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="182"/>
-    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="181"/>
-    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="180"/>
+    <tableColumn id="1" xr3:uid="{8EC256E8-91A2-4ED6-93D5-8B966F6E8A1B}" name="testCaseId" dataDxfId="220"/>
+    <tableColumn id="2" xr3:uid="{0AD80E83-32DA-4761-BF02-4DAF2BE4C4DA}" name="TestScenario" dataDxfId="219"/>
+    <tableColumn id="3" xr3:uid="{F1E1DCDC-7AC2-4500-B923-AF942604466B}" name="TestCaseTitle" dataDxfId="218"/>
+    <tableColumn id="4" xr3:uid="{643FCD7C-75F1-45B9-AF1E-713BDDACD73B}" name="Pre-requisites" dataDxfId="217"/>
+    <tableColumn id="5" xr3:uid="{F9DF658C-E883-4A31-8CF4-84A4372E84AB}" name="TestSteps" dataDxfId="216"/>
+    <tableColumn id="6" xr3:uid="{C53EBE9E-E7DE-4120-ABC7-6B607C50863B}" name="TestData" dataDxfId="215"/>
+    <tableColumn id="7" xr3:uid="{5A5A8957-E2CA-4A3A-89D1-144D4F278252}" name="ExpectedResult" dataDxfId="214"/>
+    <tableColumn id="8" xr3:uid="{223FB6C9-409D-4FC0-82F8-E7272DD03CDF}" name="actualResult" dataDxfId="213"/>
+    <tableColumn id="9" xr3:uid="{21A5B05E-4AEE-41DE-8862-31B6A517F729}" name="priority" dataDxfId="212"/>
+    <tableColumn id="10" xr3:uid="{E8CBDD0A-75EE-42F4-BD61-43B99373895F}" name="result" dataDxfId="211"/>
+    <tableColumn id="11" xr3:uid="{1C26D4C0-B623-44E1-AE02-7E5458DD891F}" name="Comments" dataDxfId="210"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}" name="Table14" displayName="Table14" ref="A7:K62" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206">
   <autoFilter ref="A7:K62" xr:uid="{E09F6931-69AB-4C14-AB2A-AABD79146972}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="173"/>
-    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="172"/>
-    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="171"/>
-    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="170"/>
-    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="169"/>
-    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="168"/>
-    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="167"/>
-    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="166"/>
-    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="165"/>
+    <tableColumn id="1" xr3:uid="{72B8A1B4-D4E0-4FED-B7E6-B8C07FECBF26}" name="testCaseId" dataDxfId="205"/>
+    <tableColumn id="2" xr3:uid="{82646464-EC57-4FB6-A075-A5AFE7E8C550}" name="TestScenario" dataDxfId="204"/>
+    <tableColumn id="3" xr3:uid="{0DD62774-A557-4742-B2C2-A8D3DCDEF09A}" name="TestCaseTitle" dataDxfId="203"/>
+    <tableColumn id="4" xr3:uid="{97A8F3DB-1523-4711-B0E1-E8F7634A40EA}" name="Pre-requisites" dataDxfId="202"/>
+    <tableColumn id="5" xr3:uid="{E2856078-53C7-4D1D-8538-52E02B9C3679}" name="TestSteps" dataDxfId="201"/>
+    <tableColumn id="6" xr3:uid="{DAB22D97-FDE4-4425-AF58-56F87DA22EEB}" name="TestData" dataDxfId="200"/>
+    <tableColumn id="7" xr3:uid="{07F3C45B-2413-48DE-8B0B-FA054E2B587E}" name="ExpectedResult" dataDxfId="199"/>
+    <tableColumn id="8" xr3:uid="{CEAF1C6D-2DBC-43E8-A57C-F25078BC9547}" name="actualResult" dataDxfId="198"/>
+    <tableColumn id="9" xr3:uid="{68F3AB2A-E23E-486F-BCE7-40CD97704893}" name="priority" dataDxfId="197"/>
+    <tableColumn id="10" xr3:uid="{C6283E1E-3597-449A-B0CD-B92723A1A88B}" name="result" dataDxfId="196"/>
+    <tableColumn id="11" xr3:uid="{1ECDA6C2-99E4-470F-A766-29CA17ECA06F}" name="Comments" dataDxfId="195"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}" name="Table15" displayName="Table15" ref="A7:K84" totalsRowShown="0" headerRowDxfId="194" dataDxfId="192" headerRowBorderDxfId="193" tableBorderDxfId="191">
   <autoFilter ref="A7:K84" xr:uid="{1C45F570-525D-4F1A-8940-E2603BA02EF9}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="160"/>
-    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="159"/>
-    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="158"/>
-    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="157"/>
-    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="156"/>
-    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="155"/>
-    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="154"/>
-    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="153"/>
-    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="152"/>
-    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="151"/>
-    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="150"/>
+    <tableColumn id="1" xr3:uid="{41FB95FF-E0B6-4B59-8903-344725741DBF}" name="testCaseId" dataDxfId="190"/>
+    <tableColumn id="2" xr3:uid="{64DF8882-5FEC-427C-B060-0DF0CDE561C9}" name="TestScenario" dataDxfId="189"/>
+    <tableColumn id="3" xr3:uid="{84635A78-2644-46CC-AE49-12C4A23CFCDD}" name="TestCaseTitle" dataDxfId="188"/>
+    <tableColumn id="4" xr3:uid="{A9A8F65D-A481-4F73-9AA9-5EDB9094E38B}" name="Pre-requisites" dataDxfId="187"/>
+    <tableColumn id="5" xr3:uid="{C32F6C46-36C1-4EAD-8D0A-D9515F18EFB2}" name="TestSteps" dataDxfId="186"/>
+    <tableColumn id="6" xr3:uid="{17A4D547-1599-495B-B045-DE158C531690}" name="TestData" dataDxfId="185"/>
+    <tableColumn id="7" xr3:uid="{03D5E474-2EEE-4CF7-BEE1-F86A58340BA3}" name="ExpectedResult" dataDxfId="184"/>
+    <tableColumn id="8" xr3:uid="{F65DE658-074A-42E2-A3E5-FE4FB5E95427}" name="actualResult" dataDxfId="183"/>
+    <tableColumn id="9" xr3:uid="{DE470ECC-6997-4676-A8BB-12613703B324}" name="priority" dataDxfId="182"/>
+    <tableColumn id="10" xr3:uid="{877A28E4-08B0-48F6-8E52-8A424055855F}" name="result" dataDxfId="181"/>
+    <tableColumn id="11" xr3:uid="{E66B8AEF-6052-4D01-9289-B5946FE7F75F}" name="Comments" dataDxfId="180"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="358" dataDxfId="356" headerRowBorderDxfId="357" tableBorderDxfId="355">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}" name="Table16" displayName="Table16" ref="A7:K32" totalsRowShown="0" headerRowDxfId="388" dataDxfId="386" headerRowBorderDxfId="387" tableBorderDxfId="385">
   <autoFilter ref="A7:K32" xr:uid="{99FA352D-5781-4DED-8196-86354DF74DF2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="354"/>
-    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="353"/>
-    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="352"/>
-    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="351"/>
-    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="350"/>
-    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="349"/>
-    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="348"/>
-    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="347"/>
-    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="346"/>
-    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="345"/>
-    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="344"/>
+    <tableColumn id="1" xr3:uid="{A943DE01-B073-4B7A-B63D-E6B1E36DDE0B}" name="testCaseId" dataDxfId="384"/>
+    <tableColumn id="2" xr3:uid="{AA65D4AC-BD4D-43AB-83ED-16460518E67E}" name="TestScenario" dataDxfId="383"/>
+    <tableColumn id="3" xr3:uid="{E6D35D86-2DBB-4F3E-9D10-7D2F9B396CF0}" name="TestCaseTitle" dataDxfId="382"/>
+    <tableColumn id="4" xr3:uid="{8F7A6C94-E9C4-4E06-9BA7-47257F7C3EB3}" name="Pre-requisites" dataDxfId="381"/>
+    <tableColumn id="5" xr3:uid="{1D04F011-56CE-41F0-992E-B4B8BE66ACC6}" name="TestSteps" dataDxfId="380"/>
+    <tableColumn id="6" xr3:uid="{8C46376D-DB7A-4F54-AC3E-C1A7B45A419B}" name="TestData" dataDxfId="379"/>
+    <tableColumn id="7" xr3:uid="{27C41CD3-5029-40D8-BA1F-BABF38CF3B8B}" name="ExpectedResult" dataDxfId="378"/>
+    <tableColumn id="8" xr3:uid="{F977C19E-CB3E-46BF-9106-6ED09622D84C}" name="actualResult" dataDxfId="377"/>
+    <tableColumn id="9" xr3:uid="{A0B21E76-82F8-4CD6-90AD-1D770580331E}" name="priority" dataDxfId="376"/>
+    <tableColumn id="10" xr3:uid="{C44AE9D5-FB5C-46A0-BA0E-10FE7784529B}" name="result" dataDxfId="375"/>
+    <tableColumn id="11" xr3:uid="{C782ADA1-9418-41D8-A25C-B1D2011D785C}" name="Comments" dataDxfId="374"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="147" dataDxfId="149" headerRowBorderDxfId="148" tableBorderDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}" name="Table17" displayName="Table17" ref="A7:K48" totalsRowShown="0" headerRowDxfId="177" dataDxfId="179" headerRowBorderDxfId="178" tableBorderDxfId="176">
   <autoFilter ref="A7:K48" xr:uid="{03A2A525-4F45-4920-BE3B-4DF1BF035E9A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="142"/>
-    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="140"/>
-    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="139"/>
-    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="138"/>
-    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="137"/>
-    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="136"/>
-    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="135"/>
+    <tableColumn id="1" xr3:uid="{93AC1B3F-9E1B-44CE-A7D9-D959F58CD3E7}" name="testCaseId" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{95800BB7-03B0-4BFD-8B98-66DC65958B9F}" name="TestScenario" dataDxfId="174"/>
+    <tableColumn id="3" xr3:uid="{E225D733-1A8F-414A-814E-3AC1FE8A60F3}" name="TestCaseTitle" dataDxfId="173"/>
+    <tableColumn id="4" xr3:uid="{85D96E6D-A21E-4BBD-A98E-BDCF2D8C039F}" name="Pre-requisites" dataDxfId="172"/>
+    <tableColumn id="5" xr3:uid="{E865BF22-80E3-437A-9E68-14279FBDFC0F}" name="TestSteps" dataDxfId="171"/>
+    <tableColumn id="6" xr3:uid="{12653764-A2B4-4D54-A45F-B174463F7EB4}" name="TestData" dataDxfId="170"/>
+    <tableColumn id="7" xr3:uid="{87E8BE7D-4536-4CE7-8005-740682DE7506}" name="ExpectedResult" dataDxfId="169"/>
+    <tableColumn id="8" xr3:uid="{C50BACEA-D4D0-4F2E-AC4A-D42E28FF4E59}" name="actualResult" dataDxfId="168"/>
+    <tableColumn id="9" xr3:uid="{ECDACF7B-0B0C-496C-93BD-B8B9870C1FA9}" name="priority" dataDxfId="167"/>
+    <tableColumn id="10" xr3:uid="{EE93BE67-4123-4FBA-BEF6-4030BD11069E}" name="result" dataDxfId="166"/>
+    <tableColumn id="11" xr3:uid="{F0CD75B2-5084-479C-A437-B90634EE2927}" name="Comments" dataDxfId="165"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="131" dataDxfId="134" headerRowBorderDxfId="132" tableBorderDxfId="133">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}" name="Table18" displayName="Table18" ref="A7:K72" totalsRowShown="0" headerRowDxfId="161" dataDxfId="164" headerRowBorderDxfId="162" tableBorderDxfId="163">
   <autoFilter ref="A7:K72" xr:uid="{00676335-1027-41DE-BC0C-B1E8F14CF475}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="130"/>
-    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="129"/>
-    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="127"/>
-    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="126"/>
-    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="125"/>
-    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="124"/>
-    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="123"/>
-    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="122"/>
-    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="121"/>
-    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{701EB33F-10A3-4605-AECD-926A6843E153}" name="testCaseId" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{F87CBCEC-E0E5-4FDE-A99C-A1159DA96327}" name="TestScenario" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{6D1F2A9A-10B8-406B-8165-4DA57CEDF688}" name="TestCaseTitle" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{69374052-5930-403C-8081-13855E6BAD3D}" name="Pre-requisites" dataDxfId="157"/>
+    <tableColumn id="5" xr3:uid="{034BB662-671A-4485-9CA5-CD6428DB3577}" name="TestSteps" dataDxfId="156"/>
+    <tableColumn id="6" xr3:uid="{583F95EF-E59B-4B20-977F-8F29DDEE0EEC}" name="TestData" dataDxfId="155"/>
+    <tableColumn id="7" xr3:uid="{3277F406-4F8D-40AB-8AEE-E9FF80847E43}" name="ExpectedResult" dataDxfId="154"/>
+    <tableColumn id="8" xr3:uid="{912E3C66-201C-4165-9F30-90D63E566977}" name="actualResult" dataDxfId="153"/>
+    <tableColumn id="9" xr3:uid="{D0F349F1-CE24-4955-AB82-0BBE5DEADCD2}" name="priority" dataDxfId="152"/>
+    <tableColumn id="10" xr3:uid="{20A0556D-A575-49E1-BAE8-33EBF9A9393D}" name="result" dataDxfId="151"/>
+    <tableColumn id="11" xr3:uid="{5E2046B4-7B73-43BF-BDD8-3E24FC749049}" name="Comments" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="116" dataDxfId="119" headerRowBorderDxfId="117" tableBorderDxfId="118">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}" name="Table19" displayName="Table19" ref="A7:K65" totalsRowShown="0" headerRowDxfId="146" dataDxfId="149" headerRowBorderDxfId="147" tableBorderDxfId="148">
   <autoFilter ref="A7:K65" xr:uid="{6174C89E-5465-4A47-B8F2-E0FA541415A0}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{4CAE104E-37A8-4BC7-836E-247073539068}" name="testCaseId" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{B985C636-98A4-4C58-9F8A-795580DF8D3F}" name="TestScenario" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{467CE337-1E0B-4F8B-81AF-5E7F95DFEA5D}" name="TestCaseTitle" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{8421DABC-D866-4BC3-82CF-A672FA586D3C}" name="Pre-requisites" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{D4C2F8E2-6B5D-46AC-8455-93C1546FEB2A}" name="TestSteps" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{1216F627-653B-4987-95EB-73162E8FF5DF}" name="TestData" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{F6753FB2-5CB5-425E-ADB2-46144038DFBC}" name="ExpectedResult" dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{27C599F0-167A-4A7E-AAF5-5076C59AA31D}" name="actualResult" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{44F0B824-B5CF-43A5-B883-6BB19C608B69}" name="priority" dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{A62C6FD2-DD87-461C-91BC-2802E39F41B9}" name="result" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{DF37B26E-31B0-49DE-8204-5643EBCDBA43}" name="Comments" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="340" dataDxfId="338" headerRowBorderDxfId="339" tableBorderDxfId="337" totalsRowBorderDxfId="336">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}" name="Table3" displayName="Table3" ref="A1:E39" totalsRowShown="0" headerRowDxfId="370" dataDxfId="368" headerRowBorderDxfId="369" tableBorderDxfId="367" totalsRowBorderDxfId="366">
   <autoFilter ref="A1:E39" xr:uid="{DC5C4D2F-1799-4453-B664-663E6B94B69F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="335"/>
-    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="334"/>
-    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="333"/>
-    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="332"/>
-    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="331"/>
+    <tableColumn id="1" xr3:uid="{587095D0-9279-44AA-B9F5-768E8C06289D}" name="Test Scenario ID" dataDxfId="365"/>
+    <tableColumn id="2" xr3:uid="{8E3FBDA0-1D0A-4031-B322-E00448496E26}" name="Reference" dataDxfId="364"/>
+    <tableColumn id="3" xr3:uid="{AF3546CF-3F8D-4FE0-B4AB-10CE1DFB7E71}" name="Test Scenario Description" dataDxfId="363"/>
+    <tableColumn id="4" xr3:uid="{D2FA5268-AC64-4D03-9A48-1CA71827007C}" name="Priority" dataDxfId="362"/>
+    <tableColumn id="5" xr3:uid="{00730E7D-4F05-4974-A30E-14D44BB36A32}" name="Number of Test Cases" dataDxfId="361"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}" name="Table20" displayName="Table20" ref="A7:K44" totalsRowShown="0" headerRowDxfId="101" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}" name="Table20" displayName="Table20" ref="A7:K44" totalsRowShown="0" headerRowDxfId="131" dataDxfId="133" headerRowBorderDxfId="134" tableBorderDxfId="132">
   <autoFilter ref="A7:K44" xr:uid="{7FD42495-09ED-4BDB-92CC-6D62645002A8}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E9107AEB-9917-4DCD-999F-23DED7528269}" name="testCaseId" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{4E7F2B0A-9A06-45D9-829D-517139E93FB0}" name="TestScenario" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{09C2C301-9101-42D2-87C5-CF12D84AFDE2}" name="TestCaseTitle" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{4630FF91-0DD6-4E25-827E-20AC0C3327F3}" name="Pre-requisites" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{6ACC0A37-29EE-49DB-857B-3EF893C5DD7D}" name="TestSteps" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{2AF81478-C083-4718-B4FE-A5FEC39D4683}" name="TestData" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{7FDCD6DB-5E88-42AB-9324-CD156B2F76E1}" name="ExpectedResult" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{8B796E38-6BAF-4EB8-846A-DFC533AC8C87}" name="actualResult" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{362BE16E-720C-4E90-AFB8-ED627DE3BEF5}" name="priority" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{E7237EFD-FF4D-4C9B-98AD-189BF6BF0535}" name="result" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{35851930-6F01-4446-835F-13E1EDBAF070}" name="Comments" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{E9107AEB-9917-4DCD-999F-23DED7528269}" name="testCaseId" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{4E7F2B0A-9A06-45D9-829D-517139E93FB0}" name="TestScenario" dataDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{09C2C301-9101-42D2-87C5-CF12D84AFDE2}" name="TestCaseTitle" dataDxfId="128"/>
+    <tableColumn id="4" xr3:uid="{4630FF91-0DD6-4E25-827E-20AC0C3327F3}" name="Pre-requisites" dataDxfId="127"/>
+    <tableColumn id="5" xr3:uid="{6ACC0A37-29EE-49DB-857B-3EF893C5DD7D}" name="TestSteps" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{2AF81478-C083-4718-B4FE-A5FEC39D4683}" name="TestData" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{7FDCD6DB-5E88-42AB-9324-CD156B2F76E1}" name="ExpectedResult" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{8B796E38-6BAF-4EB8-846A-DFC533AC8C87}" name="actualResult" dataDxfId="123"/>
+    <tableColumn id="9" xr3:uid="{362BE16E-720C-4E90-AFB8-ED627DE3BEF5}" name="priority" dataDxfId="122"/>
+    <tableColumn id="10" xr3:uid="{E7237EFD-FF4D-4C9B-98AD-189BF6BF0535}" name="result" dataDxfId="121"/>
+    <tableColumn id="11" xr3:uid="{35851930-6F01-4446-835F-13E1EDBAF070}" name="Comments" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}" name="Table21" displayName="Table21" ref="A7:K84" totalsRowShown="0" headerRowDxfId="86" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}" name="Table21" displayName="Table21" ref="A7:K84" totalsRowShown="0" headerRowDxfId="116" dataDxfId="118" headerRowBorderDxfId="119" tableBorderDxfId="117">
   <autoFilter ref="A7:K84" xr:uid="{FF285E1C-A3E3-44EA-80F3-1B61FFC56A10}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{15029807-7F0E-425A-BB46-0B6DB3C95839}" name="testCaseId" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{7BD8F686-C564-499F-8D06-C85E47BDAB51}" name="TestScenario" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{67E25BA4-3FF0-4F70-B233-F0E251B42D26}" name="TestCaseTitle" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{B181D3E8-3A2C-400F-B359-B20568BAB1D1}" name="Pre-requisites" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{B58B21E5-45D9-46DC-BFE5-78BDC714CE7C}" name="TestSteps" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{7D364936-A237-464A-A78D-51E3CF7B08EF}" name="TestData" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{DD78F72F-2F82-49C0-857B-9230594DFC47}" name="ExpectedResult" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{DD233399-E0C4-4DCB-918E-551AD68ACB5A}" name="actualResult" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{8D1587AC-EA15-44E2-A0C1-155707A09C86}" name="priority" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{B82BB21B-0563-40CE-B8DB-5D4ADE46287B}" name="result" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{B4AF1D65-2623-4B0C-9A46-AAAF78C4F53B}" name="Comments" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{15029807-7F0E-425A-BB46-0B6DB3C95839}" name="testCaseId" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{7BD8F686-C564-499F-8D06-C85E47BDAB51}" name="TestScenario" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{67E25BA4-3FF0-4F70-B233-F0E251B42D26}" name="TestCaseTitle" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{B181D3E8-3A2C-400F-B359-B20568BAB1D1}" name="Pre-requisites" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{B58B21E5-45D9-46DC-BFE5-78BDC714CE7C}" name="TestSteps" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{7D364936-A237-464A-A78D-51E3CF7B08EF}" name="TestData" dataDxfId="110"/>
+    <tableColumn id="7" xr3:uid="{DD78F72F-2F82-49C0-857B-9230594DFC47}" name="ExpectedResult" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{DD233399-E0C4-4DCB-918E-551AD68ACB5A}" name="actualResult" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{8D1587AC-EA15-44E2-A0C1-155707A09C86}" name="priority" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{B82BB21B-0563-40CE-B8DB-5D4ADE46287B}" name="result" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{B4AF1D65-2623-4B0C-9A46-AAAF78C4F53B}" name="Comments" dataDxfId="105"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}" name="Table22" displayName="Table22" ref="A7:K73" totalsRowShown="0" headerRowDxfId="71" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}" name="Table22" displayName="Table22" ref="A7:K73" totalsRowShown="0" headerRowDxfId="101" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102">
   <autoFilter ref="A7:K73" xr:uid="{C6769024-1D84-46C5-A63D-73C989EB9998}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{9C094CDF-2D28-4BE3-99E2-FE5BD3E1EFED}" name="testCaseId" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{94350EDF-00E0-425A-8D59-A436A634832D}" name="TestScenario" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{46F08573-9A97-4833-A375-E13614AB1CD1}" name="TestCaseTitle" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{9CAFA43D-2ED9-4B71-B10E-703FE41DF889}" name="Pre-requisites" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{6B1DCF0A-0BAA-40AF-A30E-7AF7E59D4B32}" name="TestSteps" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{254FF740-551F-44C6-85E3-0201E5C78A60}" name="TestData" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{37BC01A3-6D35-4AC9-B6E3-D024ABF0F7F6}" name="ExpectedResult" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{490207E0-C5D6-4F92-A004-D0982BA6E84D}" name="actualResult" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{2D195591-BB51-4C69-8149-6B4BCC5DCE19}" name="priority" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{D3EB2765-8091-404B-AF58-2635762A163C}" name="result" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{EA1CCBEC-876B-40ED-8BDE-8E73CB5ABE7B}" name="Comments" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{9C094CDF-2D28-4BE3-99E2-FE5BD3E1EFED}" name="testCaseId" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{94350EDF-00E0-425A-8D59-A436A634832D}" name="TestScenario" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{46F08573-9A97-4833-A375-E13614AB1CD1}" name="TestCaseTitle" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{9CAFA43D-2ED9-4B71-B10E-703FE41DF889}" name="Pre-requisites" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{6B1DCF0A-0BAA-40AF-A30E-7AF7E59D4B32}" name="TestSteps" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{254FF740-551F-44C6-85E3-0201E5C78A60}" name="TestData" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{37BC01A3-6D35-4AC9-B6E3-D024ABF0F7F6}" name="ExpectedResult" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{490207E0-C5D6-4F92-A004-D0982BA6E84D}" name="actualResult" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{2D195591-BB51-4C69-8149-6B4BCC5DCE19}" name="priority" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{D3EB2765-8091-404B-AF58-2635762A163C}" name="result" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{EA1CCBEC-876B-40ED-8BDE-8E73CB5ABE7B}" name="Comments" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{68D33CEF-CA71-4D05-A22F-64AD7D766BFE}" name="Table23" displayName="Table23" ref="A7:K55" totalsRowShown="0" headerRowDxfId="56" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{68D33CEF-CA71-4D05-A22F-64AD7D766BFE}" name="Table23" displayName="Table23" ref="A7:K55" totalsRowShown="0" headerRowDxfId="86" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87">
   <autoFilter ref="A7:K55" xr:uid="{68D33CEF-CA71-4D05-A22F-64AD7D766BFE}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{EB45F800-5532-41CB-89BE-F74E48473DD0}" name="testCaseId" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{9232284E-5738-40E3-8919-775C400215EA}" name="TestScenario" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{4EA3B8D0-97A9-4985-A57D-5A2E04A4A859}" name="TestCaseTitle" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{5E1AF50A-9662-4A96-86EC-03FD3FAF1123}" name="Pre-requisites" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{BB4ACB27-08A2-4080-9E28-9896A36E30AC}" name="TestSteps" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{B0EEDF0B-BB67-49EC-9A2B-CB5DC44066E8}" name="TestData" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{B0FFBE88-FEFB-4A88-A24F-378B78A83254}" name="ExpectedResult" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{4817BD8B-4FE8-4DD9-B2F3-B7DA04D2A3E0}" name="actualResult" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{7997A220-EC1A-4430-84A8-C8531D74BB13}" name="priority" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{D3D577BF-5FF1-4EFF-822F-E65604ACFCA3}" name="result" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{46BB6195-AF8F-4AE9-A591-5A814E6FDA36}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{EB45F800-5532-41CB-89BE-F74E48473DD0}" name="testCaseId" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{9232284E-5738-40E3-8919-775C400215EA}" name="TestScenario" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{4EA3B8D0-97A9-4985-A57D-5A2E04A4A859}" name="TestCaseTitle" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{5E1AF50A-9662-4A96-86EC-03FD3FAF1123}" name="Pre-requisites" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{BB4ACB27-08A2-4080-9E28-9896A36E30AC}" name="TestSteps" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{B0EEDF0B-BB67-49EC-9A2B-CB5DC44066E8}" name="TestData" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{B0FFBE88-FEFB-4A88-A24F-378B78A83254}" name="ExpectedResult" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{4817BD8B-4FE8-4DD9-B2F3-B7DA04D2A3E0}" name="actualResult" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{7997A220-EC1A-4430-84A8-C8531D74BB13}" name="priority" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{D3D577BF-5FF1-4EFF-822F-E65604ACFCA3}" name="result" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{46BB6195-AF8F-4AE9-A591-5A814E6FDA36}" name="Comments" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{FD17F5D9-1665-4980-BBDA-726FB1A23CA2}" name="Table24" displayName="Table24" ref="A7:K30" totalsRowShown="0" headerRowDxfId="41" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{FD17F5D9-1665-4980-BBDA-726FB1A23CA2}" name="Table24" displayName="Table24" ref="A7:K30" totalsRowShown="0" headerRowDxfId="71" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72">
   <autoFilter ref="A7:K30" xr:uid="{FD17F5D9-1665-4980-BBDA-726FB1A23CA2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{235EDE94-026F-4F64-98C8-5E31B6DE7F8E}" name="testCaseId" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{66B07AAE-FBBF-40DE-ACF7-ED15C3FDC7D1}" name="TestScenario" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{9103F5B9-0E85-4065-9EB6-5AA8C473300D}" name="TestCaseTitle" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{245EF63E-50D3-4405-838D-07A0E174322A}" name="Pre-requisites" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{1F0C6C54-8F91-4158-9226-0735A26CCDF1}" name="TestSteps" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{51104F2E-6E22-4719-8062-90335CF6F7DF}" name="TestData" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{AC76E163-1681-4CAD-8433-B5CC48CE5313}" name="ExpectedResult" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{9BA700C1-6164-4AF4-85D8-8954E78872A2}" name="actualResult" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{199390DA-0C6B-4789-984B-A089DE51DFDD}" name="priority" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{4649A77B-C6C4-4D9F-B175-B39CCF8E9ECD}" name="result" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{E5E9D353-22FE-4C44-A295-0D119BC404B8}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{235EDE94-026F-4F64-98C8-5E31B6DE7F8E}" name="testCaseId" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{66B07AAE-FBBF-40DE-ACF7-ED15C3FDC7D1}" name="TestScenario" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{9103F5B9-0E85-4065-9EB6-5AA8C473300D}" name="TestCaseTitle" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{245EF63E-50D3-4405-838D-07A0E174322A}" name="Pre-requisites" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{1F0C6C54-8F91-4158-9226-0735A26CCDF1}" name="TestSteps" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{51104F2E-6E22-4719-8062-90335CF6F7DF}" name="TestData" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{AC76E163-1681-4CAD-8433-B5CC48CE5313}" name="ExpectedResult" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{9BA700C1-6164-4AF4-85D8-8954E78872A2}" name="actualResult" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{199390DA-0C6B-4789-984B-A089DE51DFDD}" name="priority" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{4649A77B-C6C4-4D9F-B175-B39CCF8E9ECD}" name="result" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{E5E9D353-22FE-4C44-A295-0D119BC404B8}" name="Comments" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{FB7280D7-BCAD-4FF1-954E-497681E98B01}" name="Table25" displayName="Table25" ref="A7:K42" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{FB7280D7-BCAD-4FF1-954E-497681E98B01}" name="Table25" displayName="Table25" ref="A7:K42" totalsRowShown="0" headerRowDxfId="56" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A7:K42" xr:uid="{FB7280D7-BCAD-4FF1-954E-497681E98B01}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C34059EB-D8CC-4CB5-B77D-1FEA883D6627}" name="testCaseId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{4857DF9B-007C-441F-B34D-2E702E256E55}" name="TestScenario" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{BC62CFB1-CF67-4BF5-AD42-6725F64A42EA}" name="TestCaseTitle" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{8D8A7C91-2B26-43A9-93BF-E45E7B561258}" name="Pre-requisites" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{3F2E406A-A218-4064-93BC-E2634CE28D7C}" name="TestSteps" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{E3F4E357-EBA7-4F65-BC33-AC8439820FCB}" name="TestData" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{94056214-A554-4202-9399-B05BE597BDC7}" name="ExpectedResult" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{40766EFA-F7AD-49AA-B233-B5BC924682CB}" name="actualResult" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{0165342E-CEF0-4A6B-B205-2C00A198D2F4}" name="priority" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{D50A93B7-0F9E-403B-84D4-C5035A273DF2}" name="result" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{8524DFEB-A607-444E-8F12-73187F3E1599}" name="Comments" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{C34059EB-D8CC-4CB5-B77D-1FEA883D6627}" name="testCaseId" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{4857DF9B-007C-441F-B34D-2E702E256E55}" name="TestScenario" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{BC62CFB1-CF67-4BF5-AD42-6725F64A42EA}" name="TestCaseTitle" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{8D8A7C91-2B26-43A9-93BF-E45E7B561258}" name="Pre-requisites" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{3F2E406A-A218-4064-93BC-E2634CE28D7C}" name="TestSteps" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{E3F4E357-EBA7-4F65-BC33-AC8439820FCB}" name="TestData" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{94056214-A554-4202-9399-B05BE597BDC7}" name="ExpectedResult" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{40766EFA-F7AD-49AA-B233-B5BC924682CB}" name="actualResult" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{0165342E-CEF0-4A6B-B205-2C00A198D2F4}" name="priority" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{D50A93B7-0F9E-403B-84D4-C5035A273DF2}" name="result" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{8524DFEB-A607-444E-8F12-73187F3E1599}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{13186742-473F-4AAA-A23E-2B220DA71B17}" name="Table26" displayName="Table26" ref="A7:K52" totalsRowShown="0" headerRowDxfId="12" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{13186742-473F-4AAA-A23E-2B220DA71B17}" name="Table26" displayName="Table26" ref="A7:K52" totalsRowShown="0" headerRowDxfId="42" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="41">
   <autoFilter ref="A7:K52" xr:uid="{13186742-473F-4AAA-A23E-2B220DA71B17}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{44D9CBF6-8A4C-4A11-BB7B-0866FE800104}" name="testCaseId" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{1DCAEA68-69A2-46D3-9A8B-0AB366B33F66}" name="TestScenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{11A6AC34-7EB4-4A8C-B0C6-6E6FF002A79B}" name="TestCaseTitle" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{93789150-0624-43D7-8091-EDC37A54BE2B}" name="Pre-requisites" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{FFD1E138-B51A-4AFB-BF12-ADB26A6EF42E}" name="TestSteps" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{34AB9F4E-A1AB-4AF9-A8C3-A1A1AABECE87}" name="TestData" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{528D6C6B-AF55-43B1-A3D9-C1FF4522E16B}" name="ExpectedResult" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{C60DE4FE-D70C-4169-8D1E-BCC0050A0117}" name="actualResult" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{FAA5324F-E6C6-47F1-BD4F-5602167797DA}" name="priority" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{2161F82E-F261-418B-8F48-5C94CBF8E9CC}" name="result" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{F70A27B6-2C6B-459F-A595-D26B1E0BBC13}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{44D9CBF6-8A4C-4A11-BB7B-0866FE800104}" name="testCaseId" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{1DCAEA68-69A2-46D3-9A8B-0AB366B33F66}" name="TestScenario" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{11A6AC34-7EB4-4A8C-B0C6-6E6FF002A79B}" name="TestCaseTitle" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{93789150-0624-43D7-8091-EDC37A54BE2B}" name="Pre-requisites" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{FFD1E138-B51A-4AFB-BF12-ADB26A6EF42E}" name="TestSteps" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{34AB9F4E-A1AB-4AF9-A8C3-A1A1AABECE87}" name="TestData" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{528D6C6B-AF55-43B1-A3D9-C1FF4522E16B}" name="ExpectedResult" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{C60DE4FE-D70C-4169-8D1E-BCC0050A0117}" name="actualResult" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{FAA5324F-E6C6-47F1-BD4F-5602167797DA}" name="priority" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{2161F82E-F261-418B-8F48-5C94CBF8E9CC}" name="result" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{F70A27B6-2C6B-459F-A595-D26B1E0BBC13}" name="Comments" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{2FC86182-C7FB-4CE3-A301-25EF5377B201}" name="Table27" displayName="Table27" ref="A7:K50" totalsRowShown="0" headerRowDxfId="26" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+  <autoFilter ref="A7:K50" xr:uid="{2FC86182-C7FB-4CE3-A301-25EF5377B201}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{B5E29CD3-ABB0-41E4-A270-247B71A68D5D}" name="testCaseId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{110B8604-8A49-474E-9427-E7E5A60C1476}" name="TestScenario" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{227DE02D-0218-4A79-82AD-4EF41E7A34C6}" name="TestCaseTitle" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{03362C64-6EC6-4E4E-9FB4-E3D75F5C4887}" name="Pre-requisites" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{310F6D6B-591A-480C-B2DA-CC7DD9D8451C}" name="TestSteps" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{8BB9DDA6-44D0-4CBA-8AD4-470641DDEED3}" name="TestData" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{FB13DD3A-B5B4-41B0-B248-6F12BC59958E}" name="ExpectedResult" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{05178C5E-B26F-43A1-9414-6D78547DAC8A}" name="actualResult" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{C048A7DF-3DDA-406E-AAA6-EB3F418F11AF}" name="priority" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{DD540ECA-FFBB-49E7-A411-331C03319085}" name="result" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{98A7B05D-F69B-418E-A8E3-D1A57A591154}" name="Comments" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{48901816-CAA8-4389-BD2A-C11B92CE5DE2}" name="Table28" displayName="Table28" ref="A7:K31" totalsRowShown="0" headerRowDxfId="11" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+  <autoFilter ref="A7:K31" xr:uid="{48901816-CAA8-4389-BD2A-C11B92CE5DE2}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{390B641C-E246-4A5D-B4EC-60316876D4C6}" name="testCaseId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{F9F9617F-E3C4-4632-9AAD-2347EA56A6C6}" name="TestScenario" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{1ED68746-1978-4902-AB2D-E6D74834003F}" name="TestCaseTitle" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{650048C7-100A-47C4-82BE-B9E45CDE59C4}" name="Pre-requisites" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{AF44C926-AC19-4161-B32E-BE17B1426C15}" name="TestSteps" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{F68441E0-A4B4-4219-91D2-8575079BED14}" name="TestData" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{12F3FC12-E138-4EB1-87F4-60EE4193D4D7}" name="ExpectedResult" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{BB0EB4DB-B26C-4DA3-A13F-4E5D79241823}" name="actualResult" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{E97AF660-AFAE-4C81-90D9-9AE537A32068}" name="priority" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{0BEA25BC-77BC-4277-98C4-DF5BAE746463}" name="result" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{776512D8-8EA8-42FE-B7C5-55CA68224BFF}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17807,7 +19127,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{25D8AB7C-C206-4FA0-B350-DEB797DB0D49}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="330"/>
+    <tableColumn id="1" xr3:uid="{20E0049E-050E-4259-8D8D-F4CEB577D219}" name="Column1" dataDxfId="360"/>
     <tableColumn id="2" xr3:uid="{7BC360F1-7012-46CE-857F-D07291925DD7}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -17815,120 +19135,120 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="329" dataDxfId="327" headerRowBorderDxfId="328" tableBorderDxfId="326">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}" name="Table1" displayName="Table1" ref="A5:K118" totalsRowShown="0" headerRowDxfId="359" dataDxfId="357" headerRowBorderDxfId="358" tableBorderDxfId="356">
   <autoFilter ref="A5:K118" xr:uid="{75AE097C-21B1-44ED-8740-AB05B242B184}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="325"/>
-    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="324"/>
-    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="323"/>
-    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="322"/>
-    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="321"/>
-    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="320"/>
-    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="319"/>
-    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="318"/>
-    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="317"/>
-    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="316"/>
-    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="315"/>
+    <tableColumn id="1" xr3:uid="{A44B2E49-FB02-47AC-86B7-D82037C888DA}" name="testCaseId" dataDxfId="355"/>
+    <tableColumn id="2" xr3:uid="{92F5AEA3-BD4B-43A4-BA57-2763DEF9CA23}" name="TestScenario" dataDxfId="354"/>
+    <tableColumn id="3" xr3:uid="{3BFA616B-6E52-40CD-87CD-254BFA07EFF3}" name="TestCaseTitle" dataDxfId="353"/>
+    <tableColumn id="4" xr3:uid="{EE8EE367-6C0E-4C50-97A9-3B940215026F}" name="Pre-requisites" dataDxfId="352"/>
+    <tableColumn id="5" xr3:uid="{8690DFA4-80A7-4C16-AABD-8B748AE2E6C2}" name="TestSteps" dataDxfId="351"/>
+    <tableColumn id="6" xr3:uid="{98970436-1CB3-42E3-B5D2-E4938B93A4FA}" name="TestData" dataDxfId="350"/>
+    <tableColumn id="7" xr3:uid="{9FB72621-3EFF-488C-AFB1-273C185A7847}" name="ExpectedResult" dataDxfId="349"/>
+    <tableColumn id="8" xr3:uid="{754200D8-F687-4580-A6BC-FF802A202D96}" name="actualResult" dataDxfId="348"/>
+    <tableColumn id="9" xr3:uid="{4C54D81E-DF4A-4B9D-8308-23F9E0D0A42E}" name="priority" dataDxfId="347"/>
+    <tableColumn id="10" xr3:uid="{BA814378-E55D-492C-8BA1-330F901CE99E}" name="result" dataDxfId="346"/>
+    <tableColumn id="11" xr3:uid="{D6310E1F-2F92-4A8F-AACE-E8C60C423231}" name="Comments" dataDxfId="345"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="314" dataDxfId="312" headerRowBorderDxfId="313" tableBorderDxfId="311">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}" name="Table5" displayName="Table5" ref="A6:K99" totalsRowShown="0" headerRowDxfId="344" dataDxfId="342" headerRowBorderDxfId="343" tableBorderDxfId="341">
   <autoFilter ref="A6:K99" xr:uid="{6FFCF6DA-4F9A-4F8B-BFB9-50A6103329D3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="310"/>
-    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="309"/>
-    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="308"/>
-    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="307"/>
-    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="306"/>
-    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="305"/>
-    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="304"/>
-    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="303"/>
-    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="302"/>
-    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="301"/>
-    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="300"/>
+    <tableColumn id="1" xr3:uid="{1C17052C-4868-48E2-A44E-510521A69AE9}" name="testCaseId" dataDxfId="340"/>
+    <tableColumn id="2" xr3:uid="{6937BCFD-A6C0-49D9-BAC1-D6249FC45283}" name="TestScenario" dataDxfId="339"/>
+    <tableColumn id="3" xr3:uid="{04F1789E-4245-4660-8E31-AECF9F641D40}" name="TestCaseTitle" dataDxfId="338"/>
+    <tableColumn id="4" xr3:uid="{F852BEC7-D244-45D0-9F14-96C84DF6C28C}" name="Pre-requisites" dataDxfId="337"/>
+    <tableColumn id="5" xr3:uid="{4DEF79E5-19F3-4705-9F7F-AB43B4A97880}" name="TestSteps" dataDxfId="336"/>
+    <tableColumn id="6" xr3:uid="{F5A68562-DEBD-4CD2-9C0B-846AD2FF3CCB}" name="TestData" dataDxfId="335"/>
+    <tableColumn id="7" xr3:uid="{7041036A-414A-49BB-85E8-0BEE136FA7A8}" name="ExpectedResult" dataDxfId="334"/>
+    <tableColumn id="8" xr3:uid="{63E49C4A-8E10-46E0-9B77-C968E0A9EC3E}" name="actualResult" dataDxfId="333"/>
+    <tableColumn id="9" xr3:uid="{09EDF042-C02B-4280-96CB-D6A6FC639D1A}" name="priority" dataDxfId="332"/>
+    <tableColumn id="10" xr3:uid="{923A803D-5191-4673-84B0-3D827AB4995F}" name="result" dataDxfId="331"/>
+    <tableColumn id="11" xr3:uid="{E3673ABC-6199-4BED-B6CC-6D1C5F728BF8}" name="Comments" dataDxfId="330"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="299" dataDxfId="297" headerRowBorderDxfId="298" tableBorderDxfId="296">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}" name="Table6" displayName="Table6" ref="A7:K30" totalsRowShown="0" headerRowDxfId="329" dataDxfId="327" headerRowBorderDxfId="328" tableBorderDxfId="326">
   <autoFilter ref="A7:K30" xr:uid="{744D3EB5-72F3-4252-A1EB-AE29AA445119}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="295"/>
-    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="294"/>
-    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="293"/>
-    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="292"/>
-    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="291"/>
-    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="290"/>
-    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="289"/>
-    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="288"/>
-    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="287"/>
-    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="286"/>
-    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="285"/>
+    <tableColumn id="1" xr3:uid="{F1022C8E-72F9-4673-A4CD-0BF8DB369314}" name="testCaseId" dataDxfId="325"/>
+    <tableColumn id="2" xr3:uid="{6FD2F55A-2817-4EA8-BBB4-8A317A428CB6}" name="TestScenario" dataDxfId="324"/>
+    <tableColumn id="3" xr3:uid="{E1C5B13B-64A8-4F6B-892A-EE136EB3716A}" name="TestCaseTitle" dataDxfId="323"/>
+    <tableColumn id="4" xr3:uid="{81B75BE3-7AEA-46FC-B9D4-FF7B473C8CEB}" name="Pre-requisites" dataDxfId="322"/>
+    <tableColumn id="5" xr3:uid="{A4C88125-92FA-4745-8A5F-BD14BBA80207}" name="TestSteps" dataDxfId="321"/>
+    <tableColumn id="6" xr3:uid="{4483DD33-09CD-43A6-8DF2-B1717839B75C}" name="TestData" dataDxfId="320"/>
+    <tableColumn id="7" xr3:uid="{A40C0874-D70B-4E24-BB6E-B7FB2BD6C2D3}" name="ExpectedResult" dataDxfId="319"/>
+    <tableColumn id="8" xr3:uid="{91644D71-DB40-41C5-9B00-A8D0314B3967}" name="actualResult" dataDxfId="318"/>
+    <tableColumn id="9" xr3:uid="{2F9BAED5-66B0-43D5-A7EB-F7FBAB5BD0A0}" name="priority" dataDxfId="317"/>
+    <tableColumn id="10" xr3:uid="{F625A35B-2854-4B53-842B-9DCD1C7A8418}" name="result" dataDxfId="316"/>
+    <tableColumn id="11" xr3:uid="{02ED79D1-507F-4603-BD6C-6CECE7204D2C}" name="Comments" dataDxfId="315"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="284" dataDxfId="282" headerRowBorderDxfId="283" tableBorderDxfId="281">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}" name="Table7" displayName="Table7" ref="A4:K77" totalsRowShown="0" headerRowDxfId="314" dataDxfId="312" headerRowBorderDxfId="313" tableBorderDxfId="311">
   <autoFilter ref="A4:K77" xr:uid="{10621A41-DDC3-4A92-B2A6-6F824E046D1D}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="280"/>
-    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="279"/>
-    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="278"/>
-    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="277"/>
-    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="276"/>
-    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="275"/>
-    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="274"/>
-    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="273"/>
-    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="272"/>
-    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="271"/>
-    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="270"/>
+    <tableColumn id="1" xr3:uid="{81144497-9798-42D2-911A-B7EA5A11DBAF}" name="testCaseId" dataDxfId="310"/>
+    <tableColumn id="2" xr3:uid="{D57EBC8D-5683-43F2-855C-D408457C2020}" name="TestScenario" dataDxfId="309"/>
+    <tableColumn id="3" xr3:uid="{ACF8C0ED-4378-44DA-B42E-083A27C9FFD3}" name="TestCaseTitle" dataDxfId="308"/>
+    <tableColumn id="4" xr3:uid="{B211718F-D542-4ADA-B9ED-3CCDCBC818E2}" name="Pre-requisites" dataDxfId="307"/>
+    <tableColumn id="5" xr3:uid="{F29A79BB-1AFB-4545-B95E-7CFDA07C1F4A}" name="TestSteps" dataDxfId="306"/>
+    <tableColumn id="6" xr3:uid="{781CAAE0-833F-40AF-917A-3D411EC18077}" name="TestData" dataDxfId="305"/>
+    <tableColumn id="7" xr3:uid="{67442296-427C-4B59-8AB3-D17CF95E99F7}" name="ExpectedResult" dataDxfId="304"/>
+    <tableColumn id="8" xr3:uid="{04AD1331-BF61-446E-9A82-856C67DD9418}" name="actualResult" dataDxfId="303"/>
+    <tableColumn id="9" xr3:uid="{D95B4D32-1AAC-4395-82F9-240D00721EA9}" name="priority" dataDxfId="302"/>
+    <tableColumn id="10" xr3:uid="{AAAD855B-842D-475C-9D60-916343B550F2}" name="result" dataDxfId="301"/>
+    <tableColumn id="11" xr3:uid="{9C534D2A-770F-4F11-8A02-DFBB5255DF0F}" name="Comments" dataDxfId="300"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="269" dataDxfId="267" headerRowBorderDxfId="268" tableBorderDxfId="266">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}" name="Table8" displayName="Table8" ref="A7:K44" totalsRowShown="0" headerRowDxfId="299" dataDxfId="297" headerRowBorderDxfId="298" tableBorderDxfId="296">
   <autoFilter ref="A7:K44" xr:uid="{9F593292-B1B4-4FC1-9656-EA51C4D2C156}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="265"/>
-    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="264"/>
-    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="263"/>
-    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="262"/>
-    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="261"/>
-    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="260"/>
-    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="259"/>
-    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="258"/>
-    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="257"/>
-    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="256"/>
-    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="255"/>
+    <tableColumn id="1" xr3:uid="{DDAB22B1-F568-4F12-AC39-729FB7EC2EC4}" name="testCaseId" dataDxfId="295"/>
+    <tableColumn id="2" xr3:uid="{FD1D69A0-E49D-41E5-897D-4BCD05A18424}" name="TestScenario" dataDxfId="294"/>
+    <tableColumn id="3" xr3:uid="{76B08AA4-66A3-48F5-ADF8-EDAA94F6F8DE}" name="TestCaseTitle" dataDxfId="293"/>
+    <tableColumn id="4" xr3:uid="{E551C8DD-68B7-48CB-B6E2-178812D6666B}" name="Pre-requisites" dataDxfId="292"/>
+    <tableColumn id="5" xr3:uid="{22595384-390D-410B-B7C3-FB3A1850AB68}" name="TestSteps" dataDxfId="291"/>
+    <tableColumn id="6" xr3:uid="{8097B4E3-08A6-41AC-B0FD-A0F7BB246889}" name="TestData" dataDxfId="290"/>
+    <tableColumn id="7" xr3:uid="{B663CABD-7DAF-43AD-9B61-05F58BA3C88D}" name="ExpectedResult" dataDxfId="289"/>
+    <tableColumn id="8" xr3:uid="{A111EE2B-DE52-442C-BF79-39205554D5F1}" name="actualResult" dataDxfId="288"/>
+    <tableColumn id="9" xr3:uid="{31012537-782B-4FFA-A17A-E1D9EAC3545C}" name="priority" dataDxfId="287"/>
+    <tableColumn id="10" xr3:uid="{8AA87DC0-730B-42E5-AEF9-F404DD848A19}" name="result" dataDxfId="286"/>
+    <tableColumn id="11" xr3:uid="{BE7DF8EB-4CAE-4269-AC4A-47A0442AF89E}" name="Comments" dataDxfId="285"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}" name="Table9" displayName="Table9" ref="A6:K40" totalsRowShown="0" headerRowDxfId="284" dataDxfId="282" headerRowBorderDxfId="283" tableBorderDxfId="281">
   <autoFilter ref="A6:K40" xr:uid="{BD0FE4E0-4F70-4BB1-BFF3-0B2BE240D236}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="250"/>
-    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="249"/>
-    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="248"/>
-    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="247"/>
-    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="246"/>
-    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="245"/>
-    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="244"/>
-    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="243"/>
-    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="242"/>
-    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="241"/>
-    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="240"/>
+    <tableColumn id="1" xr3:uid="{D078C0A5-A459-4D18-AB6D-DABAA5D9269C}" name="testCaseId" dataDxfId="280"/>
+    <tableColumn id="2" xr3:uid="{DAE3E331-2796-4B7B-B284-09026FFC510F}" name="TestScenario" dataDxfId="279"/>
+    <tableColumn id="3" xr3:uid="{C043CE13-729F-44E8-86FD-7EEF748CDFF7}" name="TestCaseTitle" dataDxfId="278"/>
+    <tableColumn id="4" xr3:uid="{60E2E76A-24EA-4242-9CA6-E5D3A4D66C06}" name="Pre-requisites" dataDxfId="277"/>
+    <tableColumn id="5" xr3:uid="{897F1339-1D8A-4074-87F3-E51E01042643}" name="TestSteps" dataDxfId="276"/>
+    <tableColumn id="6" xr3:uid="{7CEAE383-DCE3-46D9-BF64-5CA3D3129AB7}" name="TestData" dataDxfId="275"/>
+    <tableColumn id="7" xr3:uid="{961AA0BE-7074-43B1-BD7F-003B92D277BB}" name="ExpectedResult" dataDxfId="274"/>
+    <tableColumn id="8" xr3:uid="{DE84E708-5574-4961-A7A3-37BEBDF0CD34}" name="actualResult" dataDxfId="273"/>
+    <tableColumn id="9" xr3:uid="{A3DFE587-D93F-42DD-9726-9270D93DC492}" name="priority" dataDxfId="272"/>
+    <tableColumn id="10" xr3:uid="{1303D1DA-4D4E-4070-83E5-95FD7D03C476}" name="result" dataDxfId="271"/>
+    <tableColumn id="11" xr3:uid="{3E88D465-E2C9-4C0D-8508-11DF2C887BA3}" name="Comments" dataDxfId="270"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -35706,6 +37026,1431 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D27E5CC-CD82-49DD-9D25-77978C556157}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="68"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="69" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="70"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="71.25">
+      <c r="A8" s="51" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>2148</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>2150</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>2149</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A11" s="49" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>2154</v>
+      </c>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49" t="s">
+        <v>2155</v>
+      </c>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+    </row>
+    <row r="12" spans="1:11" ht="129" thickBot="1">
+      <c r="A12" s="43" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43" t="s">
+        <v>2160</v>
+      </c>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="156.75">
+      <c r="A13" s="51" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51" t="s">
+        <v>2165</v>
+      </c>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+    </row>
+    <row r="16" spans="1:11" ht="183.75" customHeight="1">
+      <c r="A16" s="43" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43" t="s">
+        <v>2169</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11" ht="114">
+      <c r="A19" s="51" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>2172</v>
+      </c>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51" t="s">
+        <v>2174</v>
+      </c>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44" t="s">
+        <v>2173</v>
+      </c>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+    </row>
+    <row r="22" spans="1:11" ht="114">
+      <c r="A22" s="43" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>2177</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43" t="s">
+        <v>2179</v>
+      </c>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11" ht="71.25">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43" t="s">
+        <v>2178</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="99.75">
+      <c r="A27" s="51" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51" t="s">
+        <v>2184</v>
+      </c>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+    </row>
+    <row r="30" spans="1:11" ht="226.5" customHeight="1">
+      <c r="A30" s="43" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>2188</v>
+      </c>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+    </row>
+    <row r="33" spans="1:11" ht="169.5" customHeight="1">
+      <c r="A33" s="51" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B33" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>2193</v>
+      </c>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51" t="s">
+        <v>2195</v>
+      </c>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="43"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+    </row>
+    <row r="35" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
+    </row>
+    <row r="36" spans="1:11" ht="85.5">
+      <c r="A36" s="43" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B36" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43" t="s">
+        <v>2199</v>
+      </c>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" spans="1:11" ht="114">
+      <c r="A39" s="51" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51" t="s">
+        <v>2204</v>
+      </c>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
+      <c r="K39" s="51"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="43"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+    </row>
+    <row r="41" spans="1:11" ht="42.75">
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43" t="s">
+        <v>2203</v>
+      </c>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+    </row>
+    <row r="43" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+    </row>
+    <row r="44" spans="1:11" ht="114">
+      <c r="A44" s="43" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B44" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>2207</v>
+      </c>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43" t="s">
+        <v>2208</v>
+      </c>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A46" s="43"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+    </row>
+    <row r="47" spans="1:11" ht="100.5" thickBot="1">
+      <c r="A47" s="49" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B47" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="49" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D47" s="49" t="s">
+        <v>2211</v>
+      </c>
+      <c r="E47" s="49" t="s">
+        <v>2212</v>
+      </c>
+      <c r="F47" s="49"/>
+      <c r="G47" s="49" t="s">
+        <v>2213</v>
+      </c>
+      <c r="H47" s="49"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="49"/>
+      <c r="K47" s="49"/>
+    </row>
+    <row r="48" spans="1:11" ht="169.5" customHeight="1">
+      <c r="A48" s="43" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B48" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E48" s="43" t="s">
+        <v>2216</v>
+      </c>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43" t="s">
+        <v>2218</v>
+      </c>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="43"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+    </row>
+    <row r="50" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A50" s="44"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44" t="s">
+        <v>2217</v>
+      </c>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC76C381-DF73-4DE4-8713-E3799BAEA54B}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="29.7109375" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.5703125" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="57">
+      <c r="A8" s="51" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>2148</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51" t="s">
+        <v>2221</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>2036</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+    </row>
+    <row r="11" spans="1:11" ht="129" thickBot="1">
+      <c r="A11" s="49" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>2223</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>2225</v>
+      </c>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49" t="s">
+        <v>2226</v>
+      </c>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+    </row>
+    <row r="12" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A12" s="43" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>2230</v>
+      </c>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43" t="s">
+        <v>2231</v>
+      </c>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" ht="71.25">
+      <c r="A13" s="51" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51" t="s">
+        <v>2237</v>
+      </c>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" ht="29.25" thickBot="1">
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+    </row>
+    <row r="16" spans="1:11" ht="71.25">
+      <c r="A16" s="43" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>2241</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43" t="s">
+        <v>2243</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="43.5" thickBot="1">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43" t="s">
+        <v>2242</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+    </row>
+    <row r="19" spans="1:11" ht="114.75" thickBot="1">
+      <c r="A19" s="49" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E19" s="49" t="s">
+        <v>2247</v>
+      </c>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49" t="s">
+        <v>2248</v>
+      </c>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+    </row>
+    <row r="20" spans="1:11" ht="86.25" thickBot="1">
+      <c r="A20" s="43" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>2251</v>
+      </c>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43" t="s">
+        <v>2252</v>
+      </c>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:11" ht="143.25" thickBot="1">
+      <c r="A21" s="49" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E21" s="49" t="s">
+        <v>2255</v>
+      </c>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49" t="s">
+        <v>2256</v>
+      </c>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+    </row>
+    <row r="22" spans="1:11" ht="141" customHeight="1">
+      <c r="A22" s="43" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>2259</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43" t="s">
+        <v>2261</v>
+      </c>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11" ht="72" thickBot="1">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43" t="s">
+        <v>2260</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="99.75">
+      <c r="A25" s="51" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>2259</v>
+      </c>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51" t="s">
+        <v>2265</v>
+      </c>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44" t="s">
+        <v>2264</v>
+      </c>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+    </row>
+    <row r="28" spans="1:11" ht="57.75" thickBot="1">
+      <c r="A28" s="43" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43" t="s">
+        <v>2267</v>
+      </c>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11" ht="99.75">
+      <c r="A29" s="51" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B29" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>2270</v>
+      </c>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51" t="s">
+        <v>2272</v>
+      </c>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="51"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+    </row>
+    <row r="31" spans="1:11" ht="129" thickBot="1">
+      <c r="A31" s="44"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B02CE7-59C8-44CE-ACD4-D93A6AFF8528}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A657E69E-CEAF-48A5-A6BC-926A070B06A9}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A329474-7E16-4C5E-806C-DE3AF9E697F7}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/testPlan.xlsx
+++ b/testPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0DC078-8521-4742-B6B9-C05E7619B538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A343B83-70FA-46B7-A2E1-67FE9A29FE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="19" activeTab="25" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="20" activeTab="26" xr2:uid="{A3BAB37A-DF62-4D82-BA43-535E7EE8B7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <sheet name="ChangePassword" sheetId="24" r:id="rId24"/>
     <sheet name="AddressBook" sheetId="25" r:id="rId25"/>
     <sheet name="OrderHistory" sheetId="26" r:id="rId26"/>
-    <sheet name="Sheet12" sheetId="27" r:id="rId27"/>
+    <sheet name="ProductReturn" sheetId="27" r:id="rId27"/>
     <sheet name="Sheet13" sheetId="28" r:id="rId28"/>
     <sheet name="Sheet14" sheetId="29" r:id="rId29"/>
   </sheets>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3705" uniqueCount="2273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3820" uniqueCount="2347">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -7402,6 +7402,228 @@
   </si>
   <si>
     <t>Access is denied. The system prevents viewing the order details and redirects the user or shows an error.</t>
+  </si>
+  <si>
+    <t>TC_RET_001</t>
+  </si>
+  <si>
+    <t>Verify navigation to Returns form via Footer link</t>
+  </si>
+  <si>
+    <t>1. Scroll to the footer of the page.</t>
+  </si>
+  <si>
+    <t>2. Click the 'Returns' link under Customer Service.</t>
+  </si>
+  <si>
+    <t>User is routed to the Product Returns form.</t>
+  </si>
+  <si>
+    <t>TC_RET_002</t>
+  </si>
+  <si>
+    <t>Verify form pre-population for logged-in users</t>
+  </si>
+  <si>
+    <t>1. Navigate to the Product Returns form.</t>
+  </si>
+  <si>
+    <t>First Name, Last Name, E-Mail, and Telephone fields are automatically pre-populated with the user's account data.</t>
+  </si>
+  <si>
+    <t>TC_RET_003</t>
+  </si>
+  <si>
+    <t>Verify form pre-population via Order History 'Return' button</t>
+  </si>
+  <si>
+    <t>User is logged in and viewing an Order Details page</t>
+  </si>
+  <si>
+    <t>1. Click the 'Return' (red arrow) button next to a purchased product.</t>
+  </si>
+  <si>
+    <t>User is routed to the Returns form. Personal details, Order ID, Order Date, Product Name, and Product Code are all pre-populated automatically.</t>
+  </si>
+  <si>
+    <t>TC_RET_004</t>
+  </si>
+  <si>
+    <t>Verify successful submission of a Return Request</t>
+  </si>
+  <si>
+    <t>User is on the Product Returns form</t>
+  </si>
+  <si>
+    <t>1. Fill all mandatory fields (Personal details, Order ID, Product Name, Product Code).</t>
+  </si>
+  <si>
+    <t>2. Select a 'Reason for Return' radio button.</t>
+  </si>
+  <si>
+    <t>3. Click 'Submit' / 'Continue'.</t>
+  </si>
+  <si>
+    <t>A success page appears ("Thank you for submitting your return request. Your request has been sent to the relevant department for processing.").</t>
+  </si>
+  <si>
+    <t>TC_RET_005</t>
+  </si>
+  <si>
+    <t>Verify validation when Personal Details are missing</t>
+  </si>
+  <si>
+    <t>1. Leave First Name, Last Name, E-Mail, or Telephone blank.</t>
+  </si>
+  <si>
+    <t>2. Click 'Submit'.</t>
+  </si>
+  <si>
+    <t>Form does not submit. Validation error messages appear below the respective blank personal detail fields.</t>
+  </si>
+  <si>
+    <t>TC_RET_006</t>
+  </si>
+  <si>
+    <t>Verify validation when Order ID is blank</t>
+  </si>
+  <si>
+    <t>1. Leave the 'Order ID' field blank.</t>
+  </si>
+  <si>
+    <t>2. Fill all other required fields.</t>
+  </si>
+  <si>
+    <t>3. Click 'Submit'.</t>
+  </si>
+  <si>
+    <t>Form does not submit. A validation error message states that the Order ID is required.</t>
+  </si>
+  <si>
+    <t>TC_RET_007</t>
+  </si>
+  <si>
+    <t>Verify validation when Product Name is blank</t>
+  </si>
+  <si>
+    <t>1. Leave the 'Product Name' field blank.</t>
+  </si>
+  <si>
+    <t>Form does not submit. A validation error message states that the Product Name must be greater than 3 and less than 255 characters.</t>
+  </si>
+  <si>
+    <t>TC_RET_008</t>
+  </si>
+  <si>
+    <t>Verify validation when Product Code is blank</t>
+  </si>
+  <si>
+    <t>1. Leave the 'Product Code' field blank.</t>
+  </si>
+  <si>
+    <t>Form does not submit. A validation error message states that the Product Model/Code must be greater than 3 and less than 64 characters.</t>
+  </si>
+  <si>
+    <t>TC_RET_009</t>
+  </si>
+  <si>
+    <t>Verify validation when 'Reason for Return' is not selected</t>
+  </si>
+  <si>
+    <t>1. Fill all text fields correctly.</t>
+  </si>
+  <si>
+    <t>2. Do not select any radio button under 'Reason for Return'.</t>
+  </si>
+  <si>
+    <t>Form does not submit. A validation error message states that you must select a return product reason.</t>
+  </si>
+  <si>
+    <t>TC_RET_010</t>
+  </si>
+  <si>
+    <t>Verify 'Product is opened' radio buttons functionality</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Product is opened' section.</t>
+  </si>
+  <si>
+    <t>2. Select 'Yes' and then 'No'.</t>
+  </si>
+  <si>
+    <t>The radio buttons toggle successfully, allowing only one selection. (Defaults to 'Yes' in standard OpenCart).</t>
+  </si>
+  <si>
+    <t>TC_RET_011</t>
+  </si>
+  <si>
+    <t>Verify 'Faulty or other details' text area accepts input</t>
+  </si>
+  <si>
+    <t>1. Enter text explaining the defect in the 'Faulty or other details' text area.</t>
+  </si>
+  <si>
+    <t>2. Submit the form.</t>
+  </si>
+  <si>
+    <t>Form submits successfully, and the custom text is recorded in the return request details.</t>
+  </si>
+  <si>
+    <t>TC_RET_012</t>
+  </si>
+  <si>
+    <t>Verify navigation to My Account &gt; Returns history</t>
+  </si>
+  <si>
+    <t>2. Click 'View your return requests' link.</t>
+  </si>
+  <si>
+    <t>User is routed to the Product Returns list page displaying all past and pending return requests.</t>
+  </si>
+  <si>
+    <t>TC_RET_013</t>
+  </si>
+  <si>
+    <t>Verify Returns history list UI and data accuracy</t>
+  </si>
+  <si>
+    <t>User has submitted at least one return</t>
+  </si>
+  <si>
+    <t>1. Observe the Returns list page.</t>
+  </si>
+  <si>
+    <t>The table displays accurate data including Return ID, Status (e.g., Pending, Complete), Date Added, and Order ID.</t>
+  </si>
+  <si>
+    <t>TC_RET_014</t>
+  </si>
+  <si>
+    <t>Verify navigation to specific Return Details (View)</t>
+  </si>
+  <si>
+    <t>User is on the Returns history list</t>
+  </si>
+  <si>
+    <t>1. Locate a return request.</t>
+  </si>
+  <si>
+    <t>2. Click the 'View' (eye icon) button next to it.</t>
+  </si>
+  <si>
+    <t>User is routed to the 'Return Information' page detailing the specific request, the product, the reason, and the current admin status timeline.</t>
+  </si>
+  <si>
+    <t>TC_RET_015</t>
+  </si>
+  <si>
+    <t>Verify 'Continue' button functionality on Returns pages</t>
+  </si>
+  <si>
+    <t>User is viewing the Returns history list or Return Information page</t>
+  </si>
+  <si>
+    <t>User is navigated back to the My Account dashboard (from list) or back to the Returns list (from details page).</t>
   </si>
 </sst>
 </file>
@@ -8298,7 +8520,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="389">
+  <dxfs count="404">
     <dxf>
       <font>
         <b val="0"/>
@@ -8324,7 +8546,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -8355,7 +8579,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -8386,7 +8612,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -8417,7 +8645,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -8448,7 +8678,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -8479,49 +8711,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -8552,7 +8744,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -8583,7 +8777,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -8614,7 +8810,75 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -9016,6 +9280,48 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -9048,6 +9354,327 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -9091,6 +9718,38 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -9439,6 +10098,32 @@
         </top>
         <bottom style="medium">
           <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
         </bottom>
       </border>
     </dxf>
@@ -9489,32 +10174,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -9816,6 +10475,48 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -9851,6 +10552,327 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -9890,327 +10912,6 @@
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -10246,48 +10947,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -10626,6 +11285,48 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -10661,48 +11362,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -11085,6 +11744,48 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -11120,6 +11821,327 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -11159,327 +12181,6 @@
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -11515,48 +12216,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -11917,6 +12576,48 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -11952,48 +12653,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -12315,46 +12974,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color rgb="FFC4C7C5"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -12390,733 +13009,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color rgb="FFC4C7C5"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -13156,7 +13049,337 @@
       </border>
     </dxf>
     <dxf>
-      <border>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -13180,6 +13403,837 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color rgb="FFC4C7C5"/>
+        </vertical>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -18308,401 +19362,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color rgb="FFC4C7C5"/>
-        </vertical>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{DD3ECB35-2970-4076-8662-E1865940DEEF}"/>
@@ -18719,405 +19378,425 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="373">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}" name="Table2" displayName="Table2" ref="K1:L6" totalsRowShown="0" dataDxfId="403">
   <autoFilter ref="K1:L6" xr:uid="{1085A9A4-A9CB-4EF5-B882-05381EBBA56A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="372"/>
-    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="371"/>
+    <tableColumn id="1" xr3:uid="{25D9BB63-4C06-4EF5-9BFE-440447AD927E}" name="Column1" dataDxfId="402"/>
+    <tableColumn id="3" xr3:uid="{99126688-C68A-41AA-A86F-EA4861CE11CE}" name="Column2" dataDxfId="401"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="269" dataDxfId="267" headerRowBorderDxfId="268" tableBorderDxfId="266">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}" name="Table10" displayName="Table10" ref="A7:K37" totalsRowShown="0" headerRowDxfId="299" dataDxfId="297" headerRowBorderDxfId="298" tableBorderDxfId="296">
   <autoFilter ref="A7:K37" xr:uid="{8C929992-C219-401A-A8DD-7F2A8B0293F4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="265"/>
-    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="264"/>
-    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="263"/>
-    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="262"/>
-    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="261"/>
-    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="260"/>
-    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="259"/>
-    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="258"/>
-    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="257"/>
-    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="256"/>
-    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="255"/>
+    <tableColumn id="1" xr3:uid="{F2AE7ADB-2662-4A13-B901-1AB7452373B5}" name="testCaseId" dataDxfId="295"/>
+    <tableColumn id="2" xr3:uid="{89213332-667C-43EA-BADC-B46DEE87D523}" name="TestScenario" dataDxfId="294"/>
+    <tableColumn id="3" xr3:uid="{0B4A57E8-CCC3-430E-A671-63FB2F78A3BB}" name="TestCaseTitle" dataDxfId="293"/>
+    <tableColumn id="4" xr3:uid="{BD452262-7DD3-493E-8F45-BCB1082C2826}" name="Pre-requisites" dataDxfId="292"/>
+    <tableColumn id="5" xr3:uid="{F3067AF5-7048-4D04-BED3-9CB9432F7D6E}" name="TestSteps" dataDxfId="291"/>
+    <tableColumn id="6" xr3:uid="{8C989650-6A2D-41A2-AC9F-2BDD6BA86C47}" name="TestData" dataDxfId="290"/>
+    <tableColumn id="7" xr3:uid="{11C9D7C0-39B1-4A6C-87A5-6056F087EADD}" name="ExpectedResult" dataDxfId="289"/>
+    <tableColumn id="8" xr3:uid="{C6131864-4AB4-466D-B4D0-9972F6B89C70}" name="actualResult" dataDxfId="288"/>
+    <tableColumn id="9" xr3:uid="{4F577AD3-B241-45BB-B498-6AF1BACF0D5A}" name="priority" dataDxfId="287"/>
+    <tableColumn id="10" xr3:uid="{A0C5EA59-7494-48CF-B8CD-828378A34555}" name="result" dataDxfId="286"/>
+    <tableColumn id="11" xr3:uid="{857D2EE7-D445-4CD5-A561-30F1FD01942C}" name="Comments" dataDxfId="285"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}" name="Table11" displayName="Table11" ref="A7:K79" totalsRowShown="0" headerRowDxfId="284" dataDxfId="282" headerRowBorderDxfId="283" tableBorderDxfId="281">
   <autoFilter ref="A7:K79" xr:uid="{F28DBA5A-5903-4980-858A-D2CAB8F0B460}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="250"/>
-    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="249"/>
-    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="248"/>
-    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="247"/>
-    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="246"/>
-    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="245"/>
-    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="244"/>
-    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="243"/>
-    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="242"/>
-    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="241"/>
-    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="240"/>
+    <tableColumn id="1" xr3:uid="{4E263A0E-EF10-4D01-AAF5-437E1095086D}" name="estCaseId" dataDxfId="280"/>
+    <tableColumn id="2" xr3:uid="{CEDA0C10-A645-47AE-8E06-BF2A63429514}" name="TestScenario" dataDxfId="279"/>
+    <tableColumn id="3" xr3:uid="{7E68CD0F-1598-4BF9-9289-D5084F8FCD5B}" name="TestCaseTitle" dataDxfId="278"/>
+    <tableColumn id="4" xr3:uid="{D6038EBC-6C9A-413D-808D-31D74F7F7FCF}" name="Pre-requisites" dataDxfId="277"/>
+    <tableColumn id="5" xr3:uid="{5D47EADB-2C80-457D-AEF5-BA5AF5499549}" name="TestSteps" dataDxfId="276"/>
+    <tableColumn id="6" xr3:uid="{1BC31190-0DDC-478B-BE3F-C39195094798}" name="TestData" dataDxfId="275"/>
+    <tableColumn id="7" xr3:uid="{B461994B-B8B6-4095-9610-E1505155DD98}" name="ExpectedResult" dataDxfId="274"/>
+    <tableColumn id="8" xr3:uid="{CABAF997-3105-4C84-8200-B81582CE2035}" name="actualResult" dataDxfId="273"/>
+    <tableColumn id="9" xr3:uid="{7CD3DF08-4C22-4A96-9512-93EF17719BFB}" name="priority" dataDxfId="272"/>
+    <tableColumn id="10" xr3:uid="{ABEAE29F-E134-4F78-82E2-DCD132D53703}" name="result" dataDxfId="271"/>
+    <tableColumn id="11" xr3:uid="{4CD9E129-9C15-4063-B042-0D38282C7062}" name="Comments" dataDxfId="270"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}" name="Table12" displayName="Table12" ref="A7:K49" totalsRowShown="0" headerRowDxfId="269" dataDxfId="267" headerRowBorderDxfId="268" tableBorderDxfId="266">
   <autoFilter ref="A7:K49" xr:uid="{E178E97A-C5A2-48CE-987E-DE381FBF024B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="235"/>
-    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="234"/>
-    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="233"/>
-    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="232"/>
-    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="231"/>
-    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="230"/>
-    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="229"/>
-    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="228"/>
-    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="227"/>
-    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="226"/>
-    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="225"/>
+    <tableColumn id="1" xr3:uid="{CE1E266D-CA26-497F-9298-1AF8EDA42542}" name="testCaseId" dataDxfId="265"/>
+    <tableColumn id="2" xr3:uid="{AF34AC4A-19CF-4689-BC72-FA4C684282A0}" name="TestScenario" dataDxfId="264"/>
+    <tableColumn id="3" xr3:uid="{D4D680AC-F883-42BD-885A-0DEE7C71EA42}" name="TestCaseTitle" dataDxfId="263"/>
+    <tableColumn id="4" xr3:uid="{FAB345F7-A38C-4BA9-AFBC-49009E8FCA24}" name="Pre-requisites" dataDxfId="262"/>
+    <tableColumn id="5" xr3:uid="{74289435-9C66-47D8-B327-0DAEF8D29BEE}" name="TestSteps" dataDxfId="261"/>
+    <tableColumn id="6" xr3:uid="{20707235-6FE9-4461-BFBE-C5AF51B786CA}" name="TestData" dataDxfId="260"/>
+    <tableColumn id="7" xr3:uid="{2FA54E4A-676E-4C28-94C1-6FDD83EB3140}" name="ExpectedResult" dataDxfId="259"/>
+    <tableColumn id="8" xr3:uid="{3718889D-86E8-4E0D-9D81-BC010C1A7013}" name="actualResult" dataDxfId="258"/>
+    <tableColumn id="9" xr3:uid="{9D23B6FF-D141-47EB-ADBD-AF1FC615348C}" name="priority" dataDxfId="257"/>
+    <tableColumn id="10" xr3:uid="{641D6833-08D4-46EB-8974-DF265869FC03}" name="result" dataDxfId="256"/>
+    <tableColumn id="11" xr3:uid="{FD0582B5-9C15-4CB2-8AB1-50404A7EC14B}" name="Comments" dataDxfId="255"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{8BAD8DFB-6939-48F2-8A68-9B87A067FBFF}" name="Table13" displayName="Table13" ref="A7:K55" totalsRowShown="0" headerRowDx